--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185395</v>
+        <v>121185397</v>
       </c>
       <c r="B7" t="n">
-        <v>95618</v>
+        <v>90652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527048</v>
+        <v>527043</v>
       </c>
       <c r="R7" t="n">
-        <v>6938076</v>
+        <v>6938062</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185397</v>
+        <v>121185395</v>
       </c>
       <c r="B8" t="n">
-        <v>90652</v>
+        <v>95618</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527043</v>
+        <v>527048</v>
       </c>
       <c r="R8" t="n">
-        <v>6938062</v>
+        <v>6938076</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185431</v>
+        <v>121185398</v>
       </c>
       <c r="B15" t="n">
-        <v>91963</v>
+        <v>90687</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527439</v>
+        <v>526983</v>
       </c>
       <c r="R15" t="n">
-        <v>6937815</v>
+        <v>6938135</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185398</v>
+        <v>121185431</v>
       </c>
       <c r="B16" t="n">
-        <v>90687</v>
+        <v>91963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>526983</v>
+        <v>527439</v>
       </c>
       <c r="R16" t="n">
-        <v>6938135</v>
+        <v>6937815</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185405</v>
+        <v>121180712</v>
       </c>
       <c r="B17" t="n">
-        <v>90973</v>
+        <v>78598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,37 +2293,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527034</v>
+        <v>527305</v>
       </c>
       <c r="R17" t="n">
-        <v>6938099</v>
+        <v>6937895</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121180712</v>
+        <v>121185430</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>91963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,41 +2391,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527305</v>
+        <v>527460</v>
       </c>
       <c r="R18" t="n">
-        <v>6937895</v>
+        <v>6937819</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185430</v>
+        <v>121185405</v>
       </c>
       <c r="B19" t="n">
-        <v>91963</v>
+        <v>90973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527460</v>
+        <v>527034</v>
       </c>
       <c r="R19" t="n">
-        <v>6937819</v>
+        <v>6938099</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185411</v>
+        <v>121185434</v>
       </c>
       <c r="B25" t="n">
-        <v>79679</v>
+        <v>91963</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,25 +3105,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527045</v>
+        <v>526953</v>
       </c>
       <c r="R25" t="n">
-        <v>6938075</v>
+        <v>6938054</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185417</v>
+        <v>121185411</v>
       </c>
       <c r="B26" t="n">
         <v>79679</v>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527368</v>
+        <v>527045</v>
       </c>
       <c r="R26" t="n">
-        <v>6937959</v>
+        <v>6938075</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185434</v>
+        <v>121185417</v>
       </c>
       <c r="B27" t="n">
-        <v>91963</v>
+        <v>79679</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,25 +3309,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>526953</v>
+        <v>527368</v>
       </c>
       <c r="R27" t="n">
-        <v>6938054</v>
+        <v>6937959</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212752</v>
+        <v>121212694</v>
       </c>
       <c r="B56" t="n">
-        <v>78334</v>
+        <v>79708</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526804</v>
+        <v>527088</v>
       </c>
       <c r="R56" t="n">
-        <v>6938398</v>
+        <v>6938356</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212694</v>
+        <v>121212746</v>
       </c>
       <c r="B57" t="n">
-        <v>79708</v>
+        <v>79715</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212746</v>
+        <v>121212752</v>
       </c>
       <c r="B58" t="n">
-        <v>79715</v>
+        <v>78334</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527088</v>
+        <v>526804</v>
       </c>
       <c r="R58" t="n">
-        <v>6938356</v>
+        <v>6938398</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212760</v>
+        <v>121212714</v>
       </c>
       <c r="B87" t="n">
-        <v>98071</v>
+        <v>79679</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9444,25 +9444,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526842</v>
+        <v>526955</v>
       </c>
       <c r="R87" t="n">
-        <v>6938396</v>
+        <v>6938368</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9534,7 +9534,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212714</v>
+        <v>121212740</v>
       </c>
       <c r="B88" t="n">
         <v>79679</v>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526955</v>
+        <v>527350</v>
       </c>
       <c r="R88" t="n">
-        <v>6938368</v>
+        <v>6938133</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9636,10 +9636,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212740</v>
+        <v>121212760</v>
       </c>
       <c r="B89" t="n">
-        <v>79679</v>
+        <v>98071</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9648,25 +9648,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527350</v>
+        <v>526842</v>
       </c>
       <c r="R89" t="n">
-        <v>6938133</v>
+        <v>6938396</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212775</v>
+        <v>121212750</v>
       </c>
       <c r="B93" t="n">
-        <v>78598</v>
+        <v>80555</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527023</v>
+        <v>526756</v>
       </c>
       <c r="R93" t="n">
-        <v>6938359</v>
+        <v>6938437</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10146,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212750</v>
+        <v>121212713</v>
       </c>
       <c r="B94" t="n">
-        <v>80555</v>
+        <v>79679</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10162,21 +10162,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526756</v>
+        <v>526960</v>
       </c>
       <c r="R94" t="n">
-        <v>6938437</v>
+        <v>6938390</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,7 +10248,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212713</v>
+        <v>121212712</v>
       </c>
       <c r="B95" t="n">
         <v>79679</v>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>526960</v>
+        <v>526743</v>
       </c>
       <c r="R95" t="n">
-        <v>6938390</v>
+        <v>6938415</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212712</v>
+        <v>121212775</v>
       </c>
       <c r="B96" t="n">
-        <v>79679</v>
+        <v>78598</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10366,21 +10366,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526743</v>
+        <v>527023</v>
       </c>
       <c r="R96" t="n">
-        <v>6938415</v>
+        <v>6938359</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11477,10 +11477,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212759</v>
+        <v>121212733</v>
       </c>
       <c r="B107" t="n">
-        <v>98071</v>
+        <v>79679</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11489,25 +11489,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11517,10 +11517,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>526838</v>
+        <v>527186</v>
       </c>
       <c r="R107" t="n">
-        <v>6938397</v>
+        <v>6938273</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11579,10 +11579,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212733</v>
+        <v>121212759</v>
       </c>
       <c r="B108" t="n">
-        <v>79679</v>
+        <v>98071</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11591,25 +11591,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11619,10 +11619,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527186</v>
+        <v>526838</v>
       </c>
       <c r="R108" t="n">
-        <v>6938273</v>
+        <v>6938397</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -12191,7 +12191,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212735</v>
+        <v>121212739</v>
       </c>
       <c r="B114" t="n">
         <v>79679</v>
@@ -12231,10 +12231,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527245</v>
+        <v>527304</v>
       </c>
       <c r="R114" t="n">
-        <v>6938291</v>
+        <v>6938173</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12293,10 +12293,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212730</v>
+        <v>121212753</v>
       </c>
       <c r="B115" t="n">
-        <v>79679</v>
+        <v>78334</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12309,21 +12309,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12333,10 +12333,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527177</v>
+        <v>526856</v>
       </c>
       <c r="R115" t="n">
-        <v>6938273</v>
+        <v>6938391</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12395,10 +12395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212739</v>
+        <v>121212703</v>
       </c>
       <c r="B116" t="n">
-        <v>79679</v>
+        <v>90973</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12411,21 +12411,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527304</v>
+        <v>527253</v>
       </c>
       <c r="R116" t="n">
-        <v>6938173</v>
+        <v>6938232</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212703</v>
+        <v>121212698</v>
       </c>
       <c r="B117" t="n">
-        <v>90973</v>
+        <v>79680</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12513,21 +12513,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12537,10 +12537,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527253</v>
+        <v>527211</v>
       </c>
       <c r="R117" t="n">
-        <v>6938232</v>
+        <v>6938302</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12599,10 +12599,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212698</v>
+        <v>121212735</v>
       </c>
       <c r="B118" t="n">
-        <v>79680</v>
+        <v>79679</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12615,21 +12615,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12639,10 +12639,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527211</v>
+        <v>527245</v>
       </c>
       <c r="R118" t="n">
-        <v>6938302</v>
+        <v>6938291</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12701,10 +12701,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212753</v>
+        <v>121212730</v>
       </c>
       <c r="B119" t="n">
-        <v>78334</v>
+        <v>79679</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12717,21 +12717,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12741,10 +12741,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>526856</v>
+        <v>527177</v>
       </c>
       <c r="R119" t="n">
-        <v>6938391</v>
+        <v>6938273</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13318,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121219658</v>
+        <v>121226805</v>
       </c>
       <c r="B125" t="n">
-        <v>90652</v>
+        <v>79679</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,41 +13330,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526953</v>
+        <v>526203</v>
       </c>
       <c r="R125" t="n">
-        <v>6937958</v>
+        <v>6938195</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226805</v>
+        <v>121226808</v>
       </c>
       <c r="B126" t="n">
         <v>79679</v>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526203</v>
+        <v>526482</v>
       </c>
       <c r="R126" t="n">
-        <v>6938195</v>
+        <v>6938338</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226808</v>
+        <v>121219658</v>
       </c>
       <c r="B127" t="n">
-        <v>79679</v>
+        <v>90652</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526482</v>
+        <v>526953</v>
       </c>
       <c r="R127" t="n">
-        <v>6938338</v>
+        <v>6937958</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226809</v>
+        <v>121226824</v>
       </c>
       <c r="B135" t="n">
-        <v>79679</v>
+        <v>91249</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14355,25 +14355,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526518</v>
+        <v>526747</v>
       </c>
       <c r="R135" t="n">
-        <v>6938295</v>
+        <v>6937983</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,7 +14445,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226811</v>
+        <v>121226809</v>
       </c>
       <c r="B136" t="n">
         <v>79679</v>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526545</v>
+        <v>526518</v>
       </c>
       <c r="R136" t="n">
-        <v>6938319</v>
+        <v>6938295</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14547,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226824</v>
+        <v>121226811</v>
       </c>
       <c r="B137" t="n">
-        <v>91249</v>
+        <v>79679</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14559,25 +14559,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526747</v>
+        <v>526545</v>
       </c>
       <c r="R137" t="n">
-        <v>6937983</v>
+        <v>6938319</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14649,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121212789</v>
+        <v>121212776</v>
       </c>
       <c r="B138" t="n">
-        <v>91963</v>
+        <v>78598</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14661,25 +14661,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14689,10 +14689,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526823</v>
+        <v>527090</v>
       </c>
       <c r="R138" t="n">
-        <v>6938405</v>
+        <v>6938365</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14751,10 +14751,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121212776</v>
+        <v>121226810</v>
       </c>
       <c r="B139" t="n">
-        <v>78598</v>
+        <v>79679</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14767,21 +14767,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14791,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>527090</v>
+        <v>526533</v>
       </c>
       <c r="R139" t="n">
-        <v>6938365</v>
+        <v>6938315</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14821,12 +14821,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14853,10 +14853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226810</v>
+        <v>121212789</v>
       </c>
       <c r="B140" t="n">
-        <v>79679</v>
+        <v>91963</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14865,25 +14865,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526533</v>
+        <v>526823</v>
       </c>
       <c r="R140" t="n">
-        <v>6938315</v>
+        <v>6938405</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14923,12 +14923,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15057,10 +15057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121212778</v>
+        <v>121226791</v>
       </c>
       <c r="B142" t="n">
-        <v>78598</v>
+        <v>89743</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15073,21 +15073,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15097,10 +15097,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>527288</v>
+        <v>526205</v>
       </c>
       <c r="R142" t="n">
-        <v>6938221</v>
+        <v>6938282</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15127,12 +15127,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15159,10 +15159,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226791</v>
+        <v>121212778</v>
       </c>
       <c r="B143" t="n">
-        <v>89743</v>
+        <v>78598</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15175,21 +15175,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15199,10 +15199,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526205</v>
+        <v>527288</v>
       </c>
       <c r="R143" t="n">
-        <v>6938282</v>
+        <v>6938221</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15229,12 +15229,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15567,10 +15567,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226816</v>
+        <v>121226796</v>
       </c>
       <c r="B147" t="n">
-        <v>98071</v>
+        <v>90973</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15579,25 +15579,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15607,10 +15607,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526789</v>
+        <v>526796</v>
       </c>
       <c r="R147" t="n">
-        <v>6937993</v>
+        <v>6937966</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15669,10 +15669,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226796</v>
+        <v>121226816</v>
       </c>
       <c r="B148" t="n">
-        <v>90973</v>
+        <v>98071</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15681,25 +15681,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15709,10 +15709,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526796</v>
+        <v>526789</v>
       </c>
       <c r="R148" t="n">
-        <v>6937966</v>
+        <v>6937993</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15975,10 +15975,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121212779</v>
+        <v>121212791</v>
       </c>
       <c r="B151" t="n">
-        <v>78598</v>
+        <v>79714</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15987,20 +15987,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -16015,10 +16015,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>527495</v>
+        <v>527094</v>
       </c>
       <c r="R151" t="n">
-        <v>6938009</v>
+        <v>6938358</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16077,10 +16077,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121212791</v>
+        <v>121212779</v>
       </c>
       <c r="B152" t="n">
-        <v>79714</v>
+        <v>78598</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16089,20 +16089,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -16117,10 +16117,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>527094</v>
+        <v>527495</v>
       </c>
       <c r="R152" t="n">
-        <v>6938358</v>
+        <v>6938009</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185427</v>
+        <v>121185435</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>91353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,25 +1167,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527034</v>
+        <v>527008</v>
       </c>
       <c r="R6" t="n">
-        <v>6938099</v>
+        <v>6938073</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185397</v>
+        <v>121185401</v>
       </c>
       <c r="B7" t="n">
-        <v>90652</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527043</v>
+        <v>527016</v>
       </c>
       <c r="R7" t="n">
-        <v>6938062</v>
+        <v>6938060</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185395</v>
+        <v>121185399</v>
       </c>
       <c r="B8" t="n">
-        <v>95618</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527048</v>
+        <v>526989</v>
       </c>
       <c r="R8" t="n">
-        <v>6938076</v>
+        <v>6938147</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185415</v>
+        <v>121185395</v>
       </c>
       <c r="B9" t="n">
-        <v>79679</v>
+        <v>95628</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527391</v>
+        <v>527048</v>
       </c>
       <c r="R9" t="n">
-        <v>6937910</v>
+        <v>6938076</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185401</v>
+        <v>121185434</v>
       </c>
       <c r="B10" t="n">
-        <v>90687</v>
+        <v>91973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527016</v>
+        <v>526953</v>
       </c>
       <c r="R10" t="n">
-        <v>6938060</v>
+        <v>6938054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185407</v>
+        <v>121185433</v>
       </c>
       <c r="B11" t="n">
-        <v>90973</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527016</v>
+        <v>527195</v>
       </c>
       <c r="R11" t="n">
-        <v>6938062</v>
+        <v>6937884</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185399</v>
+        <v>121185417</v>
       </c>
       <c r="B12" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526989</v>
+        <v>527368</v>
       </c>
       <c r="R12" t="n">
-        <v>6938147</v>
+        <v>6937959</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185402</v>
+        <v>121185428</v>
       </c>
       <c r="B13" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527367</v>
+        <v>527439</v>
       </c>
       <c r="R13" t="n">
-        <v>6937938</v>
+        <v>6937974</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185412</v>
+        <v>121185413</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527001</v>
+        <v>527044</v>
       </c>
       <c r="R14" t="n">
-        <v>6938101</v>
+        <v>6938065</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185398</v>
+        <v>121182248</v>
       </c>
       <c r="B15" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,41 +2085,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>526983</v>
+        <v>527008</v>
       </c>
       <c r="R15" t="n">
-        <v>6938135</v>
+        <v>6938092</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185431</v>
+        <v>121180239</v>
       </c>
       <c r="B16" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,41 +2187,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527439</v>
+        <v>527495</v>
       </c>
       <c r="R16" t="n">
-        <v>6937815</v>
+        <v>6937765</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121180712</v>
+        <v>121185418</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2293,37 +2293,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527305</v>
+        <v>527437</v>
       </c>
       <c r="R17" t="n">
-        <v>6937895</v>
+        <v>6937974</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185430</v>
+        <v>121180712</v>
       </c>
       <c r="B18" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,41 +2391,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527460</v>
+        <v>527305</v>
       </c>
       <c r="R18" t="n">
-        <v>6937819</v>
+        <v>6937895</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185405</v>
+        <v>121185412</v>
       </c>
       <c r="B19" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527034</v>
+        <v>527001</v>
       </c>
       <c r="R19" t="n">
-        <v>6938099</v>
+        <v>6938101</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2586,7 +2586,7 @@
         <v>121185424</v>
       </c>
       <c r="B20" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185421</v>
+        <v>121185426</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>526958</v>
+        <v>527503</v>
       </c>
       <c r="R21" t="n">
-        <v>6938116</v>
+        <v>6937855</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185428</v>
+        <v>121185403</v>
       </c>
       <c r="B22" t="n">
-        <v>78598</v>
+        <v>90644</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2803,21 +2803,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527439</v>
+        <v>527012</v>
       </c>
       <c r="R22" t="n">
-        <v>6937974</v>
+        <v>6938063</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185429</v>
+        <v>121185397</v>
       </c>
       <c r="B23" t="n">
-        <v>91963</v>
+        <v>90662</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2905,21 +2905,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527641</v>
+        <v>527043</v>
       </c>
       <c r="R23" t="n">
-        <v>6937808</v>
+        <v>6938062</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121180291</v>
+        <v>121185432</v>
       </c>
       <c r="B24" t="n">
-        <v>90705</v>
+        <v>91973</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,41 +3003,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527492</v>
+        <v>527217</v>
       </c>
       <c r="R24" t="n">
-        <v>6937763</v>
+        <v>6937854</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185434</v>
+        <v>121185425</v>
       </c>
       <c r="B25" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,25 +3105,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>526953</v>
+        <v>527014</v>
       </c>
       <c r="R25" t="n">
-        <v>6938054</v>
+        <v>6938062</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185411</v>
+        <v>121185407</v>
       </c>
       <c r="B26" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527045</v>
+        <v>527016</v>
       </c>
       <c r="R26" t="n">
-        <v>6938075</v>
+        <v>6938062</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185417</v>
+        <v>121185414</v>
       </c>
       <c r="B27" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527368</v>
+        <v>527346</v>
       </c>
       <c r="R27" t="n">
-        <v>6937959</v>
+        <v>6937925</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121180141</v>
+        <v>121185429</v>
       </c>
       <c r="B28" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,41 +3411,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527597</v>
+        <v>527641</v>
       </c>
       <c r="R28" t="n">
-        <v>6937703</v>
+        <v>6937808</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121180239</v>
+        <v>121179977</v>
       </c>
       <c r="B29" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,25 +3513,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527495</v>
+        <v>527626</v>
       </c>
       <c r="R29" t="n">
-        <v>6937765</v>
+        <v>6937719</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185432</v>
+        <v>121185409</v>
       </c>
       <c r="B30" t="n">
-        <v>91963</v>
+        <v>79682</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,25 +3615,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527217</v>
+        <v>527108</v>
       </c>
       <c r="R30" t="n">
-        <v>6937854</v>
+        <v>6938086</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185396</v>
+        <v>121185419</v>
       </c>
       <c r="B31" t="n">
-        <v>90652</v>
+        <v>79718</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>526980</v>
+        <v>527001</v>
       </c>
       <c r="R31" t="n">
-        <v>6938115</v>
+        <v>6938096</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185416</v>
+        <v>121185406</v>
       </c>
       <c r="B32" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527367</v>
+        <v>527009</v>
       </c>
       <c r="R32" t="n">
-        <v>6937938</v>
+        <v>6938044</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121185413</v>
+        <v>121179876</v>
       </c>
       <c r="B33" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3925,37 +3925,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527044</v>
+        <v>527649</v>
       </c>
       <c r="R33" t="n">
-        <v>6938065</v>
+        <v>6937696</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185403</v>
+        <v>121185423</v>
       </c>
       <c r="B34" t="n">
-        <v>90634</v>
+        <v>98081</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527012</v>
+        <v>526974</v>
       </c>
       <c r="R34" t="n">
-        <v>6938063</v>
+        <v>6938145</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185414</v>
+        <v>121180141</v>
       </c>
       <c r="B35" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,41 +4125,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527346</v>
+        <v>527597</v>
       </c>
       <c r="R35" t="n">
-        <v>6937925</v>
+        <v>6937703</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185418</v>
+        <v>121185415</v>
       </c>
       <c r="B36" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527437</v>
+        <v>527391</v>
       </c>
       <c r="R36" t="n">
-        <v>6937974</v>
+        <v>6937910</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121185400</v>
+        <v>121185410</v>
       </c>
       <c r="B37" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4333,21 +4333,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527034</v>
+        <v>527024</v>
       </c>
       <c r="R37" t="n">
-        <v>6938099</v>
+        <v>6938111</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121180230</v>
+        <v>121185416</v>
       </c>
       <c r="B38" t="n">
-        <v>105176</v>
+        <v>79682</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4431,41 +4431,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527509</v>
+        <v>527367</v>
       </c>
       <c r="R38" t="n">
-        <v>6937756</v>
+        <v>6937938</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121185409</v>
+        <v>121183008</v>
       </c>
       <c r="B39" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,41 +4533,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527108</v>
+        <v>526999</v>
       </c>
       <c r="R39" t="n">
-        <v>6938086</v>
+        <v>6938157</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121182248</v>
+        <v>121185427</v>
       </c>
       <c r="B40" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527008</v>
+        <v>527034</v>
       </c>
       <c r="R40" t="n">
-        <v>6938092</v>
+        <v>6938099</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121183281</v>
+        <v>121180261</v>
       </c>
       <c r="B41" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4761,17 +4761,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526958</v>
+        <v>527506</v>
       </c>
       <c r="R41" t="n">
-        <v>6938109</v>
+        <v>6937752</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185422</v>
+        <v>121185421</v>
       </c>
       <c r="B42" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>526995</v>
+        <v>526958</v>
       </c>
       <c r="R42" t="n">
-        <v>6938144</v>
+        <v>6938116</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185406</v>
+        <v>121185422</v>
       </c>
       <c r="B43" t="n">
-        <v>90973</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,25 +4941,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527009</v>
+        <v>526995</v>
       </c>
       <c r="R43" t="n">
-        <v>6938044</v>
+        <v>6938144</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185423</v>
+        <v>121180230</v>
       </c>
       <c r="B44" t="n">
-        <v>98071</v>
+        <v>105186</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>526974</v>
+        <v>527509</v>
       </c>
       <c r="R44" t="n">
-        <v>6938145</v>
+        <v>6937756</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185425</v>
+        <v>121185411</v>
       </c>
       <c r="B45" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527014</v>
+        <v>527045</v>
       </c>
       <c r="R45" t="n">
-        <v>6938062</v>
+        <v>6938075</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121179876</v>
+        <v>121185430</v>
       </c>
       <c r="B46" t="n">
-        <v>90973</v>
+        <v>91973</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,41 +5247,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527649</v>
+        <v>527460</v>
       </c>
       <c r="R46" t="n">
-        <v>6937696</v>
+        <v>6937819</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121179977</v>
+        <v>121185398</v>
       </c>
       <c r="B47" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,37 +5353,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527626</v>
+        <v>526983</v>
       </c>
       <c r="R47" t="n">
-        <v>6937719</v>
+        <v>6938135</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121183008</v>
+        <v>121185400</v>
       </c>
       <c r="B48" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5451,41 +5451,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>526999</v>
+        <v>527034</v>
       </c>
       <c r="R48" t="n">
-        <v>6938157</v>
+        <v>6938099</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185410</v>
+        <v>121185405</v>
       </c>
       <c r="B49" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527024</v>
+        <v>527034</v>
       </c>
       <c r="R49" t="n">
-        <v>6938111</v>
+        <v>6938099</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121185433</v>
+        <v>121180291</v>
       </c>
       <c r="B50" t="n">
-        <v>91963</v>
+        <v>90715</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,41 +5655,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527195</v>
+        <v>527492</v>
       </c>
       <c r="R50" t="n">
-        <v>6937884</v>
+        <v>6937763</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185435</v>
+        <v>121185396</v>
       </c>
       <c r="B51" t="n">
-        <v>91343</v>
+        <v>90662</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5757,25 +5757,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527008</v>
+        <v>526980</v>
       </c>
       <c r="R51" t="n">
-        <v>6938073</v>
+        <v>6938115</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185419</v>
+        <v>121183281</v>
       </c>
       <c r="B52" t="n">
-        <v>79715</v>
+        <v>98081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,41 +5859,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527001</v>
+        <v>526958</v>
       </c>
       <c r="R52" t="n">
-        <v>6938096</v>
+        <v>6938109</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121180261</v>
+        <v>121185402</v>
       </c>
       <c r="B53" t="n">
-        <v>98071</v>
+        <v>79711</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527506</v>
+        <v>527367</v>
       </c>
       <c r="R53" t="n">
-        <v>6937752</v>
+        <v>6937938</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185426</v>
+        <v>121185431</v>
       </c>
       <c r="B54" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,25 +6063,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527503</v>
+        <v>527439</v>
       </c>
       <c r="R54" t="n">
-        <v>6937855</v>
+        <v>6937815</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212761</v>
+        <v>121212694</v>
       </c>
       <c r="B55" t="n">
-        <v>98071</v>
+        <v>79711</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526852</v>
+        <v>527088</v>
       </c>
       <c r="R55" t="n">
-        <v>6938391</v>
+        <v>6938356</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212694</v>
+        <v>121212731</v>
       </c>
       <c r="B56" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527088</v>
+        <v>527184</v>
       </c>
       <c r="R56" t="n">
-        <v>6938356</v>
+        <v>6938280</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212746</v>
+        <v>121212758</v>
       </c>
       <c r="B57" t="n">
-        <v>79715</v>
+        <v>98081</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527088</v>
+        <v>526823</v>
       </c>
       <c r="R57" t="n">
-        <v>6938356</v>
+        <v>6938405</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212752</v>
+        <v>121212744</v>
       </c>
       <c r="B58" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>526804</v>
+        <v>527495</v>
       </c>
       <c r="R58" t="n">
-        <v>6938398</v>
+        <v>6938012</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212705</v>
+        <v>121212740</v>
       </c>
       <c r="B59" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527310</v>
+        <v>527350</v>
       </c>
       <c r="R59" t="n">
-        <v>6938160</v>
+        <v>6938133</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212744</v>
+        <v>121212715</v>
       </c>
       <c r="B60" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527495</v>
+        <v>526971</v>
       </c>
       <c r="R60" t="n">
-        <v>6938012</v>
+        <v>6938369</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212722</v>
+        <v>121212751</v>
       </c>
       <c r="B61" t="n">
-        <v>79679</v>
+        <v>78337</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527075</v>
+        <v>526755</v>
       </c>
       <c r="R61" t="n">
-        <v>6938349</v>
+        <v>6938374</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212762</v>
+        <v>121212692</v>
       </c>
       <c r="B62" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526868</v>
+        <v>527210</v>
       </c>
       <c r="R62" t="n">
-        <v>6938367</v>
+        <v>6938291</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6943,6 +6943,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6969,10 +6974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212727</v>
+        <v>121212695</v>
       </c>
       <c r="B63" t="n">
-        <v>79679</v>
+        <v>79711</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6981,25 +6986,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527148</v>
+        <v>527184</v>
       </c>
       <c r="R63" t="n">
-        <v>6938301</v>
+        <v>6938280</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7071,10 +7076,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212719</v>
+        <v>121212753</v>
       </c>
       <c r="B64" t="n">
-        <v>79679</v>
+        <v>78337</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,21 +7092,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527051</v>
+        <v>526856</v>
       </c>
       <c r="R64" t="n">
-        <v>6938362</v>
+        <v>6938391</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7173,10 +7178,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212763</v>
+        <v>121212719</v>
       </c>
       <c r="B65" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7185,25 +7190,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7218,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526911</v>
+        <v>527051</v>
       </c>
       <c r="R65" t="n">
-        <v>6938360</v>
+        <v>6938362</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7275,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212771</v>
+        <v>121212760</v>
       </c>
       <c r="B66" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7315,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527317</v>
+        <v>526842</v>
       </c>
       <c r="R66" t="n">
-        <v>6938165</v>
+        <v>6938396</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7377,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212772</v>
+        <v>121212757</v>
       </c>
       <c r="B67" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7389,25 +7394,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526971</v>
+        <v>526927</v>
       </c>
       <c r="R67" t="n">
-        <v>6938369</v>
+        <v>6938376</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7453,11 +7458,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7484,10 +7484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212738</v>
+        <v>121212703</v>
       </c>
       <c r="B68" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7500,21 +7500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527288</v>
+        <v>527253</v>
       </c>
       <c r="R68" t="n">
-        <v>6938221</v>
+        <v>6938232</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7586,10 +7586,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212689</v>
+        <v>121212718</v>
       </c>
       <c r="B69" t="n">
-        <v>79216</v>
+        <v>79682</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7602,21 +7602,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526855</v>
+        <v>527038</v>
       </c>
       <c r="R69" t="n">
-        <v>6938391</v>
+        <v>6938372</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7688,10 +7688,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212756</v>
+        <v>121212725</v>
       </c>
       <c r="B70" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7700,25 +7700,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527255</v>
+        <v>527111</v>
       </c>
       <c r="R70" t="n">
-        <v>6938220</v>
+        <v>6938327</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7764,11 +7764,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7795,10 +7790,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212736</v>
+        <v>121212774</v>
       </c>
       <c r="B71" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7811,21 +7806,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7835,10 +7830,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527250</v>
+        <v>526840</v>
       </c>
       <c r="R71" t="n">
-        <v>6938289</v>
+        <v>6938383</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7897,10 +7892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212751</v>
+        <v>121212773</v>
       </c>
       <c r="B72" t="n">
-        <v>78334</v>
+        <v>78601</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7913,21 +7908,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7937,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526755</v>
+        <v>526989</v>
       </c>
       <c r="R72" t="n">
-        <v>6938374</v>
+        <v>6938371</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7973,6 +7968,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7999,10 +7999,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212717</v>
+        <v>121212772</v>
       </c>
       <c r="B73" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8015,21 +8015,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527023</v>
+        <v>526971</v>
       </c>
       <c r="R73" t="n">
-        <v>6938359</v>
+        <v>6938369</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8075,6 +8075,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8101,10 +8106,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212711</v>
+        <v>121212717</v>
       </c>
       <c r="B74" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8141,10 +8146,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527051</v>
+        <v>527023</v>
       </c>
       <c r="R74" t="n">
-        <v>6938349</v>
+        <v>6938359</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8203,10 +8208,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212692</v>
+        <v>121212689</v>
       </c>
       <c r="B75" t="n">
-        <v>57501</v>
+        <v>79219</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8219,21 +8224,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8243,10 +8248,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527210</v>
+        <v>526855</v>
       </c>
       <c r="R75" t="n">
-        <v>6938291</v>
+        <v>6938391</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8279,11 +8284,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8310,10 +8310,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212718</v>
+        <v>121212728</v>
       </c>
       <c r="B76" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8350,10 +8350,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527038</v>
+        <v>527148</v>
       </c>
       <c r="R76" t="n">
-        <v>6938372</v>
+        <v>6938301</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8412,10 +8412,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212758</v>
+        <v>121212712</v>
       </c>
       <c r="B77" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8424,25 +8424,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8452,10 +8452,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526823</v>
+        <v>526743</v>
       </c>
       <c r="R77" t="n">
-        <v>6938405</v>
+        <v>6938415</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8514,10 +8514,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212688</v>
+        <v>121212738</v>
       </c>
       <c r="B78" t="n">
-        <v>95618</v>
+        <v>79682</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8530,21 +8530,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8554,10 +8554,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527409</v>
+        <v>527288</v>
       </c>
       <c r="R78" t="n">
-        <v>6938091</v>
+        <v>6938221</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8616,10 +8616,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212765</v>
+        <v>121212752</v>
       </c>
       <c r="B79" t="n">
-        <v>98071</v>
+        <v>78337</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8628,25 +8628,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526955</v>
+        <v>526804</v>
       </c>
       <c r="R79" t="n">
-        <v>6938367</v>
+        <v>6938398</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8718,10 +8718,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212737</v>
+        <v>121212775</v>
       </c>
       <c r="B80" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8734,21 +8734,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527248</v>
+        <v>527023</v>
       </c>
       <c r="R80" t="n">
-        <v>6938256</v>
+        <v>6938359</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212745</v>
+        <v>121212697</v>
       </c>
       <c r="B81" t="n">
-        <v>79715</v>
+        <v>79683</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8832,25 +8832,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526960</v>
+        <v>527186</v>
       </c>
       <c r="R81" t="n">
-        <v>6938390</v>
+        <v>6938273</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212715</v>
+        <v>121212716</v>
       </c>
       <c r="B82" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526971</v>
+        <v>526994</v>
       </c>
       <c r="R82" t="n">
-        <v>6938369</v>
+        <v>6938374</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212757</v>
+        <v>121212762</v>
       </c>
       <c r="B83" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526927</v>
+        <v>526868</v>
       </c>
       <c r="R83" t="n">
-        <v>6938376</v>
+        <v>6938367</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212729</v>
+        <v>121212750</v>
       </c>
       <c r="B84" t="n">
-        <v>79679</v>
+        <v>80558</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9142,21 +9142,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527168</v>
+        <v>526756</v>
       </c>
       <c r="R84" t="n">
-        <v>6938291</v>
+        <v>6938437</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9228,10 +9228,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212696</v>
+        <v>121212690</v>
       </c>
       <c r="B85" t="n">
-        <v>79708</v>
+        <v>90697</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9240,25 +9240,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527288</v>
+        <v>527263</v>
       </c>
       <c r="R85" t="n">
-        <v>6938221</v>
+        <v>6938234</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212709</v>
+        <v>121212698</v>
       </c>
       <c r="B86" t="n">
-        <v>78335</v>
+        <v>79683</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9346,21 +9346,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>526856</v>
+        <v>527211</v>
       </c>
       <c r="R86" t="n">
-        <v>6938391</v>
+        <v>6938302</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212714</v>
+        <v>121212709</v>
       </c>
       <c r="B87" t="n">
-        <v>79679</v>
+        <v>78338</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9448,21 +9448,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526955</v>
+        <v>526856</v>
       </c>
       <c r="R87" t="n">
-        <v>6938368</v>
+        <v>6938391</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212740</v>
+        <v>121212745</v>
       </c>
       <c r="B88" t="n">
-        <v>79679</v>
+        <v>79718</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9546,25 +9546,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527350</v>
+        <v>526960</v>
       </c>
       <c r="R88" t="n">
-        <v>6938133</v>
+        <v>6938390</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9636,10 +9636,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212760</v>
+        <v>121212701</v>
       </c>
       <c r="B89" t="n">
-        <v>98071</v>
+        <v>90983</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9648,25 +9648,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526842</v>
+        <v>526960</v>
       </c>
       <c r="R89" t="n">
-        <v>6938396</v>
+        <v>6938387</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212723</v>
+        <v>121212696</v>
       </c>
       <c r="B90" t="n">
-        <v>79679</v>
+        <v>79711</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9750,25 +9750,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527088</v>
+        <v>527288</v>
       </c>
       <c r="R90" t="n">
-        <v>6938358</v>
+        <v>6938221</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212716</v>
+        <v>121212735</v>
       </c>
       <c r="B91" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>526994</v>
+        <v>527245</v>
       </c>
       <c r="R91" t="n">
-        <v>6938374</v>
+        <v>6938291</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212721</v>
+        <v>121212755</v>
       </c>
       <c r="B92" t="n">
-        <v>79679</v>
+        <v>78337</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9958,21 +9958,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527074</v>
+        <v>526945</v>
       </c>
       <c r="R92" t="n">
-        <v>6938353</v>
+        <v>6938389</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212750</v>
+        <v>121212737</v>
       </c>
       <c r="B93" t="n">
-        <v>80555</v>
+        <v>79682</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>526756</v>
+        <v>527248</v>
       </c>
       <c r="R93" t="n">
-        <v>6938437</v>
+        <v>6938256</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10149,7 +10149,7 @@
         <v>121212713</v>
       </c>
       <c r="B94" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212712</v>
+        <v>121212759</v>
       </c>
       <c r="B95" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10260,25 +10260,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>526743</v>
+        <v>526838</v>
       </c>
       <c r="R95" t="n">
-        <v>6938415</v>
+        <v>6938397</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212775</v>
+        <v>121212765</v>
       </c>
       <c r="B96" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10362,25 +10362,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>527023</v>
+        <v>526955</v>
       </c>
       <c r="R96" t="n">
-        <v>6938359</v>
+        <v>6938367</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212708</v>
+        <v>121212724</v>
       </c>
       <c r="B97" t="n">
-        <v>97025</v>
+        <v>79682</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10464,25 +10464,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10492,10 +10492,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527252</v>
+        <v>527109</v>
       </c>
       <c r="R97" t="n">
-        <v>6938285</v>
+        <v>6938336</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10554,10 +10554,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212734</v>
+        <v>121212710</v>
       </c>
       <c r="B98" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527214</v>
+        <v>527495</v>
       </c>
       <c r="R98" t="n">
-        <v>6938296</v>
+        <v>6938009</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10630,6 +10630,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10656,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212724</v>
+        <v>121212739</v>
       </c>
       <c r="B99" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10696,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527109</v>
+        <v>527304</v>
       </c>
       <c r="R99" t="n">
-        <v>6938336</v>
+        <v>6938173</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10758,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212710</v>
+        <v>121212771</v>
       </c>
       <c r="B100" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10770,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10798,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527495</v>
+        <v>527317</v>
       </c>
       <c r="R100" t="n">
-        <v>6938009</v>
+        <v>6938165</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10834,11 +10839,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212732</v>
+        <v>121212688</v>
       </c>
       <c r="B101" t="n">
-        <v>79679</v>
+        <v>95628</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10881,21 +10881,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527184</v>
+        <v>527409</v>
       </c>
       <c r="R101" t="n">
-        <v>6938280</v>
+        <v>6938091</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212701</v>
+        <v>121212733</v>
       </c>
       <c r="B102" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10983,21 +10983,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>526960</v>
+        <v>527186</v>
       </c>
       <c r="R102" t="n">
-        <v>6938387</v>
+        <v>6938273</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212695</v>
+        <v>121212723</v>
       </c>
       <c r="B103" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11081,25 +11081,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>527184</v>
+        <v>527088</v>
       </c>
       <c r="R103" t="n">
-        <v>6938280</v>
+        <v>6938358</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212764</v>
+        <v>121212730</v>
       </c>
       <c r="B104" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11183,25 +11183,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>526945</v>
+        <v>527177</v>
       </c>
       <c r="R104" t="n">
-        <v>6938389</v>
+        <v>6938273</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212697</v>
+        <v>121212746</v>
       </c>
       <c r="B105" t="n">
-        <v>79680</v>
+        <v>79718</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11285,25 +11285,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527186</v>
+        <v>527088</v>
       </c>
       <c r="R105" t="n">
-        <v>6938273</v>
+        <v>6938356</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212699</v>
+        <v>121212756</v>
       </c>
       <c r="B106" t="n">
-        <v>79583</v>
+        <v>98081</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11387,25 +11387,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527249</v>
+        <v>527255</v>
       </c>
       <c r="R106" t="n">
-        <v>6938289</v>
+        <v>6938220</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11451,6 +11451,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11477,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212733</v>
+        <v>121212763</v>
       </c>
       <c r="B107" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11489,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11517,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527186</v>
+        <v>526911</v>
       </c>
       <c r="R107" t="n">
-        <v>6938273</v>
+        <v>6938360</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11579,10 +11584,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212759</v>
+        <v>121212769</v>
       </c>
       <c r="B108" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11619,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>526838</v>
+        <v>527263</v>
       </c>
       <c r="R108" t="n">
-        <v>6938397</v>
+        <v>6938242</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11681,10 +11686,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212690</v>
+        <v>121212761</v>
       </c>
       <c r="B109" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11693,25 +11698,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11721,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>527263</v>
+        <v>526852</v>
       </c>
       <c r="R109" t="n">
-        <v>6938234</v>
+        <v>6938391</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11783,10 +11788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212769</v>
+        <v>121212708</v>
       </c>
       <c r="B110" t="n">
-        <v>98071</v>
+        <v>97035</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11795,25 +11800,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11823,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527263</v>
+        <v>527252</v>
       </c>
       <c r="R110" t="n">
-        <v>6938242</v>
+        <v>6938285</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11885,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212725</v>
+        <v>121212705</v>
       </c>
       <c r="B111" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11901,21 +11906,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11925,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527111</v>
+        <v>527310</v>
       </c>
       <c r="R111" t="n">
-        <v>6938327</v>
+        <v>6938160</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11987,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212774</v>
+        <v>121212714</v>
       </c>
       <c r="B112" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12003,21 +12008,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12027,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>526840</v>
+        <v>526955</v>
       </c>
       <c r="R112" t="n">
-        <v>6938383</v>
+        <v>6938368</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12089,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212755</v>
+        <v>121212734</v>
       </c>
       <c r="B113" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12105,21 +12110,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12129,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>526945</v>
+        <v>527214</v>
       </c>
       <c r="R113" t="n">
-        <v>6938389</v>
+        <v>6938296</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12191,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212739</v>
+        <v>121212699</v>
       </c>
       <c r="B114" t="n">
-        <v>79679</v>
+        <v>79586</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12203,25 +12208,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12231,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527304</v>
+        <v>527249</v>
       </c>
       <c r="R114" t="n">
-        <v>6938173</v>
+        <v>6938289</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12293,10 +12298,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212753</v>
+        <v>121212736</v>
       </c>
       <c r="B115" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12309,21 +12314,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>526856</v>
+        <v>527250</v>
       </c>
       <c r="R115" t="n">
-        <v>6938391</v>
+        <v>6938289</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12395,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212703</v>
+        <v>121212711</v>
       </c>
       <c r="B116" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12411,21 +12416,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12435,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527253</v>
+        <v>527051</v>
       </c>
       <c r="R116" t="n">
-        <v>6938232</v>
+        <v>6938349</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12497,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212698</v>
+        <v>121212764</v>
       </c>
       <c r="B117" t="n">
-        <v>79680</v>
+        <v>98081</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12509,25 +12514,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12537,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527211</v>
+        <v>526945</v>
       </c>
       <c r="R117" t="n">
-        <v>6938302</v>
+        <v>6938389</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12599,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212735</v>
+        <v>121212721</v>
       </c>
       <c r="B118" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12639,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527245</v>
+        <v>527074</v>
       </c>
       <c r="R118" t="n">
-        <v>6938291</v>
+        <v>6938353</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12701,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212730</v>
+        <v>121212722</v>
       </c>
       <c r="B119" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12741,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527177</v>
+        <v>527075</v>
       </c>
       <c r="R119" t="n">
-        <v>6938273</v>
+        <v>6938349</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12803,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212773</v>
+        <v>121212729</v>
       </c>
       <c r="B120" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12819,21 +12824,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12843,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>526989</v>
+        <v>527168</v>
       </c>
       <c r="R120" t="n">
-        <v>6938371</v>
+        <v>6938291</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12879,11 +12884,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121226817</v>
+        <v>121223305</v>
       </c>
       <c r="B121" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12946,17 +12946,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526581</v>
+        <v>526584</v>
       </c>
       <c r="R121" t="n">
-        <v>6938053</v>
+        <v>6938052</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226792</v>
+        <v>121226804</v>
       </c>
       <c r="B122" t="n">
-        <v>90687</v>
+        <v>79682</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13052,10 +13052,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526796</v>
+        <v>526224</v>
       </c>
       <c r="R122" t="n">
-        <v>6937966</v>
+        <v>6938191</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121212780</v>
+        <v>121221064</v>
       </c>
       <c r="B123" t="n">
-        <v>78598</v>
+        <v>90711</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13130,37 +13130,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>527567</v>
+        <v>526664</v>
       </c>
       <c r="R123" t="n">
-        <v>6937949</v>
+        <v>6938176</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121221199</v>
+        <v>121226817</v>
       </c>
       <c r="B124" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,41 +13228,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526592</v>
+        <v>526581</v>
       </c>
       <c r="R124" t="n">
-        <v>6938232</v>
+        <v>6938053</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13318,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226805</v>
+        <v>121226801</v>
       </c>
       <c r="B125" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526203</v>
+        <v>526714</v>
       </c>
       <c r="R125" t="n">
-        <v>6938195</v>
+        <v>6938008</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226808</v>
+        <v>121212778</v>
       </c>
       <c r="B126" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13436,21 +13436,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526482</v>
+        <v>527288</v>
       </c>
       <c r="R126" t="n">
-        <v>6938338</v>
+        <v>6938221</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121219658</v>
+        <v>121226809</v>
       </c>
       <c r="B127" t="n">
-        <v>90652</v>
+        <v>79682</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526953</v>
+        <v>526518</v>
       </c>
       <c r="R127" t="n">
-        <v>6937958</v>
+        <v>6938295</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121221064</v>
+        <v>121226822</v>
       </c>
       <c r="B128" t="n">
-        <v>90701</v>
+        <v>91973</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13636,41 +13636,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526664</v>
+        <v>526182</v>
       </c>
       <c r="R128" t="n">
-        <v>6938176</v>
+        <v>6938234</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121222671</v>
+        <v>121226813</v>
       </c>
       <c r="B129" t="n">
-        <v>78598</v>
+        <v>78337</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,37 +13742,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526275</v>
+        <v>526365</v>
       </c>
       <c r="R129" t="n">
-        <v>6938199</v>
+        <v>6938404</v>
       </c>
       <c r="S129" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13802,11 +13802,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13833,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121220094</v>
+        <v>121226820</v>
       </c>
       <c r="B130" t="n">
-        <v>78334</v>
+        <v>90711</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13849,37 +13844,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526766</v>
+        <v>526660</v>
       </c>
       <c r="R130" t="n">
-        <v>6938100</v>
+        <v>6938167</v>
       </c>
       <c r="S130" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13935,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226798</v>
+        <v>121212788</v>
       </c>
       <c r="B131" t="n">
-        <v>79679</v>
+        <v>91973</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13947,25 +13942,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526747</v>
+        <v>526776</v>
       </c>
       <c r="R131" t="n">
-        <v>6937983</v>
+        <v>6938419</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14005,12 +14000,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14037,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121223305</v>
+        <v>121222671</v>
       </c>
       <c r="B132" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14049,25 +14044,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14077,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526584</v>
+        <v>526275</v>
       </c>
       <c r="R132" t="n">
-        <v>6938052</v>
+        <v>6938199</v>
       </c>
       <c r="S132" t="n">
         <v>20</v>
@@ -14113,6 +14108,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,10 +14139,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121220916</v>
+        <v>121226802</v>
       </c>
       <c r="B133" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14151,41 +14151,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526647</v>
+        <v>526716</v>
       </c>
       <c r="R133" t="n">
-        <v>6938174</v>
+        <v>6937997</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14241,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226822</v>
+        <v>121212779</v>
       </c>
       <c r="B134" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14253,25 +14253,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526182</v>
+        <v>527495</v>
       </c>
       <c r="R134" t="n">
-        <v>6938234</v>
+        <v>6938009</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14311,12 +14311,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14343,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226824</v>
+        <v>121226792</v>
       </c>
       <c r="B135" t="n">
-        <v>91249</v>
+        <v>90697</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14355,25 +14355,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526747</v>
+        <v>526796</v>
       </c>
       <c r="R135" t="n">
-        <v>6937983</v>
+        <v>6937966</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226809</v>
+        <v>121226793</v>
       </c>
       <c r="B136" t="n">
-        <v>79679</v>
+        <v>90717</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14461,21 +14461,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526518</v>
+        <v>526519</v>
       </c>
       <c r="R136" t="n">
-        <v>6938295</v>
+        <v>6938315</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14547,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226811</v>
+        <v>121226803</v>
       </c>
       <c r="B137" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526545</v>
+        <v>526335</v>
       </c>
       <c r="R137" t="n">
-        <v>6938319</v>
+        <v>6938150</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14649,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121212776</v>
+        <v>121220916</v>
       </c>
       <c r="B138" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14661,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>527090</v>
+        <v>526647</v>
       </c>
       <c r="R138" t="n">
-        <v>6938365</v>
+        <v>6938174</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14719,12 +14719,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14751,10 +14751,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226810</v>
+        <v>121226795</v>
       </c>
       <c r="B139" t="n">
-        <v>79679</v>
+        <v>79683</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14767,21 +14767,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14791,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526533</v>
+        <v>526554</v>
       </c>
       <c r="R139" t="n">
-        <v>6938315</v>
+        <v>6938311</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14853,10 +14853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121212789</v>
+        <v>121226821</v>
       </c>
       <c r="B140" t="n">
-        <v>91963</v>
+        <v>78601</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14865,25 +14865,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526823</v>
+        <v>526199</v>
       </c>
       <c r="R140" t="n">
-        <v>6938405</v>
+        <v>6938254</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14923,12 +14923,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14955,10 +14960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226803</v>
+        <v>121212776</v>
       </c>
       <c r="B141" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14971,21 +14976,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526335</v>
+        <v>527090</v>
       </c>
       <c r="R141" t="n">
-        <v>6938150</v>
+        <v>6938365</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15025,12 +15030,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15057,10 +15062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226791</v>
+        <v>121226798</v>
       </c>
       <c r="B142" t="n">
-        <v>89743</v>
+        <v>79682</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15073,21 +15078,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526205</v>
+        <v>526747</v>
       </c>
       <c r="R142" t="n">
-        <v>6938282</v>
+        <v>6937983</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15159,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121212778</v>
+        <v>121212789</v>
       </c>
       <c r="B143" t="n">
-        <v>78598</v>
+        <v>91973</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15171,25 +15176,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15199,10 +15204,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>527288</v>
+        <v>526823</v>
       </c>
       <c r="R143" t="n">
-        <v>6938221</v>
+        <v>6938405</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15261,10 +15266,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226794</v>
+        <v>121226805</v>
       </c>
       <c r="B144" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15273,25 +15278,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15301,10 +15306,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526478</v>
+        <v>526203</v>
       </c>
       <c r="R144" t="n">
-        <v>6938348</v>
+        <v>6938195</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15366,7 +15371,7 @@
         <v>121226806</v>
       </c>
       <c r="B145" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15465,10 +15470,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121226819</v>
+        <v>121220094</v>
       </c>
       <c r="B146" t="n">
-        <v>98071</v>
+        <v>78337</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15477,41 +15482,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526646</v>
+        <v>526766</v>
       </c>
       <c r="R146" t="n">
-        <v>6938173</v>
+        <v>6938100</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15567,10 +15572,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226796</v>
+        <v>121226811</v>
       </c>
       <c r="B147" t="n">
-        <v>90973</v>
+        <v>79682</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15583,21 +15588,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15607,10 +15612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526796</v>
+        <v>526545</v>
       </c>
       <c r="R147" t="n">
-        <v>6937966</v>
+        <v>6938319</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15669,10 +15674,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226816</v>
+        <v>121221199</v>
       </c>
       <c r="B148" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15681,41 +15686,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526789</v>
+        <v>526592</v>
       </c>
       <c r="R148" t="n">
-        <v>6937993</v>
+        <v>6938232</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15771,10 +15776,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226812</v>
+        <v>121226796</v>
       </c>
       <c r="B149" t="n">
-        <v>79679</v>
+        <v>90983</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15787,21 +15792,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15811,10 +15816,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526551</v>
+        <v>526796</v>
       </c>
       <c r="R149" t="n">
-        <v>6938312</v>
+        <v>6937966</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15873,10 +15878,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121212785</v>
+        <v>121226824</v>
       </c>
       <c r="B150" t="n">
-        <v>78243</v>
+        <v>91259</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15885,25 +15890,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>353</v>
+        <v>760</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15913,10 +15918,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526753</v>
+        <v>526747</v>
       </c>
       <c r="R150" t="n">
-        <v>6938395</v>
+        <v>6937983</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15943,12 +15948,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15975,10 +15980,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121212791</v>
+        <v>121226794</v>
       </c>
       <c r="B151" t="n">
-        <v>79714</v>
+        <v>79711</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15991,21 +15996,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16015,10 +16020,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>527094</v>
+        <v>526478</v>
       </c>
       <c r="R151" t="n">
-        <v>6938358</v>
+        <v>6938348</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16045,12 +16050,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16077,10 +16082,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121212779</v>
+        <v>121226815</v>
       </c>
       <c r="B152" t="n">
-        <v>78598</v>
+        <v>78337</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16093,21 +16098,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16117,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>527495</v>
+        <v>526527</v>
       </c>
       <c r="R152" t="n">
-        <v>6938009</v>
+        <v>6938317</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16147,12 +16152,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16179,10 +16184,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226821</v>
+        <v>121212780</v>
       </c>
       <c r="B153" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16219,10 +16224,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526199</v>
+        <v>527567</v>
       </c>
       <c r="R153" t="n">
-        <v>6938254</v>
+        <v>6937949</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16249,17 +16254,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16286,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226793</v>
+        <v>121219596</v>
       </c>
       <c r="B154" t="n">
-        <v>90707</v>
+        <v>78337</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16302,37 +16302,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526519</v>
+        <v>526982</v>
       </c>
       <c r="R154" t="n">
-        <v>6938315</v>
+        <v>6937928</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16388,10 +16388,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121219596</v>
+        <v>121226810</v>
       </c>
       <c r="B155" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16404,37 +16404,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526982</v>
+        <v>526533</v>
       </c>
       <c r="R155" t="n">
-        <v>6937928</v>
+        <v>6938315</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16490,10 +16490,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212783</v>
+        <v>121226797</v>
       </c>
       <c r="B156" t="n">
-        <v>78243</v>
+        <v>79682</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16506,21 +16506,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526761</v>
+        <v>526496</v>
       </c>
       <c r="R156" t="n">
-        <v>6938348</v>
+        <v>6938343</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16560,12 +16560,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16592,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226807</v>
+        <v>121226812</v>
       </c>
       <c r="B157" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16632,10 +16637,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526201</v>
+        <v>526551</v>
       </c>
       <c r="R157" t="n">
-        <v>6938252</v>
+        <v>6938312</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16694,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226804</v>
+        <v>121226818</v>
       </c>
       <c r="B158" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16706,25 +16711,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16734,10 +16739,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526224</v>
+        <v>526525</v>
       </c>
       <c r="R158" t="n">
-        <v>6938191</v>
+        <v>6938312</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16796,10 +16801,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226818</v>
+        <v>121226819</v>
       </c>
       <c r="B159" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16836,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526525</v>
+        <v>526646</v>
       </c>
       <c r="R159" t="n">
-        <v>6938312</v>
+        <v>6938173</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16898,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226801</v>
+        <v>121212783</v>
       </c>
       <c r="B160" t="n">
-        <v>79679</v>
+        <v>78246</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16914,21 +16919,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16938,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526714</v>
+        <v>526761</v>
       </c>
       <c r="R160" t="n">
-        <v>6938008</v>
+        <v>6938348</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16968,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17000,10 +17005,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226797</v>
+        <v>121226808</v>
       </c>
       <c r="B161" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17040,10 +17045,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526496</v>
+        <v>526482</v>
       </c>
       <c r="R161" t="n">
-        <v>6938343</v>
+        <v>6938338</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17076,11 +17081,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17107,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226820</v>
+        <v>121212791</v>
       </c>
       <c r="B162" t="n">
-        <v>90701</v>
+        <v>79717</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17119,25 +17119,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17147,10 +17147,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526660</v>
+        <v>527094</v>
       </c>
       <c r="R162" t="n">
-        <v>6938167</v>
+        <v>6938358</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17177,12 +17177,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17209,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121212788</v>
+        <v>121226816</v>
       </c>
       <c r="B163" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17221,25 +17221,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526776</v>
+        <v>526789</v>
       </c>
       <c r="R163" t="n">
-        <v>6938419</v>
+        <v>6937993</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226795</v>
+        <v>121212785</v>
       </c>
       <c r="B164" t="n">
-        <v>79680</v>
+        <v>78246</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17327,21 +17327,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526554</v>
+        <v>526753</v>
       </c>
       <c r="R164" t="n">
-        <v>6938311</v>
+        <v>6938395</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17381,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226802</v>
+        <v>121219658</v>
       </c>
       <c r="B165" t="n">
-        <v>79679</v>
+        <v>90662</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,41 +17425,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526716</v>
+        <v>526953</v>
       </c>
       <c r="R165" t="n">
-        <v>6937997</v>
+        <v>6937958</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226814</v>
+        <v>121226791</v>
       </c>
       <c r="B166" t="n">
-        <v>78334</v>
+        <v>89753</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,21 +17531,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526515</v>
+        <v>526205</v>
       </c>
       <c r="R166" t="n">
-        <v>6938303</v>
+        <v>6938282</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226813</v>
+        <v>121226807</v>
       </c>
       <c r="B167" t="n">
-        <v>78334</v>
+        <v>79682</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17633,21 +17633,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526365</v>
+        <v>526201</v>
       </c>
       <c r="R167" t="n">
-        <v>6938404</v>
+        <v>6938252</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226815</v>
+        <v>121226814</v>
       </c>
       <c r="B168" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526527</v>
+        <v>526515</v>
       </c>
       <c r="R168" t="n">
-        <v>6938317</v>
+        <v>6938303</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17824,7 +17824,7 @@
         <v>121212693</v>
       </c>
       <c r="B169" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>121246286</v>
       </c>
       <c r="B170" t="n">
-        <v>91992</v>
+        <v>92002</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121185408</v>
+        <v>121179693</v>
       </c>
       <c r="B171" t="n">
-        <v>90973</v>
+        <v>91973</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527661</v>
+        <v>527779</v>
       </c>
       <c r="R171" t="n">
-        <v>6937695</v>
+        <v>6937594</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121179849</v>
+        <v>121185408</v>
       </c>
       <c r="B172" t="n">
-        <v>91127</v>
+        <v>90983</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527658</v>
+        <v>527661</v>
       </c>
       <c r="R172" t="n">
-        <v>6937694</v>
+        <v>6937695</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>121185404</v>
       </c>
       <c r="B173" t="n">
-        <v>91127</v>
+        <v>91137</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121179693</v>
+        <v>121179849</v>
       </c>
       <c r="B174" t="n">
-        <v>91963</v>
+        <v>91137</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18357,25 +18357,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18385,13 +18385,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527779</v>
+        <v>527658</v>
       </c>
       <c r="R174" t="n">
-        <v>6937594</v>
+        <v>6937694</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185413</v>
+        <v>121182248</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,41 +1983,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527044</v>
+        <v>527008</v>
       </c>
       <c r="R14" t="n">
-        <v>6938065</v>
+        <v>6938092</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121182248</v>
+        <v>121180239</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2109,17 +2109,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527008</v>
+        <v>527495</v>
       </c>
       <c r="R15" t="n">
-        <v>6938092</v>
+        <v>6937765</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121180239</v>
+        <v>121185413</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,41 +2187,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527495</v>
+        <v>527044</v>
       </c>
       <c r="R16" t="n">
-        <v>6937765</v>
+        <v>6938065</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185426</v>
+        <v>121185403</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>90644</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,25 +2697,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527503</v>
+        <v>527012</v>
       </c>
       <c r="R21" t="n">
-        <v>6937855</v>
+        <v>6938063</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185403</v>
+        <v>121185426</v>
       </c>
       <c r="B22" t="n">
-        <v>90644</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527012</v>
+        <v>527503</v>
       </c>
       <c r="R22" t="n">
-        <v>6938063</v>
+        <v>6937855</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185432</v>
+        <v>121185425</v>
       </c>
       <c r="B24" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527217</v>
+        <v>527014</v>
       </c>
       <c r="R24" t="n">
-        <v>6937854</v>
+        <v>6938062</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185425</v>
+        <v>121185432</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,25 +3105,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527014</v>
+        <v>527217</v>
       </c>
       <c r="R25" t="n">
-        <v>6938062</v>
+        <v>6937854</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185407</v>
+        <v>121185414</v>
       </c>
       <c r="B26" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527016</v>
+        <v>527346</v>
       </c>
       <c r="R26" t="n">
-        <v>6938062</v>
+        <v>6937925</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185414</v>
+        <v>121179977</v>
       </c>
       <c r="B27" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,37 +3313,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527346</v>
+        <v>527626</v>
       </c>
       <c r="R27" t="n">
-        <v>6937925</v>
+        <v>6937719</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185429</v>
+        <v>121185407</v>
       </c>
       <c r="B28" t="n">
-        <v>91973</v>
+        <v>90983</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,25 +3411,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527641</v>
+        <v>527016</v>
       </c>
       <c r="R28" t="n">
-        <v>6937808</v>
+        <v>6938062</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179977</v>
+        <v>121185429</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,41 +3513,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527626</v>
+        <v>527641</v>
       </c>
       <c r="R29" t="n">
-        <v>6937719</v>
+        <v>6937808</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121185427</v>
+        <v>121180261</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527034</v>
+        <v>527506</v>
       </c>
       <c r="R40" t="n">
-        <v>6938099</v>
+        <v>6937752</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121180261</v>
+        <v>121185421</v>
       </c>
       <c r="B41" t="n">
         <v>98081</v>
@@ -4761,17 +4761,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527506</v>
+        <v>526958</v>
       </c>
       <c r="R41" t="n">
-        <v>6937752</v>
+        <v>6938116</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185421</v>
+        <v>121185422</v>
       </c>
       <c r="B42" t="n">
         <v>98081</v>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>526958</v>
+        <v>526995</v>
       </c>
       <c r="R42" t="n">
-        <v>6938116</v>
+        <v>6938144</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185422</v>
+        <v>121180230</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526995</v>
+        <v>527509</v>
       </c>
       <c r="R43" t="n">
-        <v>6938144</v>
+        <v>6937756</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121180230</v>
+        <v>121185427</v>
       </c>
       <c r="B44" t="n">
-        <v>105186</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527509</v>
+        <v>527034</v>
       </c>
       <c r="R44" t="n">
-        <v>6937756</v>
+        <v>6938099</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121185430</v>
+        <v>121185398</v>
       </c>
       <c r="B46" t="n">
-        <v>91973</v>
+        <v>90697</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,25 +5247,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527460</v>
+        <v>526983</v>
       </c>
       <c r="R46" t="n">
-        <v>6937819</v>
+        <v>6938135</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121185398</v>
+        <v>121185400</v>
       </c>
       <c r="B47" t="n">
         <v>90697</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>526983</v>
+        <v>527034</v>
       </c>
       <c r="R47" t="n">
-        <v>6938135</v>
+        <v>6938099</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185400</v>
+        <v>121185405</v>
       </c>
       <c r="B48" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185405</v>
+        <v>121185430</v>
       </c>
       <c r="B49" t="n">
-        <v>90983</v>
+        <v>91973</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5553,25 +5553,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527034</v>
+        <v>527460</v>
       </c>
       <c r="R49" t="n">
-        <v>6938099</v>
+        <v>6937819</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121183281</v>
+        <v>121185402</v>
       </c>
       <c r="B52" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,41 +5859,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>526958</v>
+        <v>527367</v>
       </c>
       <c r="R52" t="n">
-        <v>6938109</v>
+        <v>6937938</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121185402</v>
+        <v>121183281</v>
       </c>
       <c r="B53" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527367</v>
+        <v>526958</v>
       </c>
       <c r="R53" t="n">
-        <v>6937938</v>
+        <v>6938109</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212694</v>
+        <v>121212758</v>
       </c>
       <c r="B55" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527088</v>
+        <v>526823</v>
       </c>
       <c r="R55" t="n">
-        <v>6938356</v>
+        <v>6938405</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212731</v>
+        <v>121212694</v>
       </c>
       <c r="B56" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527184</v>
+        <v>527088</v>
       </c>
       <c r="R56" t="n">
-        <v>6938280</v>
+        <v>6938356</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212758</v>
+        <v>121212731</v>
       </c>
       <c r="B57" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526823</v>
+        <v>527184</v>
       </c>
       <c r="R57" t="n">
-        <v>6938405</v>
+        <v>6938280</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -8820,10 +8820,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212697</v>
+        <v>121212762</v>
       </c>
       <c r="B81" t="n">
-        <v>79683</v>
+        <v>98081</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8832,25 +8832,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527186</v>
+        <v>526868</v>
       </c>
       <c r="R81" t="n">
-        <v>6938273</v>
+        <v>6938367</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212716</v>
+        <v>121212697</v>
       </c>
       <c r="B82" t="n">
-        <v>79682</v>
+        <v>79683</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526994</v>
+        <v>527186</v>
       </c>
       <c r="R82" t="n">
-        <v>6938374</v>
+        <v>6938273</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212762</v>
+        <v>121212716</v>
       </c>
       <c r="B83" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9036,25 +9036,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526868</v>
+        <v>526994</v>
       </c>
       <c r="R83" t="n">
-        <v>6938367</v>
+        <v>6938374</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212688</v>
+        <v>121212733</v>
       </c>
       <c r="B101" t="n">
-        <v>95628</v>
+        <v>79682</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10881,21 +10881,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527409</v>
+        <v>527186</v>
       </c>
       <c r="R101" t="n">
-        <v>6938091</v>
+        <v>6938273</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212733</v>
+        <v>121212723</v>
       </c>
       <c r="B102" t="n">
         <v>79682</v>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527186</v>
+        <v>527088</v>
       </c>
       <c r="R102" t="n">
-        <v>6938273</v>
+        <v>6938358</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212723</v>
+        <v>121212688</v>
       </c>
       <c r="B103" t="n">
-        <v>79682</v>
+        <v>95628</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>527088</v>
+        <v>527409</v>
       </c>
       <c r="R103" t="n">
-        <v>6938358</v>
+        <v>6938091</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121221064</v>
+        <v>121226817</v>
       </c>
       <c r="B123" t="n">
-        <v>90711</v>
+        <v>98081</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,41 +13126,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526664</v>
+        <v>526581</v>
       </c>
       <c r="R123" t="n">
-        <v>6938176</v>
+        <v>6938053</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226817</v>
+        <v>121221064</v>
       </c>
       <c r="B124" t="n">
-        <v>98081</v>
+        <v>90711</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,41 +13228,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526581</v>
+        <v>526664</v>
       </c>
       <c r="R124" t="n">
-        <v>6938053</v>
+        <v>6938176</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226813</v>
+        <v>121226820</v>
       </c>
       <c r="B129" t="n">
-        <v>78337</v>
+        <v>90711</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526365</v>
+        <v>526660</v>
       </c>
       <c r="R129" t="n">
-        <v>6938404</v>
+        <v>6938167</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226820</v>
+        <v>121226813</v>
       </c>
       <c r="B130" t="n">
-        <v>90711</v>
+        <v>78337</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,21 +13844,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526660</v>
+        <v>526365</v>
       </c>
       <c r="R130" t="n">
-        <v>6938167</v>
+        <v>6938404</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14853,7 +14853,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226821</v>
+        <v>121212776</v>
       </c>
       <c r="B140" t="n">
         <v>78601</v>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526199</v>
+        <v>527090</v>
       </c>
       <c r="R140" t="n">
-        <v>6938254</v>
+        <v>6938365</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14923,17 +14923,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14960,7 +14955,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121212776</v>
+        <v>121226821</v>
       </c>
       <c r="B141" t="n">
         <v>78601</v>
@@ -15000,10 +14995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>527090</v>
+        <v>526199</v>
       </c>
       <c r="R141" t="n">
-        <v>6938365</v>
+        <v>6938254</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15030,12 +15025,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15062,10 +15062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226798</v>
+        <v>121212789</v>
       </c>
       <c r="B142" t="n">
-        <v>79682</v>
+        <v>91973</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15074,25 +15074,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526747</v>
+        <v>526823</v>
       </c>
       <c r="R142" t="n">
-        <v>6937983</v>
+        <v>6938405</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15132,12 +15132,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15164,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121212789</v>
+        <v>121226805</v>
       </c>
       <c r="B143" t="n">
-        <v>91973</v>
+        <v>79682</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15176,25 +15176,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526823</v>
+        <v>526203</v>
       </c>
       <c r="R143" t="n">
-        <v>6938405</v>
+        <v>6938195</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15266,7 +15266,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226805</v>
+        <v>121226806</v>
       </c>
       <c r="B144" t="n">
         <v>79682</v>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526203</v>
+        <v>526182</v>
       </c>
       <c r="R144" t="n">
-        <v>6938195</v>
+        <v>6938206</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15368,7 +15368,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226806</v>
+        <v>121226798</v>
       </c>
       <c r="B145" t="n">
         <v>79682</v>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526182</v>
+        <v>526747</v>
       </c>
       <c r="R145" t="n">
-        <v>6938206</v>
+        <v>6937983</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15776,10 +15776,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226796</v>
+        <v>121226794</v>
       </c>
       <c r="B149" t="n">
-        <v>90983</v>
+        <v>79711</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15788,25 +15788,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526796</v>
+        <v>526478</v>
       </c>
       <c r="R149" t="n">
-        <v>6937966</v>
+        <v>6938348</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15878,10 +15878,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226824</v>
+        <v>121226815</v>
       </c>
       <c r="B150" t="n">
-        <v>91259</v>
+        <v>78337</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15890,25 +15890,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526747</v>
+        <v>526527</v>
       </c>
       <c r="R150" t="n">
-        <v>6937983</v>
+        <v>6938317</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15980,10 +15980,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226794</v>
+        <v>121226796</v>
       </c>
       <c r="B151" t="n">
-        <v>79711</v>
+        <v>90983</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15992,25 +15992,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16020,10 +16020,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526478</v>
+        <v>526796</v>
       </c>
       <c r="R151" t="n">
-        <v>6938348</v>
+        <v>6937966</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16082,10 +16082,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226815</v>
+        <v>121226824</v>
       </c>
       <c r="B152" t="n">
-        <v>78337</v>
+        <v>91259</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16094,25 +16094,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526527</v>
+        <v>526747</v>
       </c>
       <c r="R152" t="n">
-        <v>6938317</v>
+        <v>6937983</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226818</v>
+        <v>121212783</v>
       </c>
       <c r="B158" t="n">
-        <v>98081</v>
+        <v>78246</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16711,25 +16711,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526525</v>
+        <v>526761</v>
       </c>
       <c r="R158" t="n">
-        <v>6938312</v>
+        <v>6938348</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16769,12 +16769,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16801,7 +16801,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226819</v>
+        <v>121226818</v>
       </c>
       <c r="B159" t="n">
         <v>98081</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526646</v>
+        <v>526525</v>
       </c>
       <c r="R159" t="n">
-        <v>6938173</v>
+        <v>6938312</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121212783</v>
+        <v>121226819</v>
       </c>
       <c r="B160" t="n">
-        <v>78246</v>
+        <v>98081</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16915,25 +16915,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526761</v>
+        <v>526646</v>
       </c>
       <c r="R160" t="n">
-        <v>6938348</v>
+        <v>6938173</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16973,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17107,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121212791</v>
+        <v>121219658</v>
       </c>
       <c r="B162" t="n">
-        <v>79717</v>
+        <v>90662</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17123,37 +17123,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>527094</v>
+        <v>526953</v>
       </c>
       <c r="R162" t="n">
-        <v>6938358</v>
+        <v>6937958</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17177,12 +17177,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17209,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226816</v>
+        <v>121212791</v>
       </c>
       <c r="B163" t="n">
-        <v>98081</v>
+        <v>79717</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17221,25 +17221,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526789</v>
+        <v>527094</v>
       </c>
       <c r="R163" t="n">
-        <v>6937993</v>
+        <v>6938358</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121212785</v>
+        <v>121226816</v>
       </c>
       <c r="B164" t="n">
-        <v>78246</v>
+        <v>98081</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17323,25 +17323,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526753</v>
+        <v>526789</v>
       </c>
       <c r="R164" t="n">
-        <v>6938395</v>
+        <v>6937993</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17381,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121219658</v>
+        <v>121212785</v>
       </c>
       <c r="B165" t="n">
-        <v>90662</v>
+        <v>78246</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,41 +17425,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526953</v>
+        <v>526753</v>
       </c>
       <c r="R165" t="n">
-        <v>6937958</v>
+        <v>6938395</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17483,12 +17483,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185414</v>
+        <v>121185407</v>
       </c>
       <c r="B26" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527346</v>
+        <v>527016</v>
       </c>
       <c r="R26" t="n">
-        <v>6937925</v>
+        <v>6938062</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121179977</v>
+        <v>121185414</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,37 +3313,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527626</v>
+        <v>527346</v>
       </c>
       <c r="R27" t="n">
-        <v>6937719</v>
+        <v>6937925</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185407</v>
+        <v>121185429</v>
       </c>
       <c r="B28" t="n">
-        <v>90983</v>
+        <v>91973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,25 +3411,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527016</v>
+        <v>527641</v>
       </c>
       <c r="R28" t="n">
-        <v>6938062</v>
+        <v>6937808</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121185429</v>
+        <v>121179977</v>
       </c>
       <c r="B29" t="n">
-        <v>91973</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,41 +3513,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527641</v>
+        <v>527626</v>
       </c>
       <c r="R29" t="n">
-        <v>6937808</v>
+        <v>6937719</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121180141</v>
+        <v>121185415</v>
       </c>
       <c r="B35" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,41 +4125,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527597</v>
+        <v>527391</v>
       </c>
       <c r="R35" t="n">
-        <v>6937703</v>
+        <v>6937910</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185415</v>
+        <v>121180141</v>
       </c>
       <c r="B36" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,41 +4227,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527391</v>
+        <v>527597</v>
       </c>
       <c r="R36" t="n">
-        <v>6937910</v>
+        <v>6937703</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121180261</v>
+        <v>121185427</v>
       </c>
       <c r="B40" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527506</v>
+        <v>527034</v>
       </c>
       <c r="R40" t="n">
-        <v>6937752</v>
+        <v>6938099</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185421</v>
+        <v>121180261</v>
       </c>
       <c r="B41" t="n">
         <v>98081</v>
@@ -4761,17 +4761,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526958</v>
+        <v>527506</v>
       </c>
       <c r="R41" t="n">
-        <v>6938116</v>
+        <v>6937752</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185422</v>
+        <v>121185421</v>
       </c>
       <c r="B42" t="n">
         <v>98081</v>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>526995</v>
+        <v>526958</v>
       </c>
       <c r="R42" t="n">
-        <v>6938144</v>
+        <v>6938116</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121180230</v>
+        <v>121185422</v>
       </c>
       <c r="B43" t="n">
-        <v>105186</v>
+        <v>98081</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527509</v>
+        <v>526995</v>
       </c>
       <c r="R43" t="n">
-        <v>6937756</v>
+        <v>6938144</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185427</v>
+        <v>121180230</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>105186</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527034</v>
+        <v>527509</v>
       </c>
       <c r="R44" t="n">
-        <v>6938099</v>
+        <v>6937756</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212758</v>
+        <v>121212694</v>
       </c>
       <c r="B55" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526823</v>
+        <v>527088</v>
       </c>
       <c r="R55" t="n">
-        <v>6938405</v>
+        <v>6938356</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212694</v>
+        <v>121212731</v>
       </c>
       <c r="B56" t="n">
-        <v>79711</v>
+        <v>79682</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527088</v>
+        <v>527184</v>
       </c>
       <c r="R56" t="n">
-        <v>6938356</v>
+        <v>6938280</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212731</v>
+        <v>121212758</v>
       </c>
       <c r="B57" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527184</v>
+        <v>526823</v>
       </c>
       <c r="R57" t="n">
-        <v>6938280</v>
+        <v>6938405</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212755</v>
+        <v>121212759</v>
       </c>
       <c r="B92" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9954,25 +9954,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>526945</v>
+        <v>526838</v>
       </c>
       <c r="R92" t="n">
-        <v>6938389</v>
+        <v>6938397</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212737</v>
+        <v>121212765</v>
       </c>
       <c r="B93" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10056,25 +10056,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527248</v>
+        <v>526955</v>
       </c>
       <c r="R93" t="n">
-        <v>6938256</v>
+        <v>6938367</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10146,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212713</v>
+        <v>121212755</v>
       </c>
       <c r="B94" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10162,21 +10162,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526960</v>
+        <v>526945</v>
       </c>
       <c r="R94" t="n">
-        <v>6938390</v>
+        <v>6938389</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212759</v>
+        <v>121212737</v>
       </c>
       <c r="B95" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10260,25 +10260,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>526838</v>
+        <v>527248</v>
       </c>
       <c r="R95" t="n">
-        <v>6938397</v>
+        <v>6938256</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212765</v>
+        <v>121212713</v>
       </c>
       <c r="B96" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10362,25 +10362,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526955</v>
+        <v>526960</v>
       </c>
       <c r="R96" t="n">
-        <v>6938367</v>
+        <v>6938390</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212734</v>
+        <v>121212699</v>
       </c>
       <c r="B113" t="n">
-        <v>79682</v>
+        <v>79586</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12106,25 +12106,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527214</v>
+        <v>527249</v>
       </c>
       <c r="R113" t="n">
-        <v>6938296</v>
+        <v>6938289</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212699</v>
+        <v>121212734</v>
       </c>
       <c r="B114" t="n">
-        <v>79586</v>
+        <v>79682</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12208,25 +12208,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527249</v>
+        <v>527214</v>
       </c>
       <c r="R114" t="n">
-        <v>6938289</v>
+        <v>6938296</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121226817</v>
+        <v>121221064</v>
       </c>
       <c r="B123" t="n">
-        <v>98081</v>
+        <v>90711</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,41 +13126,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526581</v>
+        <v>526664</v>
       </c>
       <c r="R123" t="n">
-        <v>6938053</v>
+        <v>6938176</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121221064</v>
+        <v>121226817</v>
       </c>
       <c r="B124" t="n">
-        <v>90711</v>
+        <v>98081</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,41 +13228,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526664</v>
+        <v>526581</v>
       </c>
       <c r="R124" t="n">
-        <v>6938176</v>
+        <v>6938053</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226820</v>
+        <v>121226813</v>
       </c>
       <c r="B129" t="n">
-        <v>90711</v>
+        <v>78337</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526660</v>
+        <v>526365</v>
       </c>
       <c r="R129" t="n">
-        <v>6938167</v>
+        <v>6938404</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226813</v>
+        <v>121226820</v>
       </c>
       <c r="B130" t="n">
-        <v>78337</v>
+        <v>90711</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,21 +13844,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526365</v>
+        <v>526660</v>
       </c>
       <c r="R130" t="n">
-        <v>6938404</v>
+        <v>6938167</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226792</v>
+        <v>121226793</v>
       </c>
       <c r="B135" t="n">
-        <v>90697</v>
+        <v>90717</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14359,21 +14359,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526796</v>
+        <v>526519</v>
       </c>
       <c r="R135" t="n">
-        <v>6937966</v>
+        <v>6938315</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226793</v>
+        <v>121220916</v>
       </c>
       <c r="B136" t="n">
-        <v>90717</v>
+        <v>98081</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,41 +14457,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526519</v>
+        <v>526647</v>
       </c>
       <c r="R136" t="n">
-        <v>6938315</v>
+        <v>6938174</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14547,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226803</v>
+        <v>121226792</v>
       </c>
       <c r="B137" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14563,21 +14563,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526335</v>
+        <v>526796</v>
       </c>
       <c r="R137" t="n">
-        <v>6938150</v>
+        <v>6937966</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14649,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121220916</v>
+        <v>121226803</v>
       </c>
       <c r="B138" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14661,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526647</v>
+        <v>526335</v>
       </c>
       <c r="R138" t="n">
-        <v>6938174</v>
+        <v>6938150</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15062,10 +15062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121212789</v>
+        <v>121226798</v>
       </c>
       <c r="B142" t="n">
-        <v>91973</v>
+        <v>79682</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15074,25 +15074,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15102,10 +15102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526823</v>
+        <v>526747</v>
       </c>
       <c r="R142" t="n">
-        <v>6938405</v>
+        <v>6937983</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15132,12 +15132,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15164,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226805</v>
+        <v>121212789</v>
       </c>
       <c r="B143" t="n">
-        <v>79682</v>
+        <v>91973</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15176,25 +15176,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526203</v>
+        <v>526823</v>
       </c>
       <c r="R143" t="n">
-        <v>6938195</v>
+        <v>6938405</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15266,7 +15266,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226806</v>
+        <v>121226805</v>
       </c>
       <c r="B144" t="n">
         <v>79682</v>
@@ -15306,10 +15306,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526182</v>
+        <v>526203</v>
       </c>
       <c r="R144" t="n">
-        <v>6938206</v>
+        <v>6938195</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15368,7 +15368,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226798</v>
+        <v>121226806</v>
       </c>
       <c r="B145" t="n">
         <v>79682</v>
@@ -15408,10 +15408,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526747</v>
+        <v>526182</v>
       </c>
       <c r="R145" t="n">
-        <v>6937983</v>
+        <v>6938206</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121212783</v>
+        <v>121226818</v>
       </c>
       <c r="B158" t="n">
-        <v>78246</v>
+        <v>98081</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16711,25 +16711,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16739,10 +16739,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526761</v>
+        <v>526525</v>
       </c>
       <c r="R158" t="n">
-        <v>6938348</v>
+        <v>6938312</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16769,12 +16769,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16801,7 +16801,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226818</v>
+        <v>121226819</v>
       </c>
       <c r="B159" t="n">
         <v>98081</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526525</v>
+        <v>526646</v>
       </c>
       <c r="R159" t="n">
-        <v>6938312</v>
+        <v>6938173</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226819</v>
+        <v>121212783</v>
       </c>
       <c r="B160" t="n">
-        <v>98081</v>
+        <v>78246</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16915,25 +16915,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526646</v>
+        <v>526761</v>
       </c>
       <c r="R160" t="n">
-        <v>6938173</v>
+        <v>6938348</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16973,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17107,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121219658</v>
+        <v>121212791</v>
       </c>
       <c r="B162" t="n">
-        <v>90662</v>
+        <v>79717</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17123,37 +17123,37 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526953</v>
+        <v>527094</v>
       </c>
       <c r="R162" t="n">
-        <v>6937958</v>
+        <v>6938358</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17177,12 +17177,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17209,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121212791</v>
+        <v>121226816</v>
       </c>
       <c r="B163" t="n">
-        <v>79717</v>
+        <v>98081</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17221,25 +17221,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>527094</v>
+        <v>526789</v>
       </c>
       <c r="R163" t="n">
-        <v>6938358</v>
+        <v>6937993</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17279,12 +17279,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226816</v>
+        <v>121212785</v>
       </c>
       <c r="B164" t="n">
-        <v>98081</v>
+        <v>78246</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17323,25 +17323,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526789</v>
+        <v>526753</v>
       </c>
       <c r="R164" t="n">
-        <v>6937993</v>
+        <v>6938395</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17381,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121212785</v>
+        <v>121219658</v>
       </c>
       <c r="B165" t="n">
-        <v>78246</v>
+        <v>90662</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,41 +17425,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526753</v>
+        <v>526953</v>
       </c>
       <c r="R165" t="n">
-        <v>6938395</v>
+        <v>6937958</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17483,12 +17483,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD165" t="b">

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185435</v>
+        <v>121185396</v>
       </c>
       <c r="B6" t="n">
-        <v>91353</v>
+        <v>90662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,25 +1167,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527008</v>
+        <v>526980</v>
       </c>
       <c r="R6" t="n">
-        <v>6938073</v>
+        <v>6938115</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185401</v>
+        <v>121185427</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527016</v>
+        <v>527034</v>
       </c>
       <c r="R7" t="n">
-        <v>6938060</v>
+        <v>6938099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185399</v>
+        <v>121183008</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,41 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526989</v>
+        <v>526999</v>
       </c>
       <c r="R8" t="n">
-        <v>6938147</v>
+        <v>6938157</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185395</v>
+        <v>121185429</v>
       </c>
       <c r="B9" t="n">
-        <v>95628</v>
+        <v>91973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1473,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527048</v>
+        <v>527641</v>
       </c>
       <c r="R9" t="n">
-        <v>6938076</v>
+        <v>6937808</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185434</v>
+        <v>121185407</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526953</v>
+        <v>527016</v>
       </c>
       <c r="R10" t="n">
-        <v>6938054</v>
+        <v>6938062</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185433</v>
+        <v>121185424</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527195</v>
+        <v>527010</v>
       </c>
       <c r="R11" t="n">
-        <v>6937884</v>
+        <v>6938105</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185417</v>
+        <v>121185397</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527368</v>
+        <v>527043</v>
       </c>
       <c r="R12" t="n">
-        <v>6937959</v>
+        <v>6938062</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185428</v>
+        <v>121180261</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,41 +1881,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527439</v>
+        <v>527506</v>
       </c>
       <c r="R13" t="n">
-        <v>6937974</v>
+        <v>6937752</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121182248</v>
+        <v>121185395</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>95628</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,41 +1983,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527008</v>
+        <v>527048</v>
       </c>
       <c r="R14" t="n">
-        <v>6938092</v>
+        <v>6938076</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121180239</v>
+        <v>121185406</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>90983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,41 +2085,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527495</v>
+        <v>527009</v>
       </c>
       <c r="R15" t="n">
-        <v>6937765</v>
+        <v>6938044</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185413</v>
+        <v>121185414</v>
       </c>
       <c r="B16" t="n">
         <v>79682</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527044</v>
+        <v>527346</v>
       </c>
       <c r="R16" t="n">
-        <v>6938065</v>
+        <v>6937925</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185418</v>
+        <v>121185430</v>
       </c>
       <c r="B17" t="n">
-        <v>79682</v>
+        <v>91973</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527437</v>
+        <v>527460</v>
       </c>
       <c r="R17" t="n">
-        <v>6937974</v>
+        <v>6937819</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121180712</v>
+        <v>121185431</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,41 +2391,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527305</v>
+        <v>527439</v>
       </c>
       <c r="R18" t="n">
-        <v>6937895</v>
+        <v>6937815</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185412</v>
+        <v>121185402</v>
       </c>
       <c r="B19" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527001</v>
+        <v>527367</v>
       </c>
       <c r="R19" t="n">
-        <v>6938101</v>
+        <v>6937938</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121185424</v>
+        <v>121185433</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527010</v>
+        <v>527195</v>
       </c>
       <c r="R20" t="n">
-        <v>6938105</v>
+        <v>6937884</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185403</v>
+        <v>121179876</v>
       </c>
       <c r="B21" t="n">
-        <v>90644</v>
+        <v>90983</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,37 +2701,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527012</v>
+        <v>527649</v>
       </c>
       <c r="R21" t="n">
-        <v>6938063</v>
+        <v>6937696</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185426</v>
+        <v>121185401</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527503</v>
+        <v>527016</v>
       </c>
       <c r="R22" t="n">
-        <v>6937855</v>
+        <v>6938060</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185397</v>
+        <v>121185399</v>
       </c>
       <c r="B23" t="n">
-        <v>90662</v>
+        <v>90697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,25 +2901,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527043</v>
+        <v>526989</v>
       </c>
       <c r="R23" t="n">
-        <v>6938062</v>
+        <v>6938147</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185425</v>
+        <v>121185409</v>
       </c>
       <c r="B24" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527014</v>
+        <v>527108</v>
       </c>
       <c r="R24" t="n">
-        <v>6938062</v>
+        <v>6938086</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185432</v>
+        <v>121185415</v>
       </c>
       <c r="B25" t="n">
-        <v>91973</v>
+        <v>79682</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,25 +3105,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527217</v>
+        <v>527391</v>
       </c>
       <c r="R25" t="n">
-        <v>6937854</v>
+        <v>6937910</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185407</v>
+        <v>121183281</v>
       </c>
       <c r="B26" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,41 +3207,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527016</v>
+        <v>526958</v>
       </c>
       <c r="R26" t="n">
-        <v>6938062</v>
+        <v>6938109</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185414</v>
+        <v>121185410</v>
       </c>
       <c r="B27" t="n">
         <v>79682</v>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527346</v>
+        <v>527024</v>
       </c>
       <c r="R27" t="n">
-        <v>6937925</v>
+        <v>6938111</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185429</v>
+        <v>121185411</v>
       </c>
       <c r="B28" t="n">
-        <v>91973</v>
+        <v>79682</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,25 +3411,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527641</v>
+        <v>527045</v>
       </c>
       <c r="R28" t="n">
-        <v>6937808</v>
+        <v>6938075</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121179977</v>
+        <v>121185412</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3517,37 +3517,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527626</v>
+        <v>527001</v>
       </c>
       <c r="R29" t="n">
-        <v>6937719</v>
+        <v>6938101</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185409</v>
+        <v>121182248</v>
       </c>
       <c r="B30" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,41 +3615,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527108</v>
+        <v>527008</v>
       </c>
       <c r="R30" t="n">
-        <v>6938086</v>
+        <v>6938092</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185419</v>
+        <v>121185435</v>
       </c>
       <c r="B31" t="n">
-        <v>79718</v>
+        <v>91353</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,25 +3717,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527001</v>
+        <v>527008</v>
       </c>
       <c r="R31" t="n">
-        <v>6938096</v>
+        <v>6938073</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185406</v>
+        <v>121180712</v>
       </c>
       <c r="B32" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3823,37 +3823,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527009</v>
+        <v>527305</v>
       </c>
       <c r="R32" t="n">
-        <v>6938044</v>
+        <v>6937895</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121179876</v>
+        <v>121180239</v>
       </c>
       <c r="B33" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3921,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527649</v>
+        <v>527495</v>
       </c>
       <c r="R33" t="n">
-        <v>6937696</v>
+        <v>6937765</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185423</v>
+        <v>121185403</v>
       </c>
       <c r="B34" t="n">
-        <v>98081</v>
+        <v>90644</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>526974</v>
+        <v>527012</v>
       </c>
       <c r="R34" t="n">
-        <v>6938145</v>
+        <v>6938063</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185415</v>
+        <v>121185423</v>
       </c>
       <c r="B35" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,25 +4125,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527391</v>
+        <v>526974</v>
       </c>
       <c r="R35" t="n">
-        <v>6937910</v>
+        <v>6938145</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121180141</v>
+        <v>121185418</v>
       </c>
       <c r="B36" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,41 +4227,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527597</v>
+        <v>527437</v>
       </c>
       <c r="R36" t="n">
-        <v>6937703</v>
+        <v>6937974</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121185410</v>
+        <v>121185413</v>
       </c>
       <c r="B37" t="n">
         <v>79682</v>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527024</v>
+        <v>527044</v>
       </c>
       <c r="R37" t="n">
-        <v>6938111</v>
+        <v>6938065</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121183008</v>
+        <v>121179977</v>
       </c>
       <c r="B39" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,38 +4533,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526999</v>
+        <v>527626</v>
       </c>
       <c r="R39" t="n">
-        <v>6938157</v>
+        <v>6937719</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121185427</v>
+        <v>121180291</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4639,37 +4639,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527034</v>
+        <v>527492</v>
       </c>
       <c r="R40" t="n">
-        <v>6938099</v>
+        <v>6937763</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121180261</v>
+        <v>121185434</v>
       </c>
       <c r="B41" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,41 +4737,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527506</v>
+        <v>526953</v>
       </c>
       <c r="R41" t="n">
-        <v>6937752</v>
+        <v>6938054</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185421</v>
+        <v>121185419</v>
       </c>
       <c r="B42" t="n">
-        <v>98081</v>
+        <v>79718</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4839,25 +4839,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>526958</v>
+        <v>527001</v>
       </c>
       <c r="R42" t="n">
-        <v>6938116</v>
+        <v>6938096</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185422</v>
+        <v>121185421</v>
       </c>
       <c r="B43" t="n">
         <v>98081</v>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526995</v>
+        <v>526958</v>
       </c>
       <c r="R43" t="n">
-        <v>6938144</v>
+        <v>6938116</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121180230</v>
+        <v>121185400</v>
       </c>
       <c r="B44" t="n">
-        <v>105186</v>
+        <v>90697</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527509</v>
+        <v>527034</v>
       </c>
       <c r="R44" t="n">
-        <v>6937756</v>
+        <v>6938099</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185411</v>
+        <v>121185428</v>
       </c>
       <c r="B45" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527045</v>
+        <v>527439</v>
       </c>
       <c r="R45" t="n">
-        <v>6938075</v>
+        <v>6937974</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121185398</v>
+        <v>121185432</v>
       </c>
       <c r="B46" t="n">
-        <v>90697</v>
+        <v>91973</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,25 +5247,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>526983</v>
+        <v>527217</v>
       </c>
       <c r="R46" t="n">
-        <v>6938135</v>
+        <v>6937854</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121185400</v>
+        <v>121185425</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5349,25 +5349,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527034</v>
+        <v>527014</v>
       </c>
       <c r="R47" t="n">
-        <v>6938099</v>
+        <v>6938062</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185405</v>
+        <v>121185426</v>
       </c>
       <c r="B48" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5451,25 +5451,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527034</v>
+        <v>527503</v>
       </c>
       <c r="R48" t="n">
-        <v>6938099</v>
+        <v>6937855</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185430</v>
+        <v>121180230</v>
       </c>
       <c r="B49" t="n">
-        <v>91973</v>
+        <v>105186</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,37 +5557,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527460</v>
+        <v>527509</v>
       </c>
       <c r="R49" t="n">
-        <v>6937819</v>
+        <v>6937756</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121180291</v>
+        <v>121180141</v>
       </c>
       <c r="B50" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,25 +5655,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527492</v>
+        <v>527597</v>
       </c>
       <c r="R50" t="n">
-        <v>6937763</v>
+        <v>6937703</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185396</v>
+        <v>121185417</v>
       </c>
       <c r="B51" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5757,25 +5757,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>526980</v>
+        <v>527368</v>
       </c>
       <c r="R51" t="n">
-        <v>6938115</v>
+        <v>6937959</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185402</v>
+        <v>121185422</v>
       </c>
       <c r="B52" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527367</v>
+        <v>526995</v>
       </c>
       <c r="R52" t="n">
-        <v>6937938</v>
+        <v>6938144</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121183281</v>
+        <v>121185398</v>
       </c>
       <c r="B53" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526958</v>
+        <v>526983</v>
       </c>
       <c r="R53" t="n">
-        <v>6938109</v>
+        <v>6938135</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185431</v>
+        <v>121185405</v>
       </c>
       <c r="B54" t="n">
-        <v>91973</v>
+        <v>90983</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,25 +6063,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527439</v>
+        <v>527034</v>
       </c>
       <c r="R54" t="n">
-        <v>6937815</v>
+        <v>6938099</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212694</v>
+        <v>121212720</v>
       </c>
       <c r="B55" t="n">
-        <v>79711</v>
+        <v>79682</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527088</v>
+        <v>527051</v>
       </c>
       <c r="R55" t="n">
-        <v>6938356</v>
+        <v>6938362</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212731</v>
+        <v>121212774</v>
       </c>
       <c r="B56" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,21 +6271,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527184</v>
+        <v>526840</v>
       </c>
       <c r="R56" t="n">
-        <v>6938280</v>
+        <v>6938383</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212744</v>
+        <v>121212755</v>
       </c>
       <c r="B58" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527495</v>
+        <v>526945</v>
       </c>
       <c r="R58" t="n">
-        <v>6938012</v>
+        <v>6938389</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212740</v>
+        <v>121212733</v>
       </c>
       <c r="B59" t="n">
         <v>79682</v>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527350</v>
+        <v>527186</v>
       </c>
       <c r="R59" t="n">
-        <v>6938133</v>
+        <v>6938273</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,7 +6663,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212715</v>
+        <v>121212713</v>
       </c>
       <c r="B60" t="n">
         <v>79682</v>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526971</v>
+        <v>526960</v>
       </c>
       <c r="R60" t="n">
-        <v>6938369</v>
+        <v>6938390</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212751</v>
+        <v>121212729</v>
       </c>
       <c r="B61" t="n">
-        <v>78337</v>
+        <v>79682</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>526755</v>
+        <v>527168</v>
       </c>
       <c r="R61" t="n">
-        <v>6938374</v>
+        <v>6938291</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212692</v>
+        <v>121212751</v>
       </c>
       <c r="B62" t="n">
-        <v>57504</v>
+        <v>78337</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6883,21 +6883,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527210</v>
+        <v>526755</v>
       </c>
       <c r="R62" t="n">
-        <v>6938291</v>
+        <v>6938374</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6943,11 +6943,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6974,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212695</v>
+        <v>121212705</v>
       </c>
       <c r="B63" t="n">
-        <v>79711</v>
+        <v>90983</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6986,25 +6981,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527184</v>
+        <v>527310</v>
       </c>
       <c r="R63" t="n">
-        <v>6938280</v>
+        <v>6938160</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7076,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212753</v>
+        <v>121212701</v>
       </c>
       <c r="B64" t="n">
-        <v>78337</v>
+        <v>90983</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7092,21 +7087,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7116,10 +7111,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526856</v>
+        <v>526960</v>
       </c>
       <c r="R64" t="n">
-        <v>6938391</v>
+        <v>6938387</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7178,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212719</v>
+        <v>121212772</v>
       </c>
       <c r="B65" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7194,21 +7189,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7218,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527051</v>
+        <v>526971</v>
       </c>
       <c r="R65" t="n">
-        <v>6938362</v>
+        <v>6938369</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7254,6 +7249,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7280,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212760</v>
+        <v>121212745</v>
       </c>
       <c r="B66" t="n">
-        <v>98081</v>
+        <v>79718</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7292,25 +7292,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7320,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526842</v>
+        <v>526960</v>
       </c>
       <c r="R66" t="n">
-        <v>6938396</v>
+        <v>6938390</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212757</v>
+        <v>121212756</v>
       </c>
       <c r="B67" t="n">
         <v>98081</v>
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526927</v>
+        <v>527255</v>
       </c>
       <c r="R67" t="n">
-        <v>6938376</v>
+        <v>6938220</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7458,6 +7458,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7586,10 +7591,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212718</v>
+        <v>121212689</v>
       </c>
       <c r="B69" t="n">
-        <v>79682</v>
+        <v>79219</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7602,21 +7607,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527038</v>
+        <v>526855</v>
       </c>
       <c r="R69" t="n">
-        <v>6938372</v>
+        <v>6938391</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7688,7 +7693,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212725</v>
+        <v>121212714</v>
       </c>
       <c r="B70" t="n">
         <v>79682</v>
@@ -7728,10 +7733,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527111</v>
+        <v>526955</v>
       </c>
       <c r="R70" t="n">
-        <v>6938327</v>
+        <v>6938368</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7790,10 +7795,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212774</v>
+        <v>121212726</v>
       </c>
       <c r="B71" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7806,21 +7811,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7830,10 +7835,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526840</v>
+        <v>527148</v>
       </c>
       <c r="R71" t="n">
-        <v>6938383</v>
+        <v>6938301</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7892,10 +7897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212773</v>
+        <v>121212711</v>
       </c>
       <c r="B72" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,21 +7913,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7932,10 +7937,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526989</v>
+        <v>527051</v>
       </c>
       <c r="R72" t="n">
-        <v>6938371</v>
+        <v>6938349</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7968,11 +7973,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7999,10 +7999,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212772</v>
+        <v>121212699</v>
       </c>
       <c r="B73" t="n">
-        <v>78601</v>
+        <v>79586</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8011,25 +8011,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>526971</v>
+        <v>527249</v>
       </c>
       <c r="R73" t="n">
-        <v>6938369</v>
+        <v>6938289</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8075,11 +8075,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8106,7 +8101,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212717</v>
+        <v>121212712</v>
       </c>
       <c r="B74" t="n">
         <v>79682</v>
@@ -8146,10 +8141,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527023</v>
+        <v>526743</v>
       </c>
       <c r="R74" t="n">
-        <v>6938359</v>
+        <v>6938415</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8208,10 +8203,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212689</v>
+        <v>121212694</v>
       </c>
       <c r="B75" t="n">
-        <v>79219</v>
+        <v>79711</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8220,25 +8215,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8248,10 +8243,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>526855</v>
+        <v>527088</v>
       </c>
       <c r="R75" t="n">
-        <v>6938391</v>
+        <v>6938356</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8310,10 +8305,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212728</v>
+        <v>121212746</v>
       </c>
       <c r="B76" t="n">
-        <v>79682</v>
+        <v>79718</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8322,25 +8317,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8350,10 +8345,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527148</v>
+        <v>527088</v>
       </c>
       <c r="R76" t="n">
-        <v>6938301</v>
+        <v>6938356</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8412,10 +8407,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212712</v>
+        <v>121212761</v>
       </c>
       <c r="B77" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8424,25 +8419,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526743</v>
+        <v>526852</v>
       </c>
       <c r="R77" t="n">
-        <v>6938415</v>
+        <v>6938391</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8514,10 +8509,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212738</v>
+        <v>121212692</v>
       </c>
       <c r="B78" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8530,21 +8525,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8554,10 +8549,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527288</v>
+        <v>527210</v>
       </c>
       <c r="R78" t="n">
-        <v>6938221</v>
+        <v>6938291</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8590,6 +8585,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8616,10 +8616,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212752</v>
+        <v>121212773</v>
       </c>
       <c r="B79" t="n">
-        <v>78337</v>
+        <v>78601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8632,21 +8632,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526804</v>
+        <v>526989</v>
       </c>
       <c r="R79" t="n">
-        <v>6938398</v>
+        <v>6938371</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8692,6 +8692,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8718,10 +8723,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212775</v>
+        <v>121212717</v>
       </c>
       <c r="B80" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8734,21 +8739,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8820,10 +8825,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212762</v>
+        <v>121212775</v>
       </c>
       <c r="B81" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8832,25 +8837,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8860,10 +8865,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526868</v>
+        <v>527023</v>
       </c>
       <c r="R81" t="n">
-        <v>6938367</v>
+        <v>6938359</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8922,10 +8927,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212697</v>
+        <v>121212695</v>
       </c>
       <c r="B82" t="n">
-        <v>79683</v>
+        <v>79711</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8934,25 +8939,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8962,10 +8967,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527186</v>
+        <v>527184</v>
       </c>
       <c r="R82" t="n">
-        <v>6938273</v>
+        <v>6938280</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9024,7 +9029,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212716</v>
+        <v>121212731</v>
       </c>
       <c r="B83" t="n">
         <v>79682</v>
@@ -9064,10 +9069,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526994</v>
+        <v>527184</v>
       </c>
       <c r="R83" t="n">
-        <v>6938374</v>
+        <v>6938280</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9126,10 +9131,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212750</v>
+        <v>121212708</v>
       </c>
       <c r="B84" t="n">
-        <v>80558</v>
+        <v>97035</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9138,25 +9143,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1049</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9166,10 +9171,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526756</v>
+        <v>527252</v>
       </c>
       <c r="R84" t="n">
-        <v>6938437</v>
+        <v>6938285</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9228,10 +9233,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212690</v>
+        <v>121212765</v>
       </c>
       <c r="B85" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9240,25 +9245,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9268,10 +9273,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527263</v>
+        <v>526955</v>
       </c>
       <c r="R85" t="n">
-        <v>6938234</v>
+        <v>6938367</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9330,7 +9335,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212698</v>
+        <v>121212697</v>
       </c>
       <c r="B86" t="n">
         <v>79683</v>
@@ -9370,10 +9375,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527211</v>
+        <v>527186</v>
       </c>
       <c r="R86" t="n">
-        <v>6938302</v>
+        <v>6938273</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9432,10 +9437,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212709</v>
+        <v>121212716</v>
       </c>
       <c r="B87" t="n">
-        <v>78338</v>
+        <v>79682</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9448,21 +9453,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9472,10 +9477,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526856</v>
+        <v>526994</v>
       </c>
       <c r="R87" t="n">
-        <v>6938391</v>
+        <v>6938374</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9534,10 +9539,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212745</v>
+        <v>121212740</v>
       </c>
       <c r="B88" t="n">
-        <v>79718</v>
+        <v>79682</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9546,25 +9551,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9574,10 +9579,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526960</v>
+        <v>527350</v>
       </c>
       <c r="R88" t="n">
-        <v>6938390</v>
+        <v>6938133</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9636,10 +9641,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212701</v>
+        <v>121212688</v>
       </c>
       <c r="B89" t="n">
-        <v>90983</v>
+        <v>95628</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9652,21 +9657,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9676,10 +9681,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526960</v>
+        <v>527409</v>
       </c>
       <c r="R89" t="n">
-        <v>6938387</v>
+        <v>6938091</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9738,10 +9743,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212696</v>
+        <v>121212690</v>
       </c>
       <c r="B90" t="n">
-        <v>79711</v>
+        <v>90697</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9750,25 +9755,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9783,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527288</v>
+        <v>527263</v>
       </c>
       <c r="R90" t="n">
-        <v>6938221</v>
+        <v>6938234</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9840,7 +9845,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212735</v>
+        <v>121212725</v>
       </c>
       <c r="B91" t="n">
         <v>79682</v>
@@ -9880,10 +9885,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527245</v>
+        <v>527111</v>
       </c>
       <c r="R91" t="n">
-        <v>6938291</v>
+        <v>6938327</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9942,10 +9947,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212759</v>
+        <v>121212739</v>
       </c>
       <c r="B92" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9954,25 +9959,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9987,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>526838</v>
+        <v>527304</v>
       </c>
       <c r="R92" t="n">
-        <v>6938397</v>
+        <v>6938173</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10049,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212765</v>
+        <v>121212736</v>
       </c>
       <c r="B93" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10056,25 +10061,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10089,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>526955</v>
+        <v>527250</v>
       </c>
       <c r="R93" t="n">
-        <v>6938367</v>
+        <v>6938289</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10146,10 +10151,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212755</v>
+        <v>121212750</v>
       </c>
       <c r="B94" t="n">
-        <v>78337</v>
+        <v>80558</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10162,21 +10167,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10191,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526945</v>
+        <v>526756</v>
       </c>
       <c r="R94" t="n">
-        <v>6938389</v>
+        <v>6938437</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,10 +10253,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212737</v>
+        <v>121212753</v>
       </c>
       <c r="B95" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10264,21 +10269,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10288,10 +10293,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527248</v>
+        <v>526856</v>
       </c>
       <c r="R95" t="n">
-        <v>6938256</v>
+        <v>6938391</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10355,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212713</v>
+        <v>121212709</v>
       </c>
       <c r="B96" t="n">
-        <v>79682</v>
+        <v>78338</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10366,21 +10371,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10395,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526960</v>
+        <v>526856</v>
       </c>
       <c r="R96" t="n">
-        <v>6938390</v>
+        <v>6938391</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10452,7 +10457,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212724</v>
+        <v>121212715</v>
       </c>
       <c r="B97" t="n">
         <v>79682</v>
@@ -10492,10 +10497,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527109</v>
+        <v>526971</v>
       </c>
       <c r="R97" t="n">
-        <v>6938336</v>
+        <v>6938369</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10554,10 +10559,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212710</v>
+        <v>121212759</v>
       </c>
       <c r="B98" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10566,25 +10571,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10594,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527495</v>
+        <v>526838</v>
       </c>
       <c r="R98" t="n">
-        <v>6938009</v>
+        <v>6938397</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10630,11 +10635,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10661,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212739</v>
+        <v>121212762</v>
       </c>
       <c r="B99" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10673,25 +10673,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527304</v>
+        <v>526868</v>
       </c>
       <c r="R99" t="n">
-        <v>6938173</v>
+        <v>6938367</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10763,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212771</v>
+        <v>121212696</v>
       </c>
       <c r="B100" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10775,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10803,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527317</v>
+        <v>527288</v>
       </c>
       <c r="R100" t="n">
-        <v>6938165</v>
+        <v>6938221</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10865,7 +10865,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212733</v>
+        <v>121212737</v>
       </c>
       <c r="B101" t="n">
         <v>79682</v>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527186</v>
+        <v>527248</v>
       </c>
       <c r="R101" t="n">
-        <v>6938273</v>
+        <v>6938256</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212723</v>
+        <v>121212752</v>
       </c>
       <c r="B102" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10983,21 +10983,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527088</v>
+        <v>526804</v>
       </c>
       <c r="R102" t="n">
-        <v>6938358</v>
+        <v>6938398</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212688</v>
+        <v>121212718</v>
       </c>
       <c r="B103" t="n">
-        <v>95628</v>
+        <v>79682</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>527409</v>
+        <v>527038</v>
       </c>
       <c r="R103" t="n">
-        <v>6938091</v>
+        <v>6938372</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212730</v>
+        <v>121212764</v>
       </c>
       <c r="B104" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11183,25 +11183,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527177</v>
+        <v>526945</v>
       </c>
       <c r="R104" t="n">
-        <v>6938273</v>
+        <v>6938389</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212746</v>
+        <v>121212735</v>
       </c>
       <c r="B105" t="n">
-        <v>79718</v>
+        <v>79682</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11285,25 +11285,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527088</v>
+        <v>527245</v>
       </c>
       <c r="R105" t="n">
-        <v>6938356</v>
+        <v>6938291</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,7 +11375,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212756</v>
+        <v>121212763</v>
       </c>
       <c r="B106" t="n">
         <v>98081</v>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527255</v>
+        <v>526911</v>
       </c>
       <c r="R106" t="n">
-        <v>6938220</v>
+        <v>6938360</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11451,11 +11451,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11482,10 +11477,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212763</v>
+        <v>121212730</v>
       </c>
       <c r="B107" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11494,25 +11489,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11522,10 +11517,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>526911</v>
+        <v>527177</v>
       </c>
       <c r="R107" t="n">
-        <v>6938360</v>
+        <v>6938273</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,10 +11579,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212769</v>
+        <v>121212723</v>
       </c>
       <c r="B108" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11596,25 +11591,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11624,10 +11619,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527263</v>
+        <v>527088</v>
       </c>
       <c r="R108" t="n">
-        <v>6938242</v>
+        <v>6938358</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,7 +11681,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212761</v>
+        <v>121212760</v>
       </c>
       <c r="B109" t="n">
         <v>98081</v>
@@ -11726,10 +11721,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526852</v>
+        <v>526842</v>
       </c>
       <c r="R109" t="n">
-        <v>6938391</v>
+        <v>6938396</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11788,10 +11783,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212708</v>
+        <v>121212757</v>
       </c>
       <c r="B110" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11800,25 +11795,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11828,10 +11823,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527252</v>
+        <v>526927</v>
       </c>
       <c r="R110" t="n">
-        <v>6938285</v>
+        <v>6938376</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,10 +11885,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212705</v>
+        <v>121212744</v>
       </c>
       <c r="B111" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11906,21 +11901,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527310</v>
+        <v>527495</v>
       </c>
       <c r="R111" t="n">
-        <v>6938160</v>
+        <v>6938012</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,7 +11987,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212714</v>
+        <v>121212738</v>
       </c>
       <c r="B112" t="n">
         <v>79682</v>
@@ -12032,10 +12027,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>526955</v>
+        <v>527288</v>
       </c>
       <c r="R112" t="n">
-        <v>6938368</v>
+        <v>6938221</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12094,10 +12089,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212699</v>
+        <v>121212698</v>
       </c>
       <c r="B113" t="n">
-        <v>79586</v>
+        <v>79683</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12106,25 +12101,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12134,10 +12129,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527249</v>
+        <v>527211</v>
       </c>
       <c r="R113" t="n">
-        <v>6938289</v>
+        <v>6938302</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,7 +12191,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212734</v>
+        <v>121212724</v>
       </c>
       <c r="B114" t="n">
         <v>79682</v>
@@ -12236,10 +12231,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527214</v>
+        <v>527109</v>
       </c>
       <c r="R114" t="n">
-        <v>6938296</v>
+        <v>6938336</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,7 +12293,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212736</v>
+        <v>121212734</v>
       </c>
       <c r="B115" t="n">
         <v>79682</v>
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527250</v>
+        <v>527214</v>
       </c>
       <c r="R115" t="n">
-        <v>6938289</v>
+        <v>6938296</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,7 +12395,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212711</v>
+        <v>121212710</v>
       </c>
       <c r="B116" t="n">
         <v>79682</v>
@@ -12440,10 +12435,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527051</v>
+        <v>527495</v>
       </c>
       <c r="R116" t="n">
-        <v>6938349</v>
+        <v>6938009</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12476,6 +12471,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12502,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212764</v>
+        <v>121212722</v>
       </c>
       <c r="B117" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12514,25 +12514,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>526945</v>
+        <v>527075</v>
       </c>
       <c r="R117" t="n">
-        <v>6938389</v>
+        <v>6938349</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212721</v>
+        <v>121212771</v>
       </c>
       <c r="B118" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12616,25 +12616,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527074</v>
+        <v>527317</v>
       </c>
       <c r="R118" t="n">
-        <v>6938353</v>
+        <v>6938165</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,7 +12706,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212722</v>
+        <v>121212721</v>
       </c>
       <c r="B119" t="n">
         <v>79682</v>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527075</v>
+        <v>527074</v>
       </c>
       <c r="R119" t="n">
-        <v>6938349</v>
+        <v>6938353</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212729</v>
+        <v>121212769</v>
       </c>
       <c r="B120" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527168</v>
+        <v>527263</v>
       </c>
       <c r="R120" t="n">
-        <v>6938291</v>
+        <v>6938242</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121223305</v>
+        <v>121226802</v>
       </c>
       <c r="B121" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,41 +12922,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526584</v>
+        <v>526716</v>
       </c>
       <c r="R121" t="n">
-        <v>6938052</v>
+        <v>6937997</v>
       </c>
       <c r="S121" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226804</v>
+        <v>121220094</v>
       </c>
       <c r="B122" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,37 +13028,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526224</v>
+        <v>526766</v>
       </c>
       <c r="R122" t="n">
-        <v>6938191</v>
+        <v>6938100</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121221064</v>
+        <v>121220916</v>
       </c>
       <c r="B123" t="n">
-        <v>90711</v>
+        <v>98081</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,25 +13126,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526664</v>
+        <v>526647</v>
       </c>
       <c r="R123" t="n">
-        <v>6938176</v>
+        <v>6938174</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226817</v>
+        <v>121212788</v>
       </c>
       <c r="B124" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,25 +13228,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526581</v>
+        <v>526776</v>
       </c>
       <c r="R124" t="n">
-        <v>6938053</v>
+        <v>6938419</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13318,7 +13318,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226801</v>
+        <v>121226812</v>
       </c>
       <c r="B125" t="n">
         <v>79682</v>
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526714</v>
+        <v>526551</v>
       </c>
       <c r="R125" t="n">
-        <v>6938008</v>
+        <v>6938312</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121212778</v>
+        <v>121226817</v>
       </c>
       <c r="B126" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,25 +13432,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>527288</v>
+        <v>526581</v>
       </c>
       <c r="R126" t="n">
-        <v>6938221</v>
+        <v>6938053</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226809</v>
+        <v>121226794</v>
       </c>
       <c r="B127" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,25 +13534,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13562,10 +13562,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526518</v>
+        <v>526478</v>
       </c>
       <c r="R127" t="n">
-        <v>6938295</v>
+        <v>6938348</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226822</v>
+        <v>121221064</v>
       </c>
       <c r="B128" t="n">
-        <v>91973</v>
+        <v>90711</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13636,41 +13636,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526182</v>
+        <v>526664</v>
       </c>
       <c r="R128" t="n">
-        <v>6938234</v>
+        <v>6938176</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226813</v>
+        <v>121226820</v>
       </c>
       <c r="B129" t="n">
-        <v>78337</v>
+        <v>90711</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526365</v>
+        <v>526660</v>
       </c>
       <c r="R129" t="n">
-        <v>6938404</v>
+        <v>6938167</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226820</v>
+        <v>121226818</v>
       </c>
       <c r="B130" t="n">
-        <v>90711</v>
+        <v>98081</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13840,25 +13840,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526660</v>
+        <v>526525</v>
       </c>
       <c r="R130" t="n">
-        <v>6938167</v>
+        <v>6938312</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13930,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121212788</v>
+        <v>121212785</v>
       </c>
       <c r="B131" t="n">
-        <v>91973</v>
+        <v>78246</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13942,25 +13942,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526776</v>
+        <v>526753</v>
       </c>
       <c r="R131" t="n">
-        <v>6938419</v>
+        <v>6938395</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14032,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121222671</v>
+        <v>121226822</v>
       </c>
       <c r="B132" t="n">
-        <v>78601</v>
+        <v>91973</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14044,41 +14044,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526275</v>
+        <v>526182</v>
       </c>
       <c r="R132" t="n">
-        <v>6938199</v>
+        <v>6938234</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14108,11 +14108,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,10 +14134,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121226802</v>
+        <v>121212778</v>
       </c>
       <c r="B133" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14155,21 +14150,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14179,10 +14174,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526716</v>
+        <v>527288</v>
       </c>
       <c r="R133" t="n">
-        <v>6937997</v>
+        <v>6938221</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14209,12 +14204,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14241,10 +14236,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121212779</v>
+        <v>121226803</v>
       </c>
       <c r="B134" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14257,21 +14252,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14281,10 +14276,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>527495</v>
+        <v>526335</v>
       </c>
       <c r="R134" t="n">
-        <v>6938009</v>
+        <v>6938150</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14311,12 +14306,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14343,10 +14338,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226793</v>
+        <v>121226795</v>
       </c>
       <c r="B135" t="n">
-        <v>90717</v>
+        <v>79683</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14359,21 +14354,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5442</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14378,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526519</v>
+        <v>526554</v>
       </c>
       <c r="R135" t="n">
-        <v>6938315</v>
+        <v>6938311</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,10 +14440,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121220916</v>
+        <v>121212780</v>
       </c>
       <c r="B136" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,41 +14452,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526647</v>
+        <v>527567</v>
       </c>
       <c r="R136" t="n">
-        <v>6938174</v>
+        <v>6937949</v>
       </c>
       <c r="S136" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14515,12 +14510,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14547,10 +14542,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226792</v>
+        <v>121212791</v>
       </c>
       <c r="B137" t="n">
-        <v>90697</v>
+        <v>79717</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14559,25 +14554,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14582,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526796</v>
+        <v>527094</v>
       </c>
       <c r="R137" t="n">
-        <v>6937966</v>
+        <v>6938358</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14617,12 +14612,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14649,7 +14644,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226803</v>
+        <v>121226799</v>
       </c>
       <c r="B138" t="n">
         <v>79682</v>
@@ -14689,10 +14684,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526335</v>
+        <v>526747</v>
       </c>
       <c r="R138" t="n">
-        <v>6938150</v>
+        <v>6937983</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14751,10 +14746,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226795</v>
+        <v>121226809</v>
       </c>
       <c r="B139" t="n">
-        <v>79683</v>
+        <v>79682</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14767,21 +14762,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526554</v>
+        <v>526518</v>
       </c>
       <c r="R139" t="n">
-        <v>6938311</v>
+        <v>6938295</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14853,7 +14848,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121212776</v>
+        <v>121221199</v>
       </c>
       <c r="B140" t="n">
         <v>78601</v>
@@ -14889,17 +14884,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>527090</v>
+        <v>526592</v>
       </c>
       <c r="R140" t="n">
-        <v>6938365</v>
+        <v>6938232</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14923,12 +14918,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14955,10 +14950,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226821</v>
+        <v>121226805</v>
       </c>
       <c r="B141" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14971,21 +14966,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14995,10 +14990,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526199</v>
+        <v>526203</v>
       </c>
       <c r="R141" t="n">
-        <v>6938254</v>
+        <v>6938195</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15031,11 +15026,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15062,7 +15052,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226798</v>
+        <v>121226801</v>
       </c>
       <c r="B142" t="n">
         <v>79682</v>
@@ -15102,10 +15092,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526747</v>
+        <v>526714</v>
       </c>
       <c r="R142" t="n">
-        <v>6937983</v>
+        <v>6938008</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15164,10 +15154,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121212789</v>
+        <v>121223305</v>
       </c>
       <c r="B143" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15176,41 +15166,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526823</v>
+        <v>526584</v>
       </c>
       <c r="R143" t="n">
-        <v>6938405</v>
+        <v>6938052</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15234,12 +15224,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15266,10 +15256,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226805</v>
+        <v>121226793</v>
       </c>
       <c r="B144" t="n">
-        <v>79682</v>
+        <v>90717</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15282,21 +15272,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15306,10 +15296,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526203</v>
+        <v>526519</v>
       </c>
       <c r="R144" t="n">
-        <v>6938195</v>
+        <v>6938315</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15368,10 +15358,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226806</v>
+        <v>121226813</v>
       </c>
       <c r="B145" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15384,21 +15374,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15408,10 +15398,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526182</v>
+        <v>526365</v>
       </c>
       <c r="R145" t="n">
-        <v>6938206</v>
+        <v>6938404</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15470,10 +15460,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121220094</v>
+        <v>121226797</v>
       </c>
       <c r="B146" t="n">
-        <v>78337</v>
+        <v>79682</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15486,37 +15476,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526766</v>
+        <v>526496</v>
       </c>
       <c r="R146" t="n">
-        <v>6938100</v>
+        <v>6938343</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15546,6 +15536,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15572,7 +15567,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226811</v>
+        <v>121226807</v>
       </c>
       <c r="B147" t="n">
         <v>79682</v>
@@ -15612,10 +15607,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526545</v>
+        <v>526201</v>
       </c>
       <c r="R147" t="n">
-        <v>6938319</v>
+        <v>6938252</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15674,10 +15669,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121221199</v>
+        <v>121212783</v>
       </c>
       <c r="B148" t="n">
-        <v>78601</v>
+        <v>78246</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15690,37 +15685,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526592</v>
+        <v>526761</v>
       </c>
       <c r="R148" t="n">
-        <v>6938232</v>
+        <v>6938348</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15744,12 +15739,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15776,10 +15771,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226794</v>
+        <v>121226824</v>
       </c>
       <c r="B149" t="n">
-        <v>79711</v>
+        <v>91259</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15788,25 +15783,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15816,10 +15811,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526478</v>
+        <v>526747</v>
       </c>
       <c r="R149" t="n">
-        <v>6938348</v>
+        <v>6937983</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15878,10 +15873,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226815</v>
+        <v>121226810</v>
       </c>
       <c r="B150" t="n">
-        <v>78337</v>
+        <v>79682</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15894,21 +15889,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15918,10 +15913,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526527</v>
+        <v>526533</v>
       </c>
       <c r="R150" t="n">
-        <v>6938317</v>
+        <v>6938315</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15980,10 +15975,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226796</v>
+        <v>121226816</v>
       </c>
       <c r="B151" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15992,25 +15987,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16020,10 +16015,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526796</v>
+        <v>526789</v>
       </c>
       <c r="R151" t="n">
-        <v>6937966</v>
+        <v>6937993</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16082,10 +16077,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226824</v>
+        <v>121212789</v>
       </c>
       <c r="B152" t="n">
-        <v>91259</v>
+        <v>91973</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16094,25 +16089,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16122,10 +16117,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526747</v>
+        <v>526823</v>
       </c>
       <c r="R152" t="n">
-        <v>6937983</v>
+        <v>6938405</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16152,12 +16147,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16184,10 +16179,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121212780</v>
+        <v>121219596</v>
       </c>
       <c r="B153" t="n">
-        <v>78601</v>
+        <v>78337</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16200,37 +16195,37 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>527567</v>
+        <v>526982</v>
       </c>
       <c r="R153" t="n">
-        <v>6937949</v>
+        <v>6937928</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16254,12 +16249,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16286,10 +16281,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121219596</v>
+        <v>121226804</v>
       </c>
       <c r="B154" t="n">
-        <v>78337</v>
+        <v>79682</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16302,37 +16297,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526982</v>
+        <v>526224</v>
       </c>
       <c r="R154" t="n">
-        <v>6937928</v>
+        <v>6938191</v>
       </c>
       <c r="S154" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16388,10 +16383,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226810</v>
+        <v>121226814</v>
       </c>
       <c r="B155" t="n">
-        <v>79682</v>
+        <v>78337</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16404,21 +16399,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16428,10 +16423,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526533</v>
+        <v>526515</v>
       </c>
       <c r="R155" t="n">
-        <v>6938315</v>
+        <v>6938303</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16490,10 +16485,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121226797</v>
+        <v>121212776</v>
       </c>
       <c r="B156" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16506,21 +16501,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16525,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526496</v>
+        <v>527090</v>
       </c>
       <c r="R156" t="n">
-        <v>6938343</v>
+        <v>6938365</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16560,17 +16555,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16597,10 +16587,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226812</v>
+        <v>121226792</v>
       </c>
       <c r="B157" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16613,21 +16603,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16637,10 +16627,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526551</v>
+        <v>526796</v>
       </c>
       <c r="R157" t="n">
-        <v>6938312</v>
+        <v>6937966</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16699,10 +16689,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226818</v>
+        <v>121212779</v>
       </c>
       <c r="B158" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16711,25 +16701,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16739,10 +16729,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526525</v>
+        <v>527495</v>
       </c>
       <c r="R158" t="n">
-        <v>6938312</v>
+        <v>6938009</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16769,12 +16759,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16801,10 +16791,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226819</v>
+        <v>121226811</v>
       </c>
       <c r="B159" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16813,25 +16803,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16841,10 +16831,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526646</v>
+        <v>526545</v>
       </c>
       <c r="R159" t="n">
-        <v>6938173</v>
+        <v>6938319</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16903,10 +16893,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121212783</v>
+        <v>121222671</v>
       </c>
       <c r="B160" t="n">
-        <v>78246</v>
+        <v>78601</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16919,37 +16909,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526761</v>
+        <v>526275</v>
       </c>
       <c r="R160" t="n">
-        <v>6938348</v>
+        <v>6938199</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16973,12 +16963,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17005,10 +17000,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226808</v>
+        <v>121219658</v>
       </c>
       <c r="B161" t="n">
-        <v>79682</v>
+        <v>90662</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17017,41 +17012,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526482</v>
+        <v>526953</v>
       </c>
       <c r="R161" t="n">
-        <v>6938338</v>
+        <v>6937958</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17107,10 +17102,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121212791</v>
+        <v>121226815</v>
       </c>
       <c r="B162" t="n">
-        <v>79717</v>
+        <v>78337</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17119,25 +17114,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17147,10 +17142,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>527094</v>
+        <v>526527</v>
       </c>
       <c r="R162" t="n">
-        <v>6938358</v>
+        <v>6938317</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17177,12 +17172,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17209,10 +17204,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226816</v>
+        <v>121226821</v>
       </c>
       <c r="B163" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17221,25 +17216,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526789</v>
+        <v>526199</v>
       </c>
       <c r="R163" t="n">
-        <v>6937993</v>
+        <v>6938254</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17285,6 +17280,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121212785</v>
+        <v>121226806</v>
       </c>
       <c r="B164" t="n">
-        <v>78246</v>
+        <v>79682</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17327,21 +17327,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526753</v>
+        <v>526182</v>
       </c>
       <c r="R164" t="n">
-        <v>6938395</v>
+        <v>6938206</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17381,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121219658</v>
+        <v>121226808</v>
       </c>
       <c r="B165" t="n">
-        <v>90662</v>
+        <v>79682</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,41 +17425,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526953</v>
+        <v>526482</v>
       </c>
       <c r="R165" t="n">
-        <v>6937958</v>
+        <v>6938338</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226791</v>
+        <v>121226796</v>
       </c>
       <c r="B166" t="n">
-        <v>89753</v>
+        <v>90983</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,21 +17531,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526205</v>
+        <v>526796</v>
       </c>
       <c r="R166" t="n">
-        <v>6938282</v>
+        <v>6937966</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226807</v>
+        <v>121226819</v>
       </c>
       <c r="B167" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526201</v>
+        <v>526646</v>
       </c>
       <c r="R167" t="n">
-        <v>6938252</v>
+        <v>6938173</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226814</v>
+        <v>121226791</v>
       </c>
       <c r="B168" t="n">
-        <v>78337</v>
+        <v>89753</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17735,21 +17735,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526515</v>
+        <v>526205</v>
       </c>
       <c r="R168" t="n">
-        <v>6938303</v>
+        <v>6938282</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121179693</v>
+        <v>121185404</v>
       </c>
       <c r="B171" t="n">
-        <v>91973</v>
+        <v>91137</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527779</v>
+        <v>527659</v>
       </c>
       <c r="R171" t="n">
-        <v>6937594</v>
+        <v>6937698</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121185408</v>
+        <v>121179693</v>
       </c>
       <c r="B172" t="n">
-        <v>90983</v>
+        <v>91973</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527661</v>
+        <v>527779</v>
       </c>
       <c r="R172" t="n">
-        <v>6937695</v>
+        <v>6937594</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121185404</v>
+        <v>121179849</v>
       </c>
       <c r="B173" t="n">
         <v>91137</v>
@@ -18279,17 +18279,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>527659</v>
+        <v>527658</v>
       </c>
       <c r="R173" t="n">
-        <v>6937698</v>
+        <v>6937694</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121179849</v>
+        <v>121185408</v>
       </c>
       <c r="B174" t="n">
-        <v>91137</v>
+        <v>90983</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18357,41 +18357,41 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527658</v>
+        <v>527661</v>
       </c>
       <c r="R174" t="n">
-        <v>6937694</v>
+        <v>6937695</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185395</v>
+        <v>121185414</v>
       </c>
       <c r="B14" t="n">
-        <v>95628</v>
+        <v>79682</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527048</v>
+        <v>527346</v>
       </c>
       <c r="R14" t="n">
-        <v>6938076</v>
+        <v>6937925</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185406</v>
+        <v>121185430</v>
       </c>
       <c r="B15" t="n">
-        <v>90983</v>
+        <v>91973</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527009</v>
+        <v>527460</v>
       </c>
       <c r="R15" t="n">
-        <v>6938044</v>
+        <v>6937819</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185414</v>
+        <v>121185431</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>91973</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527346</v>
+        <v>527439</v>
       </c>
       <c r="R16" t="n">
-        <v>6937925</v>
+        <v>6937815</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185430</v>
+        <v>121185395</v>
       </c>
       <c r="B17" t="n">
-        <v>91973</v>
+        <v>95628</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527460</v>
+        <v>527048</v>
       </c>
       <c r="R17" t="n">
-        <v>6937819</v>
+        <v>6938076</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185431</v>
+        <v>121185406</v>
       </c>
       <c r="B18" t="n">
-        <v>91973</v>
+        <v>90983</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527439</v>
+        <v>527009</v>
       </c>
       <c r="R18" t="n">
-        <v>6937815</v>
+        <v>6938044</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121182248</v>
+        <v>121185435</v>
       </c>
       <c r="B30" t="n">
-        <v>98081</v>
+        <v>91353</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3619,37 +3619,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>527008</v>
       </c>
       <c r="R30" t="n">
-        <v>6938092</v>
+        <v>6938073</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185435</v>
+        <v>121180712</v>
       </c>
       <c r="B31" t="n">
-        <v>91353</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,41 +3717,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527008</v>
+        <v>527305</v>
       </c>
       <c r="R31" t="n">
-        <v>6938073</v>
+        <v>6937895</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121180712</v>
+        <v>121182248</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,38 +3819,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527305</v>
+        <v>527008</v>
       </c>
       <c r="R32" t="n">
-        <v>6937895</v>
+        <v>6938092</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185426</v>
+        <v>121180230</v>
       </c>
       <c r="B48" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5451,41 +5451,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527503</v>
+        <v>527509</v>
       </c>
       <c r="R48" t="n">
-        <v>6937855</v>
+        <v>6937756</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121180230</v>
+        <v>121185426</v>
       </c>
       <c r="B49" t="n">
-        <v>105186</v>
+        <v>98081</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5553,41 +5553,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527509</v>
+        <v>527503</v>
       </c>
       <c r="R49" t="n">
-        <v>6937756</v>
+        <v>6937855</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212705</v>
+        <v>121212756</v>
       </c>
       <c r="B63" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527310</v>
+        <v>527255</v>
       </c>
       <c r="R63" t="n">
-        <v>6938160</v>
+        <v>6938220</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7045,6 +7045,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7071,10 +7076,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212701</v>
+        <v>121212772</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,21 +7092,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526960</v>
+        <v>526971</v>
       </c>
       <c r="R64" t="n">
-        <v>6938387</v>
+        <v>6938369</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7147,6 +7152,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7173,10 +7183,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212772</v>
+        <v>121212705</v>
       </c>
       <c r="B65" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7189,21 +7199,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7223,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526971</v>
+        <v>527310</v>
       </c>
       <c r="R65" t="n">
-        <v>6938369</v>
+        <v>6938160</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7249,11 +7259,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7280,10 +7285,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212745</v>
+        <v>121212701</v>
       </c>
       <c r="B66" t="n">
-        <v>79718</v>
+        <v>90983</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7292,25 +7297,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7323,7 +7328,7 @@
         <v>526960</v>
       </c>
       <c r="R66" t="n">
-        <v>6938390</v>
+        <v>6938387</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7382,10 +7387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212756</v>
+        <v>121212745</v>
       </c>
       <c r="B67" t="n">
-        <v>98081</v>
+        <v>79718</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7394,25 +7399,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7422,10 +7427,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527255</v>
+        <v>526960</v>
       </c>
       <c r="R67" t="n">
-        <v>6938220</v>
+        <v>6938390</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7458,11 +7463,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7489,10 +7489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212703</v>
+        <v>121212689</v>
       </c>
       <c r="B68" t="n">
-        <v>90983</v>
+        <v>79219</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7505,21 +7505,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7529,10 +7529,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527253</v>
+        <v>526855</v>
       </c>
       <c r="R68" t="n">
-        <v>6938232</v>
+        <v>6938391</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212689</v>
+        <v>121212714</v>
       </c>
       <c r="B69" t="n">
-        <v>79219</v>
+        <v>79682</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7607,21 +7607,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526855</v>
+        <v>526955</v>
       </c>
       <c r="R69" t="n">
-        <v>6938391</v>
+        <v>6938368</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7693,7 +7693,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212714</v>
+        <v>121212726</v>
       </c>
       <c r="B70" t="n">
         <v>79682</v>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526955</v>
+        <v>527148</v>
       </c>
       <c r="R70" t="n">
-        <v>6938368</v>
+        <v>6938301</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212726</v>
+        <v>121212711</v>
       </c>
       <c r="B71" t="n">
         <v>79682</v>
@@ -7835,10 +7835,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527148</v>
+        <v>527051</v>
       </c>
       <c r="R71" t="n">
-        <v>6938301</v>
+        <v>6938349</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7897,10 +7897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212711</v>
+        <v>121212703</v>
       </c>
       <c r="B72" t="n">
-        <v>79682</v>
+        <v>90983</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7913,21 +7913,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7937,10 +7937,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527051</v>
+        <v>527253</v>
       </c>
       <c r="R72" t="n">
-        <v>6938349</v>
+        <v>6938232</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212708</v>
+        <v>121212765</v>
       </c>
       <c r="B84" t="n">
-        <v>97035</v>
+        <v>98081</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9143,25 +9143,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527252</v>
+        <v>526955</v>
       </c>
       <c r="R84" t="n">
-        <v>6938285</v>
+        <v>6938367</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9233,10 +9233,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212765</v>
+        <v>121212708</v>
       </c>
       <c r="B85" t="n">
-        <v>98081</v>
+        <v>97035</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9245,25 +9245,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526955</v>
+        <v>527252</v>
       </c>
       <c r="R85" t="n">
-        <v>6938367</v>
+        <v>6938285</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10763,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212696</v>
+        <v>121212752</v>
       </c>
       <c r="B100" t="n">
-        <v>79711</v>
+        <v>78337</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10775,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10803,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527288</v>
+        <v>526804</v>
       </c>
       <c r="R100" t="n">
-        <v>6938221</v>
+        <v>6938398</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10865,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212737</v>
+        <v>121212696</v>
       </c>
       <c r="B101" t="n">
-        <v>79682</v>
+        <v>79711</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10877,25 +10877,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527248</v>
+        <v>527288</v>
       </c>
       <c r="R101" t="n">
-        <v>6938256</v>
+        <v>6938221</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212752</v>
+        <v>121212764</v>
       </c>
       <c r="B102" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10979,25 +10979,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>526804</v>
+        <v>526945</v>
       </c>
       <c r="R102" t="n">
-        <v>6938398</v>
+        <v>6938389</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,7 +11069,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212718</v>
+        <v>121212737</v>
       </c>
       <c r="B103" t="n">
         <v>79682</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>527038</v>
+        <v>527248</v>
       </c>
       <c r="R103" t="n">
-        <v>6938372</v>
+        <v>6938256</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212764</v>
+        <v>121212718</v>
       </c>
       <c r="B104" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11183,25 +11183,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>526945</v>
+        <v>527038</v>
       </c>
       <c r="R104" t="n">
-        <v>6938389</v>
+        <v>6938372</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212735</v>
+        <v>121212763</v>
       </c>
       <c r="B105" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11285,25 +11285,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527245</v>
+        <v>526911</v>
       </c>
       <c r="R105" t="n">
-        <v>6938291</v>
+        <v>6938360</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212763</v>
+        <v>121212735</v>
       </c>
       <c r="B106" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11387,25 +11387,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>526911</v>
+        <v>527245</v>
       </c>
       <c r="R106" t="n">
-        <v>6938360</v>
+        <v>6938291</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121212788</v>
+        <v>121226812</v>
       </c>
       <c r="B124" t="n">
-        <v>91973</v>
+        <v>79682</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,25 +13228,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526776</v>
+        <v>526551</v>
       </c>
       <c r="R124" t="n">
-        <v>6938419</v>
+        <v>6938312</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13318,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226812</v>
+        <v>121226817</v>
       </c>
       <c r="B125" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,25 +13330,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526551</v>
+        <v>526581</v>
       </c>
       <c r="R125" t="n">
-        <v>6938312</v>
+        <v>6938053</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226817</v>
+        <v>121212788</v>
       </c>
       <c r="B126" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,25 +13432,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526581</v>
+        <v>526776</v>
       </c>
       <c r="R126" t="n">
-        <v>6938053</v>
+        <v>6938419</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226794</v>
+        <v>121221064</v>
       </c>
       <c r="B127" t="n">
-        <v>79711</v>
+        <v>90711</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526478</v>
+        <v>526664</v>
       </c>
       <c r="R127" t="n">
-        <v>6938348</v>
+        <v>6938176</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121221064</v>
+        <v>121226794</v>
       </c>
       <c r="B128" t="n">
-        <v>90711</v>
+        <v>79711</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13636,41 +13636,41 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526664</v>
+        <v>526478</v>
       </c>
       <c r="R128" t="n">
-        <v>6938176</v>
+        <v>6938348</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14542,10 +14542,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121212791</v>
+        <v>121221199</v>
       </c>
       <c r="B137" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14554,20 +14554,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -14578,17 +14578,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>527094</v>
+        <v>526592</v>
       </c>
       <c r="R137" t="n">
-        <v>6938358</v>
+        <v>6938232</v>
       </c>
       <c r="S137" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14612,12 +14612,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14644,10 +14644,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226799</v>
+        <v>121212791</v>
       </c>
       <c r="B138" t="n">
-        <v>79682</v>
+        <v>79717</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14656,25 +14656,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14684,10 +14684,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526747</v>
+        <v>527094</v>
       </c>
       <c r="R138" t="n">
-        <v>6937983</v>
+        <v>6938358</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14746,7 +14746,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226809</v>
+        <v>121226799</v>
       </c>
       <c r="B139" t="n">
         <v>79682</v>
@@ -14786,10 +14786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526518</v>
+        <v>526747</v>
       </c>
       <c r="R139" t="n">
-        <v>6938295</v>
+        <v>6937983</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14848,10 +14848,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121221199</v>
+        <v>121226809</v>
       </c>
       <c r="B140" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14864,37 +14864,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526592</v>
+        <v>526518</v>
       </c>
       <c r="R140" t="n">
-        <v>6938232</v>
+        <v>6938295</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14950,10 +14950,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226805</v>
+        <v>121226793</v>
       </c>
       <c r="B141" t="n">
-        <v>79682</v>
+        <v>90717</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14966,21 +14966,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14990,10 +14990,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526203</v>
+        <v>526519</v>
       </c>
       <c r="R141" t="n">
-        <v>6938195</v>
+        <v>6938315</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15052,10 +15052,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226801</v>
+        <v>121223305</v>
       </c>
       <c r="B142" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15064,41 +15064,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526714</v>
+        <v>526584</v>
       </c>
       <c r="R142" t="n">
-        <v>6938008</v>
+        <v>6938052</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121223305</v>
+        <v>121226805</v>
       </c>
       <c r="B143" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15166,41 +15166,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526584</v>
+        <v>526203</v>
       </c>
       <c r="R143" t="n">
-        <v>6938052</v>
+        <v>6938195</v>
       </c>
       <c r="S143" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15256,10 +15256,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226793</v>
+        <v>121226801</v>
       </c>
       <c r="B144" t="n">
-        <v>90717</v>
+        <v>79682</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15272,21 +15272,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15296,10 +15296,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526519</v>
+        <v>526714</v>
       </c>
       <c r="R144" t="n">
-        <v>6938315</v>
+        <v>6938008</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15669,10 +15669,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121212783</v>
+        <v>121226810</v>
       </c>
       <c r="B148" t="n">
-        <v>78246</v>
+        <v>79682</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15685,21 +15685,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15709,10 +15709,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526761</v>
+        <v>526533</v>
       </c>
       <c r="R148" t="n">
-        <v>6938348</v>
+        <v>6938315</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15739,12 +15739,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15771,10 +15771,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226824</v>
+        <v>121212783</v>
       </c>
       <c r="B149" t="n">
-        <v>91259</v>
+        <v>78246</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15783,25 +15783,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>760</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15811,10 +15811,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526747</v>
+        <v>526761</v>
       </c>
       <c r="R149" t="n">
-        <v>6937983</v>
+        <v>6938348</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15841,12 +15841,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15873,10 +15873,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226810</v>
+        <v>121226824</v>
       </c>
       <c r="B150" t="n">
-        <v>79682</v>
+        <v>91259</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15885,25 +15885,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15913,10 +15913,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526533</v>
+        <v>526747</v>
       </c>
       <c r="R150" t="n">
-        <v>6938315</v>
+        <v>6937983</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121185404</v>
+        <v>121179693</v>
       </c>
       <c r="B171" t="n">
-        <v>91137</v>
+        <v>91973</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527659</v>
+        <v>527779</v>
       </c>
       <c r="R171" t="n">
-        <v>6937698</v>
+        <v>6937594</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121179693</v>
+        <v>121185404</v>
       </c>
       <c r="B172" t="n">
-        <v>91973</v>
+        <v>91137</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527779</v>
+        <v>527659</v>
       </c>
       <c r="R172" t="n">
-        <v>6937594</v>
+        <v>6937698</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185396</v>
+        <v>121180230</v>
       </c>
       <c r="B6" t="n">
-        <v>90662</v>
+        <v>105199</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>526980</v>
+        <v>527509</v>
       </c>
       <c r="R6" t="n">
-        <v>6938115</v>
+        <v>6937756</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185427</v>
+        <v>121185419</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79721</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527034</v>
+        <v>527001</v>
       </c>
       <c r="R7" t="n">
-        <v>6938099</v>
+        <v>6938096</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121183008</v>
+        <v>121185402</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>79714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,41 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>526999</v>
+        <v>527367</v>
       </c>
       <c r="R8" t="n">
-        <v>6938157</v>
+        <v>6937938</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185429</v>
+        <v>121185409</v>
       </c>
       <c r="B9" t="n">
-        <v>91973</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1473,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527641</v>
+        <v>527108</v>
       </c>
       <c r="R9" t="n">
-        <v>6937808</v>
+        <v>6938086</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1566,7 +1566,7 @@
         <v>121185407</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>90995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185424</v>
+        <v>121185403</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>90656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527010</v>
+        <v>527012</v>
       </c>
       <c r="R11" t="n">
-        <v>6938105</v>
+        <v>6938063</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185397</v>
+        <v>121185400</v>
       </c>
       <c r="B12" t="n">
-        <v>90662</v>
+        <v>90709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527043</v>
+        <v>527034</v>
       </c>
       <c r="R12" t="n">
-        <v>6938062</v>
+        <v>6938099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121180261</v>
+        <v>121183008</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1905,14 +1905,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527506</v>
+        <v>526999</v>
       </c>
       <c r="R13" t="n">
-        <v>6937752</v>
+        <v>6938157</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185414</v>
+        <v>121180291</v>
       </c>
       <c r="B14" t="n">
-        <v>79682</v>
+        <v>90727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,37 +1987,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527346</v>
+        <v>527492</v>
       </c>
       <c r="R14" t="n">
-        <v>6937925</v>
+        <v>6937763</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185430</v>
+        <v>121185398</v>
       </c>
       <c r="B15" t="n">
-        <v>91973</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527460</v>
+        <v>526983</v>
       </c>
       <c r="R15" t="n">
-        <v>6937819</v>
+        <v>6938135</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185431</v>
+        <v>121185413</v>
       </c>
       <c r="B16" t="n">
-        <v>91973</v>
+        <v>79685</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527439</v>
+        <v>527044</v>
       </c>
       <c r="R16" t="n">
-        <v>6937815</v>
+        <v>6938065</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185395</v>
+        <v>121185429</v>
       </c>
       <c r="B17" t="n">
-        <v>95628</v>
+        <v>91985</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527048</v>
+        <v>527641</v>
       </c>
       <c r="R17" t="n">
-        <v>6938076</v>
+        <v>6937808</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185406</v>
+        <v>121185414</v>
       </c>
       <c r="B18" t="n">
-        <v>90983</v>
+        <v>79685</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527009</v>
+        <v>527346</v>
       </c>
       <c r="R18" t="n">
-        <v>6938044</v>
+        <v>6937925</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185402</v>
+        <v>121185432</v>
       </c>
       <c r="B19" t="n">
-        <v>79711</v>
+        <v>91985</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527367</v>
+        <v>527217</v>
       </c>
       <c r="R19" t="n">
-        <v>6937938</v>
+        <v>6937854</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121185433</v>
+        <v>121180239</v>
       </c>
       <c r="B20" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,41 +2595,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527195</v>
+        <v>527495</v>
       </c>
       <c r="R20" t="n">
-        <v>6937884</v>
+        <v>6937765</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121179876</v>
+        <v>121179977</v>
       </c>
       <c r="B21" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,13 +2725,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527649</v>
+        <v>527626</v>
       </c>
       <c r="R21" t="n">
-        <v>6937696</v>
+        <v>6937719</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185401</v>
+        <v>121185423</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527016</v>
+        <v>526974</v>
       </c>
       <c r="R22" t="n">
-        <v>6938060</v>
+        <v>6938145</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185399</v>
+        <v>121185422</v>
       </c>
       <c r="B23" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,25 +2901,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>526989</v>
+        <v>526995</v>
       </c>
       <c r="R23" t="n">
-        <v>6938147</v>
+        <v>6938144</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185409</v>
+        <v>121185418</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527108</v>
+        <v>527437</v>
       </c>
       <c r="R24" t="n">
-        <v>6938086</v>
+        <v>6937974</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185415</v>
+        <v>121185395</v>
       </c>
       <c r="B25" t="n">
-        <v>79682</v>
+        <v>95641</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527391</v>
+        <v>527048</v>
       </c>
       <c r="R25" t="n">
-        <v>6937910</v>
+        <v>6938076</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121183281</v>
+        <v>121185406</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,41 +3207,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>526958</v>
+        <v>527009</v>
       </c>
       <c r="R26" t="n">
-        <v>6938109</v>
+        <v>6938044</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185410</v>
+        <v>121185411</v>
       </c>
       <c r="B27" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527024</v>
+        <v>527045</v>
       </c>
       <c r="R27" t="n">
-        <v>6938111</v>
+        <v>6938075</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185411</v>
+        <v>121185405</v>
       </c>
       <c r="B28" t="n">
-        <v>79682</v>
+        <v>90995</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527045</v>
+        <v>527034</v>
       </c>
       <c r="R28" t="n">
-        <v>6938075</v>
+        <v>6938099</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3504,7 +3504,7 @@
         <v>121185412</v>
       </c>
       <c r="B29" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185435</v>
+        <v>121183281</v>
       </c>
       <c r="B30" t="n">
-        <v>91353</v>
+        <v>98094</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3619,37 +3619,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527008</v>
+        <v>526958</v>
       </c>
       <c r="R30" t="n">
-        <v>6938073</v>
+        <v>6938109</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121180712</v>
+        <v>121185415</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,37 +3721,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527305</v>
+        <v>527391</v>
       </c>
       <c r="R31" t="n">
-        <v>6937895</v>
+        <v>6937910</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121182248</v>
+        <v>121185399</v>
       </c>
       <c r="B32" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,41 +3819,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527008</v>
+        <v>526989</v>
       </c>
       <c r="R32" t="n">
-        <v>6938092</v>
+        <v>6938147</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121180239</v>
+        <v>121185424</v>
       </c>
       <c r="B33" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527495</v>
+        <v>527010</v>
       </c>
       <c r="R33" t="n">
-        <v>6937765</v>
+        <v>6938105</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185403</v>
+        <v>121185425</v>
       </c>
       <c r="B34" t="n">
-        <v>90644</v>
+        <v>98094</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527012</v>
+        <v>527014</v>
       </c>
       <c r="R34" t="n">
-        <v>6938063</v>
+        <v>6938062</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185423</v>
+        <v>121185421</v>
       </c>
       <c r="B35" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526974</v>
+        <v>526958</v>
       </c>
       <c r="R35" t="n">
-        <v>6938145</v>
+        <v>6938116</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185418</v>
+        <v>121185426</v>
       </c>
       <c r="B36" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,25 +4227,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527437</v>
+        <v>527503</v>
       </c>
       <c r="R36" t="n">
-        <v>6937974</v>
+        <v>6937855</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121185413</v>
+        <v>121180141</v>
       </c>
       <c r="B37" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4329,41 +4329,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527044</v>
+        <v>527597</v>
       </c>
       <c r="R37" t="n">
-        <v>6938065</v>
+        <v>6937703</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121185416</v>
+        <v>121185434</v>
       </c>
       <c r="B38" t="n">
-        <v>79682</v>
+        <v>91985</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527367</v>
+        <v>526953</v>
       </c>
       <c r="R38" t="n">
-        <v>6937938</v>
+        <v>6938054</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121179977</v>
+        <v>121185431</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,41 +4533,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527626</v>
+        <v>527439</v>
       </c>
       <c r="R39" t="n">
-        <v>6937719</v>
+        <v>6937815</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121180291</v>
+        <v>121185416</v>
       </c>
       <c r="B40" t="n">
-        <v>90715</v>
+        <v>79685</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4639,37 +4639,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527492</v>
+        <v>527367</v>
       </c>
       <c r="R40" t="n">
-        <v>6937763</v>
+        <v>6937938</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185434</v>
+        <v>121185430</v>
       </c>
       <c r="B41" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526953</v>
+        <v>527460</v>
       </c>
       <c r="R41" t="n">
-        <v>6938054</v>
+        <v>6937819</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185419</v>
+        <v>121185433</v>
       </c>
       <c r="B42" t="n">
-        <v>79718</v>
+        <v>91985</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4843,21 +4843,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527001</v>
+        <v>527195</v>
       </c>
       <c r="R42" t="n">
-        <v>6938096</v>
+        <v>6937884</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185421</v>
+        <v>121180712</v>
       </c>
       <c r="B43" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>526958</v>
+        <v>527305</v>
       </c>
       <c r="R43" t="n">
-        <v>6938116</v>
+        <v>6937895</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185400</v>
+        <v>121185427</v>
       </c>
       <c r="B44" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5047,21 +5047,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185428</v>
+        <v>121185397</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527439</v>
+        <v>527043</v>
       </c>
       <c r="R45" t="n">
-        <v>6937974</v>
+        <v>6938062</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121185432</v>
+        <v>121180261</v>
       </c>
       <c r="B46" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,41 +5247,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527217</v>
+        <v>527506</v>
       </c>
       <c r="R46" t="n">
-        <v>6937854</v>
+        <v>6937752</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121185425</v>
+        <v>121179876</v>
       </c>
       <c r="B47" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5349,41 +5349,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527014</v>
+        <v>527649</v>
       </c>
       <c r="R47" t="n">
-        <v>6938062</v>
+        <v>6937696</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121180230</v>
+        <v>121185428</v>
       </c>
       <c r="B48" t="n">
-        <v>105186</v>
+        <v>78604</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5451,41 +5451,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527509</v>
+        <v>527439</v>
       </c>
       <c r="R48" t="n">
-        <v>6937756</v>
+        <v>6937974</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185426</v>
+        <v>121185396</v>
       </c>
       <c r="B49" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5553,25 +5553,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527503</v>
+        <v>526980</v>
       </c>
       <c r="R49" t="n">
-        <v>6937855</v>
+        <v>6938115</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121180141</v>
+        <v>121185417</v>
       </c>
       <c r="B50" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,41 +5655,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527597</v>
+        <v>527368</v>
       </c>
       <c r="R50" t="n">
-        <v>6937703</v>
+        <v>6937959</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185417</v>
+        <v>121185401</v>
       </c>
       <c r="B51" t="n">
-        <v>79682</v>
+        <v>90709</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5761,21 +5761,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527368</v>
+        <v>527016</v>
       </c>
       <c r="R51" t="n">
-        <v>6937959</v>
+        <v>6938060</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185422</v>
+        <v>121185410</v>
       </c>
       <c r="B52" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>526995</v>
+        <v>527024</v>
       </c>
       <c r="R52" t="n">
-        <v>6938144</v>
+        <v>6938111</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121185398</v>
+        <v>121182248</v>
       </c>
       <c r="B53" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526983</v>
+        <v>527008</v>
       </c>
       <c r="R53" t="n">
-        <v>6938135</v>
+        <v>6938092</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185405</v>
+        <v>121185435</v>
       </c>
       <c r="B54" t="n">
-        <v>90983</v>
+        <v>91365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,25 +6063,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527034</v>
+        <v>527008</v>
       </c>
       <c r="R54" t="n">
-        <v>6938099</v>
+        <v>6938073</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212720</v>
+        <v>121212724</v>
       </c>
       <c r="B55" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527051</v>
+        <v>527109</v>
       </c>
       <c r="R55" t="n">
-        <v>6938362</v>
+        <v>6938336</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212774</v>
+        <v>121212717</v>
       </c>
       <c r="B56" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6271,21 +6271,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526840</v>
+        <v>527023</v>
       </c>
       <c r="R56" t="n">
-        <v>6938383</v>
+        <v>6938359</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212758</v>
+        <v>121212712</v>
       </c>
       <c r="B57" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526823</v>
+        <v>526743</v>
       </c>
       <c r="R57" t="n">
-        <v>6938405</v>
+        <v>6938415</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212755</v>
+        <v>121212764</v>
       </c>
       <c r="B58" t="n">
-        <v>78337</v>
+        <v>98094</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212733</v>
+        <v>121212757</v>
       </c>
       <c r="B59" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527186</v>
+        <v>526927</v>
       </c>
       <c r="R59" t="n">
-        <v>6938273</v>
+        <v>6938376</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212713</v>
+        <v>121212688</v>
       </c>
       <c r="B60" t="n">
-        <v>79682</v>
+        <v>95641</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,21 +6679,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526960</v>
+        <v>527409</v>
       </c>
       <c r="R60" t="n">
-        <v>6938390</v>
+        <v>6938091</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212729</v>
+        <v>121212733</v>
       </c>
       <c r="B61" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527168</v>
+        <v>527186</v>
       </c>
       <c r="R61" t="n">
-        <v>6938291</v>
+        <v>6938273</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212751</v>
+        <v>121212745</v>
       </c>
       <c r="B62" t="n">
-        <v>78337</v>
+        <v>79721</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6879,25 +6879,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526755</v>
+        <v>526960</v>
       </c>
       <c r="R62" t="n">
-        <v>6938374</v>
+        <v>6938390</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212756</v>
+        <v>121212728</v>
       </c>
       <c r="B63" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6981,25 +6981,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527255</v>
+        <v>527148</v>
       </c>
       <c r="R63" t="n">
-        <v>6938220</v>
+        <v>6938301</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7045,11 +7045,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7076,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212772</v>
+        <v>121212735</v>
       </c>
       <c r="B64" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7092,21 +7087,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7116,10 +7111,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526971</v>
+        <v>527245</v>
       </c>
       <c r="R64" t="n">
-        <v>6938369</v>
+        <v>6938291</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7152,11 +7147,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7183,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212705</v>
+        <v>121212752</v>
       </c>
       <c r="B65" t="n">
-        <v>90983</v>
+        <v>78340</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7199,21 +7189,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7223,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527310</v>
+        <v>526804</v>
       </c>
       <c r="R65" t="n">
-        <v>6938160</v>
+        <v>6938398</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7285,10 +7275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212701</v>
+        <v>121212708</v>
       </c>
       <c r="B66" t="n">
-        <v>90983</v>
+        <v>97048</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7297,25 +7287,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7325,10 +7315,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526960</v>
+        <v>527252</v>
       </c>
       <c r="R66" t="n">
-        <v>6938387</v>
+        <v>6938285</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7387,10 +7377,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212745</v>
+        <v>121212765</v>
       </c>
       <c r="B67" t="n">
-        <v>79718</v>
+        <v>98094</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7399,25 +7389,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526960</v>
+        <v>526955</v>
       </c>
       <c r="R67" t="n">
-        <v>6938390</v>
+        <v>6938367</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7489,10 +7479,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212689</v>
+        <v>121212701</v>
       </c>
       <c r="B68" t="n">
-        <v>79219</v>
+        <v>90995</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7505,21 +7495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7529,10 +7519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526855</v>
+        <v>526960</v>
       </c>
       <c r="R68" t="n">
-        <v>6938391</v>
+        <v>6938387</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7591,10 +7581,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212714</v>
+        <v>121212698</v>
       </c>
       <c r="B69" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7607,21 +7597,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7621,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>526955</v>
+        <v>527211</v>
       </c>
       <c r="R69" t="n">
-        <v>6938368</v>
+        <v>6938302</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7693,10 +7683,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212726</v>
+        <v>121212720</v>
       </c>
       <c r="B70" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7733,10 +7723,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527148</v>
+        <v>527051</v>
       </c>
       <c r="R70" t="n">
-        <v>6938301</v>
+        <v>6938362</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7795,10 +7785,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212711</v>
+        <v>121212753</v>
       </c>
       <c r="B71" t="n">
-        <v>79682</v>
+        <v>78340</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7811,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7835,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527051</v>
+        <v>526856</v>
       </c>
       <c r="R71" t="n">
-        <v>6938349</v>
+        <v>6938391</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7897,10 +7887,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212703</v>
+        <v>121212723</v>
       </c>
       <c r="B72" t="n">
-        <v>90983</v>
+        <v>79685</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7913,21 +7903,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7937,10 +7927,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527253</v>
+        <v>527088</v>
       </c>
       <c r="R72" t="n">
-        <v>6938232</v>
+        <v>6938358</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7999,10 +7989,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212699</v>
+        <v>121212718</v>
       </c>
       <c r="B73" t="n">
-        <v>79586</v>
+        <v>79685</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8011,25 +8001,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8039,10 +8029,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527249</v>
+        <v>527038</v>
       </c>
       <c r="R73" t="n">
-        <v>6938289</v>
+        <v>6938372</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8101,10 +8091,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212712</v>
+        <v>121212725</v>
       </c>
       <c r="B74" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8141,10 +8131,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526743</v>
+        <v>527111</v>
       </c>
       <c r="R74" t="n">
-        <v>6938415</v>
+        <v>6938327</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8203,10 +8193,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212694</v>
+        <v>121212696</v>
       </c>
       <c r="B75" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8243,10 +8233,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527088</v>
+        <v>527288</v>
       </c>
       <c r="R75" t="n">
-        <v>6938356</v>
+        <v>6938221</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8305,10 +8295,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212746</v>
+        <v>121212750</v>
       </c>
       <c r="B76" t="n">
-        <v>79718</v>
+        <v>80561</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8317,25 +8307,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>1049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8345,10 +8335,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527088</v>
+        <v>526756</v>
       </c>
       <c r="R76" t="n">
-        <v>6938356</v>
+        <v>6938437</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8407,10 +8397,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212761</v>
+        <v>121212739</v>
       </c>
       <c r="B77" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8419,25 +8409,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8447,10 +8437,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526852</v>
+        <v>527304</v>
       </c>
       <c r="R77" t="n">
-        <v>6938391</v>
+        <v>6938173</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8509,10 +8499,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212692</v>
+        <v>121212775</v>
       </c>
       <c r="B78" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8525,21 +8515,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8549,10 +8539,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527210</v>
+        <v>527023</v>
       </c>
       <c r="R78" t="n">
-        <v>6938291</v>
+        <v>6938359</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8585,11 +8575,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8616,10 +8601,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212773</v>
+        <v>121212694</v>
       </c>
       <c r="B79" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8628,25 +8613,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8656,10 +8641,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526989</v>
+        <v>527088</v>
       </c>
       <c r="R79" t="n">
-        <v>6938371</v>
+        <v>6938356</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8692,11 +8677,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8723,10 +8703,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212717</v>
+        <v>121212730</v>
       </c>
       <c r="B80" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8763,10 +8743,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527023</v>
+        <v>527177</v>
       </c>
       <c r="R80" t="n">
-        <v>6938359</v>
+        <v>6938273</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8825,10 +8805,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212775</v>
+        <v>121212729</v>
       </c>
       <c r="B81" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8841,21 +8821,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8865,10 +8845,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527023</v>
+        <v>527168</v>
       </c>
       <c r="R81" t="n">
-        <v>6938359</v>
+        <v>6938291</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8927,10 +8907,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212695</v>
+        <v>121212774</v>
       </c>
       <c r="B82" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8939,25 +8919,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8967,10 +8947,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527184</v>
+        <v>526840</v>
       </c>
       <c r="R82" t="n">
-        <v>6938280</v>
+        <v>6938383</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9029,10 +9009,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212731</v>
+        <v>121212772</v>
       </c>
       <c r="B83" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9045,21 +9025,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9069,10 +9049,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527184</v>
+        <v>526971</v>
       </c>
       <c r="R83" t="n">
-        <v>6938280</v>
+        <v>6938369</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9105,6 +9085,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9131,10 +9116,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212765</v>
+        <v>121212756</v>
       </c>
       <c r="B84" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9171,10 +9156,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526955</v>
+        <v>527255</v>
       </c>
       <c r="R84" t="n">
-        <v>6938367</v>
+        <v>6938220</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9207,6 +9192,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9233,10 +9223,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212708</v>
+        <v>121212758</v>
       </c>
       <c r="B85" t="n">
-        <v>97035</v>
+        <v>98094</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9245,25 +9235,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9273,10 +9263,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527252</v>
+        <v>526823</v>
       </c>
       <c r="R85" t="n">
-        <v>6938285</v>
+        <v>6938405</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9335,10 +9325,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212697</v>
+        <v>121212751</v>
       </c>
       <c r="B86" t="n">
-        <v>79683</v>
+        <v>78340</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9351,21 +9341,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9375,10 +9365,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527186</v>
+        <v>526755</v>
       </c>
       <c r="R86" t="n">
-        <v>6938273</v>
+        <v>6938374</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9437,10 +9427,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212716</v>
+        <v>121212703</v>
       </c>
       <c r="B87" t="n">
-        <v>79682</v>
+        <v>90995</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9453,21 +9443,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9477,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526994</v>
+        <v>527253</v>
       </c>
       <c r="R87" t="n">
-        <v>6938374</v>
+        <v>6938232</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9539,10 +9529,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212740</v>
+        <v>121212734</v>
       </c>
       <c r="B88" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9579,10 +9569,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527350</v>
+        <v>527214</v>
       </c>
       <c r="R88" t="n">
-        <v>6938133</v>
+        <v>6938296</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9641,10 +9631,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212688</v>
+        <v>121212731</v>
       </c>
       <c r="B89" t="n">
-        <v>95628</v>
+        <v>79685</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9657,21 +9647,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9681,10 +9671,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527409</v>
+        <v>527184</v>
       </c>
       <c r="R89" t="n">
-        <v>6938091</v>
+        <v>6938280</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9743,10 +9733,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212690</v>
+        <v>121212740</v>
       </c>
       <c r="B90" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9759,21 +9749,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9783,10 +9773,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527263</v>
+        <v>527350</v>
       </c>
       <c r="R90" t="n">
-        <v>6938234</v>
+        <v>6938133</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9845,10 +9835,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212725</v>
+        <v>121212692</v>
       </c>
       <c r="B91" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9861,21 +9851,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9885,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527111</v>
+        <v>527210</v>
       </c>
       <c r="R91" t="n">
-        <v>6938327</v>
+        <v>6938291</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9921,6 +9911,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9947,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212739</v>
+        <v>121212773</v>
       </c>
       <c r="B92" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9963,21 +9958,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9987,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527304</v>
+        <v>526989</v>
       </c>
       <c r="R92" t="n">
-        <v>6938173</v>
+        <v>6938371</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10023,6 +10018,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10049,10 +10049,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212736</v>
+        <v>121212710</v>
       </c>
       <c r="B93" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527250</v>
+        <v>527495</v>
       </c>
       <c r="R93" t="n">
-        <v>6938289</v>
+        <v>6938009</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10125,6 +10125,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10151,10 +10156,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212750</v>
+        <v>121212714</v>
       </c>
       <c r="B94" t="n">
-        <v>80558</v>
+        <v>79685</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10167,21 +10172,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10191,10 +10196,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526756</v>
+        <v>526955</v>
       </c>
       <c r="R94" t="n">
-        <v>6938437</v>
+        <v>6938368</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10253,10 +10258,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212753</v>
+        <v>121212722</v>
       </c>
       <c r="B95" t="n">
-        <v>78337</v>
+        <v>79685</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10269,21 +10274,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10293,10 +10298,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>526856</v>
+        <v>527075</v>
       </c>
       <c r="R95" t="n">
-        <v>6938391</v>
+        <v>6938349</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10355,10 +10360,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212709</v>
+        <v>121212721</v>
       </c>
       <c r="B96" t="n">
-        <v>78338</v>
+        <v>79685</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10371,21 +10376,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10395,10 +10400,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526856</v>
+        <v>527074</v>
       </c>
       <c r="R96" t="n">
-        <v>6938391</v>
+        <v>6938353</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10457,10 +10462,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212715</v>
+        <v>121212713</v>
       </c>
       <c r="B97" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10497,10 +10502,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>526971</v>
+        <v>526960</v>
       </c>
       <c r="R97" t="n">
-        <v>6938369</v>
+        <v>6938390</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10559,10 +10564,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212759</v>
+        <v>121212705</v>
       </c>
       <c r="B98" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10571,25 +10576,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10599,10 +10604,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>526838</v>
+        <v>527310</v>
       </c>
       <c r="R98" t="n">
-        <v>6938397</v>
+        <v>6938160</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10661,10 +10666,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212762</v>
+        <v>121212761</v>
       </c>
       <c r="B99" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10701,10 +10706,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>526868</v>
+        <v>526852</v>
       </c>
       <c r="R99" t="n">
-        <v>6938367</v>
+        <v>6938391</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10763,10 +10768,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212752</v>
+        <v>121212736</v>
       </c>
       <c r="B100" t="n">
-        <v>78337</v>
+        <v>79685</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10779,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10803,10 +10808,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>526804</v>
+        <v>527250</v>
       </c>
       <c r="R100" t="n">
-        <v>6938398</v>
+        <v>6938289</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10865,10 +10870,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212696</v>
+        <v>121212690</v>
       </c>
       <c r="B101" t="n">
-        <v>79711</v>
+        <v>90709</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10877,25 +10882,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10910,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527288</v>
+        <v>527263</v>
       </c>
       <c r="R101" t="n">
-        <v>6938221</v>
+        <v>6938234</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,10 +10972,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212764</v>
+        <v>121212746</v>
       </c>
       <c r="B102" t="n">
-        <v>98081</v>
+        <v>79721</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10979,25 +10984,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>526945</v>
+        <v>527088</v>
       </c>
       <c r="R102" t="n">
-        <v>6938389</v>
+        <v>6938356</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11074,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212737</v>
+        <v>121212763</v>
       </c>
       <c r="B103" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11081,25 +11086,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>527248</v>
+        <v>526911</v>
       </c>
       <c r="R103" t="n">
-        <v>6938256</v>
+        <v>6938360</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11176,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212718</v>
+        <v>121212709</v>
       </c>
       <c r="B104" t="n">
-        <v>79682</v>
+        <v>78341</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11187,21 +11192,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11216,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527038</v>
+        <v>526856</v>
       </c>
       <c r="R104" t="n">
-        <v>6938372</v>
+        <v>6938391</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11278,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212763</v>
+        <v>121212760</v>
       </c>
       <c r="B105" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11313,10 +11318,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>526911</v>
+        <v>526842</v>
       </c>
       <c r="R105" t="n">
-        <v>6938360</v>
+        <v>6938396</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,10 +11380,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212735</v>
+        <v>121212762</v>
       </c>
       <c r="B106" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11387,25 +11392,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11415,10 +11420,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527245</v>
+        <v>526868</v>
       </c>
       <c r="R106" t="n">
-        <v>6938291</v>
+        <v>6938367</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11477,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212730</v>
+        <v>121212769</v>
       </c>
       <c r="B107" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11489,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11517,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527177</v>
+        <v>527263</v>
       </c>
       <c r="R107" t="n">
-        <v>6938273</v>
+        <v>6938242</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11579,10 +11584,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212723</v>
+        <v>121212771</v>
       </c>
       <c r="B108" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11591,25 +11596,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11619,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527088</v>
+        <v>527317</v>
       </c>
       <c r="R108" t="n">
-        <v>6938358</v>
+        <v>6938165</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11681,10 +11686,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212760</v>
+        <v>121212695</v>
       </c>
       <c r="B109" t="n">
-        <v>98081</v>
+        <v>79714</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11693,25 +11698,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11721,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526842</v>
+        <v>527184</v>
       </c>
       <c r="R109" t="n">
-        <v>6938396</v>
+        <v>6938280</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11783,10 +11788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212757</v>
+        <v>121212738</v>
       </c>
       <c r="B110" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11795,25 +11800,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11823,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>526927</v>
+        <v>527288</v>
       </c>
       <c r="R110" t="n">
-        <v>6938376</v>
+        <v>6938221</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11885,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212744</v>
+        <v>121212715</v>
       </c>
       <c r="B111" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11925,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527495</v>
+        <v>526971</v>
       </c>
       <c r="R111" t="n">
-        <v>6938012</v>
+        <v>6938369</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11987,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212738</v>
+        <v>121212689</v>
       </c>
       <c r="B112" t="n">
-        <v>79682</v>
+        <v>79222</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12003,21 +12008,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12027,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>527288</v>
+        <v>526855</v>
       </c>
       <c r="R112" t="n">
-        <v>6938221</v>
+        <v>6938391</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12089,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212698</v>
+        <v>121212759</v>
       </c>
       <c r="B113" t="n">
-        <v>79683</v>
+        <v>98094</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12101,25 +12106,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12129,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527211</v>
+        <v>526838</v>
       </c>
       <c r="R113" t="n">
-        <v>6938302</v>
+        <v>6938397</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12191,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212724</v>
+        <v>121212744</v>
       </c>
       <c r="B114" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12231,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527109</v>
+        <v>527495</v>
       </c>
       <c r="R114" t="n">
-        <v>6938336</v>
+        <v>6938012</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12293,10 +12298,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212734</v>
+        <v>121212716</v>
       </c>
       <c r="B115" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12333,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527214</v>
+        <v>526994</v>
       </c>
       <c r="R115" t="n">
-        <v>6938296</v>
+        <v>6938374</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12395,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212710</v>
+        <v>121212711</v>
       </c>
       <c r="B116" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12435,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527495</v>
+        <v>527051</v>
       </c>
       <c r="R116" t="n">
-        <v>6938009</v>
+        <v>6938349</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12471,11 +12476,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12502,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212722</v>
+        <v>121212737</v>
       </c>
       <c r="B117" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527075</v>
+        <v>527248</v>
       </c>
       <c r="R117" t="n">
-        <v>6938349</v>
+        <v>6938256</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212771</v>
+        <v>121212755</v>
       </c>
       <c r="B118" t="n">
-        <v>98081</v>
+        <v>78340</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12616,25 +12616,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527317</v>
+        <v>526945</v>
       </c>
       <c r="R118" t="n">
-        <v>6938165</v>
+        <v>6938389</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212721</v>
+        <v>121212699</v>
       </c>
       <c r="B119" t="n">
-        <v>79682</v>
+        <v>79589</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,25 +12718,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527074</v>
+        <v>527249</v>
       </c>
       <c r="R119" t="n">
-        <v>6938353</v>
+        <v>6938289</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212769</v>
+        <v>121212697</v>
       </c>
       <c r="B120" t="n">
-        <v>98081</v>
+        <v>79686</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527263</v>
+        <v>527186</v>
       </c>
       <c r="R120" t="n">
-        <v>6938242</v>
+        <v>6938273</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121226802</v>
+        <v>121226805</v>
       </c>
       <c r="B121" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526716</v>
+        <v>526203</v>
       </c>
       <c r="R121" t="n">
-        <v>6937997</v>
+        <v>6938195</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13015,7 +13015,7 @@
         <v>121220094</v>
       </c>
       <c r="B122" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121220916</v>
+        <v>121226799</v>
       </c>
       <c r="B123" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,41 +13126,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526647</v>
+        <v>526747</v>
       </c>
       <c r="R123" t="n">
-        <v>6938174</v>
+        <v>6937983</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226812</v>
+        <v>121226801</v>
       </c>
       <c r="B124" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526551</v>
+        <v>526714</v>
       </c>
       <c r="R124" t="n">
-        <v>6938312</v>
+        <v>6938008</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13318,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226817</v>
+        <v>121226796</v>
       </c>
       <c r="B125" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,25 +13330,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526581</v>
+        <v>526796</v>
       </c>
       <c r="R125" t="n">
-        <v>6938053</v>
+        <v>6937966</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121212788</v>
+        <v>121226822</v>
       </c>
       <c r="B126" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13460,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526776</v>
+        <v>526182</v>
       </c>
       <c r="R126" t="n">
-        <v>6938419</v>
+        <v>6938234</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13490,12 +13490,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121221064</v>
+        <v>121226815</v>
       </c>
       <c r="B127" t="n">
-        <v>90711</v>
+        <v>78340</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13538,37 +13538,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526664</v>
+        <v>526527</v>
       </c>
       <c r="R127" t="n">
-        <v>6938176</v>
+        <v>6938317</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226794</v>
+        <v>121226807</v>
       </c>
       <c r="B128" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13636,25 +13636,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526478</v>
+        <v>526201</v>
       </c>
       <c r="R128" t="n">
-        <v>6938348</v>
+        <v>6938252</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226820</v>
+        <v>121212780</v>
       </c>
       <c r="B129" t="n">
-        <v>90711</v>
+        <v>78604</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526660</v>
+        <v>527567</v>
       </c>
       <c r="R129" t="n">
-        <v>6938167</v>
+        <v>6937949</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13796,12 +13796,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226818</v>
+        <v>121221064</v>
       </c>
       <c r="B130" t="n">
-        <v>98081</v>
+        <v>90723</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13840,41 +13840,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526525</v>
+        <v>526664</v>
       </c>
       <c r="R130" t="n">
-        <v>6938312</v>
+        <v>6938176</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13930,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121212785</v>
+        <v>121226792</v>
       </c>
       <c r="B131" t="n">
-        <v>78246</v>
+        <v>90709</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13946,21 +13946,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526753</v>
+        <v>526796</v>
       </c>
       <c r="R131" t="n">
-        <v>6938395</v>
+        <v>6937966</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14000,12 +14000,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14032,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121226822</v>
+        <v>121226824</v>
       </c>
       <c r="B132" t="n">
-        <v>91973</v>
+        <v>91271</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14044,25 +14044,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>760</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14072,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526182</v>
+        <v>526747</v>
       </c>
       <c r="R132" t="n">
-        <v>6938234</v>
+        <v>6937983</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14134,10 +14134,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121212778</v>
+        <v>121222671</v>
       </c>
       <c r="B133" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14170,17 +14170,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>527288</v>
+        <v>526275</v>
       </c>
       <c r="R133" t="n">
-        <v>6938221</v>
+        <v>6938199</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14204,12 +14204,17 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14236,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226803</v>
+        <v>121226821</v>
       </c>
       <c r="B134" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,21 +14257,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14276,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526335</v>
+        <v>526199</v>
       </c>
       <c r="R134" t="n">
-        <v>6938150</v>
+        <v>6938254</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14312,6 +14317,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14338,10 +14348,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226795</v>
+        <v>121226812</v>
       </c>
       <c r="B135" t="n">
-        <v>79683</v>
+        <v>79685</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14354,21 +14364,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14378,10 +14388,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526554</v>
+        <v>526551</v>
       </c>
       <c r="R135" t="n">
-        <v>6938311</v>
+        <v>6938312</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14440,10 +14450,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121212780</v>
+        <v>121212791</v>
       </c>
       <c r="B136" t="n">
-        <v>78601</v>
+        <v>79720</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14452,20 +14462,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -14480,10 +14490,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>527567</v>
+        <v>527094</v>
       </c>
       <c r="R136" t="n">
-        <v>6937949</v>
+        <v>6938358</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14542,10 +14552,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121221199</v>
+        <v>121226794</v>
       </c>
       <c r="B137" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14554,41 +14564,41 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526592</v>
+        <v>526478</v>
       </c>
       <c r="R137" t="n">
-        <v>6938232</v>
+        <v>6938348</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14644,10 +14654,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121212791</v>
+        <v>121226817</v>
       </c>
       <c r="B138" t="n">
-        <v>79717</v>
+        <v>98094</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14656,25 +14666,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14684,10 +14694,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>527094</v>
+        <v>526581</v>
       </c>
       <c r="R138" t="n">
-        <v>6938358</v>
+        <v>6938053</v>
       </c>
       <c r="S138" t="n">
         <v>25</v>
@@ -14714,12 +14724,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14746,10 +14756,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226799</v>
+        <v>121226793</v>
       </c>
       <c r="B139" t="n">
-        <v>79682</v>
+        <v>90729</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14762,21 +14772,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14786,10 +14796,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526747</v>
+        <v>526519</v>
       </c>
       <c r="R139" t="n">
-        <v>6937983</v>
+        <v>6938315</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14848,10 +14858,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226809</v>
+        <v>121226806</v>
       </c>
       <c r="B140" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14888,10 +14898,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526518</v>
+        <v>526182</v>
       </c>
       <c r="R140" t="n">
-        <v>6938295</v>
+        <v>6938206</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14950,10 +14960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226793</v>
+        <v>121221199</v>
       </c>
       <c r="B141" t="n">
-        <v>90717</v>
+        <v>78604</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14966,37 +14976,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526519</v>
+        <v>526592</v>
       </c>
       <c r="R141" t="n">
-        <v>6938315</v>
+        <v>6938232</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15052,10 +15062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121223305</v>
+        <v>121212778</v>
       </c>
       <c r="B142" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15064,41 +15074,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526584</v>
+        <v>527288</v>
       </c>
       <c r="R142" t="n">
-        <v>6938052</v>
+        <v>6938221</v>
       </c>
       <c r="S142" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15122,12 +15132,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15154,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226805</v>
+        <v>121226819</v>
       </c>
       <c r="B143" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15166,25 +15176,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15194,10 +15204,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526203</v>
+        <v>526646</v>
       </c>
       <c r="R143" t="n">
-        <v>6938195</v>
+        <v>6938173</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15256,10 +15266,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226801</v>
+        <v>121212789</v>
       </c>
       <c r="B144" t="n">
-        <v>79682</v>
+        <v>91985</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15268,25 +15278,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15296,10 +15306,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526714</v>
+        <v>526823</v>
       </c>
       <c r="R144" t="n">
-        <v>6938008</v>
+        <v>6938405</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15326,12 +15336,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15358,10 +15368,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226813</v>
+        <v>121226803</v>
       </c>
       <c r="B145" t="n">
-        <v>78337</v>
+        <v>79685</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15374,21 +15384,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15398,10 +15408,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526365</v>
+        <v>526335</v>
       </c>
       <c r="R145" t="n">
-        <v>6938404</v>
+        <v>6938150</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15460,10 +15470,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121226797</v>
+        <v>121212783</v>
       </c>
       <c r="B146" t="n">
-        <v>79682</v>
+        <v>78249</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15476,21 +15486,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15500,10 +15510,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526496</v>
+        <v>526761</v>
       </c>
       <c r="R146" t="n">
-        <v>6938343</v>
+        <v>6938348</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15530,17 +15540,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15567,10 +15572,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226807</v>
+        <v>121226813</v>
       </c>
       <c r="B147" t="n">
-        <v>79682</v>
+        <v>78340</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15583,21 +15588,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15607,10 +15612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526201</v>
+        <v>526365</v>
       </c>
       <c r="R147" t="n">
-        <v>6938252</v>
+        <v>6938404</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -15669,10 +15674,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226810</v>
+        <v>121220916</v>
       </c>
       <c r="B148" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15681,41 +15686,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526533</v>
+        <v>526647</v>
       </c>
       <c r="R148" t="n">
-        <v>6938315</v>
+        <v>6938174</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15771,10 +15776,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121212783</v>
+        <v>121212779</v>
       </c>
       <c r="B149" t="n">
-        <v>78246</v>
+        <v>78604</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15787,21 +15792,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15811,10 +15816,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526761</v>
+        <v>527495</v>
       </c>
       <c r="R149" t="n">
-        <v>6938348</v>
+        <v>6938009</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15873,10 +15878,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226824</v>
+        <v>121226814</v>
       </c>
       <c r="B150" t="n">
-        <v>91259</v>
+        <v>78340</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15885,25 +15890,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15913,10 +15918,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526747</v>
+        <v>526515</v>
       </c>
       <c r="R150" t="n">
-        <v>6937983</v>
+        <v>6938303</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15975,10 +15980,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226816</v>
+        <v>121226809</v>
       </c>
       <c r="B151" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15987,25 +15992,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16015,10 +16020,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526789</v>
+        <v>526518</v>
       </c>
       <c r="R151" t="n">
-        <v>6937993</v>
+        <v>6938295</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16077,10 +16082,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121212789</v>
+        <v>121226811</v>
       </c>
       <c r="B152" t="n">
-        <v>91973</v>
+        <v>79685</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16089,25 +16094,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16117,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526823</v>
+        <v>526545</v>
       </c>
       <c r="R152" t="n">
-        <v>6938405</v>
+        <v>6938319</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16147,12 +16152,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16179,10 +16184,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121219596</v>
+        <v>121223305</v>
       </c>
       <c r="B153" t="n">
-        <v>78337</v>
+        <v>98094</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16191,25 +16196,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16219,13 +16224,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526982</v>
+        <v>526584</v>
       </c>
       <c r="R153" t="n">
-        <v>6937928</v>
+        <v>6938052</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16281,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226804</v>
+        <v>121226791</v>
       </c>
       <c r="B154" t="n">
-        <v>79682</v>
+        <v>89760</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16297,21 +16302,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16321,10 +16326,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526224</v>
+        <v>526205</v>
       </c>
       <c r="R154" t="n">
-        <v>6938191</v>
+        <v>6938282</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16383,10 +16388,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226814</v>
+        <v>121226808</v>
       </c>
       <c r="B155" t="n">
-        <v>78337</v>
+        <v>79685</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16399,21 +16404,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16423,10 +16428,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526515</v>
+        <v>526482</v>
       </c>
       <c r="R155" t="n">
-        <v>6938303</v>
+        <v>6938338</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16485,10 +16490,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212776</v>
+        <v>121212785</v>
       </c>
       <c r="B156" t="n">
-        <v>78601</v>
+        <v>78249</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16501,21 +16506,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16525,10 +16530,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>527090</v>
+        <v>526753</v>
       </c>
       <c r="R156" t="n">
-        <v>6938365</v>
+        <v>6938395</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16587,10 +16592,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226792</v>
+        <v>121226820</v>
       </c>
       <c r="B157" t="n">
-        <v>90697</v>
+        <v>90723</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16603,21 +16608,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16627,10 +16632,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526796</v>
+        <v>526660</v>
       </c>
       <c r="R157" t="n">
-        <v>6937966</v>
+        <v>6938167</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16689,10 +16694,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121212779</v>
+        <v>121219658</v>
       </c>
       <c r="B158" t="n">
-        <v>78601</v>
+        <v>90674</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16701,41 +16706,41 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>527495</v>
+        <v>526953</v>
       </c>
       <c r="R158" t="n">
-        <v>6938009</v>
+        <v>6937958</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16759,12 +16764,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16791,10 +16796,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226811</v>
+        <v>121226795</v>
       </c>
       <c r="B159" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16807,21 +16812,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16831,10 +16836,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526545</v>
+        <v>526554</v>
       </c>
       <c r="R159" t="n">
-        <v>6938319</v>
+        <v>6938311</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16893,10 +16898,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121222671</v>
+        <v>121212788</v>
       </c>
       <c r="B160" t="n">
-        <v>78601</v>
+        <v>91985</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16905,41 +16910,41 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526275</v>
+        <v>526776</v>
       </c>
       <c r="R160" t="n">
-        <v>6938199</v>
+        <v>6938419</v>
       </c>
       <c r="S160" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16963,17 +16968,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17000,10 +17000,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121219658</v>
+        <v>121226802</v>
       </c>
       <c r="B161" t="n">
-        <v>90662</v>
+        <v>79685</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17012,41 +17012,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526953</v>
+        <v>526716</v>
       </c>
       <c r="R161" t="n">
-        <v>6937958</v>
+        <v>6937997</v>
       </c>
       <c r="S161" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17102,10 +17102,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226815</v>
+        <v>121212776</v>
       </c>
       <c r="B162" t="n">
-        <v>78337</v>
+        <v>78604</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17118,21 +17118,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526527</v>
+        <v>527090</v>
       </c>
       <c r="R162" t="n">
-        <v>6938317</v>
+        <v>6938365</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17172,12 +17172,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17204,10 +17204,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226821</v>
+        <v>121226816</v>
       </c>
       <c r="B163" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17216,25 +17216,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17244,10 +17244,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526199</v>
+        <v>526789</v>
       </c>
       <c r="R163" t="n">
-        <v>6938254</v>
+        <v>6937993</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17280,11 +17280,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,10 +17306,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226806</v>
+        <v>121226818</v>
       </c>
       <c r="B164" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17323,25 +17318,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17346,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526182</v>
+        <v>526525</v>
       </c>
       <c r="R164" t="n">
-        <v>6938206</v>
+        <v>6938312</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17413,10 +17408,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226808</v>
+        <v>121226804</v>
       </c>
       <c r="B165" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17453,10 +17448,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526482</v>
+        <v>526224</v>
       </c>
       <c r="R165" t="n">
-        <v>6938338</v>
+        <v>6938191</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17515,10 +17510,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226796</v>
+        <v>121226810</v>
       </c>
       <c r="B166" t="n">
-        <v>90983</v>
+        <v>79685</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,21 +17526,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17550,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526796</v>
+        <v>526533</v>
       </c>
       <c r="R166" t="n">
-        <v>6937966</v>
+        <v>6938315</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17617,10 +17612,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226819</v>
+        <v>121226797</v>
       </c>
       <c r="B167" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17624,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17652,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526646</v>
+        <v>526496</v>
       </c>
       <c r="R167" t="n">
-        <v>6938173</v>
+        <v>6938343</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17693,6 +17688,11 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226791</v>
+        <v>121219596</v>
       </c>
       <c r="B168" t="n">
-        <v>89753</v>
+        <v>78340</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17735,37 +17735,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526205</v>
+        <v>526982</v>
       </c>
       <c r="R168" t="n">
-        <v>6938282</v>
+        <v>6937928</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17821,10 +17821,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121212693</v>
+        <v>121246286</v>
       </c>
       <c r="B169" t="n">
-        <v>91977</v>
+        <v>92014</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17837,27 +17837,24 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -17904,7 +17901,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp under samma tallåga</t>
+          <t>Även smalfotad taggsvamp under samma låga</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17913,7 +17910,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17932,10 +17928,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121246286</v>
+        <v>121212693</v>
       </c>
       <c r="B170" t="n">
-        <v>92002</v>
+        <v>91989</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17948,24 +17944,27 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -18012,7 +18011,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Även smalfotad taggsvamp under samma låga</t>
+          <t>Tajgataggsvamp under samma tallåga</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18021,6 +18020,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121179693</v>
+        <v>121185408</v>
       </c>
       <c r="B171" t="n">
-        <v>91973</v>
+        <v>90995</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527779</v>
+        <v>527661</v>
       </c>
       <c r="R171" t="n">
-        <v>6937594</v>
+        <v>6937695</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121185404</v>
+        <v>121179849</v>
       </c>
       <c r="B172" t="n">
-        <v>91137</v>
+        <v>91149</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18177,17 +18177,17 @@
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527659</v>
+        <v>527658</v>
       </c>
       <c r="R172" t="n">
-        <v>6937698</v>
+        <v>6937694</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121179849</v>
+        <v>121179693</v>
       </c>
       <c r="B173" t="n">
-        <v>91137</v>
+        <v>91985</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18255,25 +18255,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18283,13 +18283,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>527658</v>
+        <v>527779</v>
       </c>
       <c r="R173" t="n">
-        <v>6937694</v>
+        <v>6937594</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121185408</v>
+        <v>121185404</v>
       </c>
       <c r="B174" t="n">
-        <v>90983</v>
+        <v>91149</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18357,25 +18357,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527661</v>
+        <v>527659</v>
       </c>
       <c r="R174" t="n">
-        <v>6937695</v>
+        <v>6937698</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121180230</v>
+        <v>121182248</v>
       </c>
       <c r="B6" t="n">
-        <v>105199</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,38 +1167,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527509</v>
+        <v>527008</v>
       </c>
       <c r="R6" t="n">
-        <v>6937756</v>
+        <v>6938092</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185419</v>
+        <v>121185403</v>
       </c>
       <c r="B7" t="n">
-        <v>79721</v>
+        <v>90657</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527001</v>
+        <v>527012</v>
       </c>
       <c r="R7" t="n">
-        <v>6938096</v>
+        <v>6938063</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185402</v>
+        <v>121185409</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527367</v>
+        <v>527108</v>
       </c>
       <c r="R8" t="n">
-        <v>6937938</v>
+        <v>6938086</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185409</v>
+        <v>121185398</v>
       </c>
       <c r="B9" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527108</v>
+        <v>526983</v>
       </c>
       <c r="R9" t="n">
-        <v>6938086</v>
+        <v>6938135</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185407</v>
+        <v>121185397</v>
       </c>
       <c r="B10" t="n">
-        <v>90995</v>
+        <v>90675</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527016</v>
+        <v>527043</v>
       </c>
       <c r="R10" t="n">
         <v>6938062</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185403</v>
+        <v>121185424</v>
       </c>
       <c r="B11" t="n">
-        <v>90656</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527012</v>
+        <v>527010</v>
       </c>
       <c r="R11" t="n">
-        <v>6938063</v>
+        <v>6938105</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185400</v>
+        <v>121185428</v>
       </c>
       <c r="B12" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527034</v>
+        <v>527439</v>
       </c>
       <c r="R12" t="n">
-        <v>6938099</v>
+        <v>6937974</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121183008</v>
+        <v>121185418</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,41 +1881,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526999</v>
+        <v>527437</v>
       </c>
       <c r="R13" t="n">
-        <v>6938157</v>
+        <v>6937974</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121180291</v>
+        <v>121185427</v>
       </c>
       <c r="B14" t="n">
-        <v>90727</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,37 +1987,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527492</v>
+        <v>527034</v>
       </c>
       <c r="R14" t="n">
-        <v>6937763</v>
+        <v>6938099</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185398</v>
+        <v>121185400</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>526983</v>
+        <v>527034</v>
       </c>
       <c r="R15" t="n">
-        <v>6938135</v>
+        <v>6938099</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185413</v>
+        <v>121180141</v>
       </c>
       <c r="B16" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,41 +2187,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527044</v>
+        <v>527597</v>
       </c>
       <c r="R16" t="n">
-        <v>6938065</v>
+        <v>6937703</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185429</v>
+        <v>121185422</v>
       </c>
       <c r="B17" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527641</v>
+        <v>526995</v>
       </c>
       <c r="R17" t="n">
-        <v>6937808</v>
+        <v>6938144</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185414</v>
+        <v>121185435</v>
       </c>
       <c r="B18" t="n">
-        <v>79685</v>
+        <v>91366</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527346</v>
+        <v>527008</v>
       </c>
       <c r="R18" t="n">
-        <v>6937925</v>
+        <v>6938073</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185432</v>
+        <v>121180291</v>
       </c>
       <c r="B19" t="n">
-        <v>91985</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,41 +2493,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527217</v>
+        <v>527492</v>
       </c>
       <c r="R19" t="n">
-        <v>6937854</v>
+        <v>6937763</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121180239</v>
+        <v>121185430</v>
       </c>
       <c r="B20" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,41 +2595,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527495</v>
+        <v>527460</v>
       </c>
       <c r="R20" t="n">
-        <v>6937765</v>
+        <v>6937819</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121179977</v>
+        <v>121185433</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>91986</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,41 +2697,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527626</v>
+        <v>527195</v>
       </c>
       <c r="R21" t="n">
-        <v>6937719</v>
+        <v>6937884</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185423</v>
+        <v>121185416</v>
       </c>
       <c r="B22" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>526974</v>
+        <v>527367</v>
       </c>
       <c r="R22" t="n">
-        <v>6938145</v>
+        <v>6937938</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185422</v>
+        <v>121185396</v>
       </c>
       <c r="B23" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,25 +2901,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>526995</v>
+        <v>526980</v>
       </c>
       <c r="R23" t="n">
-        <v>6938144</v>
+        <v>6938115</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185418</v>
+        <v>121185407</v>
       </c>
       <c r="B24" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527437</v>
+        <v>527016</v>
       </c>
       <c r="R24" t="n">
-        <v>6937974</v>
+        <v>6938062</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185395</v>
+        <v>121185405</v>
       </c>
       <c r="B25" t="n">
-        <v>95641</v>
+        <v>90996</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527048</v>
+        <v>527034</v>
       </c>
       <c r="R25" t="n">
-        <v>6938076</v>
+        <v>6938099</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185406</v>
+        <v>121185419</v>
       </c>
       <c r="B26" t="n">
-        <v>90995</v>
+        <v>79721</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,25 +3207,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527009</v>
+        <v>527001</v>
       </c>
       <c r="R26" t="n">
-        <v>6938044</v>
+        <v>6938096</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185411</v>
+        <v>121185401</v>
       </c>
       <c r="B27" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527045</v>
+        <v>527016</v>
       </c>
       <c r="R27" t="n">
-        <v>6938075</v>
+        <v>6938060</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185405</v>
+        <v>121185413</v>
       </c>
       <c r="B28" t="n">
-        <v>90995</v>
+        <v>79685</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,21 +3415,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527034</v>
+        <v>527044</v>
       </c>
       <c r="R28" t="n">
-        <v>6938099</v>
+        <v>6938065</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3501,7 +3501,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121185412</v>
+        <v>121185414</v>
       </c>
       <c r="B29" t="n">
         <v>79685</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527001</v>
+        <v>527346</v>
       </c>
       <c r="R29" t="n">
-        <v>6938101</v>
+        <v>6937925</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121183281</v>
+        <v>121183008</v>
       </c>
       <c r="B30" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526958</v>
+        <v>526999</v>
       </c>
       <c r="R30" t="n">
-        <v>6938109</v>
+        <v>6938157</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185415</v>
+        <v>121185399</v>
       </c>
       <c r="B31" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527391</v>
+        <v>526989</v>
       </c>
       <c r="R31" t="n">
-        <v>6937910</v>
+        <v>6938147</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185399</v>
+        <v>121185434</v>
       </c>
       <c r="B32" t="n">
-        <v>90709</v>
+        <v>91986</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,25 +3819,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>526989</v>
+        <v>526953</v>
       </c>
       <c r="R32" t="n">
-        <v>6938147</v>
+        <v>6938054</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121185424</v>
+        <v>121185432</v>
       </c>
       <c r="B33" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3921,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527010</v>
+        <v>527217</v>
       </c>
       <c r="R33" t="n">
-        <v>6938105</v>
+        <v>6937854</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185425</v>
+        <v>121185415</v>
       </c>
       <c r="B34" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527014</v>
+        <v>527391</v>
       </c>
       <c r="R34" t="n">
-        <v>6938062</v>
+        <v>6937910</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185421</v>
+        <v>121185429</v>
       </c>
       <c r="B35" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,25 +4125,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>526958</v>
+        <v>527641</v>
       </c>
       <c r="R35" t="n">
-        <v>6938116</v>
+        <v>6937808</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185426</v>
+        <v>121179977</v>
       </c>
       <c r="B36" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,41 +4227,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527503</v>
+        <v>527626</v>
       </c>
       <c r="R36" t="n">
-        <v>6937855</v>
+        <v>6937719</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121180141</v>
+        <v>121185423</v>
       </c>
       <c r="B37" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4353,17 +4353,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527597</v>
+        <v>526974</v>
       </c>
       <c r="R37" t="n">
-        <v>6937703</v>
+        <v>6938145</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121185434</v>
+        <v>121185421</v>
       </c>
       <c r="B38" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526953</v>
+        <v>526958</v>
       </c>
       <c r="R38" t="n">
-        <v>6938054</v>
+        <v>6938116</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121185431</v>
+        <v>121183281</v>
       </c>
       <c r="B39" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,41 +4533,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527439</v>
+        <v>526958</v>
       </c>
       <c r="R39" t="n">
-        <v>6937815</v>
+        <v>6938109</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121185416</v>
+        <v>121180261</v>
       </c>
       <c r="B40" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527367</v>
+        <v>527506</v>
       </c>
       <c r="R40" t="n">
-        <v>6937938</v>
+        <v>6937752</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185430</v>
+        <v>121185406</v>
       </c>
       <c r="B41" t="n">
-        <v>91985</v>
+        <v>90996</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,25 +4737,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527460</v>
+        <v>527009</v>
       </c>
       <c r="R41" t="n">
-        <v>6937819</v>
+        <v>6938044</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185433</v>
+        <v>121185431</v>
       </c>
       <c r="B42" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527195</v>
+        <v>527439</v>
       </c>
       <c r="R42" t="n">
-        <v>6937884</v>
+        <v>6937815</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121180712</v>
+        <v>121180239</v>
       </c>
       <c r="B43" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,25 +4941,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,13 +4969,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527305</v>
+        <v>527495</v>
       </c>
       <c r="R43" t="n">
-        <v>6937895</v>
+        <v>6937765</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185427</v>
+        <v>121180712</v>
       </c>
       <c r="B44" t="n">
         <v>78604</v>
@@ -5067,17 +5067,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527034</v>
+        <v>527305</v>
       </c>
       <c r="R44" t="n">
-        <v>6938099</v>
+        <v>6937895</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185397</v>
+        <v>121185410</v>
       </c>
       <c r="B45" t="n">
-        <v>90674</v>
+        <v>79685</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527043</v>
+        <v>527024</v>
       </c>
       <c r="R45" t="n">
-        <v>6938062</v>
+        <v>6938111</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121180261</v>
+        <v>121180230</v>
       </c>
       <c r="B46" t="n">
-        <v>98094</v>
+        <v>105200</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,25 +5247,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527506</v>
+        <v>527509</v>
       </c>
       <c r="R46" t="n">
-        <v>6937752</v>
+        <v>6937756</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>121179876</v>
       </c>
       <c r="B47" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185428</v>
+        <v>121185411</v>
       </c>
       <c r="B48" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527439</v>
+        <v>527045</v>
       </c>
       <c r="R48" t="n">
-        <v>6937974</v>
+        <v>6938075</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185396</v>
+        <v>121185402</v>
       </c>
       <c r="B49" t="n">
-        <v>90674</v>
+        <v>79714</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>526980</v>
+        <v>527367</v>
       </c>
       <c r="R49" t="n">
-        <v>6938115</v>
+        <v>6937938</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121185417</v>
+        <v>121185412</v>
       </c>
       <c r="B50" t="n">
         <v>79685</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527368</v>
+        <v>527001</v>
       </c>
       <c r="R50" t="n">
-        <v>6937959</v>
+        <v>6938101</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185401</v>
+        <v>121185426</v>
       </c>
       <c r="B51" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5757,25 +5757,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527016</v>
+        <v>527503</v>
       </c>
       <c r="R51" t="n">
-        <v>6938060</v>
+        <v>6937855</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185410</v>
+        <v>121185425</v>
       </c>
       <c r="B52" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527024</v>
+        <v>527014</v>
       </c>
       <c r="R52" t="n">
-        <v>6938111</v>
+        <v>6938062</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121182248</v>
+        <v>121185395</v>
       </c>
       <c r="B53" t="n">
-        <v>98094</v>
+        <v>95642</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527008</v>
+        <v>527048</v>
       </c>
       <c r="R53" t="n">
-        <v>6938092</v>
+        <v>6938076</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185435</v>
+        <v>121185417</v>
       </c>
       <c r="B54" t="n">
-        <v>91365</v>
+        <v>79685</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,25 +6063,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527008</v>
+        <v>527368</v>
       </c>
       <c r="R54" t="n">
-        <v>6938073</v>
+        <v>6937959</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212724</v>
+        <v>121212761</v>
       </c>
       <c r="B55" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527109</v>
+        <v>526852</v>
       </c>
       <c r="R55" t="n">
-        <v>6938336</v>
+        <v>6938391</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212717</v>
+        <v>121212769</v>
       </c>
       <c r="B56" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527023</v>
+        <v>527263</v>
       </c>
       <c r="R56" t="n">
-        <v>6938359</v>
+        <v>6938242</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212712</v>
+        <v>121212753</v>
       </c>
       <c r="B57" t="n">
-        <v>79685</v>
+        <v>78340</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526743</v>
+        <v>526856</v>
       </c>
       <c r="R57" t="n">
-        <v>6938415</v>
+        <v>6938391</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212764</v>
+        <v>121212739</v>
       </c>
       <c r="B58" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>526945</v>
+        <v>527304</v>
       </c>
       <c r="R58" t="n">
-        <v>6938389</v>
+        <v>6938173</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212757</v>
+        <v>121212772</v>
       </c>
       <c r="B59" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526927</v>
+        <v>526971</v>
       </c>
       <c r="R59" t="n">
-        <v>6938376</v>
+        <v>6938369</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6637,6 +6637,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6663,10 +6668,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212688</v>
+        <v>121212763</v>
       </c>
       <c r="B60" t="n">
-        <v>95641</v>
+        <v>98095</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6675,25 +6680,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6703,10 +6708,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527409</v>
+        <v>526911</v>
       </c>
       <c r="R60" t="n">
-        <v>6938091</v>
+        <v>6938360</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,7 +6770,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212733</v>
+        <v>121212724</v>
       </c>
       <c r="B61" t="n">
         <v>79685</v>
@@ -6805,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527186</v>
+        <v>527109</v>
       </c>
       <c r="R61" t="n">
-        <v>6938273</v>
+        <v>6938336</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212745</v>
+        <v>121212717</v>
       </c>
       <c r="B62" t="n">
-        <v>79721</v>
+        <v>79685</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6879,25 +6884,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526960</v>
+        <v>527023</v>
       </c>
       <c r="R62" t="n">
-        <v>6938390</v>
+        <v>6938359</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6969,10 +6974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212728</v>
+        <v>121212773</v>
       </c>
       <c r="B63" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,21 +6990,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527148</v>
+        <v>526989</v>
       </c>
       <c r="R63" t="n">
-        <v>6938301</v>
+        <v>6938371</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7045,6 +7050,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7071,10 +7081,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212735</v>
+        <v>121212760</v>
       </c>
       <c r="B64" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7083,25 +7093,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7111,10 +7121,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527245</v>
+        <v>526842</v>
       </c>
       <c r="R64" t="n">
-        <v>6938291</v>
+        <v>6938396</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7173,10 +7183,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212752</v>
+        <v>121212708</v>
       </c>
       <c r="B65" t="n">
-        <v>78340</v>
+        <v>97049</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7185,25 +7195,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7223,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526804</v>
+        <v>527252</v>
       </c>
       <c r="R65" t="n">
-        <v>6938398</v>
+        <v>6938285</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7275,10 +7285,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212708</v>
+        <v>121212725</v>
       </c>
       <c r="B66" t="n">
-        <v>97048</v>
+        <v>79685</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7287,25 +7297,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7315,10 +7325,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527252</v>
+        <v>527111</v>
       </c>
       <c r="R66" t="n">
-        <v>6938285</v>
+        <v>6938327</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7377,10 +7387,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212765</v>
+        <v>121212689</v>
       </c>
       <c r="B67" t="n">
-        <v>98094</v>
+        <v>79222</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7389,25 +7399,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7427,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526955</v>
+        <v>526855</v>
       </c>
       <c r="R67" t="n">
-        <v>6938367</v>
+        <v>6938391</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7479,10 +7489,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212701</v>
+        <v>121212727</v>
       </c>
       <c r="B68" t="n">
-        <v>90995</v>
+        <v>79685</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7495,21 +7505,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7519,10 +7529,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526960</v>
+        <v>527148</v>
       </c>
       <c r="R68" t="n">
-        <v>6938387</v>
+        <v>6938301</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7581,10 +7591,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212698</v>
+        <v>121212722</v>
       </c>
       <c r="B69" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7597,21 +7607,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7621,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527211</v>
+        <v>527075</v>
       </c>
       <c r="R69" t="n">
-        <v>6938302</v>
+        <v>6938349</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7683,7 +7693,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212720</v>
+        <v>121212735</v>
       </c>
       <c r="B70" t="n">
         <v>79685</v>
@@ -7723,10 +7733,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527051</v>
+        <v>527245</v>
       </c>
       <c r="R70" t="n">
-        <v>6938362</v>
+        <v>6938291</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7785,10 +7795,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212753</v>
+        <v>121212774</v>
       </c>
       <c r="B71" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7801,21 +7811,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7835,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526856</v>
+        <v>526840</v>
       </c>
       <c r="R71" t="n">
-        <v>6938391</v>
+        <v>6938383</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7887,10 +7897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212723</v>
+        <v>121212758</v>
       </c>
       <c r="B72" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7899,25 +7909,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7927,10 +7937,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527088</v>
+        <v>526823</v>
       </c>
       <c r="R72" t="n">
-        <v>6938358</v>
+        <v>6938405</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7989,10 +7999,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212718</v>
+        <v>121212696</v>
       </c>
       <c r="B73" t="n">
-        <v>79685</v>
+        <v>79714</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8001,25 +8011,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8029,10 +8039,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527038</v>
+        <v>527288</v>
       </c>
       <c r="R73" t="n">
-        <v>6938372</v>
+        <v>6938221</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8091,10 +8101,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212725</v>
+        <v>121212759</v>
       </c>
       <c r="B74" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8103,25 +8113,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8131,10 +8141,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527111</v>
+        <v>526838</v>
       </c>
       <c r="R74" t="n">
-        <v>6938327</v>
+        <v>6938397</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8193,10 +8203,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212696</v>
+        <v>121212737</v>
       </c>
       <c r="B75" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8205,25 +8215,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8233,10 +8243,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527288</v>
+        <v>527248</v>
       </c>
       <c r="R75" t="n">
-        <v>6938221</v>
+        <v>6938256</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8295,10 +8305,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212750</v>
+        <v>121212716</v>
       </c>
       <c r="B76" t="n">
-        <v>80561</v>
+        <v>79685</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8311,21 +8321,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8335,10 +8345,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>526756</v>
+        <v>526994</v>
       </c>
       <c r="R76" t="n">
-        <v>6938437</v>
+        <v>6938374</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8397,7 +8407,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212739</v>
+        <v>121212740</v>
       </c>
       <c r="B77" t="n">
         <v>79685</v>
@@ -8437,10 +8447,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>527304</v>
+        <v>527350</v>
       </c>
       <c r="R77" t="n">
-        <v>6938173</v>
+        <v>6938133</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8499,10 +8509,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212775</v>
+        <v>121212736</v>
       </c>
       <c r="B78" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8515,21 +8525,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8539,10 +8549,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527023</v>
+        <v>527250</v>
       </c>
       <c r="R78" t="n">
-        <v>6938359</v>
+        <v>6938289</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8601,10 +8611,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212694</v>
+        <v>121212715</v>
       </c>
       <c r="B79" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8613,25 +8623,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8641,10 +8651,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527088</v>
+        <v>526971</v>
       </c>
       <c r="R79" t="n">
-        <v>6938356</v>
+        <v>6938369</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8703,10 +8713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212730</v>
+        <v>121212699</v>
       </c>
       <c r="B80" t="n">
-        <v>79685</v>
+        <v>79589</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8715,25 +8725,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8743,10 +8753,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527177</v>
+        <v>527249</v>
       </c>
       <c r="R80" t="n">
-        <v>6938273</v>
+        <v>6938289</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8805,7 +8815,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212729</v>
+        <v>121212712</v>
       </c>
       <c r="B81" t="n">
         <v>79685</v>
@@ -8845,10 +8855,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527168</v>
+        <v>526743</v>
       </c>
       <c r="R81" t="n">
-        <v>6938291</v>
+        <v>6938415</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8907,10 +8917,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212774</v>
+        <v>121212695</v>
       </c>
       <c r="B82" t="n">
-        <v>78604</v>
+        <v>79714</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8919,25 +8929,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8947,10 +8957,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>526840</v>
+        <v>527184</v>
       </c>
       <c r="R82" t="n">
-        <v>6938383</v>
+        <v>6938280</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9009,10 +9019,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212772</v>
+        <v>121212718</v>
       </c>
       <c r="B83" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9025,21 +9035,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9049,10 +9059,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526971</v>
+        <v>527038</v>
       </c>
       <c r="R83" t="n">
-        <v>6938369</v>
+        <v>6938372</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9085,11 +9095,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9116,10 +9121,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212756</v>
+        <v>121212714</v>
       </c>
       <c r="B84" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9128,25 +9133,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9156,10 +9161,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527255</v>
+        <v>526955</v>
       </c>
       <c r="R84" t="n">
-        <v>6938220</v>
+        <v>6938368</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9192,11 +9197,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9223,10 +9223,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212758</v>
+        <v>121212732</v>
       </c>
       <c r="B85" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9235,25 +9235,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526823</v>
+        <v>527184</v>
       </c>
       <c r="R85" t="n">
-        <v>6938405</v>
+        <v>6938280</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9325,10 +9325,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212751</v>
+        <v>121212703</v>
       </c>
       <c r="B86" t="n">
-        <v>78340</v>
+        <v>90996</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9341,21 +9341,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>526755</v>
+        <v>527253</v>
       </c>
       <c r="R86" t="n">
-        <v>6938374</v>
+        <v>6938232</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9427,10 +9427,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212703</v>
+        <v>121212701</v>
       </c>
       <c r="B87" t="n">
-        <v>90995</v>
+        <v>90996</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527253</v>
+        <v>526960</v>
       </c>
       <c r="R87" t="n">
-        <v>6938232</v>
+        <v>6938387</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9631,10 +9631,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212731</v>
+        <v>121212762</v>
       </c>
       <c r="B89" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9643,25 +9643,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527184</v>
+        <v>526868</v>
       </c>
       <c r="R89" t="n">
-        <v>6938280</v>
+        <v>6938367</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9733,7 +9733,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212740</v>
+        <v>121212723</v>
       </c>
       <c r="B90" t="n">
         <v>79685</v>
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527350</v>
+        <v>527088</v>
       </c>
       <c r="R90" t="n">
-        <v>6938133</v>
+        <v>6938358</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9835,10 +9835,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212692</v>
+        <v>121212756</v>
       </c>
       <c r="B91" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9847,25 +9847,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527210</v>
+        <v>527255</v>
       </c>
       <c r="R91" t="n">
-        <v>6938291</v>
+        <v>6938220</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>1 adult</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9942,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212773</v>
+        <v>121212730</v>
       </c>
       <c r="B92" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9958,21 +9958,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>526989</v>
+        <v>527177</v>
       </c>
       <c r="R92" t="n">
-        <v>6938371</v>
+        <v>6938273</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10018,11 +10018,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10049,7 +10044,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212710</v>
+        <v>121212713</v>
       </c>
       <c r="B93" t="n">
         <v>79685</v>
@@ -10089,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527495</v>
+        <v>526960</v>
       </c>
       <c r="R93" t="n">
-        <v>6938009</v>
+        <v>6938390</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10125,11 +10120,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10156,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212714</v>
+        <v>121212697</v>
       </c>
       <c r="B94" t="n">
-        <v>79685</v>
+        <v>79686</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10172,21 +10162,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10196,10 +10186,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526955</v>
+        <v>527186</v>
       </c>
       <c r="R94" t="n">
-        <v>6938368</v>
+        <v>6938273</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10258,7 +10248,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212722</v>
+        <v>121212711</v>
       </c>
       <c r="B95" t="n">
         <v>79685</v>
@@ -10298,7 +10288,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527075</v>
+        <v>527051</v>
       </c>
       <c r="R95" t="n">
         <v>6938349</v>
@@ -10360,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212721</v>
+        <v>121212698</v>
       </c>
       <c r="B96" t="n">
-        <v>79685</v>
+        <v>79686</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10376,21 +10366,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10400,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>527074</v>
+        <v>527211</v>
       </c>
       <c r="R96" t="n">
-        <v>6938353</v>
+        <v>6938302</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10462,7 +10452,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212713</v>
+        <v>121212729</v>
       </c>
       <c r="B97" t="n">
         <v>79685</v>
@@ -10502,10 +10492,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>526960</v>
+        <v>527168</v>
       </c>
       <c r="R97" t="n">
-        <v>6938390</v>
+        <v>6938291</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10564,10 +10554,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212705</v>
+        <v>121212746</v>
       </c>
       <c r="B98" t="n">
-        <v>90995</v>
+        <v>79721</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10576,25 +10566,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10604,10 +10594,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527310</v>
+        <v>527088</v>
       </c>
       <c r="R98" t="n">
-        <v>6938160</v>
+        <v>6938356</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10666,10 +10656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212761</v>
+        <v>121212721</v>
       </c>
       <c r="B99" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10678,25 +10668,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10706,10 +10696,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>526852</v>
+        <v>527074</v>
       </c>
       <c r="R99" t="n">
-        <v>6938391</v>
+        <v>6938353</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10768,7 +10758,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212736</v>
+        <v>121212710</v>
       </c>
       <c r="B100" t="n">
         <v>79685</v>
@@ -10808,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527250</v>
+        <v>527495</v>
       </c>
       <c r="R100" t="n">
-        <v>6938289</v>
+        <v>6938009</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10844,6 +10834,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10870,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212690</v>
+        <v>121212752</v>
       </c>
       <c r="B101" t="n">
-        <v>90709</v>
+        <v>78340</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10886,21 +10881,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10910,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527263</v>
+        <v>526804</v>
       </c>
       <c r="R101" t="n">
-        <v>6938234</v>
+        <v>6938398</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10972,10 +10967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212746</v>
+        <v>121212720</v>
       </c>
       <c r="B102" t="n">
-        <v>79721</v>
+        <v>79685</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10984,25 +10979,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11012,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527088</v>
+        <v>527051</v>
       </c>
       <c r="R102" t="n">
-        <v>6938356</v>
+        <v>6938362</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11074,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212763</v>
+        <v>121212765</v>
       </c>
       <c r="B103" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526911</v>
+        <v>526955</v>
       </c>
       <c r="R103" t="n">
-        <v>6938360</v>
+        <v>6938367</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11176,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212709</v>
+        <v>121212688</v>
       </c>
       <c r="B104" t="n">
-        <v>78341</v>
+        <v>95642</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11192,21 +11187,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11216,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>526856</v>
+        <v>527409</v>
       </c>
       <c r="R104" t="n">
-        <v>6938391</v>
+        <v>6938091</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11278,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212760</v>
+        <v>121212744</v>
       </c>
       <c r="B105" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11290,25 +11285,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11318,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>526842</v>
+        <v>527495</v>
       </c>
       <c r="R105" t="n">
-        <v>6938396</v>
+        <v>6938012</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11380,10 +11375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212762</v>
+        <v>121212745</v>
       </c>
       <c r="B106" t="n">
-        <v>98094</v>
+        <v>79721</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11392,25 +11387,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11420,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>526868</v>
+        <v>526960</v>
       </c>
       <c r="R106" t="n">
-        <v>6938367</v>
+        <v>6938390</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11482,10 +11477,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212769</v>
+        <v>121212771</v>
       </c>
       <c r="B107" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11522,10 +11517,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527263</v>
+        <v>527317</v>
       </c>
       <c r="R107" t="n">
-        <v>6938242</v>
+        <v>6938165</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,10 +11579,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212771</v>
+        <v>121212757</v>
       </c>
       <c r="B108" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11624,10 +11619,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527317</v>
+        <v>526927</v>
       </c>
       <c r="R108" t="n">
-        <v>6938165</v>
+        <v>6938376</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,10 +11681,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212695</v>
+        <v>121212692</v>
       </c>
       <c r="B109" t="n">
-        <v>79714</v>
+        <v>57504</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11698,25 +11693,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11726,10 +11721,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>527184</v>
+        <v>527210</v>
       </c>
       <c r="R109" t="n">
-        <v>6938280</v>
+        <v>6938291</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11762,6 +11757,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11788,10 +11788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212738</v>
+        <v>121212709</v>
       </c>
       <c r="B110" t="n">
-        <v>79685</v>
+        <v>78341</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11804,21 +11804,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527288</v>
+        <v>526856</v>
       </c>
       <c r="R110" t="n">
-        <v>6938221</v>
+        <v>6938391</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212715</v>
+        <v>121212690</v>
       </c>
       <c r="B111" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11906,21 +11906,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>526971</v>
+        <v>527263</v>
       </c>
       <c r="R111" t="n">
-        <v>6938369</v>
+        <v>6938234</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212689</v>
+        <v>121212755</v>
       </c>
       <c r="B112" t="n">
-        <v>79222</v>
+        <v>78340</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12008,21 +12008,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>526855</v>
+        <v>526945</v>
       </c>
       <c r="R112" t="n">
-        <v>6938391</v>
+        <v>6938389</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212759</v>
+        <v>121212733</v>
       </c>
       <c r="B113" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12106,25 +12106,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>526838</v>
+        <v>527186</v>
       </c>
       <c r="R113" t="n">
-        <v>6938397</v>
+        <v>6938273</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212744</v>
+        <v>121212751</v>
       </c>
       <c r="B114" t="n">
-        <v>79685</v>
+        <v>78340</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12212,21 +12212,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527495</v>
+        <v>526755</v>
       </c>
       <c r="R114" t="n">
-        <v>6938012</v>
+        <v>6938374</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212716</v>
+        <v>121212764</v>
       </c>
       <c r="B115" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12310,25 +12310,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>526994</v>
+        <v>526945</v>
       </c>
       <c r="R115" t="n">
-        <v>6938374</v>
+        <v>6938389</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212711</v>
+        <v>121212705</v>
       </c>
       <c r="B116" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12416,21 +12416,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527051</v>
+        <v>527310</v>
       </c>
       <c r="R116" t="n">
-        <v>6938349</v>
+        <v>6938160</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212737</v>
+        <v>121212750</v>
       </c>
       <c r="B117" t="n">
-        <v>79685</v>
+        <v>80561</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12518,21 +12518,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527248</v>
+        <v>526756</v>
       </c>
       <c r="R117" t="n">
-        <v>6938256</v>
+        <v>6938437</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212755</v>
+        <v>121212775</v>
       </c>
       <c r="B118" t="n">
-        <v>78340</v>
+        <v>78604</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12620,21 +12620,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>526945</v>
+        <v>527023</v>
       </c>
       <c r="R118" t="n">
-        <v>6938389</v>
+        <v>6938359</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212699</v>
+        <v>121212694</v>
       </c>
       <c r="B119" t="n">
-        <v>79589</v>
+        <v>79714</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12722,21 +12722,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527249</v>
+        <v>527088</v>
       </c>
       <c r="R119" t="n">
-        <v>6938289</v>
+        <v>6938356</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212697</v>
+        <v>121212738</v>
       </c>
       <c r="B120" t="n">
-        <v>79686</v>
+        <v>79685</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12824,21 +12824,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527186</v>
+        <v>527288</v>
       </c>
       <c r="R120" t="n">
-        <v>6938273</v>
+        <v>6938221</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,7 +12910,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121226805</v>
+        <v>121226812</v>
       </c>
       <c r="B121" t="n">
         <v>79685</v>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526203</v>
+        <v>526551</v>
       </c>
       <c r="R121" t="n">
-        <v>6938195</v>
+        <v>6938312</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121220094</v>
+        <v>121226792</v>
       </c>
       <c r="B122" t="n">
-        <v>78340</v>
+        <v>90710</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,37 +13028,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526766</v>
+        <v>526796</v>
       </c>
       <c r="R122" t="n">
-        <v>6938100</v>
+        <v>6937966</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121226799</v>
+        <v>121226809</v>
       </c>
       <c r="B123" t="n">
         <v>79685</v>
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526747</v>
+        <v>526518</v>
       </c>
       <c r="R123" t="n">
-        <v>6937983</v>
+        <v>6938295</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226801</v>
+        <v>121226821</v>
       </c>
       <c r="B124" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13232,21 +13232,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526714</v>
+        <v>526199</v>
       </c>
       <c r="R124" t="n">
-        <v>6938008</v>
+        <v>6938254</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13292,6 +13292,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13318,10 +13323,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226796</v>
+        <v>121212789</v>
       </c>
       <c r="B125" t="n">
-        <v>90995</v>
+        <v>91986</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,25 +13335,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13358,10 +13363,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526796</v>
+        <v>526823</v>
       </c>
       <c r="R125" t="n">
-        <v>6937966</v>
+        <v>6938405</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13388,12 +13393,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13420,10 +13425,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226822</v>
+        <v>121226817</v>
       </c>
       <c r="B126" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,25 +13437,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13460,10 +13465,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526182</v>
+        <v>526581</v>
       </c>
       <c r="R126" t="n">
-        <v>6938234</v>
+        <v>6938053</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13522,10 +13527,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226815</v>
+        <v>121226806</v>
       </c>
       <c r="B127" t="n">
-        <v>78340</v>
+        <v>79685</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13538,21 +13543,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13562,10 +13567,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526527</v>
+        <v>526182</v>
       </c>
       <c r="R127" t="n">
-        <v>6938317</v>
+        <v>6938206</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13624,7 +13629,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226807</v>
+        <v>121226799</v>
       </c>
       <c r="B128" t="n">
         <v>79685</v>
@@ -13664,10 +13669,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526201</v>
+        <v>526747</v>
       </c>
       <c r="R128" t="n">
-        <v>6938252</v>
+        <v>6937983</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13726,10 +13731,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121212780</v>
+        <v>121226808</v>
       </c>
       <c r="B129" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13747,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13771,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>527567</v>
+        <v>526482</v>
       </c>
       <c r="R129" t="n">
-        <v>6937949</v>
+        <v>6938338</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13796,12 +13801,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13828,10 +13833,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121221064</v>
+        <v>121226801</v>
       </c>
       <c r="B130" t="n">
-        <v>90723</v>
+        <v>79685</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,37 +13849,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526664</v>
+        <v>526714</v>
       </c>
       <c r="R130" t="n">
-        <v>6938176</v>
+        <v>6938008</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13930,10 +13935,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226792</v>
+        <v>121226824</v>
       </c>
       <c r="B131" t="n">
-        <v>90709</v>
+        <v>91272</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13942,25 +13947,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526796</v>
+        <v>526747</v>
       </c>
       <c r="R131" t="n">
-        <v>6937966</v>
+        <v>6937983</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14032,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121226824</v>
+        <v>121220094</v>
       </c>
       <c r="B132" t="n">
-        <v>91271</v>
+        <v>78340</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14044,41 +14049,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526747</v>
+        <v>526766</v>
       </c>
       <c r="R132" t="n">
-        <v>6937983</v>
+        <v>6938100</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14134,7 +14139,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121222671</v>
+        <v>121212778</v>
       </c>
       <c r="B133" t="n">
         <v>78604</v>
@@ -14170,17 +14175,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526275</v>
+        <v>527288</v>
       </c>
       <c r="R133" t="n">
-        <v>6938199</v>
+        <v>6938221</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14204,17 +14209,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14241,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226821</v>
+        <v>121226793</v>
       </c>
       <c r="B134" t="n">
-        <v>78604</v>
+        <v>90730</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526199</v>
+        <v>526519</v>
       </c>
       <c r="R134" t="n">
-        <v>6938254</v>
+        <v>6938315</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14317,11 +14317,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14348,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226812</v>
+        <v>121226814</v>
       </c>
       <c r="B135" t="n">
-        <v>79685</v>
+        <v>78340</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14364,21 +14359,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14388,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526551</v>
+        <v>526515</v>
       </c>
       <c r="R135" t="n">
-        <v>6938312</v>
+        <v>6938303</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14450,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121212791</v>
+        <v>121226811</v>
       </c>
       <c r="B136" t="n">
-        <v>79720</v>
+        <v>79685</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14462,25 +14457,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14490,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>527094</v>
+        <v>526545</v>
       </c>
       <c r="R136" t="n">
-        <v>6938358</v>
+        <v>6938319</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14520,12 +14515,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14552,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226794</v>
+        <v>121212776</v>
       </c>
       <c r="B137" t="n">
-        <v>79714</v>
+        <v>78604</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14564,25 +14559,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14592,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526478</v>
+        <v>527090</v>
       </c>
       <c r="R137" t="n">
-        <v>6938348</v>
+        <v>6938365</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14622,12 +14617,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14654,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226817</v>
+        <v>121219658</v>
       </c>
       <c r="B138" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14666,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526581</v>
+        <v>526953</v>
       </c>
       <c r="R138" t="n">
-        <v>6938053</v>
+        <v>6937958</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14756,10 +14751,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226793</v>
+        <v>121226802</v>
       </c>
       <c r="B139" t="n">
-        <v>90729</v>
+        <v>79685</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14772,21 +14767,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14796,10 +14791,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526519</v>
+        <v>526716</v>
       </c>
       <c r="R139" t="n">
-        <v>6938315</v>
+        <v>6937997</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14858,10 +14853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226806</v>
+        <v>121212780</v>
       </c>
       <c r="B140" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14874,21 +14869,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14898,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526182</v>
+        <v>527567</v>
       </c>
       <c r="R140" t="n">
-        <v>6938206</v>
+        <v>6937949</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14928,12 +14923,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14960,10 +14955,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121221199</v>
+        <v>121226805</v>
       </c>
       <c r="B141" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14976,37 +14971,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526592</v>
+        <v>526203</v>
       </c>
       <c r="R141" t="n">
-        <v>6938232</v>
+        <v>6938195</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15062,10 +15057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121212778</v>
+        <v>121226818</v>
       </c>
       <c r="B142" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15074,25 +15069,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15102,10 +15097,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>527288</v>
+        <v>526525</v>
       </c>
       <c r="R142" t="n">
-        <v>6938221</v>
+        <v>6938312</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15132,12 +15127,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15167,7 +15162,7 @@
         <v>121226819</v>
       </c>
       <c r="B143" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15266,10 +15261,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121212789</v>
+        <v>121226813</v>
       </c>
       <c r="B144" t="n">
-        <v>91985</v>
+        <v>78340</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15278,25 +15273,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15306,10 +15301,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526823</v>
+        <v>526365</v>
       </c>
       <c r="R144" t="n">
-        <v>6938405</v>
+        <v>6938404</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15336,12 +15331,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15470,10 +15465,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121212783</v>
+        <v>121222671</v>
       </c>
       <c r="B146" t="n">
-        <v>78249</v>
+        <v>78604</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15486,37 +15481,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526761</v>
+        <v>526275</v>
       </c>
       <c r="R146" t="n">
-        <v>6938348</v>
+        <v>6938199</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15540,12 +15535,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15572,10 +15572,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226813</v>
+        <v>121221064</v>
       </c>
       <c r="B147" t="n">
-        <v>78340</v>
+        <v>90724</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15588,37 +15588,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526365</v>
+        <v>526664</v>
       </c>
       <c r="R147" t="n">
-        <v>6938404</v>
+        <v>6938176</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121220916</v>
+        <v>121226822</v>
       </c>
       <c r="B148" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15686,41 +15686,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526647</v>
+        <v>526182</v>
       </c>
       <c r="R148" t="n">
-        <v>6938174</v>
+        <v>6938234</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15776,10 +15776,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121212779</v>
+        <v>121226794</v>
       </c>
       <c r="B149" t="n">
-        <v>78604</v>
+        <v>79714</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15788,25 +15788,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15816,10 +15816,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>527495</v>
+        <v>526478</v>
       </c>
       <c r="R149" t="n">
-        <v>6938009</v>
+        <v>6938348</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15846,12 +15846,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15878,10 +15878,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226814</v>
+        <v>121226791</v>
       </c>
       <c r="B150" t="n">
-        <v>78340</v>
+        <v>89761</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15894,21 +15894,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15918,10 +15918,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526515</v>
+        <v>526205</v>
       </c>
       <c r="R150" t="n">
-        <v>6938303</v>
+        <v>6938282</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15980,10 +15980,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226809</v>
+        <v>121223305</v>
       </c>
       <c r="B151" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15992,41 +15992,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526518</v>
+        <v>526584</v>
       </c>
       <c r="R151" t="n">
-        <v>6938295</v>
+        <v>6938052</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226811</v>
+        <v>121226804</v>
       </c>
       <c r="B152" t="n">
         <v>79685</v>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526545</v>
+        <v>526224</v>
       </c>
       <c r="R152" t="n">
-        <v>6938319</v>
+        <v>6938191</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16184,10 +16184,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121223305</v>
+        <v>121226807</v>
       </c>
       <c r="B153" t="n">
-        <v>98094</v>
+        <v>79685</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16196,41 +16196,41 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526584</v>
+        <v>526201</v>
       </c>
       <c r="R153" t="n">
-        <v>6938052</v>
+        <v>6938252</v>
       </c>
       <c r="S153" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16286,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226791</v>
+        <v>121226797</v>
       </c>
       <c r="B154" t="n">
-        <v>89760</v>
+        <v>79685</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16302,21 +16302,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526205</v>
+        <v>526496</v>
       </c>
       <c r="R154" t="n">
-        <v>6938282</v>
+        <v>6938343</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16362,6 +16362,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16388,10 +16393,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226808</v>
+        <v>121226796</v>
       </c>
       <c r="B155" t="n">
-        <v>79685</v>
+        <v>90996</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16404,21 +16409,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16428,10 +16433,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526482</v>
+        <v>526796</v>
       </c>
       <c r="R155" t="n">
-        <v>6938338</v>
+        <v>6937966</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16490,10 +16495,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212785</v>
+        <v>121226820</v>
       </c>
       <c r="B156" t="n">
-        <v>78249</v>
+        <v>90724</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16506,21 +16511,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16535,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526753</v>
+        <v>526660</v>
       </c>
       <c r="R156" t="n">
-        <v>6938395</v>
+        <v>6938167</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16560,12 +16565,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16592,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226820</v>
+        <v>121226815</v>
       </c>
       <c r="B157" t="n">
-        <v>90723</v>
+        <v>78340</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16608,21 +16613,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16632,10 +16637,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526660</v>
+        <v>526527</v>
       </c>
       <c r="R157" t="n">
-        <v>6938167</v>
+        <v>6938317</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -16694,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121219658</v>
+        <v>121221199</v>
       </c>
       <c r="B158" t="n">
-        <v>90674</v>
+        <v>78604</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16706,25 +16711,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16734,10 +16739,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526953</v>
+        <v>526592</v>
       </c>
       <c r="R158" t="n">
-        <v>6937958</v>
+        <v>6938232</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16796,10 +16801,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226795</v>
+        <v>121219596</v>
       </c>
       <c r="B159" t="n">
-        <v>79686</v>
+        <v>78340</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16812,37 +16817,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526554</v>
+        <v>526982</v>
       </c>
       <c r="R159" t="n">
-        <v>6938311</v>
+        <v>6937928</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16898,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121212788</v>
+        <v>121226810</v>
       </c>
       <c r="B160" t="n">
-        <v>91985</v>
+        <v>79685</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16910,25 +16915,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16938,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526776</v>
+        <v>526533</v>
       </c>
       <c r="R160" t="n">
-        <v>6938419</v>
+        <v>6938315</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16968,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17000,10 +17005,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226802</v>
+        <v>121212779</v>
       </c>
       <c r="B161" t="n">
-        <v>79685</v>
+        <v>78604</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17016,21 +17021,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17040,10 +17045,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526716</v>
+        <v>527495</v>
       </c>
       <c r="R161" t="n">
-        <v>6937997</v>
+        <v>6938009</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17070,12 +17075,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17102,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121212776</v>
+        <v>121220916</v>
       </c>
       <c r="B162" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17114,41 +17119,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>527090</v>
+        <v>526647</v>
       </c>
       <c r="R162" t="n">
-        <v>6938365</v>
+        <v>6938174</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17172,12 +17177,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17204,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226816</v>
+        <v>121212785</v>
       </c>
       <c r="B163" t="n">
-        <v>98094</v>
+        <v>78249</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17216,25 +17221,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526789</v>
+        <v>526753</v>
       </c>
       <c r="R163" t="n">
-        <v>6937993</v>
+        <v>6938395</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17274,12 +17279,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17306,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226818</v>
+        <v>121212783</v>
       </c>
       <c r="B164" t="n">
-        <v>98094</v>
+        <v>78249</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17318,25 +17323,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17346,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526525</v>
+        <v>526761</v>
       </c>
       <c r="R164" t="n">
-        <v>6938312</v>
+        <v>6938348</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17376,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17408,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226804</v>
+        <v>121226795</v>
       </c>
       <c r="B165" t="n">
-        <v>79685</v>
+        <v>79686</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17424,21 +17429,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17448,10 +17453,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526224</v>
+        <v>526554</v>
       </c>
       <c r="R165" t="n">
-        <v>6938191</v>
+        <v>6938311</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17510,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226810</v>
+        <v>121212791</v>
       </c>
       <c r="B166" t="n">
-        <v>79685</v>
+        <v>79720</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17522,25 +17527,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17550,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526533</v>
+        <v>527094</v>
       </c>
       <c r="R166" t="n">
-        <v>6938315</v>
+        <v>6938358</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17580,12 +17585,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17612,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226797</v>
+        <v>121226816</v>
       </c>
       <c r="B167" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17624,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17652,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526496</v>
+        <v>526789</v>
       </c>
       <c r="R167" t="n">
-        <v>6938343</v>
+        <v>6937993</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17688,11 +17693,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121219596</v>
+        <v>121212788</v>
       </c>
       <c r="B168" t="n">
-        <v>78340</v>
+        <v>91986</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,41 +17731,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526982</v>
+        <v>526776</v>
       </c>
       <c r="R168" t="n">
-        <v>6937928</v>
+        <v>6938419</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17789,12 +17789,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17821,10 +17821,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121246286</v>
+        <v>121212693</v>
       </c>
       <c r="B169" t="n">
-        <v>92014</v>
+        <v>91990</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17837,24 +17837,27 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -17901,7 +17904,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Även smalfotad taggsvamp under samma låga</t>
+          <t>Tajgataggsvamp under samma tallåga</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17910,6 +17913,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17928,10 +17932,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121212693</v>
+        <v>121246286</v>
       </c>
       <c r="B170" t="n">
-        <v>91989</v>
+        <v>92015</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17944,27 +17948,24 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -18011,7 +18012,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp under samma tallåga</t>
+          <t>Även smalfotad taggsvamp under samma låga</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18020,7 +18021,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121185408</v>
+        <v>121179693</v>
       </c>
       <c r="B171" t="n">
-        <v>90995</v>
+        <v>91986</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527661</v>
+        <v>527779</v>
       </c>
       <c r="R171" t="n">
-        <v>6937695</v>
+        <v>6937594</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121179849</v>
+        <v>121185408</v>
       </c>
       <c r="B172" t="n">
-        <v>91149</v>
+        <v>90996</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527658</v>
+        <v>527661</v>
       </c>
       <c r="R172" t="n">
-        <v>6937694</v>
+        <v>6937695</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121179693</v>
+        <v>121185404</v>
       </c>
       <c r="B173" t="n">
-        <v>91985</v>
+        <v>91150</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18255,41 +18255,41 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>527779</v>
+        <v>527659</v>
       </c>
       <c r="R173" t="n">
-        <v>6937594</v>
+        <v>6937698</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121185404</v>
+        <v>121179849</v>
       </c>
       <c r="B174" t="n">
-        <v>91149</v>
+        <v>91150</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18381,17 +18381,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527659</v>
+        <v>527658</v>
       </c>
       <c r="R174" t="n">
-        <v>6937698</v>
+        <v>6937694</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121182248</v>
+        <v>121179876</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>90999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,38 +1167,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527008</v>
+        <v>527649</v>
       </c>
       <c r="R6" t="n">
-        <v>6938092</v>
+        <v>6937696</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185403</v>
+        <v>121185426</v>
       </c>
       <c r="B7" t="n">
-        <v>90657</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527012</v>
+        <v>527503</v>
       </c>
       <c r="R7" t="n">
-        <v>6938063</v>
+        <v>6937855</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185409</v>
+        <v>121185418</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527108</v>
+        <v>527437</v>
       </c>
       <c r="R8" t="n">
-        <v>6938086</v>
+        <v>6937974</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185398</v>
+        <v>121185410</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526983</v>
+        <v>527024</v>
       </c>
       <c r="R9" t="n">
-        <v>6938135</v>
+        <v>6938111</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185397</v>
+        <v>121185411</v>
       </c>
       <c r="B10" t="n">
-        <v>90675</v>
+        <v>79688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527043</v>
+        <v>527045</v>
       </c>
       <c r="R10" t="n">
-        <v>6938062</v>
+        <v>6938075</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185424</v>
+        <v>121180291</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,41 +1677,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527010</v>
+        <v>527492</v>
       </c>
       <c r="R11" t="n">
-        <v>6938105</v>
+        <v>6937763</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185428</v>
+        <v>121185397</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>90678</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527439</v>
+        <v>527043</v>
       </c>
       <c r="R12" t="n">
-        <v>6937974</v>
+        <v>6938062</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185418</v>
+        <v>121185400</v>
       </c>
       <c r="B13" t="n">
-        <v>79685</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527437</v>
+        <v>527034</v>
       </c>
       <c r="R13" t="n">
-        <v>6937974</v>
+        <v>6938099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185427</v>
+        <v>121185433</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>91989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527034</v>
+        <v>527195</v>
       </c>
       <c r="R14" t="n">
-        <v>6938099</v>
+        <v>6937884</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185400</v>
+        <v>121185412</v>
       </c>
       <c r="B15" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,21 +2089,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527034</v>
+        <v>527001</v>
       </c>
       <c r="R15" t="n">
-        <v>6938099</v>
+        <v>6938101</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121180141</v>
+        <v>121185424</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,17 +2211,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527597</v>
+        <v>527010</v>
       </c>
       <c r="R16" t="n">
-        <v>6937703</v>
+        <v>6938105</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185422</v>
+        <v>121185425</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>526995</v>
+        <v>527014</v>
       </c>
       <c r="R17" t="n">
-        <v>6938144</v>
+        <v>6938062</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185435</v>
+        <v>121185407</v>
       </c>
       <c r="B18" t="n">
-        <v>91366</v>
+        <v>90999</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527008</v>
+        <v>527016</v>
       </c>
       <c r="R18" t="n">
-        <v>6938073</v>
+        <v>6938062</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121180291</v>
+        <v>121185434</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>91989</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,41 +2493,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>527492</v>
+        <v>526953</v>
       </c>
       <c r="R19" t="n">
-        <v>6937763</v>
+        <v>6938054</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121185430</v>
+        <v>121183281</v>
       </c>
       <c r="B20" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,41 +2595,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527460</v>
+        <v>526958</v>
       </c>
       <c r="R20" t="n">
-        <v>6937819</v>
+        <v>6938109</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185433</v>
+        <v>121185422</v>
       </c>
       <c r="B21" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,25 +2697,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527195</v>
+        <v>526995</v>
       </c>
       <c r="R21" t="n">
-        <v>6937884</v>
+        <v>6938144</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185416</v>
+        <v>121185409</v>
       </c>
       <c r="B22" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527367</v>
+        <v>527108</v>
       </c>
       <c r="R22" t="n">
-        <v>6937938</v>
+        <v>6938086</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2892,7 +2892,7 @@
         <v>121185396</v>
       </c>
       <c r="B23" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185407</v>
+        <v>121185430</v>
       </c>
       <c r="B24" t="n">
-        <v>90996</v>
+        <v>91989</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527016</v>
+        <v>527460</v>
       </c>
       <c r="R24" t="n">
-        <v>6938062</v>
+        <v>6937819</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185405</v>
+        <v>121180261</v>
       </c>
       <c r="B25" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,41 +3105,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527034</v>
+        <v>527506</v>
       </c>
       <c r="R25" t="n">
-        <v>6938099</v>
+        <v>6937752</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185419</v>
+        <v>121185428</v>
       </c>
       <c r="B26" t="n">
-        <v>79721</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,25 +3207,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527001</v>
+        <v>527439</v>
       </c>
       <c r="R26" t="n">
-        <v>6938096</v>
+        <v>6937974</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185401</v>
+        <v>121179977</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,37 +3313,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527016</v>
+        <v>527626</v>
       </c>
       <c r="R27" t="n">
-        <v>6938060</v>
+        <v>6937719</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121185413</v>
+        <v>121180230</v>
       </c>
       <c r="B28" t="n">
-        <v>79685</v>
+        <v>105203</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,41 +3411,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527044</v>
+        <v>527509</v>
       </c>
       <c r="R28" t="n">
-        <v>6938065</v>
+        <v>6937756</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121185414</v>
+        <v>121185431</v>
       </c>
       <c r="B29" t="n">
-        <v>79685</v>
+        <v>91989</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,25 +3513,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527346</v>
+        <v>527439</v>
       </c>
       <c r="R29" t="n">
-        <v>6937925</v>
+        <v>6937815</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121183008</v>
+        <v>121185403</v>
       </c>
       <c r="B30" t="n">
-        <v>98095</v>
+        <v>90660</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,41 +3615,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>526999</v>
+        <v>527012</v>
       </c>
       <c r="R30" t="n">
-        <v>6938157</v>
+        <v>6938063</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185399</v>
+        <v>121185406</v>
       </c>
       <c r="B31" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>526989</v>
+        <v>527009</v>
       </c>
       <c r="R31" t="n">
-        <v>6938147</v>
+        <v>6938044</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185434</v>
+        <v>121185405</v>
       </c>
       <c r="B32" t="n">
-        <v>91986</v>
+        <v>90999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,25 +3819,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>526953</v>
+        <v>527034</v>
       </c>
       <c r="R32" t="n">
-        <v>6938054</v>
+        <v>6938099</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121185432</v>
+        <v>121185395</v>
       </c>
       <c r="B33" t="n">
-        <v>91986</v>
+        <v>95645</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3921,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527217</v>
+        <v>527048</v>
       </c>
       <c r="R33" t="n">
-        <v>6937854</v>
+        <v>6938076</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185415</v>
+        <v>121185416</v>
       </c>
       <c r="B34" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527391</v>
+        <v>527367</v>
       </c>
       <c r="R34" t="n">
-        <v>6937910</v>
+        <v>6937938</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185429</v>
+        <v>121180141</v>
       </c>
       <c r="B35" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,41 +4125,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527641</v>
+        <v>527597</v>
       </c>
       <c r="R35" t="n">
-        <v>6937808</v>
+        <v>6937703</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121179977</v>
+        <v>121185432</v>
       </c>
       <c r="B36" t="n">
-        <v>78604</v>
+        <v>91989</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,41 +4227,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527626</v>
+        <v>527217</v>
       </c>
       <c r="R36" t="n">
-        <v>6937719</v>
+        <v>6937854</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121185423</v>
+        <v>121180239</v>
       </c>
       <c r="B37" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4353,17 +4353,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526974</v>
+        <v>527495</v>
       </c>
       <c r="R37" t="n">
-        <v>6938145</v>
+        <v>6937765</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121185421</v>
+        <v>121183008</v>
       </c>
       <c r="B38" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4455,17 +4455,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526958</v>
+        <v>526999</v>
       </c>
       <c r="R38" t="n">
-        <v>6938116</v>
+        <v>6938157</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121183281</v>
+        <v>121185417</v>
       </c>
       <c r="B39" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,41 +4533,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526958</v>
+        <v>527368</v>
       </c>
       <c r="R39" t="n">
-        <v>6938109</v>
+        <v>6937959</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121180261</v>
+        <v>121185429</v>
       </c>
       <c r="B40" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527506</v>
+        <v>527641</v>
       </c>
       <c r="R40" t="n">
-        <v>6937752</v>
+        <v>6937808</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185406</v>
+        <v>121185398</v>
       </c>
       <c r="B41" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4741,21 +4741,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527009</v>
+        <v>526983</v>
       </c>
       <c r="R41" t="n">
-        <v>6938044</v>
+        <v>6938135</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185431</v>
+        <v>121185399</v>
       </c>
       <c r="B42" t="n">
-        <v>91986</v>
+        <v>90713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4839,25 +4839,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527439</v>
+        <v>526989</v>
       </c>
       <c r="R42" t="n">
-        <v>6937815</v>
+        <v>6938147</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121180239</v>
+        <v>121185413</v>
       </c>
       <c r="B43" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,41 +4941,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527495</v>
+        <v>527044</v>
       </c>
       <c r="R43" t="n">
-        <v>6937765</v>
+        <v>6938065</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121180712</v>
+        <v>121185402</v>
       </c>
       <c r="B44" t="n">
-        <v>78604</v>
+        <v>79717</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527305</v>
+        <v>527367</v>
       </c>
       <c r="R44" t="n">
-        <v>6937895</v>
+        <v>6937938</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185410</v>
+        <v>121185421</v>
       </c>
       <c r="B45" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>527024</v>
+        <v>526958</v>
       </c>
       <c r="R45" t="n">
-        <v>6938111</v>
+        <v>6938116</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121180230</v>
+        <v>121185423</v>
       </c>
       <c r="B46" t="n">
-        <v>105200</v>
+        <v>98098</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,41 +5247,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527509</v>
+        <v>526974</v>
       </c>
       <c r="R46" t="n">
-        <v>6937756</v>
+        <v>6938145</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121179876</v>
+        <v>121185401</v>
       </c>
       <c r="B47" t="n">
-        <v>90996</v>
+        <v>90713</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,37 +5353,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527649</v>
+        <v>527016</v>
       </c>
       <c r="R47" t="n">
-        <v>6937696</v>
+        <v>6938060</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185411</v>
+        <v>121180712</v>
       </c>
       <c r="B48" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,37 +5455,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527045</v>
+        <v>527305</v>
       </c>
       <c r="R48" t="n">
-        <v>6938075</v>
+        <v>6937895</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185402</v>
+        <v>121185419</v>
       </c>
       <c r="B49" t="n">
-        <v>79714</v>
+        <v>79724</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527367</v>
+        <v>527001</v>
       </c>
       <c r="R49" t="n">
-        <v>6937938</v>
+        <v>6938096</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121185412</v>
+        <v>121185435</v>
       </c>
       <c r="B50" t="n">
-        <v>79685</v>
+        <v>91369</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,25 +5655,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527001</v>
+        <v>527008</v>
       </c>
       <c r="R50" t="n">
-        <v>6938101</v>
+        <v>6938073</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185426</v>
+        <v>121185414</v>
       </c>
       <c r="B51" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5757,25 +5757,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527503</v>
+        <v>527346</v>
       </c>
       <c r="R51" t="n">
-        <v>6937855</v>
+        <v>6937925</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185425</v>
+        <v>121185427</v>
       </c>
       <c r="B52" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527014</v>
+        <v>527034</v>
       </c>
       <c r="R52" t="n">
-        <v>6938062</v>
+        <v>6938099</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121185395</v>
+        <v>121185415</v>
       </c>
       <c r="B53" t="n">
-        <v>95642</v>
+        <v>79688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,21 +5965,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5989,10 +5989,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527048</v>
+        <v>527391</v>
       </c>
       <c r="R53" t="n">
-        <v>6938076</v>
+        <v>6937910</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185417</v>
+        <v>121182248</v>
       </c>
       <c r="B54" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,41 +6063,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527368</v>
+        <v>527008</v>
       </c>
       <c r="R54" t="n">
-        <v>6937959</v>
+        <v>6938092</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212761</v>
+        <v>121212740</v>
       </c>
       <c r="B55" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526852</v>
+        <v>527350</v>
       </c>
       <c r="R55" t="n">
-        <v>6938391</v>
+        <v>6938133</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212769</v>
+        <v>121212758</v>
       </c>
       <c r="B56" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527263</v>
+        <v>526823</v>
       </c>
       <c r="R56" t="n">
-        <v>6938242</v>
+        <v>6938405</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212753</v>
+        <v>121212709</v>
       </c>
       <c r="B57" t="n">
-        <v>78340</v>
+        <v>78344</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212739</v>
+        <v>121212771</v>
       </c>
       <c r="B58" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527304</v>
+        <v>527317</v>
       </c>
       <c r="R58" t="n">
-        <v>6938173</v>
+        <v>6938165</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212772</v>
+        <v>121212752</v>
       </c>
       <c r="B59" t="n">
-        <v>78604</v>
+        <v>78343</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6577,21 +6577,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526971</v>
+        <v>526804</v>
       </c>
       <c r="R59" t="n">
-        <v>6938369</v>
+        <v>6938398</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6637,11 +6637,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6668,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212763</v>
+        <v>121212719</v>
       </c>
       <c r="B60" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6680,25 +6675,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6708,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526911</v>
+        <v>527051</v>
       </c>
       <c r="R60" t="n">
-        <v>6938360</v>
+        <v>6938362</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6770,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212724</v>
+        <v>121212711</v>
       </c>
       <c r="B61" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6810,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527109</v>
+        <v>527051</v>
       </c>
       <c r="R61" t="n">
-        <v>6938336</v>
+        <v>6938349</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6872,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212717</v>
+        <v>121212751</v>
       </c>
       <c r="B62" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6888,21 +6883,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527023</v>
+        <v>526755</v>
       </c>
       <c r="R62" t="n">
-        <v>6938359</v>
+        <v>6938374</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6974,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212773</v>
+        <v>121212724</v>
       </c>
       <c r="B63" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6990,21 +6985,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>526989</v>
+        <v>527109</v>
       </c>
       <c r="R63" t="n">
-        <v>6938371</v>
+        <v>6938336</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7050,11 +7045,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7081,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212760</v>
+        <v>121212712</v>
       </c>
       <c r="B64" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7093,25 +7083,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7121,10 +7111,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526842</v>
+        <v>526743</v>
       </c>
       <c r="R64" t="n">
-        <v>6938396</v>
+        <v>6938415</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7183,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212708</v>
+        <v>121212750</v>
       </c>
       <c r="B65" t="n">
-        <v>97049</v>
+        <v>80564</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7195,25 +7185,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7223,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527252</v>
+        <v>526756</v>
       </c>
       <c r="R65" t="n">
-        <v>6938285</v>
+        <v>6938437</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7285,10 +7275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212725</v>
+        <v>121212698</v>
       </c>
       <c r="B66" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7301,21 +7291,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7325,10 +7315,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527111</v>
+        <v>527211</v>
       </c>
       <c r="R66" t="n">
-        <v>6938327</v>
+        <v>6938302</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7387,10 +7377,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212689</v>
+        <v>121212730</v>
       </c>
       <c r="B67" t="n">
-        <v>79222</v>
+        <v>79688</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7403,21 +7393,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7427,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526855</v>
+        <v>527177</v>
       </c>
       <c r="R67" t="n">
-        <v>6938391</v>
+        <v>6938273</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7492,7 +7482,7 @@
         <v>121212727</v>
       </c>
       <c r="B68" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7591,10 +7581,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212722</v>
+        <v>121212688</v>
       </c>
       <c r="B69" t="n">
-        <v>79685</v>
+        <v>95645</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7607,21 +7597,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7621,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527075</v>
+        <v>527409</v>
       </c>
       <c r="R69" t="n">
-        <v>6938349</v>
+        <v>6938091</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7693,10 +7683,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212735</v>
+        <v>121212774</v>
       </c>
       <c r="B70" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7709,21 +7699,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7733,10 +7723,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527245</v>
+        <v>526840</v>
       </c>
       <c r="R70" t="n">
-        <v>6938291</v>
+        <v>6938383</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7795,10 +7785,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212774</v>
+        <v>121212710</v>
       </c>
       <c r="B71" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7811,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7835,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526840</v>
+        <v>527495</v>
       </c>
       <c r="R71" t="n">
-        <v>6938383</v>
+        <v>6938009</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7871,6 +7861,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7897,10 +7892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212758</v>
+        <v>121212717</v>
       </c>
       <c r="B72" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7909,25 +7904,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7937,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526823</v>
+        <v>527023</v>
       </c>
       <c r="R72" t="n">
-        <v>6938405</v>
+        <v>6938359</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7999,10 +7994,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212696</v>
+        <v>121212692</v>
       </c>
       <c r="B73" t="n">
-        <v>79714</v>
+        <v>57507</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8011,25 +8006,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8039,10 +8034,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527288</v>
+        <v>527210</v>
       </c>
       <c r="R73" t="n">
-        <v>6938221</v>
+        <v>6938291</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8075,6 +8070,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8101,10 +8101,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212759</v>
+        <v>121212713</v>
       </c>
       <c r="B74" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8113,25 +8113,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526838</v>
+        <v>526960</v>
       </c>
       <c r="R74" t="n">
-        <v>6938397</v>
+        <v>6938390</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8203,10 +8203,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212737</v>
+        <v>121212697</v>
       </c>
       <c r="B75" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8219,21 +8219,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527248</v>
+        <v>527186</v>
       </c>
       <c r="R75" t="n">
-        <v>6938256</v>
+        <v>6938273</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8305,10 +8305,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212716</v>
+        <v>121212699</v>
       </c>
       <c r="B76" t="n">
-        <v>79685</v>
+        <v>79592</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8317,25 +8317,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>526994</v>
+        <v>527249</v>
       </c>
       <c r="R76" t="n">
-        <v>6938374</v>
+        <v>6938289</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8407,10 +8407,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212740</v>
+        <v>121212753</v>
       </c>
       <c r="B77" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8423,21 +8423,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>527350</v>
+        <v>526856</v>
       </c>
       <c r="R77" t="n">
-        <v>6938133</v>
+        <v>6938391</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8509,10 +8509,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212736</v>
+        <v>121212718</v>
       </c>
       <c r="B78" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8549,10 +8549,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527250</v>
+        <v>527038</v>
       </c>
       <c r="R78" t="n">
-        <v>6938289</v>
+        <v>6938372</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8614,7 +8614,7 @@
         <v>121212715</v>
       </c>
       <c r="B79" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8713,10 +8713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212699</v>
+        <v>121212703</v>
       </c>
       <c r="B80" t="n">
-        <v>79589</v>
+        <v>90999</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8725,25 +8725,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8753,10 +8753,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527249</v>
+        <v>527253</v>
       </c>
       <c r="R80" t="n">
-        <v>6938289</v>
+        <v>6938232</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212712</v>
+        <v>121212735</v>
       </c>
       <c r="B81" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526743</v>
+        <v>527245</v>
       </c>
       <c r="R81" t="n">
-        <v>6938415</v>
+        <v>6938291</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212695</v>
+        <v>121212733</v>
       </c>
       <c r="B82" t="n">
-        <v>79714</v>
+        <v>79688</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8929,25 +8929,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527184</v>
+        <v>527186</v>
       </c>
       <c r="R82" t="n">
-        <v>6938280</v>
+        <v>6938273</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9019,10 +9019,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212718</v>
+        <v>121212722</v>
       </c>
       <c r="B83" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527038</v>
+        <v>527075</v>
       </c>
       <c r="R83" t="n">
-        <v>6938372</v>
+        <v>6938349</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212714</v>
+        <v>121212739</v>
       </c>
       <c r="B84" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526955</v>
+        <v>527304</v>
       </c>
       <c r="R84" t="n">
-        <v>6938368</v>
+        <v>6938173</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212732</v>
+        <v>121212761</v>
       </c>
       <c r="B85" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9235,25 +9235,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527184</v>
+        <v>526852</v>
       </c>
       <c r="R85" t="n">
-        <v>6938280</v>
+        <v>6938391</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9325,10 +9325,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212703</v>
+        <v>121212759</v>
       </c>
       <c r="B86" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9337,25 +9337,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527253</v>
+        <v>526838</v>
       </c>
       <c r="R86" t="n">
-        <v>6938232</v>
+        <v>6938397</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9427,10 +9427,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212701</v>
+        <v>121212757</v>
       </c>
       <c r="B87" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9439,25 +9439,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526960</v>
+        <v>526927</v>
       </c>
       <c r="R87" t="n">
-        <v>6938387</v>
+        <v>6938376</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9529,10 +9529,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212734</v>
+        <v>121212756</v>
       </c>
       <c r="B88" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9541,25 +9541,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527214</v>
+        <v>527255</v>
       </c>
       <c r="R88" t="n">
-        <v>6938296</v>
+        <v>6938220</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9605,6 +9605,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9631,10 +9636,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212762</v>
+        <v>121212745</v>
       </c>
       <c r="B89" t="n">
-        <v>98095</v>
+        <v>79724</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9643,25 +9648,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9671,10 +9676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526868</v>
+        <v>526960</v>
       </c>
       <c r="R89" t="n">
-        <v>6938367</v>
+        <v>6938390</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9733,10 +9738,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212723</v>
+        <v>121212755</v>
       </c>
       <c r="B90" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9749,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9773,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527088</v>
+        <v>526945</v>
       </c>
       <c r="R90" t="n">
-        <v>6938358</v>
+        <v>6938389</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9835,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212756</v>
+        <v>121212772</v>
       </c>
       <c r="B91" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9847,25 +9852,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9875,10 +9880,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527255</v>
+        <v>526971</v>
       </c>
       <c r="R91" t="n">
-        <v>6938220</v>
+        <v>6938369</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9942,10 +9947,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212730</v>
+        <v>121212731</v>
       </c>
       <c r="B92" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9982,10 +9987,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527177</v>
+        <v>527184</v>
       </c>
       <c r="R92" t="n">
-        <v>6938273</v>
+        <v>6938280</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10049,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212713</v>
+        <v>121212716</v>
       </c>
       <c r="B93" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10084,10 +10089,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>526960</v>
+        <v>526994</v>
       </c>
       <c r="R93" t="n">
-        <v>6938390</v>
+        <v>6938374</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10146,10 +10151,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212697</v>
+        <v>121212765</v>
       </c>
       <c r="B94" t="n">
-        <v>79686</v>
+        <v>98098</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10158,25 +10163,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10191,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>527186</v>
+        <v>526955</v>
       </c>
       <c r="R94" t="n">
-        <v>6938273</v>
+        <v>6938367</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,10 +10253,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212711</v>
+        <v>121212762</v>
       </c>
       <c r="B95" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10260,25 +10265,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10288,10 +10293,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527051</v>
+        <v>526868</v>
       </c>
       <c r="R95" t="n">
-        <v>6938349</v>
+        <v>6938367</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10355,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212698</v>
+        <v>121212763</v>
       </c>
       <c r="B96" t="n">
-        <v>79686</v>
+        <v>98098</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10362,25 +10367,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10395,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>527211</v>
+        <v>526911</v>
       </c>
       <c r="R96" t="n">
-        <v>6938302</v>
+        <v>6938360</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10452,10 +10457,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212729</v>
+        <v>121212694</v>
       </c>
       <c r="B97" t="n">
-        <v>79685</v>
+        <v>79717</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10464,25 +10469,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10492,10 +10497,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527168</v>
+        <v>527088</v>
       </c>
       <c r="R97" t="n">
-        <v>6938291</v>
+        <v>6938356</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10554,10 +10559,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212746</v>
+        <v>121212695</v>
       </c>
       <c r="B98" t="n">
-        <v>79721</v>
+        <v>79717</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10570,21 +10575,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10594,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527088</v>
+        <v>527184</v>
       </c>
       <c r="R98" t="n">
-        <v>6938356</v>
+        <v>6938280</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10656,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212721</v>
+        <v>121212744</v>
       </c>
       <c r="B99" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10696,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527074</v>
+        <v>527495</v>
       </c>
       <c r="R99" t="n">
-        <v>6938353</v>
+        <v>6938012</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10758,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212710</v>
+        <v>121212746</v>
       </c>
       <c r="B100" t="n">
-        <v>79685</v>
+        <v>79724</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10770,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10798,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527495</v>
+        <v>527088</v>
       </c>
       <c r="R100" t="n">
-        <v>6938009</v>
+        <v>6938356</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10834,11 +10839,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10865,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212752</v>
+        <v>121212705</v>
       </c>
       <c r="B101" t="n">
-        <v>78340</v>
+        <v>90999</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10881,21 +10881,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>526804</v>
+        <v>527310</v>
       </c>
       <c r="R101" t="n">
-        <v>6938398</v>
+        <v>6938160</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212720</v>
+        <v>121212737</v>
       </c>
       <c r="B102" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527051</v>
+        <v>527248</v>
       </c>
       <c r="R102" t="n">
-        <v>6938362</v>
+        <v>6938256</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11069,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212765</v>
+        <v>121212760</v>
       </c>
       <c r="B103" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526955</v>
+        <v>526842</v>
       </c>
       <c r="R103" t="n">
-        <v>6938367</v>
+        <v>6938396</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11171,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212688</v>
+        <v>121212696</v>
       </c>
       <c r="B104" t="n">
-        <v>95642</v>
+        <v>79717</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11183,25 +11183,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527409</v>
+        <v>527288</v>
       </c>
       <c r="R104" t="n">
-        <v>6938091</v>
+        <v>6938221</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11273,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212744</v>
+        <v>121212689</v>
       </c>
       <c r="B105" t="n">
-        <v>79685</v>
+        <v>79225</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,21 +11289,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11313,10 +11313,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527495</v>
+        <v>526855</v>
       </c>
       <c r="R105" t="n">
-        <v>6938012</v>
+        <v>6938391</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212745</v>
+        <v>121212773</v>
       </c>
       <c r="B106" t="n">
-        <v>79721</v>
+        <v>78607</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11387,25 +11387,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11415,10 +11415,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>526960</v>
+        <v>526989</v>
       </c>
       <c r="R106" t="n">
-        <v>6938390</v>
+        <v>6938371</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11451,6 +11451,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11477,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212771</v>
+        <v>121212729</v>
       </c>
       <c r="B107" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11489,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11517,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527317</v>
+        <v>527168</v>
       </c>
       <c r="R107" t="n">
-        <v>6938165</v>
+        <v>6938291</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11579,10 +11584,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212757</v>
+        <v>121212738</v>
       </c>
       <c r="B108" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11591,25 +11596,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11619,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>526927</v>
+        <v>527288</v>
       </c>
       <c r="R108" t="n">
-        <v>6938376</v>
+        <v>6938221</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11681,10 +11686,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212692</v>
+        <v>121212725</v>
       </c>
       <c r="B109" t="n">
-        <v>57504</v>
+        <v>79688</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11697,21 +11702,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11721,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>527210</v>
+        <v>527111</v>
       </c>
       <c r="R109" t="n">
-        <v>6938291</v>
+        <v>6938327</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11757,11 +11762,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11788,10 +11788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212709</v>
+        <v>121212734</v>
       </c>
       <c r="B110" t="n">
-        <v>78341</v>
+        <v>79688</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11804,21 +11804,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>526856</v>
+        <v>527214</v>
       </c>
       <c r="R110" t="n">
-        <v>6938391</v>
+        <v>6938296</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212690</v>
+        <v>121212701</v>
       </c>
       <c r="B111" t="n">
-        <v>90710</v>
+        <v>90999</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11906,21 +11906,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527263</v>
+        <v>526960</v>
       </c>
       <c r="R111" t="n">
-        <v>6938234</v>
+        <v>6938387</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212755</v>
+        <v>121212708</v>
       </c>
       <c r="B112" t="n">
-        <v>78340</v>
+        <v>97052</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12004,25 +12004,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>526945</v>
+        <v>527252</v>
       </c>
       <c r="R112" t="n">
-        <v>6938389</v>
+        <v>6938285</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212733</v>
+        <v>121212723</v>
       </c>
       <c r="B113" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527186</v>
+        <v>527088</v>
       </c>
       <c r="R113" t="n">
-        <v>6938273</v>
+        <v>6938358</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212751</v>
+        <v>121212769</v>
       </c>
       <c r="B114" t="n">
-        <v>78340</v>
+        <v>98098</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12208,25 +12208,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>526755</v>
+        <v>527263</v>
       </c>
       <c r="R114" t="n">
-        <v>6938374</v>
+        <v>6938242</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212764</v>
+        <v>121212721</v>
       </c>
       <c r="B115" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12310,25 +12310,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>526945</v>
+        <v>527074</v>
       </c>
       <c r="R115" t="n">
-        <v>6938389</v>
+        <v>6938353</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212705</v>
+        <v>121212775</v>
       </c>
       <c r="B116" t="n">
-        <v>90996</v>
+        <v>78607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12416,21 +12416,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527310</v>
+        <v>527023</v>
       </c>
       <c r="R116" t="n">
-        <v>6938160</v>
+        <v>6938359</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212750</v>
+        <v>121212690</v>
       </c>
       <c r="B117" t="n">
-        <v>80561</v>
+        <v>90713</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12518,21 +12518,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>526756</v>
+        <v>527263</v>
       </c>
       <c r="R117" t="n">
-        <v>6938437</v>
+        <v>6938234</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212775</v>
+        <v>121212714</v>
       </c>
       <c r="B118" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12620,21 +12620,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527023</v>
+        <v>526955</v>
       </c>
       <c r="R118" t="n">
-        <v>6938359</v>
+        <v>6938368</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212694</v>
+        <v>121212736</v>
       </c>
       <c r="B119" t="n">
-        <v>79714</v>
+        <v>79688</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,25 +12718,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527088</v>
+        <v>527250</v>
       </c>
       <c r="R119" t="n">
-        <v>6938356</v>
+        <v>6938289</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212738</v>
+        <v>121212764</v>
       </c>
       <c r="B120" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527288</v>
+        <v>526945</v>
       </c>
       <c r="R120" t="n">
-        <v>6938221</v>
+        <v>6938389</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121226812</v>
+        <v>121226822</v>
       </c>
       <c r="B121" t="n">
-        <v>79685</v>
+        <v>91989</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,25 +12922,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526551</v>
+        <v>526182</v>
       </c>
       <c r="R121" t="n">
-        <v>6938312</v>
+        <v>6938234</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226792</v>
+        <v>121226805</v>
       </c>
       <c r="B122" t="n">
-        <v>90710</v>
+        <v>79688</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13052,10 +13052,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526796</v>
+        <v>526203</v>
       </c>
       <c r="R122" t="n">
-        <v>6937966</v>
+        <v>6938195</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121226809</v>
+        <v>121212778</v>
       </c>
       <c r="B123" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13130,21 +13130,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526518</v>
+        <v>527288</v>
       </c>
       <c r="R123" t="n">
-        <v>6938295</v>
+        <v>6938221</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226821</v>
+        <v>121226797</v>
       </c>
       <c r="B124" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13232,21 +13232,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526199</v>
+        <v>526496</v>
       </c>
       <c r="R124" t="n">
-        <v>6938254</v>
+        <v>6938343</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13323,10 +13323,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121212789</v>
+        <v>121220094</v>
       </c>
       <c r="B125" t="n">
-        <v>91986</v>
+        <v>78343</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13335,41 +13335,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526823</v>
+        <v>526766</v>
       </c>
       <c r="R125" t="n">
-        <v>6938405</v>
+        <v>6938100</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13393,12 +13393,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13425,10 +13425,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226817</v>
+        <v>121226793</v>
       </c>
       <c r="B126" t="n">
-        <v>98095</v>
+        <v>90733</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13437,25 +13437,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526581</v>
+        <v>526519</v>
       </c>
       <c r="R126" t="n">
-        <v>6938053</v>
+        <v>6938315</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13527,10 +13527,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226806</v>
+        <v>121226802</v>
       </c>
       <c r="B127" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526182</v>
+        <v>526716</v>
       </c>
       <c r="R127" t="n">
-        <v>6938206</v>
+        <v>6937997</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13632,7 +13632,7 @@
         <v>121226799</v>
       </c>
       <c r="B128" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13731,10 +13731,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226808</v>
+        <v>121226810</v>
       </c>
       <c r="B129" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13771,10 +13771,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526482</v>
+        <v>526533</v>
       </c>
       <c r="R129" t="n">
-        <v>6938338</v>
+        <v>6938315</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13833,10 +13833,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226801</v>
+        <v>121226816</v>
       </c>
       <c r="B130" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13845,25 +13845,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526714</v>
+        <v>526789</v>
       </c>
       <c r="R130" t="n">
-        <v>6938008</v>
+        <v>6937993</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13935,10 +13935,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226824</v>
+        <v>121226813</v>
       </c>
       <c r="B131" t="n">
-        <v>91272</v>
+        <v>78343</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13947,25 +13947,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526747</v>
+        <v>526365</v>
       </c>
       <c r="R131" t="n">
-        <v>6937983</v>
+        <v>6938404</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14037,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121220094</v>
+        <v>121212783</v>
       </c>
       <c r="B132" t="n">
-        <v>78340</v>
+        <v>78252</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14053,37 +14053,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526766</v>
+        <v>526761</v>
       </c>
       <c r="R132" t="n">
-        <v>6938100</v>
+        <v>6938348</v>
       </c>
       <c r="S132" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14107,12 +14107,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,10 +14139,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121212778</v>
+        <v>121226796</v>
       </c>
       <c r="B133" t="n">
-        <v>78604</v>
+        <v>90999</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14155,21 +14155,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14179,10 +14179,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>527288</v>
+        <v>526796</v>
       </c>
       <c r="R133" t="n">
-        <v>6938221</v>
+        <v>6937966</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14241,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226793</v>
+        <v>121226820</v>
       </c>
       <c r="B134" t="n">
-        <v>90730</v>
+        <v>90727</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5442</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526519</v>
+        <v>526660</v>
       </c>
       <c r="R134" t="n">
-        <v>6938315</v>
+        <v>6938167</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226814</v>
+        <v>121226824</v>
       </c>
       <c r="B135" t="n">
-        <v>78340</v>
+        <v>91275</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14355,25 +14355,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526515</v>
+        <v>526747</v>
       </c>
       <c r="R135" t="n">
-        <v>6938303</v>
+        <v>6937983</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226811</v>
+        <v>121226795</v>
       </c>
       <c r="B136" t="n">
-        <v>79685</v>
+        <v>79689</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14461,21 +14461,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526545</v>
+        <v>526554</v>
       </c>
       <c r="R136" t="n">
-        <v>6938319</v>
+        <v>6938311</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14547,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121212776</v>
+        <v>121226807</v>
       </c>
       <c r="B137" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14563,21 +14563,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>527090</v>
+        <v>526201</v>
       </c>
       <c r="R137" t="n">
-        <v>6938365</v>
+        <v>6938252</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14617,12 +14617,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14649,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121219658</v>
+        <v>121226814</v>
       </c>
       <c r="B138" t="n">
-        <v>90675</v>
+        <v>78343</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14661,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526953</v>
+        <v>526515</v>
       </c>
       <c r="R138" t="n">
-        <v>6937958</v>
+        <v>6938303</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14751,10 +14751,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226802</v>
+        <v>121212785</v>
       </c>
       <c r="B139" t="n">
-        <v>79685</v>
+        <v>78252</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14767,21 +14767,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14791,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526716</v>
+        <v>526753</v>
       </c>
       <c r="R139" t="n">
-        <v>6937997</v>
+        <v>6938395</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14821,12 +14821,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14853,10 +14853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121212780</v>
+        <v>121226806</v>
       </c>
       <c r="B140" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14869,21 +14869,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14893,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>527567</v>
+        <v>526182</v>
       </c>
       <c r="R140" t="n">
-        <v>6937949</v>
+        <v>6938206</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14923,12 +14923,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14955,10 +14955,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226805</v>
+        <v>121212780</v>
       </c>
       <c r="B141" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14971,21 +14971,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526203</v>
+        <v>527567</v>
       </c>
       <c r="R141" t="n">
-        <v>6938195</v>
+        <v>6937949</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15025,12 +15025,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15057,10 +15057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226818</v>
+        <v>121222671</v>
       </c>
       <c r="B142" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15069,41 +15069,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526525</v>
+        <v>526275</v>
       </c>
       <c r="R142" t="n">
-        <v>6938312</v>
+        <v>6938199</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15133,6 +15133,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15159,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226819</v>
+        <v>121219596</v>
       </c>
       <c r="B143" t="n">
-        <v>98095</v>
+        <v>78343</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15171,41 +15176,41 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526646</v>
+        <v>526982</v>
       </c>
       <c r="R143" t="n">
-        <v>6938173</v>
+        <v>6937928</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15261,10 +15266,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226813</v>
+        <v>121226794</v>
       </c>
       <c r="B144" t="n">
-        <v>78340</v>
+        <v>79717</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15273,25 +15278,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15301,10 +15306,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526365</v>
+        <v>526478</v>
       </c>
       <c r="R144" t="n">
-        <v>6938404</v>
+        <v>6938348</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15363,10 +15368,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226803</v>
+        <v>121226815</v>
       </c>
       <c r="B145" t="n">
-        <v>79685</v>
+        <v>78343</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15379,21 +15384,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15403,10 +15408,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526335</v>
+        <v>526527</v>
       </c>
       <c r="R145" t="n">
-        <v>6938150</v>
+        <v>6938317</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15465,10 +15470,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121222671</v>
+        <v>121226803</v>
       </c>
       <c r="B146" t="n">
-        <v>78604</v>
+        <v>79688</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15481,37 +15486,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526275</v>
+        <v>526335</v>
       </c>
       <c r="R146" t="n">
-        <v>6938199</v>
+        <v>6938150</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15541,11 +15546,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15572,10 +15572,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121221064</v>
+        <v>121226821</v>
       </c>
       <c r="B147" t="n">
-        <v>90724</v>
+        <v>78607</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15588,37 +15588,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526664</v>
+        <v>526199</v>
       </c>
       <c r="R147" t="n">
-        <v>6938176</v>
+        <v>6938254</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15648,6 +15648,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15674,10 +15679,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226822</v>
+        <v>121220916</v>
       </c>
       <c r="B148" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15686,41 +15691,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526182</v>
+        <v>526647</v>
       </c>
       <c r="R148" t="n">
-        <v>6938234</v>
+        <v>6938174</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15776,10 +15781,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226794</v>
+        <v>121226819</v>
       </c>
       <c r="B149" t="n">
-        <v>79714</v>
+        <v>98098</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15788,25 +15793,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15816,10 +15821,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526478</v>
+        <v>526646</v>
       </c>
       <c r="R149" t="n">
-        <v>6938348</v>
+        <v>6938173</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15878,10 +15883,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226791</v>
+        <v>121212779</v>
       </c>
       <c r="B150" t="n">
-        <v>89761</v>
+        <v>78607</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15894,21 +15899,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15918,10 +15923,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526205</v>
+        <v>527495</v>
       </c>
       <c r="R150" t="n">
-        <v>6938282</v>
+        <v>6938009</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15948,12 +15953,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15980,10 +15985,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121223305</v>
+        <v>121226812</v>
       </c>
       <c r="B151" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15992,41 +15997,41 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526584</v>
+        <v>526551</v>
       </c>
       <c r="R151" t="n">
-        <v>6938052</v>
+        <v>6938312</v>
       </c>
       <c r="S151" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16082,10 +16087,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226804</v>
+        <v>121226808</v>
       </c>
       <c r="B152" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16122,10 +16127,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526224</v>
+        <v>526482</v>
       </c>
       <c r="R152" t="n">
-        <v>6938191</v>
+        <v>6938338</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16184,10 +16189,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226807</v>
+        <v>121226804</v>
       </c>
       <c r="B153" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16224,10 +16229,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526201</v>
+        <v>526224</v>
       </c>
       <c r="R153" t="n">
-        <v>6938252</v>
+        <v>6938191</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16286,10 +16291,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226797</v>
+        <v>121212789</v>
       </c>
       <c r="B154" t="n">
-        <v>79685</v>
+        <v>91989</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16298,25 +16303,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16326,10 +16331,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526496</v>
+        <v>526823</v>
       </c>
       <c r="R154" t="n">
-        <v>6938343</v>
+        <v>6938405</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16356,17 +16361,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16393,10 +16393,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226796</v>
+        <v>121226817</v>
       </c>
       <c r="B155" t="n">
-        <v>90996</v>
+        <v>98098</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16405,25 +16405,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16433,10 +16433,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526796</v>
+        <v>526581</v>
       </c>
       <c r="R155" t="n">
-        <v>6937966</v>
+        <v>6938053</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16495,10 +16495,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121226820</v>
+        <v>121212791</v>
       </c>
       <c r="B156" t="n">
-        <v>90724</v>
+        <v>79723</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16507,25 +16507,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526660</v>
+        <v>527094</v>
       </c>
       <c r="R156" t="n">
-        <v>6938167</v>
+        <v>6938358</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16597,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226815</v>
+        <v>121221064</v>
       </c>
       <c r="B157" t="n">
-        <v>78340</v>
+        <v>90727</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16613,37 +16613,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>1204</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526527</v>
+        <v>526664</v>
       </c>
       <c r="R157" t="n">
-        <v>6938317</v>
+        <v>6938176</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121221199</v>
+        <v>121226792</v>
       </c>
       <c r="B158" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16715,37 +16715,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526592</v>
+        <v>526796</v>
       </c>
       <c r="R158" t="n">
-        <v>6938232</v>
+        <v>6937966</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16801,10 +16801,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121219596</v>
+        <v>121226818</v>
       </c>
       <c r="B159" t="n">
-        <v>78340</v>
+        <v>98098</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16813,41 +16813,41 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526982</v>
+        <v>526525</v>
       </c>
       <c r="R159" t="n">
-        <v>6937928</v>
+        <v>6938312</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226810</v>
+        <v>121226809</v>
       </c>
       <c r="B160" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526533</v>
+        <v>526518</v>
       </c>
       <c r="R160" t="n">
-        <v>6938315</v>
+        <v>6938295</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17005,10 +17005,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121212779</v>
+        <v>121223305</v>
       </c>
       <c r="B161" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17017,41 +17017,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>527495</v>
+        <v>526584</v>
       </c>
       <c r="R161" t="n">
-        <v>6938009</v>
+        <v>6938052</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17075,12 +17075,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17107,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121220916</v>
+        <v>121226791</v>
       </c>
       <c r="B162" t="n">
-        <v>98095</v>
+        <v>89764</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17119,41 +17119,41 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526647</v>
+        <v>526205</v>
       </c>
       <c r="R162" t="n">
-        <v>6938174</v>
+        <v>6938282</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17209,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121212785</v>
+        <v>121212776</v>
       </c>
       <c r="B163" t="n">
-        <v>78249</v>
+        <v>78607</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17225,21 +17225,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526753</v>
+        <v>527090</v>
       </c>
       <c r="R163" t="n">
-        <v>6938395</v>
+        <v>6938365</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121212783</v>
+        <v>121226801</v>
       </c>
       <c r="B164" t="n">
-        <v>78249</v>
+        <v>79688</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17327,21 +17327,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526761</v>
+        <v>526714</v>
       </c>
       <c r="R164" t="n">
-        <v>6938348</v>
+        <v>6938008</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17381,12 +17381,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226795</v>
+        <v>121226811</v>
       </c>
       <c r="B165" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17429,21 +17429,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17453,10 +17453,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526554</v>
+        <v>526545</v>
       </c>
       <c r="R165" t="n">
-        <v>6938311</v>
+        <v>6938319</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121212791</v>
+        <v>121221199</v>
       </c>
       <c r="B166" t="n">
-        <v>79720</v>
+        <v>78607</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17527,20 +17527,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -17551,17 +17551,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>527094</v>
+        <v>526592</v>
       </c>
       <c r="R166" t="n">
-        <v>6938358</v>
+        <v>6938232</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17585,12 +17585,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226816</v>
+        <v>121212788</v>
       </c>
       <c r="B167" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526789</v>
+        <v>526776</v>
       </c>
       <c r="R167" t="n">
-        <v>6937993</v>
+        <v>6938419</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121212788</v>
+        <v>121219658</v>
       </c>
       <c r="B168" t="n">
-        <v>91986</v>
+        <v>90678</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17735,37 +17735,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526776</v>
+        <v>526953</v>
       </c>
       <c r="R168" t="n">
-        <v>6938419</v>
+        <v>6937958</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -17789,12 +17789,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17824,7 +17824,7 @@
         <v>121212693</v>
       </c>
       <c r="B169" t="n">
-        <v>91990</v>
+        <v>91993</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>121246286</v>
       </c>
       <c r="B170" t="n">
-        <v>92015</v>
+        <v>92018</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121179693</v>
+        <v>121185408</v>
       </c>
       <c r="B171" t="n">
-        <v>91986</v>
+        <v>90999</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527779</v>
+        <v>527661</v>
       </c>
       <c r="R171" t="n">
-        <v>6937594</v>
+        <v>6937695</v>
       </c>
       <c r="S171" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121185408</v>
+        <v>121179693</v>
       </c>
       <c r="B172" t="n">
-        <v>90996</v>
+        <v>91989</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527661</v>
+        <v>527779</v>
       </c>
       <c r="R172" t="n">
-        <v>6937695</v>
+        <v>6937594</v>
       </c>
       <c r="S172" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121185404</v>
+        <v>121179849</v>
       </c>
       <c r="B173" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18279,17 +18279,17 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>527659</v>
+        <v>527658</v>
       </c>
       <c r="R173" t="n">
-        <v>6937698</v>
+        <v>6937694</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121179849</v>
+        <v>121185404</v>
       </c>
       <c r="B174" t="n">
-        <v>91150</v>
+        <v>91153</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18381,17 +18381,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527658</v>
+        <v>527659</v>
       </c>
       <c r="R174" t="n">
-        <v>6937694</v>
+        <v>6937698</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121179876</v>
+        <v>121185424</v>
       </c>
       <c r="B6" t="n">
-        <v>90999</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,41 +1167,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527649</v>
+        <v>527010</v>
       </c>
       <c r="R6" t="n">
-        <v>6937696</v>
+        <v>6938105</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185426</v>
+        <v>121185405</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>90999</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527503</v>
+        <v>527034</v>
       </c>
       <c r="R7" t="n">
-        <v>6937855</v>
+        <v>6938099</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185418</v>
+        <v>121179876</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,37 +1375,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527437</v>
+        <v>527649</v>
       </c>
       <c r="R8" t="n">
-        <v>6937974</v>
+        <v>6937696</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185410</v>
+        <v>121185428</v>
       </c>
       <c r="B9" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527024</v>
+        <v>527439</v>
       </c>
       <c r="R9" t="n">
-        <v>6938111</v>
+        <v>6937974</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121185411</v>
+        <v>121180141</v>
       </c>
       <c r="B10" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,41 +1575,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527045</v>
+        <v>527597</v>
       </c>
       <c r="R10" t="n">
-        <v>6938075</v>
+        <v>6937703</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121180291</v>
+        <v>121185432</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,41 +1677,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527492</v>
+        <v>527217</v>
       </c>
       <c r="R11" t="n">
-        <v>6937763</v>
+        <v>6937854</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185397</v>
+        <v>121185400</v>
       </c>
       <c r="B12" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527043</v>
+        <v>527034</v>
       </c>
       <c r="R12" t="n">
-        <v>6938062</v>
+        <v>6938099</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185400</v>
+        <v>121185413</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527034</v>
+        <v>527044</v>
       </c>
       <c r="R13" t="n">
-        <v>6938099</v>
+        <v>6938065</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185433</v>
+        <v>121185402</v>
       </c>
       <c r="B14" t="n">
-        <v>91989</v>
+        <v>79717</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527195</v>
+        <v>527367</v>
       </c>
       <c r="R14" t="n">
-        <v>6937884</v>
+        <v>6937938</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185412</v>
+        <v>121185397</v>
       </c>
       <c r="B15" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527001</v>
+        <v>527043</v>
       </c>
       <c r="R15" t="n">
-        <v>6938101</v>
+        <v>6938062</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185424</v>
+        <v>121185426</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527010</v>
+        <v>527503</v>
       </c>
       <c r="R16" t="n">
-        <v>6938105</v>
+        <v>6937855</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185425</v>
+        <v>121180230</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>105203</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,41 +2289,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527014</v>
+        <v>527509</v>
       </c>
       <c r="R17" t="n">
-        <v>6938062</v>
+        <v>6937756</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185407</v>
+        <v>121185435</v>
       </c>
       <c r="B18" t="n">
-        <v>90999</v>
+        <v>91369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527016</v>
+        <v>527008</v>
       </c>
       <c r="R18" t="n">
-        <v>6938062</v>
+        <v>6938073</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185434</v>
+        <v>121185423</v>
       </c>
       <c r="B19" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>526953</v>
+        <v>526974</v>
       </c>
       <c r="R19" t="n">
-        <v>6938054</v>
+        <v>6938145</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121183281</v>
+        <v>121180291</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>90731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,38 +2595,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>526958</v>
+        <v>527492</v>
       </c>
       <c r="R20" t="n">
-        <v>6938109</v>
+        <v>6937763</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185422</v>
+        <v>121185418</v>
       </c>
       <c r="B21" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,25 +2697,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>526995</v>
+        <v>527437</v>
       </c>
       <c r="R21" t="n">
-        <v>6938144</v>
+        <v>6937974</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2787,7 +2787,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185409</v>
+        <v>121185412</v>
       </c>
       <c r="B22" t="n">
         <v>79688</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527108</v>
+        <v>527001</v>
       </c>
       <c r="R22" t="n">
-        <v>6938086</v>
+        <v>6938101</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185396</v>
+        <v>121185401</v>
       </c>
       <c r="B23" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,25 +2901,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>526980</v>
+        <v>527016</v>
       </c>
       <c r="R23" t="n">
-        <v>6938115</v>
+        <v>6938060</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185430</v>
+        <v>121185421</v>
       </c>
       <c r="B24" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>527460</v>
+        <v>526958</v>
       </c>
       <c r="R24" t="n">
-        <v>6937819</v>
+        <v>6938116</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121180261</v>
+        <v>121185396</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,41 +3105,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527506</v>
+        <v>526980</v>
       </c>
       <c r="R25" t="n">
-        <v>6937752</v>
+        <v>6938115</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185428</v>
+        <v>121180261</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,41 +3207,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527439</v>
+        <v>527506</v>
       </c>
       <c r="R26" t="n">
-        <v>6937974</v>
+        <v>6937752</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121179977</v>
+        <v>121185434</v>
       </c>
       <c r="B27" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,41 +3309,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>527626</v>
+        <v>526953</v>
       </c>
       <c r="R27" t="n">
-        <v>6937719</v>
+        <v>6938054</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121180230</v>
+        <v>121183281</v>
       </c>
       <c r="B28" t="n">
-        <v>105203</v>
+        <v>98098</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,38 +3411,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>527509</v>
+        <v>526958</v>
       </c>
       <c r="R28" t="n">
-        <v>6937756</v>
+        <v>6938109</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121185431</v>
+        <v>121185395</v>
       </c>
       <c r="B29" t="n">
-        <v>91989</v>
+        <v>95645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,25 +3513,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527439</v>
+        <v>527048</v>
       </c>
       <c r="R29" t="n">
-        <v>6937815</v>
+        <v>6938076</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185403</v>
+        <v>121185411</v>
       </c>
       <c r="B30" t="n">
-        <v>90660</v>
+        <v>79688</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3619,21 +3619,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527012</v>
+        <v>527045</v>
       </c>
       <c r="R30" t="n">
-        <v>6938063</v>
+        <v>6938075</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185406</v>
+        <v>121185417</v>
       </c>
       <c r="B31" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527009</v>
+        <v>527368</v>
       </c>
       <c r="R31" t="n">
-        <v>6938044</v>
+        <v>6937959</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185405</v>
+        <v>121185407</v>
       </c>
       <c r="B32" t="n">
         <v>90999</v>
@@ -3847,10 +3847,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527034</v>
+        <v>527016</v>
       </c>
       <c r="R32" t="n">
-        <v>6938099</v>
+        <v>6938062</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121185395</v>
+        <v>121179977</v>
       </c>
       <c r="B33" t="n">
-        <v>95645</v>
+        <v>78607</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3925,37 +3925,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527048</v>
+        <v>527626</v>
       </c>
       <c r="R33" t="n">
-        <v>6938076</v>
+        <v>6937719</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185416</v>
+        <v>121185430</v>
       </c>
       <c r="B34" t="n">
-        <v>79688</v>
+        <v>91989</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527367</v>
+        <v>527460</v>
       </c>
       <c r="R34" t="n">
-        <v>6937938</v>
+        <v>6937819</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121180141</v>
+        <v>121185410</v>
       </c>
       <c r="B35" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,41 +4125,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527597</v>
+        <v>527024</v>
       </c>
       <c r="R35" t="n">
-        <v>6937703</v>
+        <v>6938111</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185432</v>
+        <v>121185425</v>
       </c>
       <c r="B36" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,25 +4227,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527217</v>
+        <v>527014</v>
       </c>
       <c r="R36" t="n">
-        <v>6937854</v>
+        <v>6938062</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121180239</v>
+        <v>121183008</v>
       </c>
       <c r="B37" t="n">
         <v>98098</v>
@@ -4353,14 +4353,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>527495</v>
+        <v>526999</v>
       </c>
       <c r="R37" t="n">
-        <v>6937765</v>
+        <v>6938157</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4419,7 +4419,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121183008</v>
+        <v>121180239</v>
       </c>
       <c r="B38" t="n">
         <v>98098</v>
@@ -4455,14 +4455,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>526999</v>
+        <v>527495</v>
       </c>
       <c r="R38" t="n">
-        <v>6938157</v>
+        <v>6937765</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121185417</v>
+        <v>121185422</v>
       </c>
       <c r="B39" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,25 +4533,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527368</v>
+        <v>526995</v>
       </c>
       <c r="R39" t="n">
-        <v>6937959</v>
+        <v>6938144</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121185429</v>
+        <v>121180712</v>
       </c>
       <c r="B40" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527641</v>
+        <v>527305</v>
       </c>
       <c r="R40" t="n">
-        <v>6937808</v>
+        <v>6937895</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185398</v>
+        <v>121182248</v>
       </c>
       <c r="B41" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,41 +4737,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>526983</v>
+        <v>527008</v>
       </c>
       <c r="R41" t="n">
-        <v>6938135</v>
+        <v>6938092</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185399</v>
+        <v>121185416</v>
       </c>
       <c r="B42" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4843,21 +4843,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>526989</v>
+        <v>527367</v>
       </c>
       <c r="R42" t="n">
-        <v>6938147</v>
+        <v>6937938</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185413</v>
+        <v>121185415</v>
       </c>
       <c r="B43" t="n">
         <v>79688</v>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527044</v>
+        <v>527391</v>
       </c>
       <c r="R43" t="n">
-        <v>6938065</v>
+        <v>6937910</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185402</v>
+        <v>121185431</v>
       </c>
       <c r="B44" t="n">
-        <v>79717</v>
+        <v>91989</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5047,21 +5047,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527367</v>
+        <v>527439</v>
       </c>
       <c r="R44" t="n">
-        <v>6937938</v>
+        <v>6937815</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185421</v>
+        <v>121185398</v>
       </c>
       <c r="B45" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526958</v>
+        <v>526983</v>
       </c>
       <c r="R45" t="n">
-        <v>6938116</v>
+        <v>6938135</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121185423</v>
+        <v>121185403</v>
       </c>
       <c r="B46" t="n">
-        <v>98098</v>
+        <v>90660</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5247,25 +5247,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>526974</v>
+        <v>527012</v>
       </c>
       <c r="R46" t="n">
-        <v>6938145</v>
+        <v>6938063</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121185401</v>
+        <v>121185399</v>
       </c>
       <c r="B47" t="n">
         <v>90713</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>527016</v>
+        <v>526989</v>
       </c>
       <c r="R47" t="n">
-        <v>6938060</v>
+        <v>6938147</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5439,7 +5439,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121180712</v>
+        <v>121185427</v>
       </c>
       <c r="B48" t="n">
         <v>78607</v>
@@ -5475,17 +5475,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527305</v>
+        <v>527034</v>
       </c>
       <c r="R48" t="n">
-        <v>6937895</v>
+        <v>6938099</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185419</v>
+        <v>121185409</v>
       </c>
       <c r="B49" t="n">
-        <v>79724</v>
+        <v>79688</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5553,25 +5553,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527001</v>
+        <v>527108</v>
       </c>
       <c r="R49" t="n">
-        <v>6938096</v>
+        <v>6938086</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121185435</v>
+        <v>121185419</v>
       </c>
       <c r="B50" t="n">
-        <v>91369</v>
+        <v>79724</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,25 +5655,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>898</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527008</v>
+        <v>527001</v>
       </c>
       <c r="R50" t="n">
-        <v>6938073</v>
+        <v>6938096</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185427</v>
+        <v>121185429</v>
       </c>
       <c r="B52" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527034</v>
+        <v>527641</v>
       </c>
       <c r="R52" t="n">
-        <v>6938099</v>
+        <v>6937808</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121185415</v>
+        <v>121185406</v>
       </c>
       <c r="B53" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5965,21 +5965,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5989,10 +5989,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527391</v>
+        <v>527009</v>
       </c>
       <c r="R53" t="n">
-        <v>6937910</v>
+        <v>6938044</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121182248</v>
+        <v>121185433</v>
       </c>
       <c r="B54" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,41 +6063,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527008</v>
+        <v>527195</v>
       </c>
       <c r="R54" t="n">
-        <v>6938092</v>
+        <v>6937884</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212740</v>
+        <v>121212738</v>
       </c>
       <c r="B55" t="n">
         <v>79688</v>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527350</v>
+        <v>527288</v>
       </c>
       <c r="R55" t="n">
-        <v>6938133</v>
+        <v>6938221</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212758</v>
+        <v>121212746</v>
       </c>
       <c r="B56" t="n">
-        <v>98098</v>
+        <v>79724</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>526823</v>
+        <v>527088</v>
       </c>
       <c r="R56" t="n">
-        <v>6938405</v>
+        <v>6938356</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212709</v>
+        <v>121212761</v>
       </c>
       <c r="B57" t="n">
-        <v>78344</v>
+        <v>98098</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526856</v>
+        <v>526852</v>
       </c>
       <c r="R57" t="n">
         <v>6938391</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212771</v>
+        <v>121212710</v>
       </c>
       <c r="B58" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527317</v>
+        <v>527495</v>
       </c>
       <c r="R58" t="n">
-        <v>6938165</v>
+        <v>6938009</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6535,6 +6535,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6561,7 +6566,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212752</v>
+        <v>121212753</v>
       </c>
       <c r="B59" t="n">
         <v>78343</v>
@@ -6601,10 +6606,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526804</v>
+        <v>526856</v>
       </c>
       <c r="R59" t="n">
-        <v>6938398</v>
+        <v>6938391</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,7 +6668,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212719</v>
+        <v>121212726</v>
       </c>
       <c r="B60" t="n">
         <v>79688</v>
@@ -6703,10 +6708,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527051</v>
+        <v>527148</v>
       </c>
       <c r="R60" t="n">
-        <v>6938362</v>
+        <v>6938301</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6770,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212711</v>
+        <v>121212745</v>
       </c>
       <c r="B61" t="n">
-        <v>79688</v>
+        <v>79724</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6777,25 +6782,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6805,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527051</v>
+        <v>526960</v>
       </c>
       <c r="R61" t="n">
-        <v>6938349</v>
+        <v>6938390</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212751</v>
+        <v>121212769</v>
       </c>
       <c r="B62" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6879,25 +6884,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526755</v>
+        <v>527263</v>
       </c>
       <c r="R62" t="n">
-        <v>6938374</v>
+        <v>6938242</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6969,10 +6974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212724</v>
+        <v>121212690</v>
       </c>
       <c r="B63" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,21 +6990,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527109</v>
+        <v>527263</v>
       </c>
       <c r="R63" t="n">
-        <v>6938336</v>
+        <v>6938234</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7071,10 +7076,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212712</v>
+        <v>121212689</v>
       </c>
       <c r="B64" t="n">
-        <v>79688</v>
+        <v>79225</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,21 +7092,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526743</v>
+        <v>526855</v>
       </c>
       <c r="R64" t="n">
-        <v>6938415</v>
+        <v>6938391</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7173,10 +7178,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212750</v>
+        <v>121212725</v>
       </c>
       <c r="B65" t="n">
-        <v>80564</v>
+        <v>79688</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7189,21 +7194,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7218,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526756</v>
+        <v>527111</v>
       </c>
       <c r="R65" t="n">
-        <v>6938437</v>
+        <v>6938327</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7275,10 +7280,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212698</v>
+        <v>121212715</v>
       </c>
       <c r="B66" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7291,21 +7296,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7315,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527211</v>
+        <v>526971</v>
       </c>
       <c r="R66" t="n">
-        <v>6938302</v>
+        <v>6938369</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7377,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212730</v>
+        <v>121212763</v>
       </c>
       <c r="B67" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7389,25 +7394,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527177</v>
+        <v>526911</v>
       </c>
       <c r="R67" t="n">
-        <v>6938273</v>
+        <v>6938360</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7479,10 +7484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212727</v>
+        <v>121212756</v>
       </c>
       <c r="B68" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7491,25 +7496,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7519,10 +7524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527148</v>
+        <v>527255</v>
       </c>
       <c r="R68" t="n">
-        <v>6938301</v>
+        <v>6938220</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7555,6 +7560,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7581,10 +7591,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212688</v>
+        <v>121212775</v>
       </c>
       <c r="B69" t="n">
-        <v>95645</v>
+        <v>78607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7597,21 +7607,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7621,10 +7631,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527409</v>
+        <v>527023</v>
       </c>
       <c r="R69" t="n">
-        <v>6938091</v>
+        <v>6938359</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7683,10 +7693,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212774</v>
+        <v>121212705</v>
       </c>
       <c r="B70" t="n">
-        <v>78607</v>
+        <v>90999</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7699,21 +7709,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7723,10 +7733,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>526840</v>
+        <v>527310</v>
       </c>
       <c r="R70" t="n">
-        <v>6938383</v>
+        <v>6938160</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7785,10 +7795,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212710</v>
+        <v>121212703</v>
       </c>
       <c r="B71" t="n">
-        <v>79688</v>
+        <v>90999</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7801,21 +7811,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7835,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527495</v>
+        <v>527253</v>
       </c>
       <c r="R71" t="n">
-        <v>6938009</v>
+        <v>6938232</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7861,11 +7871,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7892,10 +7897,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212717</v>
+        <v>121212692</v>
       </c>
       <c r="B72" t="n">
-        <v>79688</v>
+        <v>57507</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,21 +7913,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7932,10 +7937,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527023</v>
+        <v>527210</v>
       </c>
       <c r="R72" t="n">
-        <v>6938359</v>
+        <v>6938291</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7968,6 +7973,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7994,10 +8004,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212692</v>
+        <v>121212701</v>
       </c>
       <c r="B73" t="n">
-        <v>57507</v>
+        <v>90999</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8010,21 +8020,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8034,10 +8044,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527210</v>
+        <v>526960</v>
       </c>
       <c r="R73" t="n">
-        <v>6938291</v>
+        <v>6938387</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8070,11 +8080,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8101,7 +8106,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212713</v>
+        <v>121212735</v>
       </c>
       <c r="B74" t="n">
         <v>79688</v>
@@ -8141,10 +8146,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526960</v>
+        <v>527245</v>
       </c>
       <c r="R74" t="n">
-        <v>6938390</v>
+        <v>6938291</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8203,10 +8208,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212697</v>
+        <v>121212737</v>
       </c>
       <c r="B75" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8219,21 +8224,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8243,10 +8248,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527186</v>
+        <v>527248</v>
       </c>
       <c r="R75" t="n">
-        <v>6938273</v>
+        <v>6938256</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8305,10 +8310,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212699</v>
+        <v>121212736</v>
       </c>
       <c r="B76" t="n">
-        <v>79592</v>
+        <v>79688</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8317,25 +8322,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8345,7 +8350,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527249</v>
+        <v>527250</v>
       </c>
       <c r="R76" t="n">
         <v>6938289</v>
@@ -8407,10 +8412,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212753</v>
+        <v>121212759</v>
       </c>
       <c r="B77" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8419,25 +8424,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8447,10 +8452,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526856</v>
+        <v>526838</v>
       </c>
       <c r="R77" t="n">
-        <v>6938391</v>
+        <v>6938397</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8509,7 +8514,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212718</v>
+        <v>121212717</v>
       </c>
       <c r="B78" t="n">
         <v>79688</v>
@@ -8549,10 +8554,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527038</v>
+        <v>527023</v>
       </c>
       <c r="R78" t="n">
-        <v>6938372</v>
+        <v>6938359</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8611,7 +8616,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212715</v>
+        <v>121212739</v>
       </c>
       <c r="B79" t="n">
         <v>79688</v>
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526971</v>
+        <v>527304</v>
       </c>
       <c r="R79" t="n">
-        <v>6938369</v>
+        <v>6938173</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8713,10 +8718,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212703</v>
+        <v>121212731</v>
       </c>
       <c r="B80" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8729,21 +8734,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8753,10 +8758,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527253</v>
+        <v>527184</v>
       </c>
       <c r="R80" t="n">
-        <v>6938232</v>
+        <v>6938280</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8815,7 +8820,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212735</v>
+        <v>121212718</v>
       </c>
       <c r="B81" t="n">
         <v>79688</v>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527245</v>
+        <v>527038</v>
       </c>
       <c r="R81" t="n">
-        <v>6938291</v>
+        <v>6938372</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8917,10 +8922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212733</v>
+        <v>121212694</v>
       </c>
       <c r="B82" t="n">
-        <v>79688</v>
+        <v>79717</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8929,25 +8934,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8957,10 +8962,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527186</v>
+        <v>527088</v>
       </c>
       <c r="R82" t="n">
-        <v>6938273</v>
+        <v>6938356</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9019,10 +9024,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212722</v>
+        <v>121212773</v>
       </c>
       <c r="B83" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9035,21 +9040,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>527075</v>
+        <v>526989</v>
       </c>
       <c r="R83" t="n">
-        <v>6938349</v>
+        <v>6938371</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9095,6 +9100,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9121,7 +9131,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212739</v>
+        <v>121212719</v>
       </c>
       <c r="B84" t="n">
         <v>79688</v>
@@ -9161,10 +9171,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527304</v>
+        <v>527051</v>
       </c>
       <c r="R84" t="n">
-        <v>6938173</v>
+        <v>6938362</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9223,10 +9233,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212761</v>
+        <v>121212698</v>
       </c>
       <c r="B85" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9235,25 +9245,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9263,10 +9273,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526852</v>
+        <v>527211</v>
       </c>
       <c r="R85" t="n">
-        <v>6938391</v>
+        <v>6938302</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9325,10 +9335,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212759</v>
+        <v>121212744</v>
       </c>
       <c r="B86" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9337,25 +9347,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9365,10 +9375,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>526838</v>
+        <v>527495</v>
       </c>
       <c r="R86" t="n">
-        <v>6938397</v>
+        <v>6938012</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9427,10 +9437,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212757</v>
+        <v>121212713</v>
       </c>
       <c r="B87" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9439,25 +9449,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9467,10 +9477,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526927</v>
+        <v>526960</v>
       </c>
       <c r="R87" t="n">
-        <v>6938376</v>
+        <v>6938390</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9529,10 +9539,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212756</v>
+        <v>121212711</v>
       </c>
       <c r="B88" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9541,25 +9551,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9569,10 +9579,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527255</v>
+        <v>527051</v>
       </c>
       <c r="R88" t="n">
-        <v>6938220</v>
+        <v>6938349</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9605,11 +9615,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9636,10 +9641,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212745</v>
+        <v>121212730</v>
       </c>
       <c r="B89" t="n">
-        <v>79724</v>
+        <v>79688</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9648,25 +9653,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9676,10 +9681,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526960</v>
+        <v>527177</v>
       </c>
       <c r="R89" t="n">
-        <v>6938390</v>
+        <v>6938273</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9738,10 +9743,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212755</v>
+        <v>121212696</v>
       </c>
       <c r="B90" t="n">
-        <v>78343</v>
+        <v>79717</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9750,25 +9755,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9783,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>526945</v>
+        <v>527288</v>
       </c>
       <c r="R90" t="n">
-        <v>6938389</v>
+        <v>6938221</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9840,10 +9845,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212772</v>
+        <v>121212716</v>
       </c>
       <c r="B91" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9856,21 +9861,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9880,10 +9885,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>526971</v>
+        <v>526994</v>
       </c>
       <c r="R91" t="n">
-        <v>6938369</v>
+        <v>6938374</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9916,11 +9921,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9947,10 +9947,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212731</v>
+        <v>121212764</v>
       </c>
       <c r="B92" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9959,25 +9959,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9987,10 +9987,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527184</v>
+        <v>526945</v>
       </c>
       <c r="R92" t="n">
-        <v>6938280</v>
+        <v>6938389</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10049,10 +10049,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212716</v>
+        <v>121212758</v>
       </c>
       <c r="B93" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10061,25 +10061,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>526994</v>
+        <v>526823</v>
       </c>
       <c r="R93" t="n">
-        <v>6938374</v>
+        <v>6938405</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10151,10 +10151,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212765</v>
+        <v>121212752</v>
       </c>
       <c r="B94" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10163,25 +10163,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10191,10 +10191,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526955</v>
+        <v>526804</v>
       </c>
       <c r="R94" t="n">
-        <v>6938367</v>
+        <v>6938398</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10253,10 +10253,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212762</v>
+        <v>121212729</v>
       </c>
       <c r="B95" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10265,25 +10265,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10293,10 +10293,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>526868</v>
+        <v>527168</v>
       </c>
       <c r="R95" t="n">
-        <v>6938367</v>
+        <v>6938291</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10355,10 +10355,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212763</v>
+        <v>121212750</v>
       </c>
       <c r="B96" t="n">
-        <v>98098</v>
+        <v>80564</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10367,25 +10367,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10395,10 +10395,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526911</v>
+        <v>526756</v>
       </c>
       <c r="R96" t="n">
-        <v>6938360</v>
+        <v>6938437</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10457,10 +10457,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212694</v>
+        <v>121212755</v>
       </c>
       <c r="B97" t="n">
-        <v>79717</v>
+        <v>78343</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10469,25 +10469,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10497,10 +10497,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527088</v>
+        <v>526945</v>
       </c>
       <c r="R97" t="n">
-        <v>6938356</v>
+        <v>6938389</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10559,10 +10559,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212695</v>
+        <v>121212765</v>
       </c>
       <c r="B98" t="n">
-        <v>79717</v>
+        <v>98098</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10571,25 +10571,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10599,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527184</v>
+        <v>526955</v>
       </c>
       <c r="R98" t="n">
-        <v>6938280</v>
+        <v>6938367</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10661,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212744</v>
+        <v>121212774</v>
       </c>
       <c r="B99" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10677,21 +10677,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527495</v>
+        <v>526840</v>
       </c>
       <c r="R99" t="n">
-        <v>6938012</v>
+        <v>6938383</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10763,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212746</v>
+        <v>121212772</v>
       </c>
       <c r="B100" t="n">
-        <v>79724</v>
+        <v>78607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10775,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10803,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527088</v>
+        <v>526971</v>
       </c>
       <c r="R100" t="n">
-        <v>6938356</v>
+        <v>6938369</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10839,6 +10839,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10865,10 +10870,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212705</v>
+        <v>121212688</v>
       </c>
       <c r="B101" t="n">
-        <v>90999</v>
+        <v>95645</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10881,21 +10886,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10905,10 +10910,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527310</v>
+        <v>527409</v>
       </c>
       <c r="R101" t="n">
-        <v>6938160</v>
+        <v>6938091</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10967,7 +10972,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212737</v>
+        <v>121212723</v>
       </c>
       <c r="B102" t="n">
         <v>79688</v>
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527248</v>
+        <v>527088</v>
       </c>
       <c r="R102" t="n">
-        <v>6938256</v>
+        <v>6938358</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11069,10 +11074,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212760</v>
+        <v>121212751</v>
       </c>
       <c r="B103" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11081,25 +11086,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11109,10 +11114,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526842</v>
+        <v>526755</v>
       </c>
       <c r="R103" t="n">
-        <v>6938396</v>
+        <v>6938374</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11171,10 +11176,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212696</v>
+        <v>121212697</v>
       </c>
       <c r="B104" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11183,25 +11188,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11211,10 +11216,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527288</v>
+        <v>527186</v>
       </c>
       <c r="R104" t="n">
-        <v>6938221</v>
+        <v>6938273</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11273,10 +11278,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212689</v>
+        <v>121212724</v>
       </c>
       <c r="B105" t="n">
-        <v>79225</v>
+        <v>79688</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11289,21 +11294,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11313,10 +11318,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>526855</v>
+        <v>527109</v>
       </c>
       <c r="R105" t="n">
-        <v>6938391</v>
+        <v>6938336</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11375,10 +11380,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212773</v>
+        <v>121212695</v>
       </c>
       <c r="B106" t="n">
-        <v>78607</v>
+        <v>79717</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11387,25 +11392,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11415,10 +11420,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>526989</v>
+        <v>527184</v>
       </c>
       <c r="R106" t="n">
-        <v>6938371</v>
+        <v>6938280</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11451,11 +11456,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11482,7 +11482,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212729</v>
+        <v>121212734</v>
       </c>
       <c r="B107" t="n">
         <v>79688</v>
@@ -11522,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527168</v>
+        <v>527214</v>
       </c>
       <c r="R107" t="n">
-        <v>6938291</v>
+        <v>6938296</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,7 +11584,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212738</v>
+        <v>121212733</v>
       </c>
       <c r="B108" t="n">
         <v>79688</v>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527288</v>
+        <v>527186</v>
       </c>
       <c r="R108" t="n">
-        <v>6938221</v>
+        <v>6938273</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212725</v>
+        <v>121212714</v>
       </c>
       <c r="B109" t="n">
         <v>79688</v>
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>527111</v>
+        <v>526955</v>
       </c>
       <c r="R109" t="n">
-        <v>6938327</v>
+        <v>6938368</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212734</v>
+        <v>121212722</v>
       </c>
       <c r="B110" t="n">
         <v>79688</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527214</v>
+        <v>527075</v>
       </c>
       <c r="R110" t="n">
-        <v>6938296</v>
+        <v>6938349</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212701</v>
+        <v>121212740</v>
       </c>
       <c r="B111" t="n">
-        <v>90999</v>
+        <v>79688</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11906,21 +11906,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>526960</v>
+        <v>527350</v>
       </c>
       <c r="R111" t="n">
-        <v>6938387</v>
+        <v>6938133</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -12094,7 +12094,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212723</v>
+        <v>121212721</v>
       </c>
       <c r="B113" t="n">
         <v>79688</v>
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527088</v>
+        <v>527074</v>
       </c>
       <c r="R113" t="n">
-        <v>6938358</v>
+        <v>6938353</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212769</v>
+        <v>121212699</v>
       </c>
       <c r="B114" t="n">
-        <v>98098</v>
+        <v>79592</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12208,25 +12208,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527263</v>
+        <v>527249</v>
       </c>
       <c r="R114" t="n">
-        <v>6938242</v>
+        <v>6938289</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,7 +12298,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212721</v>
+        <v>121212712</v>
       </c>
       <c r="B115" t="n">
         <v>79688</v>
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527074</v>
+        <v>526743</v>
       </c>
       <c r="R115" t="n">
-        <v>6938353</v>
+        <v>6938415</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212775</v>
+        <v>121212762</v>
       </c>
       <c r="B116" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12412,25 +12412,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527023</v>
+        <v>526868</v>
       </c>
       <c r="R116" t="n">
-        <v>6938359</v>
+        <v>6938367</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212690</v>
+        <v>121212760</v>
       </c>
       <c r="B117" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12514,25 +12514,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527263</v>
+        <v>526842</v>
       </c>
       <c r="R117" t="n">
-        <v>6938234</v>
+        <v>6938396</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212714</v>
+        <v>121212757</v>
       </c>
       <c r="B118" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12616,25 +12616,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>526955</v>
+        <v>526927</v>
       </c>
       <c r="R118" t="n">
-        <v>6938368</v>
+        <v>6938376</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212736</v>
+        <v>121212771</v>
       </c>
       <c r="B119" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,25 +12718,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527250</v>
+        <v>527317</v>
       </c>
       <c r="R119" t="n">
-        <v>6938289</v>
+        <v>6938165</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212764</v>
+        <v>121212709</v>
       </c>
       <c r="B120" t="n">
-        <v>98098</v>
+        <v>78344</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>526945</v>
+        <v>526856</v>
       </c>
       <c r="R120" t="n">
-        <v>6938389</v>
+        <v>6938391</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121226822</v>
+        <v>121219596</v>
       </c>
       <c r="B121" t="n">
-        <v>91989</v>
+        <v>78343</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,41 +12922,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526182</v>
+        <v>526982</v>
       </c>
       <c r="R121" t="n">
-        <v>6938234</v>
+        <v>6937928</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226805</v>
+        <v>121220094</v>
       </c>
       <c r="B122" t="n">
-        <v>79688</v>
+        <v>78343</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,37 +13028,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526203</v>
+        <v>526766</v>
       </c>
       <c r="R122" t="n">
-        <v>6938195</v>
+        <v>6938100</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226797</v>
+        <v>121220916</v>
       </c>
       <c r="B124" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,41 +13228,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526496</v>
+        <v>526647</v>
       </c>
       <c r="R124" t="n">
-        <v>6938343</v>
+        <v>6938174</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13292,11 +13292,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13323,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121220094</v>
+        <v>121226810</v>
       </c>
       <c r="B125" t="n">
-        <v>78343</v>
+        <v>79688</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13339,37 +13334,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526766</v>
+        <v>526533</v>
       </c>
       <c r="R125" t="n">
-        <v>6938100</v>
+        <v>6938315</v>
       </c>
       <c r="S125" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13425,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226793</v>
+        <v>121226799</v>
       </c>
       <c r="B126" t="n">
-        <v>90733</v>
+        <v>79688</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13441,21 +13436,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13465,10 +13460,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526519</v>
+        <v>526747</v>
       </c>
       <c r="R126" t="n">
-        <v>6938315</v>
+        <v>6937983</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13527,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226802</v>
+        <v>121219658</v>
       </c>
       <c r="B127" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13539,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526716</v>
+        <v>526953</v>
       </c>
       <c r="R127" t="n">
-        <v>6937997</v>
+        <v>6937958</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13629,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226799</v>
+        <v>121226795</v>
       </c>
       <c r="B128" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13645,21 +13640,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526747</v>
+        <v>526554</v>
       </c>
       <c r="R128" t="n">
-        <v>6937983</v>
+        <v>6938311</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13731,7 +13726,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226810</v>
+        <v>121226807</v>
       </c>
       <c r="B129" t="n">
         <v>79688</v>
@@ -13771,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526533</v>
+        <v>526201</v>
       </c>
       <c r="R129" t="n">
-        <v>6938315</v>
+        <v>6938252</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13833,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226816</v>
+        <v>121212791</v>
       </c>
       <c r="B130" t="n">
-        <v>98098</v>
+        <v>79723</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13845,25 +13840,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526789</v>
+        <v>527094</v>
       </c>
       <c r="R130" t="n">
-        <v>6937993</v>
+        <v>6938358</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13903,12 +13898,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13935,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226813</v>
+        <v>121226819</v>
       </c>
       <c r="B131" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13947,25 +13942,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13975,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526365</v>
+        <v>526646</v>
       </c>
       <c r="R131" t="n">
-        <v>6938404</v>
+        <v>6938173</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14037,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121212783</v>
+        <v>121226791</v>
       </c>
       <c r="B132" t="n">
-        <v>78252</v>
+        <v>89764</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14053,21 +14048,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14077,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526761</v>
+        <v>526205</v>
       </c>
       <c r="R132" t="n">
-        <v>6938348</v>
+        <v>6938282</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14107,12 +14102,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,10 +14134,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121226796</v>
+        <v>121223305</v>
       </c>
       <c r="B133" t="n">
-        <v>90999</v>
+        <v>98098</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14151,41 +14146,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526796</v>
+        <v>526584</v>
       </c>
       <c r="R133" t="n">
-        <v>6937966</v>
+        <v>6938052</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14241,10 +14236,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226820</v>
+        <v>121212783</v>
       </c>
       <c r="B134" t="n">
-        <v>90727</v>
+        <v>78252</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14257,21 +14252,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14281,10 +14276,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526660</v>
+        <v>526761</v>
       </c>
       <c r="R134" t="n">
-        <v>6938167</v>
+        <v>6938348</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14311,12 +14306,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14343,10 +14338,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226824</v>
+        <v>121226796</v>
       </c>
       <c r="B135" t="n">
-        <v>91275</v>
+        <v>90999</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14355,25 +14350,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14383,10 +14378,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526747</v>
+        <v>526796</v>
       </c>
       <c r="R135" t="n">
-        <v>6937983</v>
+        <v>6937966</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14445,10 +14440,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226795</v>
+        <v>121226808</v>
       </c>
       <c r="B136" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14461,21 +14456,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14485,10 +14480,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526554</v>
+        <v>526482</v>
       </c>
       <c r="R136" t="n">
-        <v>6938311</v>
+        <v>6938338</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14547,10 +14542,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226807</v>
+        <v>121226814</v>
       </c>
       <c r="B137" t="n">
-        <v>79688</v>
+        <v>78343</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14563,21 +14558,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14582,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526201</v>
+        <v>526515</v>
       </c>
       <c r="R137" t="n">
-        <v>6938252</v>
+        <v>6938303</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14649,10 +14644,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226814</v>
+        <v>121221199</v>
       </c>
       <c r="B138" t="n">
-        <v>78343</v>
+        <v>78607</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14665,37 +14660,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526515</v>
+        <v>526592</v>
       </c>
       <c r="R138" t="n">
-        <v>6938303</v>
+        <v>6938232</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14751,10 +14746,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121212785</v>
+        <v>121212780</v>
       </c>
       <c r="B139" t="n">
-        <v>78252</v>
+        <v>78607</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14767,21 +14762,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526753</v>
+        <v>527567</v>
       </c>
       <c r="R139" t="n">
-        <v>6938395</v>
+        <v>6937949</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14853,7 +14848,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226806</v>
+        <v>121226804</v>
       </c>
       <c r="B140" t="n">
         <v>79688</v>
@@ -14893,10 +14888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526182</v>
+        <v>526224</v>
       </c>
       <c r="R140" t="n">
-        <v>6938206</v>
+        <v>6938191</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14955,10 +14950,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121212780</v>
+        <v>121226801</v>
       </c>
       <c r="B141" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14971,21 +14966,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14995,10 +14990,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>527567</v>
+        <v>526714</v>
       </c>
       <c r="R141" t="n">
-        <v>6937949</v>
+        <v>6938008</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15025,12 +15020,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15057,10 +15052,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121222671</v>
+        <v>121226802</v>
       </c>
       <c r="B142" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15073,37 +15068,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526275</v>
+        <v>526716</v>
       </c>
       <c r="R142" t="n">
-        <v>6938199</v>
+        <v>6937997</v>
       </c>
       <c r="S142" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15133,11 +15128,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15164,7 +15154,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121219596</v>
+        <v>121226813</v>
       </c>
       <c r="B143" t="n">
         <v>78343</v>
@@ -15200,17 +15190,17 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526982</v>
+        <v>526365</v>
       </c>
       <c r="R143" t="n">
-        <v>6937928</v>
+        <v>6938404</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15470,10 +15460,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121226803</v>
+        <v>121226793</v>
       </c>
       <c r="B146" t="n">
-        <v>79688</v>
+        <v>90733</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15486,21 +15476,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15510,10 +15500,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526335</v>
+        <v>526519</v>
       </c>
       <c r="R146" t="n">
-        <v>6938150</v>
+        <v>6938315</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15572,7 +15562,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226821</v>
+        <v>121222671</v>
       </c>
       <c r="B147" t="n">
         <v>78607</v>
@@ -15608,17 +15598,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526199</v>
+        <v>526275</v>
       </c>
       <c r="R147" t="n">
-        <v>6938254</v>
+        <v>6938199</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15679,10 +15669,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121220916</v>
+        <v>121226809</v>
       </c>
       <c r="B148" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15691,41 +15681,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526647</v>
+        <v>526518</v>
       </c>
       <c r="R148" t="n">
-        <v>6938174</v>
+        <v>6938295</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15781,10 +15771,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226819</v>
+        <v>121226821</v>
       </c>
       <c r="B149" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15793,25 +15783,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15821,10 +15811,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526646</v>
+        <v>526199</v>
       </c>
       <c r="R149" t="n">
-        <v>6938173</v>
+        <v>6938254</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15857,6 +15847,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15883,10 +15878,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121212779</v>
+        <v>121226817</v>
       </c>
       <c r="B150" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15895,25 +15890,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15923,10 +15918,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>527495</v>
+        <v>526581</v>
       </c>
       <c r="R150" t="n">
-        <v>6938009</v>
+        <v>6938053</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15953,12 +15948,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15985,10 +15980,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226812</v>
+        <v>121226822</v>
       </c>
       <c r="B151" t="n">
-        <v>79688</v>
+        <v>91989</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15997,25 +15992,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526551</v>
+        <v>526182</v>
       </c>
       <c r="R151" t="n">
-        <v>6938312</v>
+        <v>6938234</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16087,10 +16082,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226808</v>
+        <v>121226792</v>
       </c>
       <c r="B152" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16103,21 +16098,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16127,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526482</v>
+        <v>526796</v>
       </c>
       <c r="R152" t="n">
-        <v>6938338</v>
+        <v>6937966</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16189,7 +16184,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226804</v>
+        <v>121226805</v>
       </c>
       <c r="B153" t="n">
         <v>79688</v>
@@ -16229,10 +16224,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526224</v>
+        <v>526203</v>
       </c>
       <c r="R153" t="n">
-        <v>6938191</v>
+        <v>6938195</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16291,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121212789</v>
+        <v>121212776</v>
       </c>
       <c r="B154" t="n">
-        <v>91989</v>
+        <v>78607</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16303,25 +16298,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16331,10 +16326,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526823</v>
+        <v>527090</v>
       </c>
       <c r="R154" t="n">
-        <v>6938405</v>
+        <v>6938365</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16393,10 +16388,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226817</v>
+        <v>121212789</v>
       </c>
       <c r="B155" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16405,25 +16400,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16433,10 +16428,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526581</v>
+        <v>526823</v>
       </c>
       <c r="R155" t="n">
-        <v>6938053</v>
+        <v>6938405</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16463,12 +16458,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16495,10 +16490,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212791</v>
+        <v>121212788</v>
       </c>
       <c r="B156" t="n">
-        <v>79723</v>
+        <v>91989</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16511,21 +16506,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16535,10 +16530,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>527094</v>
+        <v>526776</v>
       </c>
       <c r="R156" t="n">
-        <v>6938358</v>
+        <v>6938419</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16597,10 +16592,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121221064</v>
+        <v>121212785</v>
       </c>
       <c r="B157" t="n">
-        <v>90727</v>
+        <v>78252</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16613,37 +16608,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1204</v>
+        <v>353</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526664</v>
+        <v>526753</v>
       </c>
       <c r="R157" t="n">
-        <v>6938176</v>
+        <v>6938395</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16667,12 +16662,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16699,10 +16694,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226792</v>
+        <v>121226824</v>
       </c>
       <c r="B158" t="n">
-        <v>90713</v>
+        <v>91275</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16711,25 +16706,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16739,10 +16734,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526796</v>
+        <v>526747</v>
       </c>
       <c r="R158" t="n">
-        <v>6937966</v>
+        <v>6937983</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16801,10 +16796,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226818</v>
+        <v>121226803</v>
       </c>
       <c r="B159" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16813,25 +16808,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16841,10 +16836,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526525</v>
+        <v>526335</v>
       </c>
       <c r="R159" t="n">
-        <v>6938312</v>
+        <v>6938150</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16903,10 +16898,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226809</v>
+        <v>121212779</v>
       </c>
       <c r="B160" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16919,21 +16914,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16943,10 +16938,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526518</v>
+        <v>527495</v>
       </c>
       <c r="R160" t="n">
-        <v>6938295</v>
+        <v>6938009</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16973,12 +16968,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17005,7 +17000,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121223305</v>
+        <v>121226818</v>
       </c>
       <c r="B161" t="n">
         <v>98098</v>
@@ -17041,17 +17036,17 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526584</v>
+        <v>526525</v>
       </c>
       <c r="R161" t="n">
-        <v>6938052</v>
+        <v>6938312</v>
       </c>
       <c r="S161" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17107,10 +17102,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226791</v>
+        <v>121226820</v>
       </c>
       <c r="B162" t="n">
-        <v>89764</v>
+        <v>90727</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17123,21 +17118,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17147,10 +17142,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526205</v>
+        <v>526660</v>
       </c>
       <c r="R162" t="n">
-        <v>6938282</v>
+        <v>6938167</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17209,10 +17204,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121212776</v>
+        <v>121226812</v>
       </c>
       <c r="B163" t="n">
-        <v>78607</v>
+        <v>79688</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17225,21 +17220,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>527090</v>
+        <v>526551</v>
       </c>
       <c r="R163" t="n">
-        <v>6938365</v>
+        <v>6938312</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17279,12 +17274,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17311,7 +17306,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226801</v>
+        <v>121226811</v>
       </c>
       <c r="B164" t="n">
         <v>79688</v>
@@ -17351,10 +17346,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526714</v>
+        <v>526545</v>
       </c>
       <c r="R164" t="n">
-        <v>6938008</v>
+        <v>6938319</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17413,7 +17408,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226811</v>
+        <v>121226797</v>
       </c>
       <c r="B165" t="n">
         <v>79688</v>
@@ -17453,10 +17448,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526545</v>
+        <v>526496</v>
       </c>
       <c r="R165" t="n">
-        <v>6938319</v>
+        <v>6938343</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17489,6 +17484,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121221199</v>
+        <v>121221064</v>
       </c>
       <c r="B166" t="n">
-        <v>78607</v>
+        <v>90727</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,21 +17531,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526592</v>
+        <v>526664</v>
       </c>
       <c r="R166" t="n">
-        <v>6938232</v>
+        <v>6938176</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121212788</v>
+        <v>121226806</v>
       </c>
       <c r="B167" t="n">
-        <v>91989</v>
+        <v>79688</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526776</v>
+        <v>526182</v>
       </c>
       <c r="R167" t="n">
-        <v>6938419</v>
+        <v>6938206</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121219658</v>
+        <v>121226816</v>
       </c>
       <c r="B168" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,41 +17731,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526953</v>
+        <v>526789</v>
       </c>
       <c r="R168" t="n">
-        <v>6937958</v>
+        <v>6937993</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18039,10 +18039,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121185408</v>
+        <v>121179849</v>
       </c>
       <c r="B171" t="n">
-        <v>90999</v>
+        <v>91153</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18051,41 +18051,41 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>527661</v>
+        <v>527658</v>
       </c>
       <c r="R171" t="n">
-        <v>6937695</v>
+        <v>6937694</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121179693</v>
+        <v>121185408</v>
       </c>
       <c r="B172" t="n">
-        <v>91989</v>
+        <v>90999</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,41 +18153,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527779</v>
+        <v>527661</v>
       </c>
       <c r="R172" t="n">
-        <v>6937594</v>
+        <v>6937695</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18243,10 +18243,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121179849</v>
+        <v>121179693</v>
       </c>
       <c r="B173" t="n">
-        <v>91153</v>
+        <v>91989</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18255,25 +18255,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18283,13 +18283,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>527658</v>
+        <v>527779</v>
       </c>
       <c r="R173" t="n">
-        <v>6937694</v>
+        <v>6937594</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121185396</v>
+        <v>121180261</v>
       </c>
       <c r="B25" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,41 +3105,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>526980</v>
+        <v>527506</v>
       </c>
       <c r="R25" t="n">
-        <v>6938115</v>
+        <v>6937752</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121180261</v>
+        <v>121185396</v>
       </c>
       <c r="B26" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,41 +3207,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>527506</v>
+        <v>526980</v>
       </c>
       <c r="R26" t="n">
-        <v>6937752</v>
+        <v>6938115</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185430</v>
+        <v>121185410</v>
       </c>
       <c r="B34" t="n">
-        <v>91989</v>
+        <v>79688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527460</v>
+        <v>527024</v>
       </c>
       <c r="R34" t="n">
-        <v>6937819</v>
+        <v>6938111</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185410</v>
+        <v>121185430</v>
       </c>
       <c r="B35" t="n">
-        <v>79688</v>
+        <v>91989</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,25 +4125,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527024</v>
+        <v>527460</v>
       </c>
       <c r="R35" t="n">
-        <v>6938111</v>
+        <v>6937819</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212710</v>
+        <v>121212769</v>
       </c>
       <c r="B58" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527495</v>
+        <v>527263</v>
       </c>
       <c r="R58" t="n">
-        <v>6938009</v>
+        <v>6938242</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6535,11 +6535,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6566,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212753</v>
+        <v>121212710</v>
       </c>
       <c r="B59" t="n">
-        <v>78343</v>
+        <v>79688</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6582,21 +6577,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6606,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526856</v>
+        <v>527495</v>
       </c>
       <c r="R59" t="n">
-        <v>6938391</v>
+        <v>6938009</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6642,6 +6637,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6668,10 +6668,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212726</v>
+        <v>121212753</v>
       </c>
       <c r="B60" t="n">
-        <v>79688</v>
+        <v>78343</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,21 +6684,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527148</v>
+        <v>526856</v>
       </c>
       <c r="R60" t="n">
-        <v>6938301</v>
+        <v>6938391</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6770,10 +6770,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212745</v>
+        <v>121212726</v>
       </c>
       <c r="B61" t="n">
-        <v>79724</v>
+        <v>79688</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6782,25 +6782,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>526960</v>
+        <v>527148</v>
       </c>
       <c r="R61" t="n">
-        <v>6938390</v>
+        <v>6938301</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6872,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212769</v>
+        <v>121212745</v>
       </c>
       <c r="B62" t="n">
-        <v>98098</v>
+        <v>79724</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6884,25 +6884,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527263</v>
+        <v>526960</v>
       </c>
       <c r="R62" t="n">
-        <v>6938242</v>
+        <v>6938390</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7693,10 +7693,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212705</v>
+        <v>121212692</v>
       </c>
       <c r="B70" t="n">
-        <v>90999</v>
+        <v>57507</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7709,21 +7709,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527310</v>
+        <v>527210</v>
       </c>
       <c r="R70" t="n">
-        <v>6938160</v>
+        <v>6938291</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7769,6 +7769,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7795,7 +7800,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212703</v>
+        <v>121212705</v>
       </c>
       <c r="B71" t="n">
         <v>90999</v>
@@ -7835,10 +7840,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527253</v>
+        <v>527310</v>
       </c>
       <c r="R71" t="n">
-        <v>6938232</v>
+        <v>6938160</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7897,10 +7902,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212692</v>
+        <v>121212703</v>
       </c>
       <c r="B72" t="n">
-        <v>57507</v>
+        <v>90999</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7913,21 +7918,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7937,10 +7942,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527210</v>
+        <v>527253</v>
       </c>
       <c r="R72" t="n">
-        <v>6938291</v>
+        <v>6938232</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7973,11 +7978,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9233,10 +9233,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212698</v>
+        <v>121212744</v>
       </c>
       <c r="B85" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9249,21 +9249,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527211</v>
+        <v>527495</v>
       </c>
       <c r="R85" t="n">
-        <v>6938302</v>
+        <v>6938012</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9335,7 +9335,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212744</v>
+        <v>121212713</v>
       </c>
       <c r="B86" t="n">
         <v>79688</v>
@@ -9375,10 +9375,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527495</v>
+        <v>526960</v>
       </c>
       <c r="R86" t="n">
-        <v>6938012</v>
+        <v>6938390</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212713</v>
+        <v>121212711</v>
       </c>
       <c r="B87" t="n">
         <v>79688</v>
@@ -9477,10 +9477,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526960</v>
+        <v>527051</v>
       </c>
       <c r="R87" t="n">
-        <v>6938390</v>
+        <v>6938349</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9539,10 +9539,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212711</v>
+        <v>121212698</v>
       </c>
       <c r="B88" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9555,21 +9555,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9579,10 +9579,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527051</v>
+        <v>527211</v>
       </c>
       <c r="R88" t="n">
-        <v>6938349</v>
+        <v>6938302</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212697</v>
+        <v>121212708</v>
       </c>
       <c r="B104" t="n">
-        <v>79689</v>
+        <v>97052</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11188,25 +11188,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11216,10 +11216,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527186</v>
+        <v>527252</v>
       </c>
       <c r="R104" t="n">
-        <v>6938273</v>
+        <v>6938285</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11278,10 +11278,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212724</v>
+        <v>121212697</v>
       </c>
       <c r="B105" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11294,21 +11294,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527109</v>
+        <v>527186</v>
       </c>
       <c r="R105" t="n">
-        <v>6938336</v>
+        <v>6938273</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11380,10 +11380,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212695</v>
+        <v>121212724</v>
       </c>
       <c r="B106" t="n">
-        <v>79717</v>
+        <v>79688</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11392,25 +11392,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11420,10 +11420,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527184</v>
+        <v>527109</v>
       </c>
       <c r="R106" t="n">
-        <v>6938280</v>
+        <v>6938336</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11482,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212734</v>
+        <v>121212695</v>
       </c>
       <c r="B107" t="n">
-        <v>79688</v>
+        <v>79717</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11494,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11522,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527214</v>
+        <v>527184</v>
       </c>
       <c r="R107" t="n">
-        <v>6938296</v>
+        <v>6938280</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,7 +11584,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212733</v>
+        <v>121212734</v>
       </c>
       <c r="B108" t="n">
         <v>79688</v>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527186</v>
+        <v>527214</v>
       </c>
       <c r="R108" t="n">
-        <v>6938273</v>
+        <v>6938296</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212714</v>
+        <v>121212733</v>
       </c>
       <c r="B109" t="n">
         <v>79688</v>
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526955</v>
+        <v>527186</v>
       </c>
       <c r="R109" t="n">
-        <v>6938368</v>
+        <v>6938273</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212722</v>
+        <v>121212714</v>
       </c>
       <c r="B110" t="n">
         <v>79688</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527075</v>
+        <v>526955</v>
       </c>
       <c r="R110" t="n">
-        <v>6938349</v>
+        <v>6938368</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,7 +11890,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212740</v>
+        <v>121212722</v>
       </c>
       <c r="B111" t="n">
         <v>79688</v>
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527350</v>
+        <v>527075</v>
       </c>
       <c r="R111" t="n">
-        <v>6938133</v>
+        <v>6938349</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212708</v>
+        <v>121212740</v>
       </c>
       <c r="B112" t="n">
-        <v>97052</v>
+        <v>79688</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12004,25 +12004,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>527252</v>
+        <v>527350</v>
       </c>
       <c r="R112" t="n">
-        <v>6938285</v>
+        <v>6938133</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12094,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212721</v>
+        <v>121212709</v>
       </c>
       <c r="B113" t="n">
-        <v>79688</v>
+        <v>78344</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12110,21 +12110,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12134,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>527074</v>
+        <v>526856</v>
       </c>
       <c r="R113" t="n">
-        <v>6938353</v>
+        <v>6938391</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12196,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212699</v>
+        <v>121212721</v>
       </c>
       <c r="B114" t="n">
-        <v>79592</v>
+        <v>79688</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12208,25 +12208,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12236,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527249</v>
+        <v>527074</v>
       </c>
       <c r="R114" t="n">
-        <v>6938289</v>
+        <v>6938353</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,10 +12298,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212712</v>
+        <v>121212699</v>
       </c>
       <c r="B115" t="n">
-        <v>79688</v>
+        <v>79592</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12310,25 +12310,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>526743</v>
+        <v>527249</v>
       </c>
       <c r="R115" t="n">
-        <v>6938415</v>
+        <v>6938289</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,10 +12400,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212762</v>
+        <v>121212712</v>
       </c>
       <c r="B116" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12412,25 +12412,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12440,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>526868</v>
+        <v>526743</v>
       </c>
       <c r="R116" t="n">
-        <v>6938367</v>
+        <v>6938415</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12502,7 +12502,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212760</v>
+        <v>121212762</v>
       </c>
       <c r="B117" t="n">
         <v>98098</v>
@@ -12542,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>526842</v>
+        <v>526868</v>
       </c>
       <c r="R117" t="n">
-        <v>6938396</v>
+        <v>6938367</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,7 +12604,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212757</v>
+        <v>121212760</v>
       </c>
       <c r="B118" t="n">
         <v>98098</v>
@@ -12644,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>526927</v>
+        <v>526842</v>
       </c>
       <c r="R118" t="n">
-        <v>6938376</v>
+        <v>6938396</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12706,7 +12706,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212771</v>
+        <v>121212757</v>
       </c>
       <c r="B119" t="n">
         <v>98098</v>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527317</v>
+        <v>526927</v>
       </c>
       <c r="R119" t="n">
-        <v>6938165</v>
+        <v>6938376</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212709</v>
+        <v>121212771</v>
       </c>
       <c r="B120" t="n">
-        <v>78344</v>
+        <v>98098</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>526856</v>
+        <v>527317</v>
       </c>
       <c r="R120" t="n">
-        <v>6938391</v>
+        <v>6938165</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226799</v>
+        <v>121219658</v>
       </c>
       <c r="B126" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,41 +13432,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526747</v>
+        <v>526953</v>
       </c>
       <c r="R126" t="n">
-        <v>6937983</v>
+        <v>6937958</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121219658</v>
+        <v>121226799</v>
       </c>
       <c r="B127" t="n">
-        <v>90678</v>
+        <v>79688</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526953</v>
+        <v>526747</v>
       </c>
       <c r="R127" t="n">
-        <v>6937958</v>
+        <v>6937983</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121221064</v>
+        <v>121226806</v>
       </c>
       <c r="B166" t="n">
-        <v>90727</v>
+        <v>79688</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,37 +17531,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526664</v>
+        <v>526182</v>
       </c>
       <c r="R166" t="n">
-        <v>6938176</v>
+        <v>6938206</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226806</v>
+        <v>121226816</v>
       </c>
       <c r="B167" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526182</v>
+        <v>526789</v>
       </c>
       <c r="R167" t="n">
-        <v>6938206</v>
+        <v>6937993</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226816</v>
+        <v>121221064</v>
       </c>
       <c r="B168" t="n">
-        <v>98098</v>
+        <v>90727</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,41 +17731,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526789</v>
+        <v>526664</v>
       </c>
       <c r="R168" t="n">
-        <v>6937993</v>
+        <v>6938176</v>
       </c>
       <c r="S168" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185432</v>
+        <v>121185400</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>90713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527217</v>
+        <v>527034</v>
       </c>
       <c r="R11" t="n">
-        <v>6937854</v>
+        <v>6938099</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185400</v>
+        <v>121185413</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,21 +1783,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527034</v>
+        <v>527044</v>
       </c>
       <c r="R12" t="n">
-        <v>6938099</v>
+        <v>6938065</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185413</v>
+        <v>121185402</v>
       </c>
       <c r="B13" t="n">
-        <v>79688</v>
+        <v>79717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527044</v>
+        <v>527367</v>
       </c>
       <c r="R13" t="n">
-        <v>6938065</v>
+        <v>6937938</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185402</v>
+        <v>121185432</v>
       </c>
       <c r="B14" t="n">
-        <v>79717</v>
+        <v>91989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527367</v>
+        <v>527217</v>
       </c>
       <c r="R14" t="n">
-        <v>6937938</v>
+        <v>6937854</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121185426</v>
+        <v>121180230</v>
       </c>
       <c r="B16" t="n">
-        <v>98098</v>
+        <v>105203</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,41 +2187,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527503</v>
+        <v>527509</v>
       </c>
       <c r="R16" t="n">
-        <v>6937855</v>
+        <v>6937756</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121180230</v>
+        <v>121185426</v>
       </c>
       <c r="B17" t="n">
-        <v>105203</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,41 +2289,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527509</v>
+        <v>527503</v>
       </c>
       <c r="R17" t="n">
-        <v>6937756</v>
+        <v>6937855</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185410</v>
+        <v>121185430</v>
       </c>
       <c r="B34" t="n">
-        <v>79688</v>
+        <v>91989</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527024</v>
+        <v>527460</v>
       </c>
       <c r="R34" t="n">
-        <v>6938111</v>
+        <v>6937819</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185430</v>
+        <v>121185410</v>
       </c>
       <c r="B35" t="n">
-        <v>91989</v>
+        <v>79688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,25 +4125,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527460</v>
+        <v>527024</v>
       </c>
       <c r="R35" t="n">
-        <v>6937819</v>
+        <v>6938111</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -11176,10 +11176,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212708</v>
+        <v>121212697</v>
       </c>
       <c r="B104" t="n">
-        <v>97052</v>
+        <v>79689</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11188,25 +11188,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11216,10 +11216,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527252</v>
+        <v>527186</v>
       </c>
       <c r="R104" t="n">
-        <v>6938285</v>
+        <v>6938273</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11278,10 +11278,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212697</v>
+        <v>121212724</v>
       </c>
       <c r="B105" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11294,21 +11294,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527186</v>
+        <v>527109</v>
       </c>
       <c r="R105" t="n">
-        <v>6938273</v>
+        <v>6938336</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11380,10 +11380,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212724</v>
+        <v>121212695</v>
       </c>
       <c r="B106" t="n">
-        <v>79688</v>
+        <v>79717</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11392,25 +11392,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11420,10 +11420,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527109</v>
+        <v>527184</v>
       </c>
       <c r="R106" t="n">
-        <v>6938336</v>
+        <v>6938280</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11482,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212695</v>
+        <v>121212734</v>
       </c>
       <c r="B107" t="n">
-        <v>79717</v>
+        <v>79688</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11494,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11522,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527184</v>
+        <v>527214</v>
       </c>
       <c r="R107" t="n">
-        <v>6938280</v>
+        <v>6938296</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,7 +11584,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212734</v>
+        <v>121212733</v>
       </c>
       <c r="B108" t="n">
         <v>79688</v>
@@ -11624,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527214</v>
+        <v>527186</v>
       </c>
       <c r="R108" t="n">
-        <v>6938296</v>
+        <v>6938273</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,7 +11686,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212733</v>
+        <v>121212714</v>
       </c>
       <c r="B109" t="n">
         <v>79688</v>
@@ -11726,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>527186</v>
+        <v>526955</v>
       </c>
       <c r="R109" t="n">
-        <v>6938273</v>
+        <v>6938368</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212714</v>
+        <v>121212722</v>
       </c>
       <c r="B110" t="n">
         <v>79688</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>526955</v>
+        <v>527075</v>
       </c>
       <c r="R110" t="n">
-        <v>6938368</v>
+        <v>6938349</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,7 +11890,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212722</v>
+        <v>121212740</v>
       </c>
       <c r="B111" t="n">
         <v>79688</v>
@@ -11930,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527075</v>
+        <v>527350</v>
       </c>
       <c r="R111" t="n">
-        <v>6938349</v>
+        <v>6938133</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212740</v>
+        <v>121212708</v>
       </c>
       <c r="B112" t="n">
-        <v>79688</v>
+        <v>97052</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12004,25 +12004,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12032,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>527350</v>
+        <v>527252</v>
       </c>
       <c r="R112" t="n">
-        <v>6938133</v>
+        <v>6938285</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121219658</v>
+        <v>121226799</v>
       </c>
       <c r="B126" t="n">
-        <v>90678</v>
+        <v>79688</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,41 +13432,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526953</v>
+        <v>526747</v>
       </c>
       <c r="R126" t="n">
-        <v>6937958</v>
+        <v>6937983</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226799</v>
+        <v>121219658</v>
       </c>
       <c r="B127" t="n">
-        <v>79688</v>
+        <v>90678</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13534,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526747</v>
+        <v>526953</v>
       </c>
       <c r="R127" t="n">
-        <v>6937983</v>
+        <v>6937958</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226795</v>
+        <v>121226807</v>
       </c>
       <c r="B128" t="n">
-        <v>79689</v>
+        <v>79688</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13640,21 +13640,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526554</v>
+        <v>526201</v>
       </c>
       <c r="R128" t="n">
-        <v>6938311</v>
+        <v>6938252</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226807</v>
+        <v>121212791</v>
       </c>
       <c r="B129" t="n">
-        <v>79688</v>
+        <v>79723</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13738,25 +13738,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526201</v>
+        <v>527094</v>
       </c>
       <c r="R129" t="n">
-        <v>6938252</v>
+        <v>6938358</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13796,12 +13796,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121212791</v>
+        <v>121226795</v>
       </c>
       <c r="B130" t="n">
-        <v>79723</v>
+        <v>79689</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13840,25 +13840,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>527094</v>
+        <v>526554</v>
       </c>
       <c r="R130" t="n">
-        <v>6938358</v>
+        <v>6938311</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13898,12 +13898,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16082,10 +16082,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226792</v>
+        <v>121226805</v>
       </c>
       <c r="B152" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16098,21 +16098,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16122,10 +16122,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526796</v>
+        <v>526203</v>
       </c>
       <c r="R152" t="n">
-        <v>6937966</v>
+        <v>6938195</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16184,10 +16184,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226805</v>
+        <v>121212776</v>
       </c>
       <c r="B153" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16200,21 +16200,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16224,10 +16224,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526203</v>
+        <v>527090</v>
       </c>
       <c r="R153" t="n">
-        <v>6938195</v>
+        <v>6938365</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16254,12 +16254,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16286,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121212776</v>
+        <v>121212789</v>
       </c>
       <c r="B154" t="n">
-        <v>78607</v>
+        <v>91989</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16298,25 +16298,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16326,10 +16326,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>527090</v>
+        <v>526823</v>
       </c>
       <c r="R154" t="n">
-        <v>6938365</v>
+        <v>6938405</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16388,7 +16388,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121212789</v>
+        <v>121212788</v>
       </c>
       <c r="B155" t="n">
         <v>91989</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526823</v>
+        <v>526776</v>
       </c>
       <c r="R155" t="n">
-        <v>6938405</v>
+        <v>6938419</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16490,10 +16490,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212788</v>
+        <v>121226792</v>
       </c>
       <c r="B156" t="n">
-        <v>91989</v>
+        <v>90713</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16502,25 +16502,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526776</v>
+        <v>526796</v>
       </c>
       <c r="R156" t="n">
-        <v>6938419</v>
+        <v>6937966</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16560,12 +16560,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226806</v>
+        <v>121221064</v>
       </c>
       <c r="B166" t="n">
-        <v>79688</v>
+        <v>90727</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,37 +17531,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526182</v>
+        <v>526664</v>
       </c>
       <c r="R166" t="n">
-        <v>6938206</v>
+        <v>6938176</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226816</v>
+        <v>121226806</v>
       </c>
       <c r="B167" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17629,25 +17629,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526789</v>
+        <v>526182</v>
       </c>
       <c r="R167" t="n">
-        <v>6937993</v>
+        <v>6938206</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121221064</v>
+        <v>121226816</v>
       </c>
       <c r="B168" t="n">
-        <v>90727</v>
+        <v>98098</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,41 +17731,41 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526664</v>
+        <v>526789</v>
       </c>
       <c r="R168" t="n">
-        <v>6938176</v>
+        <v>6937993</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121185424</v>
+        <v>121185425</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>527010</v>
+        <v>527014</v>
       </c>
       <c r="R6" t="n">
-        <v>6938105</v>
+        <v>6938062</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185405</v>
+        <v>121185430</v>
       </c>
       <c r="B7" t="n">
-        <v>90999</v>
+        <v>91995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527034</v>
+        <v>527460</v>
       </c>
       <c r="R7" t="n">
-        <v>6938099</v>
+        <v>6937819</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121179876</v>
+        <v>121185411</v>
       </c>
       <c r="B8" t="n">
-        <v>90999</v>
+        <v>79689</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,37 +1375,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527649</v>
+        <v>527045</v>
       </c>
       <c r="R8" t="n">
-        <v>6937696</v>
+        <v>6938075</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185428</v>
+        <v>121185421</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1473,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527439</v>
+        <v>526958</v>
       </c>
       <c r="R9" t="n">
-        <v>6937974</v>
+        <v>6938116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121180141</v>
+        <v>121180239</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,13 +1603,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527597</v>
+        <v>527495</v>
       </c>
       <c r="R10" t="n">
-        <v>6937703</v>
+        <v>6937765</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121185400</v>
+        <v>121185399</v>
       </c>
       <c r="B11" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>527034</v>
+        <v>526989</v>
       </c>
       <c r="R11" t="n">
-        <v>6938099</v>
+        <v>6938147</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121185413</v>
+        <v>121185423</v>
       </c>
       <c r="B12" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,25 +1779,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>527044</v>
+        <v>526974</v>
       </c>
       <c r="R12" t="n">
-        <v>6938065</v>
+        <v>6938145</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1869,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121185402</v>
+        <v>121185400</v>
       </c>
       <c r="B13" t="n">
-        <v>79717</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,25 +1881,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527367</v>
+        <v>527034</v>
       </c>
       <c r="R13" t="n">
-        <v>6937938</v>
+        <v>6938099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121185432</v>
+        <v>121185396</v>
       </c>
       <c r="B14" t="n">
-        <v>91989</v>
+        <v>90684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527217</v>
+        <v>526980</v>
       </c>
       <c r="R14" t="n">
-        <v>6937854</v>
+        <v>6938115</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121185397</v>
+        <v>121185410</v>
       </c>
       <c r="B15" t="n">
-        <v>90678</v>
+        <v>79689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527043</v>
+        <v>527024</v>
       </c>
       <c r="R15" t="n">
-        <v>6938062</v>
+        <v>6938111</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121180230</v>
+        <v>121185426</v>
       </c>
       <c r="B16" t="n">
-        <v>105203</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,41 +2187,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527509</v>
+        <v>527503</v>
       </c>
       <c r="R16" t="n">
-        <v>6937756</v>
+        <v>6937855</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121185426</v>
+        <v>121185422</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>527503</v>
+        <v>526995</v>
       </c>
       <c r="R17" t="n">
-        <v>6937855</v>
+        <v>6938144</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121185435</v>
+        <v>121185416</v>
       </c>
       <c r="B18" t="n">
-        <v>91369</v>
+        <v>79689</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>527008</v>
+        <v>527367</v>
       </c>
       <c r="R18" t="n">
-        <v>6938073</v>
+        <v>6937938</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121185423</v>
+        <v>121185403</v>
       </c>
       <c r="B19" t="n">
-        <v>98098</v>
+        <v>90666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,25 +2493,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>526974</v>
+        <v>527012</v>
       </c>
       <c r="R19" t="n">
-        <v>6938145</v>
+        <v>6938063</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121180291</v>
+        <v>121185414</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>79689</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2599,37 +2599,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>527492</v>
+        <v>527346</v>
       </c>
       <c r="R20" t="n">
-        <v>6937763</v>
+        <v>6937925</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121185418</v>
+        <v>121180291</v>
       </c>
       <c r="B21" t="n">
-        <v>79688</v>
+        <v>90737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,37 +2701,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>527437</v>
+        <v>527492</v>
       </c>
       <c r="R21" t="n">
-        <v>6937974</v>
+        <v>6937763</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121185412</v>
+        <v>121185432</v>
       </c>
       <c r="B22" t="n">
-        <v>79688</v>
+        <v>91995</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2799,25 +2799,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>527001</v>
+        <v>527217</v>
       </c>
       <c r="R22" t="n">
-        <v>6938101</v>
+        <v>6937854</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121185401</v>
+        <v>121180230</v>
       </c>
       <c r="B23" t="n">
-        <v>90713</v>
+        <v>105209</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,41 +2901,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>527016</v>
+        <v>527509</v>
       </c>
       <c r="R23" t="n">
-        <v>6938060</v>
+        <v>6937756</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121185421</v>
+        <v>121185412</v>
       </c>
       <c r="B24" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,25 +3003,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>526958</v>
+        <v>527001</v>
       </c>
       <c r="R24" t="n">
-        <v>6938116</v>
+        <v>6938101</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121180261</v>
+        <v>121185427</v>
       </c>
       <c r="B25" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,41 +3105,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>527506</v>
+        <v>527034</v>
       </c>
       <c r="R25" t="n">
-        <v>6937752</v>
+        <v>6938099</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121185396</v>
+        <v>121182248</v>
       </c>
       <c r="B26" t="n">
-        <v>90678</v>
+        <v>98104</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,41 +3207,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>526980</v>
+        <v>527008</v>
       </c>
       <c r="R26" t="n">
-        <v>6938115</v>
+        <v>6938092</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3297,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121185434</v>
+        <v>121179977</v>
       </c>
       <c r="B27" t="n">
-        <v>91989</v>
+        <v>78608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,41 +3309,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>526953</v>
+        <v>527626</v>
       </c>
       <c r="R27" t="n">
-        <v>6938054</v>
+        <v>6937719</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3399,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121183281</v>
+        <v>121185398</v>
       </c>
       <c r="B28" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3411,41 +3411,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>526958</v>
+        <v>526983</v>
       </c>
       <c r="R28" t="n">
-        <v>6938109</v>
+        <v>6938135</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121185395</v>
+        <v>121185435</v>
       </c>
       <c r="B29" t="n">
-        <v>95645</v>
+        <v>91375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,25 +3513,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>898</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>527048</v>
+        <v>527008</v>
       </c>
       <c r="R29" t="n">
-        <v>6938076</v>
+        <v>6938073</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185411</v>
+        <v>121185415</v>
       </c>
       <c r="B30" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527045</v>
+        <v>527391</v>
       </c>
       <c r="R30" t="n">
-        <v>6938075</v>
+        <v>6937910</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185417</v>
+        <v>121185424</v>
       </c>
       <c r="B31" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,25 +3717,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527368</v>
+        <v>527010</v>
       </c>
       <c r="R31" t="n">
-        <v>6937959</v>
+        <v>6938105</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121185407</v>
+        <v>121180141</v>
       </c>
       <c r="B32" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,41 +3819,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527016</v>
+        <v>527597</v>
       </c>
       <c r="R32" t="n">
-        <v>6938062</v>
+        <v>6937703</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121179977</v>
+        <v>121180712</v>
       </c>
       <c r="B33" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527626</v>
+        <v>527305</v>
       </c>
       <c r="R33" t="n">
-        <v>6937719</v>
+        <v>6937895</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4011,10 +4011,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121185430</v>
+        <v>121185401</v>
       </c>
       <c r="B34" t="n">
-        <v>91989</v>
+        <v>90719</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4023,25 +4023,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>527460</v>
+        <v>527016</v>
       </c>
       <c r="R34" t="n">
-        <v>6937819</v>
+        <v>6938060</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121185410</v>
+        <v>121185434</v>
       </c>
       <c r="B35" t="n">
-        <v>79688</v>
+        <v>91995</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4125,25 +4125,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4153,10 +4153,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>527024</v>
+        <v>526953</v>
       </c>
       <c r="R35" t="n">
-        <v>6938111</v>
+        <v>6938054</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121185425</v>
+        <v>121185433</v>
       </c>
       <c r="B36" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4227,25 +4227,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4255,10 +4255,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>527014</v>
+        <v>527195</v>
       </c>
       <c r="R36" t="n">
-        <v>6938062</v>
+        <v>6937884</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4317,10 +4317,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121183008</v>
+        <v>121185409</v>
       </c>
       <c r="B37" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4329,41 +4329,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>526999</v>
+        <v>527108</v>
       </c>
       <c r="R37" t="n">
-        <v>6938157</v>
+        <v>6938086</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121180239</v>
+        <v>121185407</v>
       </c>
       <c r="B38" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4431,41 +4431,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>527495</v>
+        <v>527016</v>
       </c>
       <c r="R38" t="n">
-        <v>6937765</v>
+        <v>6938062</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121185422</v>
+        <v>121185431</v>
       </c>
       <c r="B39" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,25 +4533,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>526995</v>
+        <v>527439</v>
       </c>
       <c r="R39" t="n">
-        <v>6938144</v>
+        <v>6937815</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121180712</v>
+        <v>121185429</v>
       </c>
       <c r="B40" t="n">
-        <v>78607</v>
+        <v>91995</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4635,41 +4635,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527305</v>
+        <v>527641</v>
       </c>
       <c r="R40" t="n">
-        <v>6937895</v>
+        <v>6937808</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121182248</v>
+        <v>121185418</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,41 +4737,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527008</v>
+        <v>527437</v>
       </c>
       <c r="R41" t="n">
-        <v>6938092</v>
+        <v>6937974</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185416</v>
+        <v>121185419</v>
       </c>
       <c r="B42" t="n">
-        <v>79688</v>
+        <v>79725</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4839,25 +4839,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527367</v>
+        <v>527001</v>
       </c>
       <c r="R42" t="n">
-        <v>6937938</v>
+        <v>6938096</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185415</v>
+        <v>121185402</v>
       </c>
       <c r="B43" t="n">
-        <v>79688</v>
+        <v>79718</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,25 +4941,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527391</v>
+        <v>527367</v>
       </c>
       <c r="R43" t="n">
-        <v>6937910</v>
+        <v>6937938</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121185431</v>
+        <v>121183008</v>
       </c>
       <c r="B44" t="n">
-        <v>91989</v>
+        <v>98104</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>527439</v>
+        <v>526999</v>
       </c>
       <c r="R44" t="n">
-        <v>6937815</v>
+        <v>6938157</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5133,10 +5133,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121185398</v>
+        <v>121185406</v>
       </c>
       <c r="B45" t="n">
-        <v>90713</v>
+        <v>91005</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>526983</v>
+        <v>527009</v>
       </c>
       <c r="R45" t="n">
-        <v>6938135</v>
+        <v>6938044</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121185403</v>
+        <v>121185417</v>
       </c>
       <c r="B46" t="n">
-        <v>90660</v>
+        <v>79689</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5251,21 +5251,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>527012</v>
+        <v>527368</v>
       </c>
       <c r="R46" t="n">
-        <v>6938063</v>
+        <v>6937959</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5337,10 +5337,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121185399</v>
+        <v>121185428</v>
       </c>
       <c r="B47" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>526989</v>
+        <v>527439</v>
       </c>
       <c r="R47" t="n">
-        <v>6938147</v>
+        <v>6937974</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121185427</v>
+        <v>121185413</v>
       </c>
       <c r="B48" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>527034</v>
+        <v>527044</v>
       </c>
       <c r="R48" t="n">
-        <v>6938099</v>
+        <v>6938065</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121185409</v>
+        <v>121179876</v>
       </c>
       <c r="B49" t="n">
-        <v>79688</v>
+        <v>91005</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5557,37 +5557,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>527108</v>
+        <v>527649</v>
       </c>
       <c r="R49" t="n">
-        <v>6938086</v>
+        <v>6937696</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121185419</v>
+        <v>121180261</v>
       </c>
       <c r="B50" t="n">
-        <v>79724</v>
+        <v>98104</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5655,41 +5655,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>527001</v>
+        <v>527506</v>
       </c>
       <c r="R50" t="n">
-        <v>6938096</v>
+        <v>6937752</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121185414</v>
+        <v>121185405</v>
       </c>
       <c r="B51" t="n">
-        <v>79688</v>
+        <v>91005</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5761,21 +5761,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>527346</v>
+        <v>527034</v>
       </c>
       <c r="R51" t="n">
-        <v>6937925</v>
+        <v>6938099</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -5847,10 +5847,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121185429</v>
+        <v>121185395</v>
       </c>
       <c r="B52" t="n">
-        <v>91989</v>
+        <v>95651</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5859,25 +5859,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>527641</v>
+        <v>527048</v>
       </c>
       <c r="R52" t="n">
-        <v>6937808</v>
+        <v>6938076</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121185406</v>
+        <v>121183281</v>
       </c>
       <c r="B53" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>527009</v>
+        <v>526958</v>
       </c>
       <c r="R53" t="n">
-        <v>6938044</v>
+        <v>6938109</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185433</v>
+        <v>121185397</v>
       </c>
       <c r="B54" t="n">
-        <v>91989</v>
+        <v>90684</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6067,21 +6067,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527195</v>
+        <v>527043</v>
       </c>
       <c r="R54" t="n">
-        <v>6937884</v>
+        <v>6938062</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212738</v>
+        <v>121212694</v>
       </c>
       <c r="B55" t="n">
-        <v>79688</v>
+        <v>79718</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527288</v>
+        <v>527088</v>
       </c>
       <c r="R55" t="n">
-        <v>6938221</v>
+        <v>6938356</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212746</v>
+        <v>121212735</v>
       </c>
       <c r="B56" t="n">
-        <v>79724</v>
+        <v>79689</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527088</v>
+        <v>527245</v>
       </c>
       <c r="R56" t="n">
-        <v>6938356</v>
+        <v>6938291</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212761</v>
+        <v>121212730</v>
       </c>
       <c r="B57" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6369,25 +6369,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526852</v>
+        <v>527177</v>
       </c>
       <c r="R57" t="n">
-        <v>6938391</v>
+        <v>6938273</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212769</v>
+        <v>121212701</v>
       </c>
       <c r="B58" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6471,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527263</v>
+        <v>526960</v>
       </c>
       <c r="R58" t="n">
-        <v>6938242</v>
+        <v>6938387</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212710</v>
+        <v>121212763</v>
       </c>
       <c r="B59" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527495</v>
+        <v>526911</v>
       </c>
       <c r="R59" t="n">
-        <v>6938009</v>
+        <v>6938360</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6637,11 +6637,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6668,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212753</v>
+        <v>121212734</v>
       </c>
       <c r="B60" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6684,21 +6679,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6708,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526856</v>
+        <v>527214</v>
       </c>
       <c r="R60" t="n">
-        <v>6938391</v>
+        <v>6938296</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6770,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212726</v>
+        <v>121212714</v>
       </c>
       <c r="B61" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6810,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527148</v>
+        <v>526955</v>
       </c>
       <c r="R61" t="n">
-        <v>6938301</v>
+        <v>6938368</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6872,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212745</v>
+        <v>121212712</v>
       </c>
       <c r="B62" t="n">
-        <v>79724</v>
+        <v>79689</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6884,25 +6879,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526960</v>
+        <v>526743</v>
       </c>
       <c r="R62" t="n">
-        <v>6938390</v>
+        <v>6938415</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6974,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212690</v>
+        <v>121212732</v>
       </c>
       <c r="B63" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6990,21 +6985,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7014,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527263</v>
+        <v>527184</v>
       </c>
       <c r="R63" t="n">
-        <v>6938234</v>
+        <v>6938280</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7076,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212689</v>
+        <v>121212737</v>
       </c>
       <c r="B64" t="n">
-        <v>79225</v>
+        <v>79689</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7092,21 +7087,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7116,10 +7111,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>526855</v>
+        <v>527248</v>
       </c>
       <c r="R64" t="n">
-        <v>6938391</v>
+        <v>6938256</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7178,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212725</v>
+        <v>121212726</v>
       </c>
       <c r="B65" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7218,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527111</v>
+        <v>527148</v>
       </c>
       <c r="R65" t="n">
-        <v>6938327</v>
+        <v>6938301</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7280,10 +7275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212715</v>
+        <v>121212717</v>
       </c>
       <c r="B66" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7320,10 +7315,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>526971</v>
+        <v>527023</v>
       </c>
       <c r="R66" t="n">
-        <v>6938369</v>
+        <v>6938359</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7382,10 +7377,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212763</v>
+        <v>121212739</v>
       </c>
       <c r="B67" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7394,25 +7389,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7422,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526911</v>
+        <v>527304</v>
       </c>
       <c r="R67" t="n">
-        <v>6938360</v>
+        <v>6938173</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7484,10 +7479,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212756</v>
+        <v>121212708</v>
       </c>
       <c r="B68" t="n">
-        <v>98098</v>
+        <v>97058</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7496,25 +7491,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7524,10 +7519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527255</v>
+        <v>527252</v>
       </c>
       <c r="R68" t="n">
-        <v>6938220</v>
+        <v>6938285</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7560,11 +7555,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7591,10 +7581,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212775</v>
+        <v>121212722</v>
       </c>
       <c r="B69" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7607,21 +7597,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7631,10 +7621,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527023</v>
+        <v>527075</v>
       </c>
       <c r="R69" t="n">
-        <v>6938359</v>
+        <v>6938349</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7693,10 +7683,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212692</v>
+        <v>121212696</v>
       </c>
       <c r="B70" t="n">
-        <v>57507</v>
+        <v>79718</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7705,25 +7695,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7733,10 +7723,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527210</v>
+        <v>527288</v>
       </c>
       <c r="R70" t="n">
-        <v>6938291</v>
+        <v>6938221</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7769,11 +7759,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7800,10 +7785,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212705</v>
+        <v>121212773</v>
       </c>
       <c r="B71" t="n">
-        <v>90999</v>
+        <v>78608</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7816,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7840,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527310</v>
+        <v>526989</v>
       </c>
       <c r="R71" t="n">
-        <v>6938160</v>
+        <v>6938371</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7876,6 +7861,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7902,10 +7892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212703</v>
+        <v>121212750</v>
       </c>
       <c r="B72" t="n">
-        <v>90999</v>
+        <v>80565</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7918,21 +7908,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>1049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7942,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527253</v>
+        <v>526756</v>
       </c>
       <c r="R72" t="n">
-        <v>6938232</v>
+        <v>6938437</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8004,10 +7994,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212701</v>
+        <v>121212698</v>
       </c>
       <c r="B73" t="n">
-        <v>90999</v>
+        <v>79690</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8020,21 +8010,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8044,10 +8034,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>526960</v>
+        <v>527211</v>
       </c>
       <c r="R73" t="n">
-        <v>6938387</v>
+        <v>6938302</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8106,10 +8096,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212735</v>
+        <v>121212718</v>
       </c>
       <c r="B74" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8146,10 +8136,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527245</v>
+        <v>527038</v>
       </c>
       <c r="R74" t="n">
-        <v>6938291</v>
+        <v>6938372</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8208,10 +8198,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212737</v>
+        <v>121212711</v>
       </c>
       <c r="B75" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8248,10 +8238,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527248</v>
+        <v>527051</v>
       </c>
       <c r="R75" t="n">
-        <v>6938256</v>
+        <v>6938349</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8310,10 +8300,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212736</v>
+        <v>121212775</v>
       </c>
       <c r="B76" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8326,21 +8316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8350,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527250</v>
+        <v>527023</v>
       </c>
       <c r="R76" t="n">
-        <v>6938289</v>
+        <v>6938359</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8412,10 +8402,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212759</v>
+        <v>121212762</v>
       </c>
       <c r="B77" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8452,10 +8442,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526838</v>
+        <v>526868</v>
       </c>
       <c r="R77" t="n">
-        <v>6938397</v>
+        <v>6938367</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8514,10 +8504,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212717</v>
+        <v>121212771</v>
       </c>
       <c r="B78" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8526,25 +8516,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8554,10 +8544,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527023</v>
+        <v>527317</v>
       </c>
       <c r="R78" t="n">
-        <v>6938359</v>
+        <v>6938165</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8616,10 +8606,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212739</v>
+        <v>121212692</v>
       </c>
       <c r="B79" t="n">
-        <v>79688</v>
+        <v>57508</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8632,21 +8622,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8656,10 +8646,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527304</v>
+        <v>527210</v>
       </c>
       <c r="R79" t="n">
-        <v>6938173</v>
+        <v>6938291</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8692,6 +8682,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8718,10 +8713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212731</v>
+        <v>121212697</v>
       </c>
       <c r="B80" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8734,21 +8729,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8758,10 +8753,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527184</v>
+        <v>527186</v>
       </c>
       <c r="R80" t="n">
-        <v>6938280</v>
+        <v>6938273</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8820,10 +8815,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212718</v>
+        <v>121212689</v>
       </c>
       <c r="B81" t="n">
-        <v>79688</v>
+        <v>79226</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8836,21 +8831,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8860,10 +8855,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>527038</v>
+        <v>526855</v>
       </c>
       <c r="R81" t="n">
-        <v>6938372</v>
+        <v>6938391</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8922,10 +8917,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212694</v>
+        <v>121212744</v>
       </c>
       <c r="B82" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8934,25 +8929,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8962,10 +8957,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527088</v>
+        <v>527495</v>
       </c>
       <c r="R82" t="n">
-        <v>6938356</v>
+        <v>6938012</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9024,10 +9019,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212773</v>
+        <v>121212759</v>
       </c>
       <c r="B83" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9036,25 +9031,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9064,10 +9059,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526989</v>
+        <v>526838</v>
       </c>
       <c r="R83" t="n">
-        <v>6938371</v>
+        <v>6938397</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9100,11 +9095,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9131,10 +9121,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212719</v>
+        <v>121212765</v>
       </c>
       <c r="B84" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9143,25 +9133,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9171,10 +9161,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527051</v>
+        <v>526955</v>
       </c>
       <c r="R84" t="n">
-        <v>6938362</v>
+        <v>6938367</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9233,10 +9223,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212744</v>
+        <v>121212709</v>
       </c>
       <c r="B85" t="n">
-        <v>79688</v>
+        <v>78345</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9249,21 +9239,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9273,10 +9263,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>527495</v>
+        <v>526856</v>
       </c>
       <c r="R85" t="n">
-        <v>6938012</v>
+        <v>6938391</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9335,10 +9325,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212713</v>
+        <v>121212688</v>
       </c>
       <c r="B86" t="n">
-        <v>79688</v>
+        <v>95651</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9351,21 +9341,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9375,10 +9365,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>526960</v>
+        <v>527409</v>
       </c>
       <c r="R86" t="n">
-        <v>6938390</v>
+        <v>6938091</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9437,10 +9427,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212711</v>
+        <v>121212761</v>
       </c>
       <c r="B87" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9449,25 +9439,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9477,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>527051</v>
+        <v>526852</v>
       </c>
       <c r="R87" t="n">
-        <v>6938349</v>
+        <v>6938391</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9539,10 +9529,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212698</v>
+        <v>121212764</v>
       </c>
       <c r="B88" t="n">
-        <v>79689</v>
+        <v>98104</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9551,25 +9541,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9579,10 +9569,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>527211</v>
+        <v>526945</v>
       </c>
       <c r="R88" t="n">
-        <v>6938302</v>
+        <v>6938389</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9641,10 +9631,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212730</v>
+        <v>121212756</v>
       </c>
       <c r="B89" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9653,25 +9643,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9681,10 +9671,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527177</v>
+        <v>527255</v>
       </c>
       <c r="R89" t="n">
-        <v>6938273</v>
+        <v>6938220</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9717,6 +9707,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9743,10 +9738,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212696</v>
+        <v>121212720</v>
       </c>
       <c r="B90" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9755,25 +9750,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9783,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527288</v>
+        <v>527051</v>
       </c>
       <c r="R90" t="n">
-        <v>6938221</v>
+        <v>6938362</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9845,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212716</v>
+        <v>121212699</v>
       </c>
       <c r="B91" t="n">
-        <v>79688</v>
+        <v>79593</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9857,25 +9852,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9885,10 +9880,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>526994</v>
+        <v>527249</v>
       </c>
       <c r="R91" t="n">
-        <v>6938374</v>
+        <v>6938289</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9947,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212764</v>
+        <v>121212733</v>
       </c>
       <c r="B92" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9959,25 +9954,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9987,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>526945</v>
+        <v>527186</v>
       </c>
       <c r="R92" t="n">
-        <v>6938389</v>
+        <v>6938273</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10049,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212758</v>
+        <v>121212738</v>
       </c>
       <c r="B93" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10061,25 +10056,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10089,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>526823</v>
+        <v>527288</v>
       </c>
       <c r="R93" t="n">
-        <v>6938405</v>
+        <v>6938221</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10151,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212752</v>
+        <v>121212716</v>
       </c>
       <c r="B94" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10167,21 +10162,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10191,10 +10186,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526804</v>
+        <v>526994</v>
       </c>
       <c r="R94" t="n">
-        <v>6938398</v>
+        <v>6938374</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10253,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212729</v>
+        <v>121212740</v>
       </c>
       <c r="B95" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10293,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527168</v>
+        <v>527350</v>
       </c>
       <c r="R95" t="n">
-        <v>6938291</v>
+        <v>6938133</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10355,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212750</v>
+        <v>121212705</v>
       </c>
       <c r="B96" t="n">
-        <v>80564</v>
+        <v>91005</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10371,21 +10366,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1049</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10395,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>526756</v>
+        <v>527310</v>
       </c>
       <c r="R96" t="n">
-        <v>6938437</v>
+        <v>6938160</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10457,10 +10452,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212755</v>
+        <v>121212721</v>
       </c>
       <c r="B97" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10473,21 +10468,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10497,10 +10492,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>526945</v>
+        <v>527074</v>
       </c>
       <c r="R97" t="n">
-        <v>6938389</v>
+        <v>6938353</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10559,10 +10554,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212765</v>
+        <v>121212736</v>
       </c>
       <c r="B98" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10571,25 +10566,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10599,10 +10594,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>526955</v>
+        <v>527250</v>
       </c>
       <c r="R98" t="n">
-        <v>6938367</v>
+        <v>6938289</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10661,10 +10656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212774</v>
+        <v>121212746</v>
       </c>
       <c r="B99" t="n">
-        <v>78607</v>
+        <v>79725</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10673,25 +10668,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,10 +10696,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>526840</v>
+        <v>527088</v>
       </c>
       <c r="R99" t="n">
-        <v>6938383</v>
+        <v>6938356</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10763,10 +10758,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212772</v>
+        <v>121212725</v>
       </c>
       <c r="B100" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10779,21 +10774,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10803,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>526971</v>
+        <v>527111</v>
       </c>
       <c r="R100" t="n">
-        <v>6938369</v>
+        <v>6938327</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10839,11 +10834,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10870,10 +10860,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212688</v>
+        <v>121212752</v>
       </c>
       <c r="B101" t="n">
-        <v>95645</v>
+        <v>78344</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10886,21 +10876,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10910,10 +10900,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527409</v>
+        <v>526804</v>
       </c>
       <c r="R101" t="n">
-        <v>6938091</v>
+        <v>6938398</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10972,10 +10962,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212723</v>
+        <v>121212745</v>
       </c>
       <c r="B102" t="n">
-        <v>79688</v>
+        <v>79725</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10984,25 +10974,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11012,10 +11002,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527088</v>
+        <v>526960</v>
       </c>
       <c r="R102" t="n">
-        <v>6938358</v>
+        <v>6938390</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11074,10 +11064,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212751</v>
+        <v>121212760</v>
       </c>
       <c r="B103" t="n">
-        <v>78343</v>
+        <v>98104</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11086,25 +11076,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11114,10 +11104,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526755</v>
+        <v>526842</v>
       </c>
       <c r="R103" t="n">
-        <v>6938374</v>
+        <v>6938396</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11176,7 +11166,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212697</v>
+        <v>121212724</v>
       </c>
       <c r="B104" t="n">
         <v>79689</v>
@@ -11192,21 +11182,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11216,10 +11206,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527186</v>
+        <v>527109</v>
       </c>
       <c r="R104" t="n">
-        <v>6938273</v>
+        <v>6938336</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11278,10 +11268,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212724</v>
+        <v>121212695</v>
       </c>
       <c r="B105" t="n">
-        <v>79688</v>
+        <v>79718</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11290,25 +11280,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11318,10 +11308,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527109</v>
+        <v>527184</v>
       </c>
       <c r="R105" t="n">
-        <v>6938336</v>
+        <v>6938280</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11380,10 +11370,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212695</v>
+        <v>121212729</v>
       </c>
       <c r="B106" t="n">
-        <v>79717</v>
+        <v>79689</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11392,25 +11382,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11420,10 +11410,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527184</v>
+        <v>527168</v>
       </c>
       <c r="R106" t="n">
-        <v>6938280</v>
+        <v>6938291</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11482,10 +11472,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212734</v>
+        <v>121212703</v>
       </c>
       <c r="B107" t="n">
-        <v>79688</v>
+        <v>91005</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11498,21 +11488,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11522,10 +11512,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527214</v>
+        <v>527253</v>
       </c>
       <c r="R107" t="n">
-        <v>6938296</v>
+        <v>6938232</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11584,10 +11574,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212733</v>
+        <v>121212751</v>
       </c>
       <c r="B108" t="n">
-        <v>79688</v>
+        <v>78344</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11600,21 +11590,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11624,10 +11614,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>527186</v>
+        <v>526755</v>
       </c>
       <c r="R108" t="n">
-        <v>6938273</v>
+        <v>6938374</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11686,10 +11676,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212714</v>
+        <v>121212772</v>
       </c>
       <c r="B109" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11702,21 +11692,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11726,10 +11716,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526955</v>
+        <v>526971</v>
       </c>
       <c r="R109" t="n">
-        <v>6938368</v>
+        <v>6938369</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11762,6 +11752,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11788,10 +11783,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212722</v>
+        <v>121212690</v>
       </c>
       <c r="B110" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11804,21 +11799,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11828,10 +11823,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527075</v>
+        <v>527263</v>
       </c>
       <c r="R110" t="n">
-        <v>6938349</v>
+        <v>6938234</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11890,10 +11885,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212740</v>
+        <v>121212753</v>
       </c>
       <c r="B111" t="n">
-        <v>79688</v>
+        <v>78344</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11906,21 +11901,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11930,10 +11925,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527350</v>
+        <v>526856</v>
       </c>
       <c r="R111" t="n">
-        <v>6938133</v>
+        <v>6938391</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11992,10 +11987,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212708</v>
+        <v>121212755</v>
       </c>
       <c r="B112" t="n">
-        <v>97052</v>
+        <v>78344</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12004,25 +11999,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12032,10 +12027,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>527252</v>
+        <v>526945</v>
       </c>
       <c r="R112" t="n">
-        <v>6938285</v>
+        <v>6938389</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12094,10 +12089,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212709</v>
+        <v>121212713</v>
       </c>
       <c r="B113" t="n">
-        <v>78344</v>
+        <v>79689</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12110,21 +12105,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12134,10 +12129,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>526856</v>
+        <v>526960</v>
       </c>
       <c r="R113" t="n">
-        <v>6938391</v>
+        <v>6938390</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12196,10 +12191,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212721</v>
+        <v>121212723</v>
       </c>
       <c r="B114" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12236,10 +12231,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527074</v>
+        <v>527088</v>
       </c>
       <c r="R114" t="n">
-        <v>6938353</v>
+        <v>6938358</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12298,10 +12293,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212699</v>
+        <v>121212774</v>
       </c>
       <c r="B115" t="n">
-        <v>79592</v>
+        <v>78608</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12310,25 +12305,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527249</v>
+        <v>526840</v>
       </c>
       <c r="R115" t="n">
-        <v>6938289</v>
+        <v>6938383</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12400,10 +12395,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212712</v>
+        <v>121212757</v>
       </c>
       <c r="B116" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12412,25 +12407,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12440,10 +12435,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>526743</v>
+        <v>526927</v>
       </c>
       <c r="R116" t="n">
-        <v>6938415</v>
+        <v>6938376</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12502,10 +12497,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212762</v>
+        <v>121212758</v>
       </c>
       <c r="B117" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12542,10 +12537,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>526868</v>
+        <v>526823</v>
       </c>
       <c r="R117" t="n">
-        <v>6938367</v>
+        <v>6938405</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12604,10 +12599,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212760</v>
+        <v>121212710</v>
       </c>
       <c r="B118" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12616,25 +12611,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12644,10 +12639,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>526842</v>
+        <v>527495</v>
       </c>
       <c r="R118" t="n">
-        <v>6938396</v>
+        <v>6938009</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12680,6 +12675,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12706,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212757</v>
+        <v>121212715</v>
       </c>
       <c r="B119" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,25 +12718,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>526927</v>
+        <v>526971</v>
       </c>
       <c r="R119" t="n">
-        <v>6938376</v>
+        <v>6938369</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212771</v>
+        <v>121212769</v>
       </c>
       <c r="B120" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12848,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527317</v>
+        <v>527263</v>
       </c>
       <c r="R120" t="n">
-        <v>6938165</v>
+        <v>6938242</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121219596</v>
+        <v>121212779</v>
       </c>
       <c r="B121" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12926,37 +12926,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526982</v>
+        <v>527495</v>
       </c>
       <c r="R121" t="n">
-        <v>6937928</v>
+        <v>6938009</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12980,12 +12980,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121220094</v>
+        <v>121221199</v>
       </c>
       <c r="B122" t="n">
-        <v>78343</v>
+        <v>78608</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13052,13 +13052,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526766</v>
+        <v>526592</v>
       </c>
       <c r="R122" t="n">
-        <v>6938100</v>
+        <v>6938232</v>
       </c>
       <c r="S122" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121212778</v>
+        <v>121219596</v>
       </c>
       <c r="B123" t="n">
-        <v>78607</v>
+        <v>78344</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13130,37 +13130,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>527288</v>
+        <v>526982</v>
       </c>
       <c r="R123" t="n">
-        <v>6938221</v>
+        <v>6937928</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121220916</v>
+        <v>121222671</v>
       </c>
       <c r="B124" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,25 +13228,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,13 +13256,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526647</v>
+        <v>526275</v>
       </c>
       <c r="R124" t="n">
-        <v>6938174</v>
+        <v>6938199</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13292,6 +13292,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13318,10 +13323,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226810</v>
+        <v>121212776</v>
       </c>
       <c r="B125" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13334,21 +13339,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13358,10 +13363,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526533</v>
+        <v>527090</v>
       </c>
       <c r="R125" t="n">
-        <v>6938315</v>
+        <v>6938365</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13388,12 +13393,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13420,10 +13425,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226799</v>
+        <v>121212778</v>
       </c>
       <c r="B126" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13436,21 +13441,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13460,10 +13465,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526747</v>
+        <v>527288</v>
       </c>
       <c r="R126" t="n">
-        <v>6937983</v>
+        <v>6938221</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13490,12 +13495,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13522,10 +13527,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121219658</v>
+        <v>121226820</v>
       </c>
       <c r="B127" t="n">
-        <v>90678</v>
+        <v>90733</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,41 +13539,41 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526953</v>
+        <v>526660</v>
       </c>
       <c r="R127" t="n">
-        <v>6937958</v>
+        <v>6938167</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13624,10 +13629,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226807</v>
+        <v>121226792</v>
       </c>
       <c r="B128" t="n">
-        <v>79688</v>
+        <v>90719</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13640,21 +13645,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13664,10 +13669,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526201</v>
+        <v>526796</v>
       </c>
       <c r="R128" t="n">
-        <v>6938252</v>
+        <v>6937966</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13726,10 +13731,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121212791</v>
+        <v>121226794</v>
       </c>
       <c r="B129" t="n">
-        <v>79723</v>
+        <v>79718</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13747,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13771,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>527094</v>
+        <v>526478</v>
       </c>
       <c r="R129" t="n">
-        <v>6938358</v>
+        <v>6938348</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13796,12 +13801,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13828,10 +13833,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226795</v>
+        <v>121221064</v>
       </c>
       <c r="B130" t="n">
-        <v>79689</v>
+        <v>90733</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,37 +13849,37 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526554</v>
+        <v>526664</v>
       </c>
       <c r="R130" t="n">
-        <v>6938311</v>
+        <v>6938176</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13930,10 +13935,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226819</v>
+        <v>121226802</v>
       </c>
       <c r="B131" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13942,25 +13947,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526646</v>
+        <v>526716</v>
       </c>
       <c r="R131" t="n">
-        <v>6938173</v>
+        <v>6937997</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14032,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121226791</v>
+        <v>121226798</v>
       </c>
       <c r="B132" t="n">
-        <v>89764</v>
+        <v>79689</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14048,21 +14053,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14072,10 +14077,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526205</v>
+        <v>526747</v>
       </c>
       <c r="R132" t="n">
-        <v>6938282</v>
+        <v>6937983</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14134,10 +14139,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121223305</v>
+        <v>121226814</v>
       </c>
       <c r="B133" t="n">
-        <v>98098</v>
+        <v>78344</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14146,41 +14151,41 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526584</v>
+        <v>526515</v>
       </c>
       <c r="R133" t="n">
-        <v>6938052</v>
+        <v>6938303</v>
       </c>
       <c r="S133" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14236,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121212783</v>
+        <v>121226811</v>
       </c>
       <c r="B134" t="n">
-        <v>78252</v>
+        <v>79689</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,21 +14257,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14276,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526761</v>
+        <v>526545</v>
       </c>
       <c r="R134" t="n">
-        <v>6938348</v>
+        <v>6938319</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14306,12 +14311,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14338,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121226796</v>
+        <v>121220916</v>
       </c>
       <c r="B135" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14350,41 +14355,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526796</v>
+        <v>526647</v>
       </c>
       <c r="R135" t="n">
-        <v>6937966</v>
+        <v>6938174</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14440,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226808</v>
+        <v>121226795</v>
       </c>
       <c r="B136" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14456,21 +14461,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14480,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526482</v>
+        <v>526554</v>
       </c>
       <c r="R136" t="n">
-        <v>6938338</v>
+        <v>6938311</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14542,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226814</v>
+        <v>121212783</v>
       </c>
       <c r="B137" t="n">
-        <v>78343</v>
+        <v>78253</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14558,21 +14563,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14582,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526515</v>
+        <v>526761</v>
       </c>
       <c r="R137" t="n">
-        <v>6938303</v>
+        <v>6938348</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14612,12 +14617,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14644,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121221199</v>
+        <v>121226822</v>
       </c>
       <c r="B138" t="n">
-        <v>78607</v>
+        <v>91995</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14656,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526592</v>
+        <v>526182</v>
       </c>
       <c r="R138" t="n">
-        <v>6938232</v>
+        <v>6938234</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14746,10 +14751,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121212780</v>
+        <v>121226824</v>
       </c>
       <c r="B139" t="n">
-        <v>78607</v>
+        <v>91281</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14758,25 +14763,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14786,10 +14791,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>527567</v>
+        <v>526747</v>
       </c>
       <c r="R139" t="n">
-        <v>6937949</v>
+        <v>6937983</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14816,12 +14821,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14848,10 +14853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226804</v>
+        <v>121226818</v>
       </c>
       <c r="B140" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14860,25 +14865,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14888,10 +14893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526224</v>
+        <v>526525</v>
       </c>
       <c r="R140" t="n">
-        <v>6938191</v>
+        <v>6938312</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14950,10 +14955,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226801</v>
+        <v>121226817</v>
       </c>
       <c r="B141" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14962,25 +14967,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14990,10 +14995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526714</v>
+        <v>526581</v>
       </c>
       <c r="R141" t="n">
-        <v>6938008</v>
+        <v>6938053</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15052,10 +15057,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226802</v>
+        <v>121226803</v>
       </c>
       <c r="B142" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15092,10 +15097,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526716</v>
+        <v>526335</v>
       </c>
       <c r="R142" t="n">
-        <v>6937997</v>
+        <v>6938150</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15154,10 +15159,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226813</v>
+        <v>121226809</v>
       </c>
       <c r="B143" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15170,21 +15175,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15194,10 +15199,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526365</v>
+        <v>526518</v>
       </c>
       <c r="R143" t="n">
-        <v>6938404</v>
+        <v>6938295</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15256,10 +15261,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226794</v>
+        <v>121212791</v>
       </c>
       <c r="B144" t="n">
-        <v>79717</v>
+        <v>79724</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15272,21 +15277,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15296,10 +15301,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526478</v>
+        <v>527094</v>
       </c>
       <c r="R144" t="n">
-        <v>6938348</v>
+        <v>6938358</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15326,12 +15331,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15358,10 +15363,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226815</v>
+        <v>121226797</v>
       </c>
       <c r="B145" t="n">
-        <v>78343</v>
+        <v>79689</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15374,21 +15379,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15398,10 +15403,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526527</v>
+        <v>526496</v>
       </c>
       <c r="R145" t="n">
-        <v>6938317</v>
+        <v>6938343</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15434,6 +15439,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15460,10 +15470,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121226793</v>
+        <v>121226821</v>
       </c>
       <c r="B146" t="n">
-        <v>90733</v>
+        <v>78608</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15476,21 +15486,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15500,10 +15510,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526519</v>
+        <v>526199</v>
       </c>
       <c r="R146" t="n">
-        <v>6938315</v>
+        <v>6938254</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15536,6 +15546,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15562,10 +15577,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121222671</v>
+        <v>121226807</v>
       </c>
       <c r="B147" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15578,37 +15593,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526275</v>
+        <v>526201</v>
       </c>
       <c r="R147" t="n">
-        <v>6938199</v>
+        <v>6938252</v>
       </c>
       <c r="S147" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15638,11 +15653,6 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15669,10 +15679,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226809</v>
+        <v>121226819</v>
       </c>
       <c r="B148" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15681,25 +15691,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15709,10 +15719,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526518</v>
+        <v>526646</v>
       </c>
       <c r="R148" t="n">
-        <v>6938295</v>
+        <v>6938173</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -15771,10 +15781,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226821</v>
+        <v>121226805</v>
       </c>
       <c r="B149" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15787,21 +15797,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15811,10 +15821,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526199</v>
+        <v>526203</v>
       </c>
       <c r="R149" t="n">
-        <v>6938254</v>
+        <v>6938195</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15847,11 +15857,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15878,10 +15883,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121226817</v>
+        <v>121212788</v>
       </c>
       <c r="B150" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15890,25 +15895,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15918,10 +15923,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526581</v>
+        <v>526776</v>
       </c>
       <c r="R150" t="n">
-        <v>6938053</v>
+        <v>6938419</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15948,12 +15953,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15980,10 +15985,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121226822</v>
+        <v>121212780</v>
       </c>
       <c r="B151" t="n">
-        <v>91989</v>
+        <v>78608</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15992,25 +15997,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16020,10 +16025,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>526182</v>
+        <v>527567</v>
       </c>
       <c r="R151" t="n">
-        <v>6938234</v>
+        <v>6937949</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16050,12 +16055,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16082,10 +16087,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226805</v>
+        <v>121219658</v>
       </c>
       <c r="B152" t="n">
-        <v>79688</v>
+        <v>90684</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16094,41 +16099,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526203</v>
+        <v>526953</v>
       </c>
       <c r="R152" t="n">
-        <v>6938195</v>
+        <v>6937958</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16184,10 +16189,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121212776</v>
+        <v>121226791</v>
       </c>
       <c r="B153" t="n">
-        <v>78607</v>
+        <v>89768</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16200,21 +16205,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16224,10 +16229,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>527090</v>
+        <v>526205</v>
       </c>
       <c r="R153" t="n">
-        <v>6938365</v>
+        <v>6938282</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16254,12 +16259,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16286,10 +16291,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121212789</v>
+        <v>121226812</v>
       </c>
       <c r="B154" t="n">
-        <v>91989</v>
+        <v>79689</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16298,25 +16303,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16326,10 +16331,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526823</v>
+        <v>526551</v>
       </c>
       <c r="R154" t="n">
-        <v>6938405</v>
+        <v>6938312</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16356,12 +16361,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16388,10 +16393,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121212788</v>
+        <v>121226815</v>
       </c>
       <c r="B155" t="n">
-        <v>91989</v>
+        <v>78344</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16400,25 +16405,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16428,10 +16433,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526776</v>
+        <v>526527</v>
       </c>
       <c r="R155" t="n">
-        <v>6938419</v>
+        <v>6938317</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -16458,12 +16463,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16490,10 +16495,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121226792</v>
+        <v>121226804</v>
       </c>
       <c r="B156" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16506,21 +16511,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16535,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526796</v>
+        <v>526224</v>
       </c>
       <c r="R156" t="n">
-        <v>6937966</v>
+        <v>6938191</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16592,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121212785</v>
+        <v>121220094</v>
       </c>
       <c r="B157" t="n">
-        <v>78252</v>
+        <v>78344</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16608,37 +16613,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526753</v>
+        <v>526766</v>
       </c>
       <c r="R157" t="n">
-        <v>6938395</v>
+        <v>6938100</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16662,12 +16667,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16694,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226824</v>
+        <v>121223305</v>
       </c>
       <c r="B158" t="n">
-        <v>91275</v>
+        <v>98104</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16710,37 +16715,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526747</v>
+        <v>526584</v>
       </c>
       <c r="R158" t="n">
-        <v>6937983</v>
+        <v>6938052</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16796,10 +16801,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226803</v>
+        <v>121226816</v>
       </c>
       <c r="B159" t="n">
-        <v>79688</v>
+        <v>98104</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16808,25 +16813,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16836,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526335</v>
+        <v>526789</v>
       </c>
       <c r="R159" t="n">
-        <v>6938150</v>
+        <v>6937993</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16898,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121212779</v>
+        <v>121226793</v>
       </c>
       <c r="B160" t="n">
-        <v>78607</v>
+        <v>90739</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16914,21 +16919,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16938,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>527495</v>
+        <v>526519</v>
       </c>
       <c r="R160" t="n">
-        <v>6938009</v>
+        <v>6938315</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16968,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17000,10 +17005,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226818</v>
+        <v>121226808</v>
       </c>
       <c r="B161" t="n">
-        <v>98098</v>
+        <v>79689</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17012,25 +17017,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17040,10 +17045,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526525</v>
+        <v>526482</v>
       </c>
       <c r="R161" t="n">
-        <v>6938312</v>
+        <v>6938338</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17102,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226820</v>
+        <v>121226796</v>
       </c>
       <c r="B162" t="n">
-        <v>90727</v>
+        <v>91005</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17118,21 +17123,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17142,10 +17147,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526660</v>
+        <v>526796</v>
       </c>
       <c r="R162" t="n">
-        <v>6938167</v>
+        <v>6937966</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17204,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226812</v>
+        <v>121226806</v>
       </c>
       <c r="B163" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526551</v>
+        <v>526182</v>
       </c>
       <c r="R163" t="n">
-        <v>6938312</v>
+        <v>6938206</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17306,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226811</v>
+        <v>121226813</v>
       </c>
       <c r="B164" t="n">
-        <v>79688</v>
+        <v>78344</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17322,21 +17327,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17346,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526545</v>
+        <v>526365</v>
       </c>
       <c r="R164" t="n">
-        <v>6938319</v>
+        <v>6938404</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17408,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226797</v>
+        <v>121212785</v>
       </c>
       <c r="B165" t="n">
-        <v>79688</v>
+        <v>78253</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17424,21 +17429,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17448,10 +17453,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526496</v>
+        <v>526753</v>
       </c>
       <c r="R165" t="n">
-        <v>6938343</v>
+        <v>6938395</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17478,17 +17483,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121221064</v>
+        <v>121226801</v>
       </c>
       <c r="B166" t="n">
-        <v>90727</v>
+        <v>79689</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,37 +17531,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526664</v>
+        <v>526714</v>
       </c>
       <c r="R166" t="n">
-        <v>6938176</v>
+        <v>6938008</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226806</v>
+        <v>121226810</v>
       </c>
       <c r="B167" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526182</v>
+        <v>526533</v>
       </c>
       <c r="R167" t="n">
-        <v>6938206</v>
+        <v>6938315</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226816</v>
+        <v>121212789</v>
       </c>
       <c r="B168" t="n">
-        <v>98098</v>
+        <v>91995</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,25 +17731,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526789</v>
+        <v>526823</v>
       </c>
       <c r="R168" t="n">
-        <v>6937993</v>
+        <v>6938405</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17789,12 +17789,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -17824,7 +17824,7 @@
         <v>121212693</v>
       </c>
       <c r="B169" t="n">
-        <v>91993</v>
+        <v>91999</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>121246286</v>
       </c>
       <c r="B170" t="n">
-        <v>92018</v>
+        <v>92024</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>121179849</v>
       </c>
       <c r="B171" t="n">
-        <v>91153</v>
+        <v>91159</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121185408</v>
+        <v>121185404</v>
       </c>
       <c r="B172" t="n">
-        <v>90999</v>
+        <v>91159</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18153,25 +18153,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18181,10 +18181,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>527661</v>
+        <v>527659</v>
       </c>
       <c r="R172" t="n">
-        <v>6937695</v>
+        <v>6937698</v>
       </c>
       <c r="S172" t="n">
         <v>25</v>
@@ -18246,7 +18246,7 @@
         <v>121179693</v>
       </c>
       <c r="B173" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18345,10 +18345,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121185404</v>
+        <v>121185408</v>
       </c>
       <c r="B174" t="n">
-        <v>91153</v>
+        <v>91005</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18357,25 +18357,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18385,10 +18385,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>527659</v>
+        <v>527661</v>
       </c>
       <c r="R174" t="n">
-        <v>6937698</v>
+        <v>6937695</v>
       </c>
       <c r="S174" t="n">
         <v>25</v>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121185430</v>
+        <v>121185421</v>
       </c>
       <c r="B7" t="n">
-        <v>91995</v>
+        <v>98104</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>527460</v>
+        <v>526958</v>
       </c>
       <c r="R7" t="n">
-        <v>6937819</v>
+        <v>6938116</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121185411</v>
+        <v>121180239</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,41 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>527045</v>
+        <v>527495</v>
       </c>
       <c r="R8" t="n">
-        <v>6938075</v>
+        <v>6937765</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121185421</v>
+        <v>121185430</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>91995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1473,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526958</v>
+        <v>527460</v>
       </c>
       <c r="R9" t="n">
-        <v>6938116</v>
+        <v>6937819</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121180239</v>
+        <v>121185411</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>79689</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,41 +1575,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527495</v>
+        <v>527045</v>
       </c>
       <c r="R10" t="n">
-        <v>6937765</v>
+        <v>6938075</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121185415</v>
+        <v>121185424</v>
       </c>
       <c r="B30" t="n">
-        <v>79689</v>
+        <v>98104</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,25 +3615,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>527391</v>
+        <v>527010</v>
       </c>
       <c r="R30" t="n">
-        <v>6937910</v>
+        <v>6938105</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121185424</v>
+        <v>121180712</v>
       </c>
       <c r="B31" t="n">
-        <v>98104</v>
+        <v>78608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3717,41 +3717,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Annelund, Annelund, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>527010</v>
+        <v>527305</v>
       </c>
       <c r="R31" t="n">
-        <v>6938105</v>
+        <v>6937895</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121180141</v>
+        <v>121185415</v>
       </c>
       <c r="B32" t="n">
-        <v>98104</v>
+        <v>79689</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,41 +3819,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Annelund, Annelund, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>527597</v>
+        <v>527391</v>
       </c>
       <c r="R32" t="n">
-        <v>6937703</v>
+        <v>6937910</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121180712</v>
+        <v>121180141</v>
       </c>
       <c r="B33" t="n">
-        <v>78608</v>
+        <v>98104</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3921,25 +3921,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>527305</v>
+        <v>527597</v>
       </c>
       <c r="R33" t="n">
-        <v>6937895</v>
+        <v>6937703</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121185431</v>
+        <v>121185418</v>
       </c>
       <c r="B39" t="n">
-        <v>91995</v>
+        <v>79689</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4533,25 +4533,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>527439</v>
+        <v>527437</v>
       </c>
       <c r="R39" t="n">
-        <v>6937815</v>
+        <v>6937974</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4623,10 +4623,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121185429</v>
+        <v>121185419</v>
       </c>
       <c r="B40" t="n">
-        <v>91995</v>
+        <v>79725</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4639,21 +4639,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>527641</v>
+        <v>527001</v>
       </c>
       <c r="R40" t="n">
-        <v>6937808</v>
+        <v>6938096</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4725,10 +4725,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121185418</v>
+        <v>121185402</v>
       </c>
       <c r="B41" t="n">
-        <v>79689</v>
+        <v>79718</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,25 +4737,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>527437</v>
+        <v>527367</v>
       </c>
       <c r="R41" t="n">
-        <v>6937974</v>
+        <v>6937938</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4827,10 +4827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121185419</v>
+        <v>121183008</v>
       </c>
       <c r="B42" t="n">
-        <v>79725</v>
+        <v>98104</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4839,41 +4839,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>527001</v>
+        <v>526999</v>
       </c>
       <c r="R42" t="n">
-        <v>6938096</v>
+        <v>6938157</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121185402</v>
+        <v>121185429</v>
       </c>
       <c r="B43" t="n">
-        <v>79718</v>
+        <v>91995</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4945,21 +4945,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>527367</v>
+        <v>527641</v>
       </c>
       <c r="R43" t="n">
-        <v>6937938</v>
+        <v>6937808</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5031,10 +5031,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121183008</v>
+        <v>121185431</v>
       </c>
       <c r="B44" t="n">
-        <v>98104</v>
+        <v>91995</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5043,41 +5043,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>526999</v>
+        <v>527439</v>
       </c>
       <c r="R44" t="n">
-        <v>6938157</v>
+        <v>6937815</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121183281</v>
+        <v>121185397</v>
       </c>
       <c r="B53" t="n">
-        <v>98104</v>
+        <v>90684</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5961,41 +5961,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>526958</v>
+        <v>527043</v>
       </c>
       <c r="R53" t="n">
-        <v>6938109</v>
+        <v>6938062</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6051,10 +6051,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121185397</v>
+        <v>121183281</v>
       </c>
       <c r="B54" t="n">
-        <v>90684</v>
+        <v>98104</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6063,41 +6063,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>527043</v>
+        <v>526958</v>
       </c>
       <c r="R54" t="n">
-        <v>6938062</v>
+        <v>6938109</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212694</v>
+        <v>121212765</v>
       </c>
       <c r="B55" t="n">
-        <v>79718</v>
+        <v>98105</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>527088</v>
+        <v>526955</v>
       </c>
       <c r="R55" t="n">
-        <v>6938356</v>
+        <v>6938367</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212735</v>
+        <v>121212694</v>
       </c>
       <c r="B56" t="n">
-        <v>79689</v>
+        <v>79719</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527245</v>
+        <v>527088</v>
       </c>
       <c r="R56" t="n">
-        <v>6938291</v>
+        <v>6938356</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212730</v>
+        <v>121212713</v>
       </c>
       <c r="B57" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>527177</v>
+        <v>526960</v>
       </c>
       <c r="R57" t="n">
-        <v>6938273</v>
+        <v>6938390</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6459,10 +6459,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212701</v>
+        <v>121212738</v>
       </c>
       <c r="B58" t="n">
-        <v>91005</v>
+        <v>79690</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6475,21 +6475,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>526960</v>
+        <v>527288</v>
       </c>
       <c r="R58" t="n">
-        <v>6938387</v>
+        <v>6938221</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212763</v>
+        <v>121212728</v>
       </c>
       <c r="B59" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6601,10 +6601,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>526911</v>
+        <v>527148</v>
       </c>
       <c r="R59" t="n">
-        <v>6938360</v>
+        <v>6938301</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,10 +6663,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212734</v>
+        <v>121212752</v>
       </c>
       <c r="B60" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,21 +6679,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6703,10 +6703,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>527214</v>
+        <v>526804</v>
       </c>
       <c r="R60" t="n">
-        <v>6938296</v>
+        <v>6938398</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6765,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212714</v>
+        <v>121212722</v>
       </c>
       <c r="B61" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6805,10 +6805,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>526955</v>
+        <v>527075</v>
       </c>
       <c r="R61" t="n">
-        <v>6938368</v>
+        <v>6938349</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212712</v>
+        <v>121212688</v>
       </c>
       <c r="B62" t="n">
-        <v>79689</v>
+        <v>95652</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6883,21 +6883,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>526743</v>
+        <v>527409</v>
       </c>
       <c r="R62" t="n">
-        <v>6938415</v>
+        <v>6938091</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6969,10 +6969,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212732</v>
+        <v>121212697</v>
       </c>
       <c r="B63" t="n">
-        <v>79689</v>
+        <v>79691</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,21 +6985,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527184</v>
+        <v>527186</v>
       </c>
       <c r="R63" t="n">
-        <v>6938280</v>
+        <v>6938273</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7071,10 +7071,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212737</v>
+        <v>121212705</v>
       </c>
       <c r="B64" t="n">
-        <v>79689</v>
+        <v>91006</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7087,21 +7087,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527248</v>
+        <v>527310</v>
       </c>
       <c r="R64" t="n">
-        <v>6938256</v>
+        <v>6938160</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7173,10 +7173,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212726</v>
+        <v>121212753</v>
       </c>
       <c r="B65" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7189,21 +7189,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>527148</v>
+        <v>526856</v>
       </c>
       <c r="R65" t="n">
-        <v>6938301</v>
+        <v>6938391</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7275,10 +7275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212717</v>
+        <v>121212740</v>
       </c>
       <c r="B66" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527023</v>
+        <v>527350</v>
       </c>
       <c r="R66" t="n">
-        <v>6938359</v>
+        <v>6938133</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212739</v>
+        <v>121212762</v>
       </c>
       <c r="B67" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7389,25 +7389,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>527304</v>
+        <v>526868</v>
       </c>
       <c r="R67" t="n">
-        <v>6938173</v>
+        <v>6938367</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7479,10 +7479,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212708</v>
+        <v>121212772</v>
       </c>
       <c r="B68" t="n">
-        <v>97058</v>
+        <v>78609</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7491,25 +7491,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>527252</v>
+        <v>526971</v>
       </c>
       <c r="R68" t="n">
-        <v>6938285</v>
+        <v>6938369</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7555,6 +7555,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7581,10 +7586,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212722</v>
+        <v>121212696</v>
       </c>
       <c r="B69" t="n">
-        <v>79689</v>
+        <v>79719</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7593,25 +7598,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7621,10 +7626,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527075</v>
+        <v>527288</v>
       </c>
       <c r="R69" t="n">
-        <v>6938349</v>
+        <v>6938221</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7683,10 +7688,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212696</v>
+        <v>121212719</v>
       </c>
       <c r="B70" t="n">
-        <v>79718</v>
+        <v>79690</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7695,25 +7700,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7723,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527288</v>
+        <v>527051</v>
       </c>
       <c r="R70" t="n">
-        <v>6938221</v>
+        <v>6938362</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7785,10 +7790,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212773</v>
+        <v>121212775</v>
       </c>
       <c r="B71" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7825,10 +7830,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>526989</v>
+        <v>527023</v>
       </c>
       <c r="R71" t="n">
-        <v>6938371</v>
+        <v>6938359</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7861,11 +7866,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7892,10 +7892,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212750</v>
+        <v>121212721</v>
       </c>
       <c r="B72" t="n">
-        <v>80565</v>
+        <v>79690</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7908,21 +7908,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>526756</v>
+        <v>527074</v>
       </c>
       <c r="R72" t="n">
-        <v>6938437</v>
+        <v>6938353</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7994,7 +7994,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212698</v>
+        <v>121212735</v>
       </c>
       <c r="B73" t="n">
         <v>79690</v>
@@ -8010,21 +8010,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527211</v>
+        <v>527245</v>
       </c>
       <c r="R73" t="n">
-        <v>6938302</v>
+        <v>6938291</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212718</v>
+        <v>121212761</v>
       </c>
       <c r="B74" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8108,25 +8108,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>527038</v>
+        <v>526852</v>
       </c>
       <c r="R74" t="n">
-        <v>6938372</v>
+        <v>6938391</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8198,10 +8198,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212711</v>
+        <v>121212725</v>
       </c>
       <c r="B75" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527051</v>
+        <v>527111</v>
       </c>
       <c r="R75" t="n">
-        <v>6938349</v>
+        <v>6938327</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212775</v>
+        <v>121212710</v>
       </c>
       <c r="B76" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8316,21 +8316,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527023</v>
+        <v>527495</v>
       </c>
       <c r="R76" t="n">
-        <v>6938359</v>
+        <v>6938009</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8376,6 +8376,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8402,10 +8407,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212762</v>
+        <v>121212773</v>
       </c>
       <c r="B77" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8414,25 +8419,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8442,10 +8447,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526868</v>
+        <v>526989</v>
       </c>
       <c r="R77" t="n">
-        <v>6938367</v>
+        <v>6938371</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8478,6 +8483,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8504,10 +8514,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212771</v>
+        <v>121212716</v>
       </c>
       <c r="B78" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8516,25 +8526,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8544,10 +8554,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>527317</v>
+        <v>526994</v>
       </c>
       <c r="R78" t="n">
-        <v>6938165</v>
+        <v>6938374</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8606,10 +8616,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212692</v>
+        <v>121212701</v>
       </c>
       <c r="B79" t="n">
-        <v>57508</v>
+        <v>91006</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8622,21 +8632,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8646,10 +8656,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>527210</v>
+        <v>526960</v>
       </c>
       <c r="R79" t="n">
-        <v>6938291</v>
+        <v>6938387</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8682,11 +8692,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8713,10 +8718,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212697</v>
+        <v>121212746</v>
       </c>
       <c r="B80" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8725,25 +8730,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8753,10 +8758,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527186</v>
+        <v>527088</v>
       </c>
       <c r="R80" t="n">
-        <v>6938273</v>
+        <v>6938356</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8815,10 +8820,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212689</v>
+        <v>121212759</v>
       </c>
       <c r="B81" t="n">
-        <v>79226</v>
+        <v>98105</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8827,25 +8832,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8855,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526855</v>
+        <v>526838</v>
       </c>
       <c r="R81" t="n">
-        <v>6938391</v>
+        <v>6938397</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8917,10 +8922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212744</v>
+        <v>121212718</v>
       </c>
       <c r="B82" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8957,10 +8962,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527495</v>
+        <v>527038</v>
       </c>
       <c r="R82" t="n">
-        <v>6938012</v>
+        <v>6938372</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9019,10 +9024,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212759</v>
+        <v>121212715</v>
       </c>
       <c r="B83" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9031,25 +9036,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9059,10 +9064,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526838</v>
+        <v>526971</v>
       </c>
       <c r="R83" t="n">
-        <v>6938397</v>
+        <v>6938369</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9121,10 +9126,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212765</v>
+        <v>121212690</v>
       </c>
       <c r="B84" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9133,25 +9138,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9161,10 +9166,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>526955</v>
+        <v>527263</v>
       </c>
       <c r="R84" t="n">
-        <v>6938367</v>
+        <v>6938234</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9226,7 +9231,7 @@
         <v>121212709</v>
       </c>
       <c r="B85" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9325,10 +9330,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212688</v>
+        <v>121212734</v>
       </c>
       <c r="B86" t="n">
-        <v>95651</v>
+        <v>79690</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9341,21 +9346,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9365,10 +9370,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527409</v>
+        <v>527214</v>
       </c>
       <c r="R86" t="n">
-        <v>6938091</v>
+        <v>6938296</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9427,10 +9432,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212761</v>
+        <v>121212714</v>
       </c>
       <c r="B87" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9439,25 +9444,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9467,10 +9472,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526852</v>
+        <v>526955</v>
       </c>
       <c r="R87" t="n">
-        <v>6938391</v>
+        <v>6938368</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9529,10 +9534,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212764</v>
+        <v>121212712</v>
       </c>
       <c r="B88" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9541,25 +9546,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9569,10 +9574,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526945</v>
+        <v>526743</v>
       </c>
       <c r="R88" t="n">
-        <v>6938389</v>
+        <v>6938415</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9631,10 +9636,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212756</v>
+        <v>121212764</v>
       </c>
       <c r="B89" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9671,10 +9676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>527255</v>
+        <v>526945</v>
       </c>
       <c r="R89" t="n">
-        <v>6938220</v>
+        <v>6938389</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9707,11 +9712,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9738,10 +9738,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212720</v>
+        <v>121212755</v>
       </c>
       <c r="B90" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>527051</v>
+        <v>526945</v>
       </c>
       <c r="R90" t="n">
-        <v>6938362</v>
+        <v>6938389</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212699</v>
+        <v>121212724</v>
       </c>
       <c r="B91" t="n">
-        <v>79593</v>
+        <v>79690</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9852,25 +9852,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527249</v>
+        <v>527109</v>
       </c>
       <c r="R91" t="n">
-        <v>6938289</v>
+        <v>6938336</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212733</v>
+        <v>121212744</v>
       </c>
       <c r="B92" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527186</v>
+        <v>527495</v>
       </c>
       <c r="R92" t="n">
-        <v>6938273</v>
+        <v>6938012</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212738</v>
+        <v>121212703</v>
       </c>
       <c r="B93" t="n">
-        <v>79689</v>
+        <v>91006</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527288</v>
+        <v>527253</v>
       </c>
       <c r="R93" t="n">
-        <v>6938221</v>
+        <v>6938232</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10146,10 +10146,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212716</v>
+        <v>121212695</v>
       </c>
       <c r="B94" t="n">
-        <v>79689</v>
+        <v>79719</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10158,25 +10158,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10186,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>526994</v>
+        <v>527184</v>
       </c>
       <c r="R94" t="n">
-        <v>6938374</v>
+        <v>6938280</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212740</v>
+        <v>121212729</v>
       </c>
       <c r="B95" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527350</v>
+        <v>527168</v>
       </c>
       <c r="R95" t="n">
-        <v>6938133</v>
+        <v>6938291</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10350,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212705</v>
+        <v>121212732</v>
       </c>
       <c r="B96" t="n">
-        <v>91005</v>
+        <v>79690</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10366,21 +10366,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10390,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>527310</v>
+        <v>527184</v>
       </c>
       <c r="R96" t="n">
-        <v>6938160</v>
+        <v>6938280</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10452,10 +10452,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212721</v>
+        <v>121212736</v>
       </c>
       <c r="B97" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10492,10 +10492,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527074</v>
+        <v>527250</v>
       </c>
       <c r="R97" t="n">
-        <v>6938353</v>
+        <v>6938289</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10554,10 +10554,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212736</v>
+        <v>121212757</v>
       </c>
       <c r="B98" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10566,25 +10566,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10594,10 +10594,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>527250</v>
+        <v>526927</v>
       </c>
       <c r="R98" t="n">
-        <v>6938289</v>
+        <v>6938376</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10656,10 +10656,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212746</v>
+        <v>121212769</v>
       </c>
       <c r="B99" t="n">
-        <v>79725</v>
+        <v>98105</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10668,25 +10668,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10696,10 +10696,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527088</v>
+        <v>527263</v>
       </c>
       <c r="R99" t="n">
-        <v>6938356</v>
+        <v>6938242</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10758,10 +10758,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212725</v>
+        <v>121212758</v>
       </c>
       <c r="B100" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10770,25 +10770,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>527111</v>
+        <v>526823</v>
       </c>
       <c r="R100" t="n">
-        <v>6938327</v>
+        <v>6938405</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10860,10 +10860,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212752</v>
+        <v>121212730</v>
       </c>
       <c r="B101" t="n">
-        <v>78344</v>
+        <v>79690</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10876,21 +10876,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10900,10 +10900,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>526804</v>
+        <v>527177</v>
       </c>
       <c r="R101" t="n">
-        <v>6938398</v>
+        <v>6938273</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10962,10 +10962,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212745</v>
+        <v>121212733</v>
       </c>
       <c r="B102" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10974,25 +10974,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>526960</v>
+        <v>527186</v>
       </c>
       <c r="R102" t="n">
-        <v>6938390</v>
+        <v>6938273</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11064,10 +11064,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212760</v>
+        <v>121212774</v>
       </c>
       <c r="B103" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11076,25 +11076,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11104,10 +11104,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526842</v>
+        <v>526840</v>
       </c>
       <c r="R103" t="n">
-        <v>6938396</v>
+        <v>6938383</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11166,10 +11166,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212724</v>
+        <v>121212750</v>
       </c>
       <c r="B104" t="n">
-        <v>79689</v>
+        <v>80566</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11182,21 +11182,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11206,10 +11206,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>527109</v>
+        <v>526756</v>
       </c>
       <c r="R104" t="n">
-        <v>6938336</v>
+        <v>6938437</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11268,10 +11268,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212695</v>
+        <v>121212699</v>
       </c>
       <c r="B105" t="n">
-        <v>79718</v>
+        <v>79594</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527184</v>
+        <v>527249</v>
       </c>
       <c r="R105" t="n">
-        <v>6938280</v>
+        <v>6938289</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11370,10 +11370,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212729</v>
+        <v>121212737</v>
       </c>
       <c r="B106" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527168</v>
+        <v>527248</v>
       </c>
       <c r="R106" t="n">
-        <v>6938291</v>
+        <v>6938256</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212703</v>
+        <v>121212745</v>
       </c>
       <c r="B107" t="n">
-        <v>91005</v>
+        <v>79726</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11484,25 +11484,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>527253</v>
+        <v>526960</v>
       </c>
       <c r="R107" t="n">
-        <v>6938232</v>
+        <v>6938390</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11577,7 +11577,7 @@
         <v>121212751</v>
       </c>
       <c r="B108" t="n">
-        <v>78344</v>
+        <v>78345</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11676,10 +11676,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212772</v>
+        <v>121212760</v>
       </c>
       <c r="B109" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11688,25 +11688,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526971</v>
+        <v>526842</v>
       </c>
       <c r="R109" t="n">
-        <v>6938369</v>
+        <v>6938396</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11752,11 +11752,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11783,10 +11778,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212690</v>
+        <v>121212763</v>
       </c>
       <c r="B110" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11795,25 +11790,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11823,10 +11818,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>527263</v>
+        <v>526911</v>
       </c>
       <c r="R110" t="n">
-        <v>6938234</v>
+        <v>6938360</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11885,10 +11880,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212753</v>
+        <v>121212698</v>
       </c>
       <c r="B111" t="n">
-        <v>78344</v>
+        <v>79691</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11901,21 +11896,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11925,10 +11920,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>526856</v>
+        <v>527211</v>
       </c>
       <c r="R111" t="n">
-        <v>6938391</v>
+        <v>6938302</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11987,10 +11982,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212755</v>
+        <v>121212708</v>
       </c>
       <c r="B112" t="n">
-        <v>78344</v>
+        <v>97059</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11999,25 +11994,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12027,10 +12022,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>526945</v>
+        <v>527252</v>
       </c>
       <c r="R112" t="n">
-        <v>6938389</v>
+        <v>6938285</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12089,10 +12084,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212713</v>
+        <v>121212689</v>
       </c>
       <c r="B113" t="n">
-        <v>79689</v>
+        <v>79227</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12105,21 +12100,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12129,10 +12124,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>526960</v>
+        <v>526855</v>
       </c>
       <c r="R113" t="n">
-        <v>6938390</v>
+        <v>6938391</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12191,10 +12186,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212723</v>
+        <v>121212739</v>
       </c>
       <c r="B114" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12231,10 +12226,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527088</v>
+        <v>527304</v>
       </c>
       <c r="R114" t="n">
-        <v>6938358</v>
+        <v>6938173</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12293,10 +12288,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212774</v>
+        <v>121212711</v>
       </c>
       <c r="B115" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12309,21 +12304,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12333,10 +12328,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>526840</v>
+        <v>527051</v>
       </c>
       <c r="R115" t="n">
-        <v>6938383</v>
+        <v>6938349</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12395,10 +12390,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212757</v>
+        <v>121212717</v>
       </c>
       <c r="B116" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12407,25 +12402,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12435,10 +12430,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>526927</v>
+        <v>527023</v>
       </c>
       <c r="R116" t="n">
-        <v>6938376</v>
+        <v>6938359</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12497,10 +12492,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212758</v>
+        <v>121212723</v>
       </c>
       <c r="B117" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12509,25 +12504,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12537,10 +12532,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>526823</v>
+        <v>527088</v>
       </c>
       <c r="R117" t="n">
-        <v>6938405</v>
+        <v>6938358</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12599,10 +12594,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212710</v>
+        <v>121212756</v>
       </c>
       <c r="B118" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12611,25 +12606,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12639,10 +12634,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527495</v>
+        <v>527255</v>
       </c>
       <c r="R118" t="n">
-        <v>6938009</v>
+        <v>6938220</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12679,7 +12674,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12706,10 +12701,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212715</v>
+        <v>121212771</v>
       </c>
       <c r="B119" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12718,25 +12713,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12746,10 +12741,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>526971</v>
+        <v>527317</v>
       </c>
       <c r="R119" t="n">
-        <v>6938369</v>
+        <v>6938165</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12808,10 +12803,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212769</v>
+        <v>121212692</v>
       </c>
       <c r="B120" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12820,25 +12815,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12848,10 +12843,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527263</v>
+        <v>527210</v>
       </c>
       <c r="R120" t="n">
-        <v>6938242</v>
+        <v>6938291</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12884,6 +12879,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121212779</v>
+        <v>121220916</v>
       </c>
       <c r="B121" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,41 +12922,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>527495</v>
+        <v>526647</v>
       </c>
       <c r="R121" t="n">
-        <v>6938009</v>
+        <v>6938174</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12980,12 +12980,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121221199</v>
+        <v>121226793</v>
       </c>
       <c r="B122" t="n">
-        <v>78608</v>
+        <v>90740</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,37 +13028,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526592</v>
+        <v>526519</v>
       </c>
       <c r="R122" t="n">
-        <v>6938232</v>
+        <v>6938315</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121219596</v>
+        <v>121226822</v>
       </c>
       <c r="B123" t="n">
-        <v>78344</v>
+        <v>91996</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,41 +13126,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526982</v>
+        <v>526182</v>
       </c>
       <c r="R123" t="n">
-        <v>6937928</v>
+        <v>6938234</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121222671</v>
+        <v>121221199</v>
       </c>
       <c r="B124" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13256,13 +13256,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526275</v>
+        <v>526592</v>
       </c>
       <c r="R124" t="n">
-        <v>6938199</v>
+        <v>6938232</v>
       </c>
       <c r="S124" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13292,11 +13292,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13323,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121212776</v>
+        <v>121226799</v>
       </c>
       <c r="B125" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13339,21 +13334,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>527090</v>
+        <v>526747</v>
       </c>
       <c r="R125" t="n">
-        <v>6938365</v>
+        <v>6937983</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13393,12 +13388,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13425,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121212778</v>
+        <v>121219658</v>
       </c>
       <c r="B126" t="n">
-        <v>78608</v>
+        <v>90685</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13437,41 +13432,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>527288</v>
+        <v>526953</v>
       </c>
       <c r="R126" t="n">
-        <v>6938221</v>
+        <v>6937958</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13495,12 +13490,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13527,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226820</v>
+        <v>121226796</v>
       </c>
       <c r="B127" t="n">
-        <v>90733</v>
+        <v>91006</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13543,21 +13538,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13567,10 +13562,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526660</v>
+        <v>526796</v>
       </c>
       <c r="R127" t="n">
-        <v>6938167</v>
+        <v>6937966</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13629,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226792</v>
+        <v>121226813</v>
       </c>
       <c r="B128" t="n">
-        <v>90719</v>
+        <v>78345</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13645,21 +13640,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526796</v>
+        <v>526365</v>
       </c>
       <c r="R128" t="n">
-        <v>6937966</v>
+        <v>6938404</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -13731,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226794</v>
+        <v>121226811</v>
       </c>
       <c r="B129" t="n">
-        <v>79718</v>
+        <v>79690</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13743,25 +13738,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13771,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526478</v>
+        <v>526545</v>
       </c>
       <c r="R129" t="n">
-        <v>6938348</v>
+        <v>6938319</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13833,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121221064</v>
+        <v>121226824</v>
       </c>
       <c r="B130" t="n">
-        <v>90733</v>
+        <v>91282</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13845,41 +13840,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526664</v>
+        <v>526747</v>
       </c>
       <c r="R130" t="n">
-        <v>6938176</v>
+        <v>6937983</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13935,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226802</v>
+        <v>121226809</v>
       </c>
       <c r="B131" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13975,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526716</v>
+        <v>526518</v>
       </c>
       <c r="R131" t="n">
-        <v>6937997</v>
+        <v>6938295</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14037,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121226798</v>
+        <v>121226797</v>
       </c>
       <c r="B132" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14077,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526747</v>
+        <v>526496</v>
       </c>
       <c r="R132" t="n">
-        <v>6937983</v>
+        <v>6938343</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14113,6 +14108,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,10 +14139,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121226814</v>
+        <v>121226807</v>
       </c>
       <c r="B133" t="n">
-        <v>78344</v>
+        <v>79690</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14155,21 +14155,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14179,10 +14179,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526515</v>
+        <v>526201</v>
       </c>
       <c r="R133" t="n">
-        <v>6938303</v>
+        <v>6938252</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14241,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226811</v>
+        <v>121226804</v>
       </c>
       <c r="B134" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526545</v>
+        <v>526224</v>
       </c>
       <c r="R134" t="n">
-        <v>6938319</v>
+        <v>6938191</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14343,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121220916</v>
+        <v>121212783</v>
       </c>
       <c r="B135" t="n">
-        <v>98104</v>
+        <v>78254</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14355,41 +14355,41 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526647</v>
+        <v>526761</v>
       </c>
       <c r="R135" t="n">
-        <v>6938174</v>
+        <v>6938348</v>
       </c>
       <c r="S135" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14413,12 +14413,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14445,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121226795</v>
+        <v>121212788</v>
       </c>
       <c r="B136" t="n">
-        <v>79690</v>
+        <v>91996</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,25 +14457,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14485,10 +14485,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526554</v>
+        <v>526776</v>
       </c>
       <c r="R136" t="n">
-        <v>6938311</v>
+        <v>6938419</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14547,10 +14547,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121212783</v>
+        <v>121212780</v>
       </c>
       <c r="B137" t="n">
-        <v>78253</v>
+        <v>78609</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14563,21 +14563,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526761</v>
+        <v>527567</v>
       </c>
       <c r="R137" t="n">
-        <v>6938348</v>
+        <v>6937949</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14649,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226822</v>
+        <v>121222671</v>
       </c>
       <c r="B138" t="n">
-        <v>91995</v>
+        <v>78609</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14661,41 +14661,41 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526182</v>
+        <v>526275</v>
       </c>
       <c r="R138" t="n">
-        <v>6938234</v>
+        <v>6938199</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14725,6 +14725,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14751,10 +14756,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226824</v>
+        <v>121226812</v>
       </c>
       <c r="B139" t="n">
-        <v>91281</v>
+        <v>79690</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14763,25 +14768,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14791,10 +14796,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526747</v>
+        <v>526551</v>
       </c>
       <c r="R139" t="n">
-        <v>6937983</v>
+        <v>6938312</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14853,10 +14858,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226818</v>
+        <v>121226810</v>
       </c>
       <c r="B140" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14865,25 +14870,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14893,10 +14898,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526525</v>
+        <v>526533</v>
       </c>
       <c r="R140" t="n">
-        <v>6938312</v>
+        <v>6938315</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14955,10 +14960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226817</v>
+        <v>121226795</v>
       </c>
       <c r="B141" t="n">
-        <v>98104</v>
+        <v>79691</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14967,25 +14972,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14995,10 +15000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526581</v>
+        <v>526554</v>
       </c>
       <c r="R141" t="n">
-        <v>6938053</v>
+        <v>6938311</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15057,10 +15062,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226803</v>
+        <v>121226814</v>
       </c>
       <c r="B142" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15073,21 +15078,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15097,10 +15102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526335</v>
+        <v>526515</v>
       </c>
       <c r="R142" t="n">
-        <v>6938150</v>
+        <v>6938303</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15159,10 +15164,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226809</v>
+        <v>121226821</v>
       </c>
       <c r="B143" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15175,21 +15180,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15199,10 +15204,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526518</v>
+        <v>526199</v>
       </c>
       <c r="R143" t="n">
-        <v>6938295</v>
+        <v>6938254</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15235,6 +15240,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15261,10 +15271,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121212791</v>
+        <v>121226820</v>
       </c>
       <c r="B144" t="n">
-        <v>79724</v>
+        <v>90734</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15273,25 +15283,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15301,10 +15311,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>527094</v>
+        <v>526660</v>
       </c>
       <c r="R144" t="n">
-        <v>6938358</v>
+        <v>6938167</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15331,12 +15341,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15363,10 +15373,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226797</v>
+        <v>121226803</v>
       </c>
       <c r="B145" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15403,10 +15413,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526496</v>
+        <v>526335</v>
       </c>
       <c r="R145" t="n">
-        <v>6938343</v>
+        <v>6938150</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15439,11 +15449,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15470,10 +15475,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121226821</v>
+        <v>121221064</v>
       </c>
       <c r="B146" t="n">
-        <v>78608</v>
+        <v>90734</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15486,37 +15491,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526199</v>
+        <v>526664</v>
       </c>
       <c r="R146" t="n">
-        <v>6938254</v>
+        <v>6938176</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15546,11 +15551,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15577,10 +15577,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121226807</v>
+        <v>121219596</v>
       </c>
       <c r="B147" t="n">
-        <v>79689</v>
+        <v>78345</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15593,37 +15593,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526201</v>
+        <v>526982</v>
       </c>
       <c r="R147" t="n">
-        <v>6938252</v>
+        <v>6937928</v>
       </c>
       <c r="S147" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15679,10 +15679,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226819</v>
+        <v>121220094</v>
       </c>
       <c r="B148" t="n">
-        <v>98104</v>
+        <v>78345</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15691,41 +15691,41 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526646</v>
+        <v>526766</v>
       </c>
       <c r="R148" t="n">
-        <v>6938173</v>
+        <v>6938100</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15781,10 +15781,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226805</v>
+        <v>121226806</v>
       </c>
       <c r="B149" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15821,10 +15821,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526203</v>
+        <v>526182</v>
       </c>
       <c r="R149" t="n">
-        <v>6938195</v>
+        <v>6938206</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15883,10 +15883,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121212788</v>
+        <v>121212776</v>
       </c>
       <c r="B150" t="n">
-        <v>91995</v>
+        <v>78609</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15895,25 +15895,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15923,10 +15923,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526776</v>
+        <v>527090</v>
       </c>
       <c r="R150" t="n">
-        <v>6938419</v>
+        <v>6938365</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -15985,10 +15985,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121212780</v>
+        <v>121212779</v>
       </c>
       <c r="B151" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16025,10 +16025,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>527567</v>
+        <v>527495</v>
       </c>
       <c r="R151" t="n">
-        <v>6937949</v>
+        <v>6938009</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16087,10 +16087,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121219658</v>
+        <v>121226794</v>
       </c>
       <c r="B152" t="n">
-        <v>90684</v>
+        <v>79719</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16103,37 +16103,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526953</v>
+        <v>526478</v>
       </c>
       <c r="R152" t="n">
-        <v>6937958</v>
+        <v>6938348</v>
       </c>
       <c r="S152" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16189,10 +16189,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226791</v>
+        <v>121226818</v>
       </c>
       <c r="B153" t="n">
-        <v>89768</v>
+        <v>98105</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16201,25 +16201,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16229,10 +16229,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526205</v>
+        <v>526525</v>
       </c>
       <c r="R153" t="n">
-        <v>6938282</v>
+        <v>6938312</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16291,10 +16291,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226812</v>
+        <v>121226817</v>
       </c>
       <c r="B154" t="n">
-        <v>79689</v>
+        <v>98105</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16303,25 +16303,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16331,10 +16331,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526551</v>
+        <v>526581</v>
       </c>
       <c r="R154" t="n">
-        <v>6938312</v>
+        <v>6938053</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16393,10 +16393,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121226815</v>
+        <v>121223305</v>
       </c>
       <c r="B155" t="n">
-        <v>78344</v>
+        <v>98105</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16405,41 +16405,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526527</v>
+        <v>526584</v>
       </c>
       <c r="R155" t="n">
-        <v>6938317</v>
+        <v>6938052</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16495,10 +16495,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121226804</v>
+        <v>121212789</v>
       </c>
       <c r="B156" t="n">
-        <v>79689</v>
+        <v>91996</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16507,25 +16507,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526224</v>
+        <v>526823</v>
       </c>
       <c r="R156" t="n">
-        <v>6938191</v>
+        <v>6938405</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16597,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121220094</v>
+        <v>121226802</v>
       </c>
       <c r="B157" t="n">
-        <v>78344</v>
+        <v>79690</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16613,37 +16613,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526766</v>
+        <v>526716</v>
       </c>
       <c r="R157" t="n">
-        <v>6938100</v>
+        <v>6937997</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16699,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121223305</v>
+        <v>121226801</v>
       </c>
       <c r="B158" t="n">
-        <v>98104</v>
+        <v>79690</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16711,41 +16711,41 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526584</v>
+        <v>526714</v>
       </c>
       <c r="R158" t="n">
-        <v>6938052</v>
+        <v>6938008</v>
       </c>
       <c r="S158" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16801,10 +16801,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226816</v>
+        <v>121212791</v>
       </c>
       <c r="B159" t="n">
-        <v>98104</v>
+        <v>79725</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16813,25 +16813,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526789</v>
+        <v>527094</v>
       </c>
       <c r="R159" t="n">
-        <v>6937993</v>
+        <v>6938358</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16871,12 +16871,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16903,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226793</v>
+        <v>121226815</v>
       </c>
       <c r="B160" t="n">
-        <v>90739</v>
+        <v>78345</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16919,21 +16919,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16943,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526519</v>
+        <v>526527</v>
       </c>
       <c r="R160" t="n">
-        <v>6938315</v>
+        <v>6938317</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17005,10 +17005,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226808</v>
+        <v>121226792</v>
       </c>
       <c r="B161" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17021,21 +17021,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526482</v>
+        <v>526796</v>
       </c>
       <c r="R161" t="n">
-        <v>6938338</v>
+        <v>6937966</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226796</v>
+        <v>121226816</v>
       </c>
       <c r="B162" t="n">
-        <v>91005</v>
+        <v>98105</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17119,25 +17119,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17147,10 +17147,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526796</v>
+        <v>526789</v>
       </c>
       <c r="R162" t="n">
-        <v>6937966</v>
+        <v>6937993</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17209,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226806</v>
+        <v>121226805</v>
       </c>
       <c r="B163" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526182</v>
+        <v>526203</v>
       </c>
       <c r="R163" t="n">
-        <v>6938206</v>
+        <v>6938195</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17311,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226813</v>
+        <v>121226808</v>
       </c>
       <c r="B164" t="n">
-        <v>78344</v>
+        <v>79690</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17327,21 +17327,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526365</v>
+        <v>526482</v>
       </c>
       <c r="R164" t="n">
-        <v>6938404</v>
+        <v>6938338</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17413,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121212785</v>
+        <v>121226819</v>
       </c>
       <c r="B165" t="n">
-        <v>78253</v>
+        <v>98105</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,25 +17425,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17453,10 +17453,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526753</v>
+        <v>526646</v>
       </c>
       <c r="R165" t="n">
-        <v>6938395</v>
+        <v>6938173</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17483,12 +17483,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17515,10 +17515,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226801</v>
+        <v>121226791</v>
       </c>
       <c r="B166" t="n">
-        <v>79689</v>
+        <v>89769</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17531,21 +17531,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526714</v>
+        <v>526205</v>
       </c>
       <c r="R166" t="n">
-        <v>6938008</v>
+        <v>6938282</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17617,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226810</v>
+        <v>121212778</v>
       </c>
       <c r="B167" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17633,21 +17633,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526533</v>
+        <v>527288</v>
       </c>
       <c r="R167" t="n">
-        <v>6938315</v>
+        <v>6938221</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17687,12 +17687,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121212789</v>
+        <v>121212785</v>
       </c>
       <c r="B168" t="n">
-        <v>91995</v>
+        <v>78254</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,25 +17731,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526823</v>
+        <v>526753</v>
       </c>
       <c r="R168" t="n">
-        <v>6938405</v>
+        <v>6938395</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17821,10 +17821,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121212693</v>
+        <v>121246286</v>
       </c>
       <c r="B169" t="n">
-        <v>91999</v>
+        <v>92025</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17837,27 +17837,24 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -17904,7 +17901,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp under samma tallåga</t>
+          <t>Även smalfotad taggsvamp under samma låga</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17913,7 +17910,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17932,10 +17928,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121246286</v>
+        <v>121212693</v>
       </c>
       <c r="B170" t="n">
-        <v>92024</v>
+        <v>92000</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17948,24 +17944,27 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -18012,7 +18011,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Även smalfotad taggsvamp under samma låga</t>
+          <t>Tajgataggsvamp under samma tallåga</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18021,6 +18020,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -6153,10 +6153,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121212765</v>
+        <v>121212739</v>
       </c>
       <c r="B55" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6165,25 +6165,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>526955</v>
+        <v>527304</v>
       </c>
       <c r="R55" t="n">
-        <v>6938367</v>
+        <v>6938173</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6255,10 +6255,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121212694</v>
+        <v>121212774</v>
       </c>
       <c r="B56" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6267,25 +6267,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>527088</v>
+        <v>526840</v>
       </c>
       <c r="R56" t="n">
-        <v>6938356</v>
+        <v>6938383</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6357,10 +6357,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121212713</v>
+        <v>121212772</v>
       </c>
       <c r="B57" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6373,21 +6373,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6397,10 +6397,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>526960</v>
+        <v>526971</v>
       </c>
       <c r="R57" t="n">
-        <v>6938390</v>
+        <v>6938369</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6433,6 +6433,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6459,10 +6464,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121212738</v>
+        <v>121212769</v>
       </c>
       <c r="B58" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6471,25 +6476,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6499,10 +6504,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>527288</v>
+        <v>527263</v>
       </c>
       <c r="R58" t="n">
-        <v>6938221</v>
+        <v>6938242</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6561,7 +6566,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121212728</v>
+        <v>121212724</v>
       </c>
       <c r="B59" t="n">
         <v>79690</v>
@@ -6601,10 +6606,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>527148</v>
+        <v>527109</v>
       </c>
       <c r="R59" t="n">
-        <v>6938301</v>
+        <v>6938336</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -6663,10 +6668,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121212752</v>
+        <v>121212714</v>
       </c>
       <c r="B60" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6679,21 +6684,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6703,10 +6708,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>526804</v>
+        <v>526955</v>
       </c>
       <c r="R60" t="n">
-        <v>6938398</v>
+        <v>6938368</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -6765,10 +6770,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121212722</v>
+        <v>121212701</v>
       </c>
       <c r="B61" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6781,21 +6786,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6805,10 +6810,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>527075</v>
+        <v>526960</v>
       </c>
       <c r="R61" t="n">
-        <v>6938349</v>
+        <v>6938387</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -6867,10 +6872,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121212688</v>
+        <v>121212738</v>
       </c>
       <c r="B62" t="n">
-        <v>95652</v>
+        <v>79690</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6883,21 +6888,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6907,10 +6912,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>527409</v>
+        <v>527288</v>
       </c>
       <c r="R62" t="n">
-        <v>6938091</v>
+        <v>6938221</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -6969,10 +6974,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121212697</v>
+        <v>121212690</v>
       </c>
       <c r="B63" t="n">
-        <v>79691</v>
+        <v>90720</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6985,21 +6990,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7009,10 +7014,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>527186</v>
+        <v>527263</v>
       </c>
       <c r="R63" t="n">
-        <v>6938273</v>
+        <v>6938234</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7071,7 +7076,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121212705</v>
+        <v>121212703</v>
       </c>
       <c r="B64" t="n">
         <v>91006</v>
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>527310</v>
+        <v>527253</v>
       </c>
       <c r="R64" t="n">
-        <v>6938160</v>
+        <v>6938232</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7173,10 +7178,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121212753</v>
+        <v>121212764</v>
       </c>
       <c r="B65" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7185,25 +7190,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7213,10 +7218,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>526856</v>
+        <v>526945</v>
       </c>
       <c r="R65" t="n">
-        <v>6938391</v>
+        <v>6938389</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7275,7 +7280,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121212740</v>
+        <v>121212711</v>
       </c>
       <c r="B66" t="n">
         <v>79690</v>
@@ -7315,10 +7320,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>527350</v>
+        <v>527051</v>
       </c>
       <c r="R66" t="n">
-        <v>6938133</v>
+        <v>6938349</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7377,10 +7382,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121212762</v>
+        <v>121212705</v>
       </c>
       <c r="B67" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7389,25 +7394,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7417,10 +7422,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>526868</v>
+        <v>527310</v>
       </c>
       <c r="R67" t="n">
-        <v>6938367</v>
+        <v>6938160</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -7479,10 +7484,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121212772</v>
+        <v>121212736</v>
       </c>
       <c r="B68" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7495,21 +7500,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7519,10 +7524,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>526971</v>
+        <v>527250</v>
       </c>
       <c r="R68" t="n">
-        <v>6938369</v>
+        <v>6938289</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7555,11 +7560,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7586,10 +7586,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121212696</v>
+        <v>121212760</v>
       </c>
       <c r="B69" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>527288</v>
+        <v>526842</v>
       </c>
       <c r="R69" t="n">
-        <v>6938221</v>
+        <v>6938396</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121212719</v>
+        <v>121212722</v>
       </c>
       <c r="B70" t="n">
         <v>79690</v>
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>527051</v>
+        <v>527075</v>
       </c>
       <c r="R70" t="n">
-        <v>6938362</v>
+        <v>6938349</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7790,10 +7790,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121212775</v>
+        <v>121212751</v>
       </c>
       <c r="B71" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7806,21 +7806,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>527023</v>
+        <v>526755</v>
       </c>
       <c r="R71" t="n">
-        <v>6938359</v>
+        <v>6938374</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121212721</v>
+        <v>121212735</v>
       </c>
       <c r="B72" t="n">
         <v>79690</v>
@@ -7932,10 +7932,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>527074</v>
+        <v>527245</v>
       </c>
       <c r="R72" t="n">
-        <v>6938353</v>
+        <v>6938291</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -7994,7 +7994,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121212735</v>
+        <v>121212731</v>
       </c>
       <c r="B73" t="n">
         <v>79690</v>
@@ -8034,10 +8034,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>527245</v>
+        <v>527184</v>
       </c>
       <c r="R73" t="n">
-        <v>6938291</v>
+        <v>6938280</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8096,7 +8096,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121212761</v>
+        <v>121212765</v>
       </c>
       <c r="B74" t="n">
         <v>98105</v>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>526852</v>
+        <v>526955</v>
       </c>
       <c r="R74" t="n">
-        <v>6938391</v>
+        <v>6938367</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121212725</v>
+        <v>121212713</v>
       </c>
       <c r="B75" t="n">
         <v>79690</v>
@@ -8238,10 +8238,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>527111</v>
+        <v>526960</v>
       </c>
       <c r="R75" t="n">
-        <v>6938327</v>
+        <v>6938390</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121212710</v>
+        <v>121212756</v>
       </c>
       <c r="B76" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8312,25 +8312,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8340,10 +8340,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>527495</v>
+        <v>527255</v>
       </c>
       <c r="R76" t="n">
-        <v>6938009</v>
+        <v>6938220</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8407,10 +8407,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121212773</v>
+        <v>121212725</v>
       </c>
       <c r="B77" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8423,21 +8423,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8447,10 +8447,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>526989</v>
+        <v>527111</v>
       </c>
       <c r="R77" t="n">
-        <v>6938371</v>
+        <v>6938327</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -8483,11 +8483,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8514,10 +8509,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121212716</v>
+        <v>121212689</v>
       </c>
       <c r="B78" t="n">
-        <v>79690</v>
+        <v>79227</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8530,21 +8525,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8554,10 +8549,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>526994</v>
+        <v>526855</v>
       </c>
       <c r="R78" t="n">
-        <v>6938374</v>
+        <v>6938391</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -8616,10 +8611,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121212701</v>
+        <v>121212712</v>
       </c>
       <c r="B79" t="n">
-        <v>91006</v>
+        <v>79690</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8632,21 +8627,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8656,10 +8651,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>526960</v>
+        <v>526743</v>
       </c>
       <c r="R79" t="n">
-        <v>6938387</v>
+        <v>6938415</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -8718,10 +8713,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121212746</v>
+        <v>121212773</v>
       </c>
       <c r="B80" t="n">
-        <v>79726</v>
+        <v>78609</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8730,25 +8725,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8758,10 +8753,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>527088</v>
+        <v>526989</v>
       </c>
       <c r="R80" t="n">
-        <v>6938356</v>
+        <v>6938371</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -8794,6 +8789,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8820,10 +8820,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121212759</v>
+        <v>121212717</v>
       </c>
       <c r="B81" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8832,25 +8832,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8860,10 +8860,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>526838</v>
+        <v>527023</v>
       </c>
       <c r="R81" t="n">
-        <v>6938397</v>
+        <v>6938359</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121212718</v>
+        <v>121212755</v>
       </c>
       <c r="B82" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8938,21 +8938,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8962,10 +8962,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>527038</v>
+        <v>526945</v>
       </c>
       <c r="R82" t="n">
-        <v>6938372</v>
+        <v>6938389</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -9024,10 +9024,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121212715</v>
+        <v>121212750</v>
       </c>
       <c r="B83" t="n">
-        <v>79690</v>
+        <v>80566</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9040,21 +9040,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9064,10 +9064,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>526971</v>
+        <v>526756</v>
       </c>
       <c r="R83" t="n">
-        <v>6938369</v>
+        <v>6938437</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -9126,10 +9126,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121212690</v>
+        <v>121212715</v>
       </c>
       <c r="B84" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9142,21 +9142,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9166,10 +9166,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>527263</v>
+        <v>526971</v>
       </c>
       <c r="R84" t="n">
-        <v>6938234</v>
+        <v>6938369</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -9228,10 +9228,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121212709</v>
+        <v>121212727</v>
       </c>
       <c r="B85" t="n">
-        <v>78346</v>
+        <v>79690</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9244,21 +9244,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9268,10 +9268,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>526856</v>
+        <v>527148</v>
       </c>
       <c r="R85" t="n">
-        <v>6938391</v>
+        <v>6938301</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121212734</v>
+        <v>121212745</v>
       </c>
       <c r="B86" t="n">
-        <v>79690</v>
+        <v>79726</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9342,25 +9342,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>527214</v>
+        <v>526960</v>
       </c>
       <c r="R86" t="n">
-        <v>6938296</v>
+        <v>6938390</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -9432,10 +9432,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121212714</v>
+        <v>121212699</v>
       </c>
       <c r="B87" t="n">
-        <v>79690</v>
+        <v>79594</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9444,25 +9444,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9472,10 +9472,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>526955</v>
+        <v>527249</v>
       </c>
       <c r="R87" t="n">
-        <v>6938368</v>
+        <v>6938289</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -9534,10 +9534,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121212712</v>
+        <v>121212708</v>
       </c>
       <c r="B88" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9546,25 +9546,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9574,10 +9574,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>526743</v>
+        <v>527252</v>
       </c>
       <c r="R88" t="n">
-        <v>6938415</v>
+        <v>6938285</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -9636,10 +9636,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121212764</v>
+        <v>121212730</v>
       </c>
       <c r="B89" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9648,25 +9648,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9676,10 +9676,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>526945</v>
+        <v>527177</v>
       </c>
       <c r="R89" t="n">
-        <v>6938389</v>
+        <v>6938273</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -9738,10 +9738,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121212755</v>
+        <v>121212734</v>
       </c>
       <c r="B90" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>526945</v>
+        <v>527214</v>
       </c>
       <c r="R90" t="n">
-        <v>6938389</v>
+        <v>6938296</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -9840,7 +9840,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121212724</v>
+        <v>121212733</v>
       </c>
       <c r="B91" t="n">
         <v>79690</v>
@@ -9880,10 +9880,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>527109</v>
+        <v>527186</v>
       </c>
       <c r="R91" t="n">
-        <v>6938336</v>
+        <v>6938273</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -9942,10 +9942,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121212744</v>
+        <v>121212775</v>
       </c>
       <c r="B92" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9958,21 +9958,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>527495</v>
+        <v>527023</v>
       </c>
       <c r="R92" t="n">
-        <v>6938012</v>
+        <v>6938359</v>
       </c>
       <c r="S92" t="n">
         <v>25</v>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121212703</v>
+        <v>121212692</v>
       </c>
       <c r="B93" t="n">
-        <v>91006</v>
+        <v>57509</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10060,21 +10060,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>527253</v>
+        <v>527210</v>
       </c>
       <c r="R93" t="n">
-        <v>6938232</v>
+        <v>6938291</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -10120,6 +10120,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>1 adult</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10146,10 +10151,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121212695</v>
+        <v>121212757</v>
       </c>
       <c r="B94" t="n">
-        <v>79719</v>
+        <v>98105</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10158,25 +10163,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10186,10 +10191,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>527184</v>
+        <v>526927</v>
       </c>
       <c r="R94" t="n">
-        <v>6938280</v>
+        <v>6938376</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -10248,10 +10253,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121212729</v>
+        <v>121212753</v>
       </c>
       <c r="B95" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10264,21 +10269,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10288,10 +10293,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>527168</v>
+        <v>526856</v>
       </c>
       <c r="R95" t="n">
-        <v>6938291</v>
+        <v>6938391</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -10350,10 +10355,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121212732</v>
+        <v>121212761</v>
       </c>
       <c r="B96" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10362,25 +10367,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10390,10 +10395,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>527184</v>
+        <v>526852</v>
       </c>
       <c r="R96" t="n">
-        <v>6938280</v>
+        <v>6938391</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -10452,10 +10457,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121212736</v>
+        <v>121212762</v>
       </c>
       <c r="B97" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10464,25 +10469,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10492,10 +10497,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>527250</v>
+        <v>526868</v>
       </c>
       <c r="R97" t="n">
-        <v>6938289</v>
+        <v>6938367</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -10554,7 +10559,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121212757</v>
+        <v>121212763</v>
       </c>
       <c r="B98" t="n">
         <v>98105</v>
@@ -10594,10 +10599,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>526927</v>
+        <v>526911</v>
       </c>
       <c r="R98" t="n">
-        <v>6938376</v>
+        <v>6938360</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -10656,10 +10661,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121212769</v>
+        <v>121212721</v>
       </c>
       <c r="B99" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10668,25 +10673,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10696,10 +10701,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>527263</v>
+        <v>527074</v>
       </c>
       <c r="R99" t="n">
-        <v>6938242</v>
+        <v>6938353</v>
       </c>
       <c r="S99" t="n">
         <v>25</v>
@@ -10758,10 +10763,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121212758</v>
+        <v>121212697</v>
       </c>
       <c r="B100" t="n">
-        <v>98105</v>
+        <v>79691</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10770,25 +10775,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10798,10 +10803,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>526823</v>
+        <v>527186</v>
       </c>
       <c r="R100" t="n">
-        <v>6938405</v>
+        <v>6938273</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -10860,10 +10865,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121212730</v>
+        <v>121212758</v>
       </c>
       <c r="B101" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10872,25 +10877,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10900,10 +10905,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>527177</v>
+        <v>526823</v>
       </c>
       <c r="R101" t="n">
-        <v>6938273</v>
+        <v>6938405</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -10962,7 +10967,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121212733</v>
+        <v>121212710</v>
       </c>
       <c r="B102" t="n">
         <v>79690</v>
@@ -11002,10 +11007,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>527186</v>
+        <v>527495</v>
       </c>
       <c r="R102" t="n">
-        <v>6938273</v>
+        <v>6938009</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11038,6 +11043,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11064,10 +11074,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121212774</v>
+        <v>121212709</v>
       </c>
       <c r="B103" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11080,21 +11090,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11104,10 +11114,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>526840</v>
+        <v>526856</v>
       </c>
       <c r="R103" t="n">
-        <v>6938383</v>
+        <v>6938391</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -11166,10 +11176,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121212750</v>
+        <v>121212740</v>
       </c>
       <c r="B104" t="n">
-        <v>80566</v>
+        <v>79690</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11182,21 +11192,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11206,10 +11216,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>526756</v>
+        <v>527350</v>
       </c>
       <c r="R104" t="n">
-        <v>6938437</v>
+        <v>6938133</v>
       </c>
       <c r="S104" t="n">
         <v>25</v>
@@ -11268,10 +11278,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121212699</v>
+        <v>121212752</v>
       </c>
       <c r="B105" t="n">
-        <v>79594</v>
+        <v>78345</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11280,25 +11290,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11308,10 +11318,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>527249</v>
+        <v>526804</v>
       </c>
       <c r="R105" t="n">
-        <v>6938289</v>
+        <v>6938398</v>
       </c>
       <c r="S105" t="n">
         <v>25</v>
@@ -11370,7 +11380,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121212737</v>
+        <v>121212719</v>
       </c>
       <c r="B106" t="n">
         <v>79690</v>
@@ -11410,10 +11420,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>527248</v>
+        <v>527051</v>
       </c>
       <c r="R106" t="n">
-        <v>6938256</v>
+        <v>6938362</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -11472,10 +11482,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121212745</v>
+        <v>121212688</v>
       </c>
       <c r="B107" t="n">
-        <v>79726</v>
+        <v>95652</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11484,25 +11494,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11512,10 +11522,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>526960</v>
+        <v>527409</v>
       </c>
       <c r="R107" t="n">
-        <v>6938390</v>
+        <v>6938091</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -11574,10 +11584,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121212751</v>
+        <v>121212694</v>
       </c>
       <c r="B108" t="n">
-        <v>78345</v>
+        <v>79719</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11586,25 +11596,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11614,10 +11624,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>526755</v>
+        <v>527088</v>
       </c>
       <c r="R108" t="n">
-        <v>6938374</v>
+        <v>6938356</v>
       </c>
       <c r="S108" t="n">
         <v>25</v>
@@ -11676,10 +11686,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121212760</v>
+        <v>121212737</v>
       </c>
       <c r="B109" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11688,25 +11698,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11716,10 +11726,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>526842</v>
+        <v>527248</v>
       </c>
       <c r="R109" t="n">
-        <v>6938396</v>
+        <v>6938256</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11778,10 +11788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121212763</v>
+        <v>121212746</v>
       </c>
       <c r="B110" t="n">
-        <v>98105</v>
+        <v>79726</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11790,25 +11800,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11818,10 +11828,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>526911</v>
+        <v>527088</v>
       </c>
       <c r="R110" t="n">
-        <v>6938360</v>
+        <v>6938356</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11880,10 +11890,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121212698</v>
+        <v>121212716</v>
       </c>
       <c r="B111" t="n">
-        <v>79691</v>
+        <v>79690</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11896,21 +11906,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11920,10 +11930,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>527211</v>
+        <v>526994</v>
       </c>
       <c r="R111" t="n">
-        <v>6938302</v>
+        <v>6938374</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11982,10 +11992,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121212708</v>
+        <v>121212698</v>
       </c>
       <c r="B112" t="n">
-        <v>97059</v>
+        <v>79691</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11994,25 +12004,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12022,10 +12032,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>527252</v>
+        <v>527211</v>
       </c>
       <c r="R112" t="n">
-        <v>6938285</v>
+        <v>6938302</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -12084,10 +12094,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121212689</v>
+        <v>121212759</v>
       </c>
       <c r="B113" t="n">
-        <v>79227</v>
+        <v>98105</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12096,25 +12106,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12124,10 +12134,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>526855</v>
+        <v>526838</v>
       </c>
       <c r="R113" t="n">
-        <v>6938391</v>
+        <v>6938397</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -12186,7 +12196,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121212739</v>
+        <v>121212718</v>
       </c>
       <c r="B114" t="n">
         <v>79690</v>
@@ -12226,10 +12236,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>527304</v>
+        <v>527038</v>
       </c>
       <c r="R114" t="n">
-        <v>6938173</v>
+        <v>6938372</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12288,7 +12298,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121212711</v>
+        <v>121212729</v>
       </c>
       <c r="B115" t="n">
         <v>79690</v>
@@ -12328,10 +12338,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>527051</v>
+        <v>527168</v>
       </c>
       <c r="R115" t="n">
-        <v>6938349</v>
+        <v>6938291</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12390,7 +12400,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121212717</v>
+        <v>121212744</v>
       </c>
       <c r="B116" t="n">
         <v>79690</v>
@@ -12430,10 +12440,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>527023</v>
+        <v>527495</v>
       </c>
       <c r="R116" t="n">
-        <v>6938359</v>
+        <v>6938012</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12492,10 +12502,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121212723</v>
+        <v>121212771</v>
       </c>
       <c r="B117" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12504,25 +12514,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12532,10 +12542,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>527088</v>
+        <v>527317</v>
       </c>
       <c r="R117" t="n">
-        <v>6938358</v>
+        <v>6938165</v>
       </c>
       <c r="S117" t="n">
         <v>25</v>
@@ -12594,10 +12604,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121212756</v>
+        <v>121212695</v>
       </c>
       <c r="B118" t="n">
-        <v>98105</v>
+        <v>79719</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12606,25 +12616,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12634,10 +12644,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>527255</v>
+        <v>527184</v>
       </c>
       <c r="R118" t="n">
-        <v>6938220</v>
+        <v>6938280</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12670,11 +12680,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12701,10 +12706,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121212771</v>
+        <v>121212723</v>
       </c>
       <c r="B119" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12713,25 +12718,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12741,10 +12746,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>527317</v>
+        <v>527088</v>
       </c>
       <c r="R119" t="n">
-        <v>6938165</v>
+        <v>6938358</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12803,10 +12808,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121212692</v>
+        <v>121212696</v>
       </c>
       <c r="B120" t="n">
-        <v>57509</v>
+        <v>79719</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12815,25 +12820,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12843,10 +12848,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>527210</v>
+        <v>527288</v>
       </c>
       <c r="R120" t="n">
-        <v>6938291</v>
+        <v>6938221</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -12879,11 +12884,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>1 adult</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121220916</v>
+        <v>121212776</v>
       </c>
       <c r="B121" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,41 +12922,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>526647</v>
+        <v>527090</v>
       </c>
       <c r="R121" t="n">
-        <v>6938174</v>
+        <v>6938365</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12980,12 +12980,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226793</v>
+        <v>121226799</v>
       </c>
       <c r="B122" t="n">
-        <v>90740</v>
+        <v>79690</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13052,10 +13052,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526519</v>
+        <v>526747</v>
       </c>
       <c r="R122" t="n">
-        <v>6938315</v>
+        <v>6937983</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121226822</v>
+        <v>121212791</v>
       </c>
       <c r="B123" t="n">
-        <v>91996</v>
+        <v>79725</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13130,21 +13130,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>526182</v>
+        <v>527094</v>
       </c>
       <c r="R123" t="n">
-        <v>6938234</v>
+        <v>6938358</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13184,12 +13184,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121221199</v>
+        <v>121226817</v>
       </c>
       <c r="B124" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,41 +13228,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526592</v>
+        <v>526581</v>
       </c>
       <c r="R124" t="n">
-        <v>6938232</v>
+        <v>6938053</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13318,10 +13318,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226799</v>
+        <v>121226820</v>
       </c>
       <c r="B125" t="n">
-        <v>79690</v>
+        <v>90734</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13334,21 +13334,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13358,10 +13358,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526747</v>
+        <v>526660</v>
       </c>
       <c r="R125" t="n">
-        <v>6937983</v>
+        <v>6938167</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -13420,10 +13420,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121219658</v>
+        <v>121226803</v>
       </c>
       <c r="B126" t="n">
-        <v>90685</v>
+        <v>79690</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13432,41 +13432,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526953</v>
+        <v>526335</v>
       </c>
       <c r="R126" t="n">
-        <v>6937958</v>
+        <v>6938150</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226796</v>
+        <v>121226822</v>
       </c>
       <c r="B127" t="n">
-        <v>91006</v>
+        <v>91996</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,25 +13534,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13562,10 +13562,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526796</v>
+        <v>526182</v>
       </c>
       <c r="R127" t="n">
-        <v>6937966</v>
+        <v>6938234</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13624,10 +13624,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121226813</v>
+        <v>121221199</v>
       </c>
       <c r="B128" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13640,37 +13640,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526365</v>
+        <v>526592</v>
       </c>
       <c r="R128" t="n">
-        <v>6938404</v>
+        <v>6938232</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13726,10 +13726,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226811</v>
+        <v>121226792</v>
       </c>
       <c r="B129" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,21 +13742,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13766,10 +13766,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526545</v>
+        <v>526796</v>
       </c>
       <c r="R129" t="n">
-        <v>6938319</v>
+        <v>6937966</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -13828,10 +13828,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226824</v>
+        <v>121226819</v>
       </c>
       <c r="B130" t="n">
-        <v>91282</v>
+        <v>98105</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,21 +13844,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13868,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526747</v>
+        <v>526646</v>
       </c>
       <c r="R130" t="n">
-        <v>6937983</v>
+        <v>6938173</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13930,10 +13930,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121226809</v>
+        <v>121212778</v>
       </c>
       <c r="B131" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13946,21 +13946,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13970,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>526518</v>
+        <v>527288</v>
       </c>
       <c r="R131" t="n">
-        <v>6938295</v>
+        <v>6938221</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14000,12 +14000,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14032,10 +14032,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121226797</v>
+        <v>121212788</v>
       </c>
       <c r="B132" t="n">
-        <v>79690</v>
+        <v>91996</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14044,25 +14044,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14072,10 +14072,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526496</v>
+        <v>526776</v>
       </c>
       <c r="R132" t="n">
-        <v>6938343</v>
+        <v>6938419</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -14102,17 +14102,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14139,7 +14134,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121226807</v>
+        <v>121226808</v>
       </c>
       <c r="B133" t="n">
         <v>79690</v>
@@ -14179,10 +14174,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526201</v>
+        <v>526482</v>
       </c>
       <c r="R133" t="n">
-        <v>6938252</v>
+        <v>6938338</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14241,7 +14236,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226804</v>
+        <v>121226802</v>
       </c>
       <c r="B134" t="n">
         <v>79690</v>
@@ -14281,10 +14276,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526224</v>
+        <v>526716</v>
       </c>
       <c r="R134" t="n">
-        <v>6938191</v>
+        <v>6937997</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14445,10 +14440,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121212788</v>
+        <v>121212779</v>
       </c>
       <c r="B136" t="n">
-        <v>91996</v>
+        <v>78609</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14457,25 +14452,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14485,10 +14480,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>526776</v>
+        <v>527495</v>
       </c>
       <c r="R136" t="n">
-        <v>6938419</v>
+        <v>6938009</v>
       </c>
       <c r="S136" t="n">
         <v>25</v>
@@ -14547,10 +14542,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121212780</v>
+        <v>121226814</v>
       </c>
       <c r="B137" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14563,21 +14558,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14587,10 +14582,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>527567</v>
+        <v>526515</v>
       </c>
       <c r="R137" t="n">
-        <v>6937949</v>
+        <v>6938303</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14617,12 +14612,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14649,10 +14644,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121222671</v>
+        <v>121226812</v>
       </c>
       <c r="B138" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14665,37 +14660,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526275</v>
+        <v>526551</v>
       </c>
       <c r="R138" t="n">
-        <v>6938199</v>
+        <v>6938312</v>
       </c>
       <c r="S138" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14725,11 +14720,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14756,7 +14746,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226812</v>
+        <v>121226804</v>
       </c>
       <c r="B139" t="n">
         <v>79690</v>
@@ -14796,10 +14786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526551</v>
+        <v>526224</v>
       </c>
       <c r="R139" t="n">
-        <v>6938312</v>
+        <v>6938191</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14858,10 +14848,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226810</v>
+        <v>121226794</v>
       </c>
       <c r="B140" t="n">
-        <v>79690</v>
+        <v>79719</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14870,25 +14860,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14898,10 +14888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526533</v>
+        <v>526478</v>
       </c>
       <c r="R140" t="n">
-        <v>6938315</v>
+        <v>6938348</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14960,10 +14950,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121226795</v>
+        <v>121219596</v>
       </c>
       <c r="B141" t="n">
-        <v>79691</v>
+        <v>78345</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14976,37 +14966,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526554</v>
+        <v>526982</v>
       </c>
       <c r="R141" t="n">
-        <v>6938311</v>
+        <v>6937928</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15062,10 +15052,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121226814</v>
+        <v>121219658</v>
       </c>
       <c r="B142" t="n">
-        <v>78345</v>
+        <v>90685</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15074,41 +15064,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526515</v>
+        <v>526953</v>
       </c>
       <c r="R142" t="n">
-        <v>6938303</v>
+        <v>6937958</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15164,10 +15154,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226821</v>
+        <v>121226807</v>
       </c>
       <c r="B143" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15180,21 +15170,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15204,10 +15194,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526199</v>
+        <v>526201</v>
       </c>
       <c r="R143" t="n">
-        <v>6938254</v>
+        <v>6938252</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15240,11 +15230,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15271,10 +15256,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226820</v>
+        <v>121226797</v>
       </c>
       <c r="B144" t="n">
-        <v>90734</v>
+        <v>79690</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15287,21 +15272,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15311,10 +15296,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526660</v>
+        <v>526496</v>
       </c>
       <c r="R144" t="n">
-        <v>6938167</v>
+        <v>6938343</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15347,6 +15332,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15373,10 +15363,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226803</v>
+        <v>121226818</v>
       </c>
       <c r="B145" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15385,25 +15375,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15413,10 +15403,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526335</v>
+        <v>526525</v>
       </c>
       <c r="R145" t="n">
-        <v>6938150</v>
+        <v>6938312</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15475,10 +15465,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121221064</v>
+        <v>121212789</v>
       </c>
       <c r="B146" t="n">
-        <v>90734</v>
+        <v>91996</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15487,41 +15477,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526664</v>
+        <v>526823</v>
       </c>
       <c r="R146" t="n">
-        <v>6938176</v>
+        <v>6938405</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15545,12 +15535,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15577,7 +15567,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121219596</v>
+        <v>121220094</v>
       </c>
       <c r="B147" t="n">
         <v>78345</v>
@@ -15617,13 +15607,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526982</v>
+        <v>526766</v>
       </c>
       <c r="R147" t="n">
-        <v>6937928</v>
+        <v>6938100</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15679,10 +15669,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121220094</v>
+        <v>121226795</v>
       </c>
       <c r="B148" t="n">
-        <v>78345</v>
+        <v>79691</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15695,37 +15685,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526766</v>
+        <v>526554</v>
       </c>
       <c r="R148" t="n">
-        <v>6938100</v>
+        <v>6938311</v>
       </c>
       <c r="S148" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15781,7 +15771,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226806</v>
+        <v>121226801</v>
       </c>
       <c r="B149" t="n">
         <v>79690</v>
@@ -15821,10 +15811,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526182</v>
+        <v>526714</v>
       </c>
       <c r="R149" t="n">
-        <v>6938206</v>
+        <v>6938008</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15883,10 +15873,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121212776</v>
+        <v>121221064</v>
       </c>
       <c r="B150" t="n">
-        <v>78609</v>
+        <v>90734</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15899,37 +15889,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>527090</v>
+        <v>526664</v>
       </c>
       <c r="R150" t="n">
-        <v>6938365</v>
+        <v>6938176</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15953,12 +15943,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15985,7 +15975,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121212779</v>
+        <v>121212780</v>
       </c>
       <c r="B151" t="n">
         <v>78609</v>
@@ -16025,10 +16015,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>527495</v>
+        <v>527567</v>
       </c>
       <c r="R151" t="n">
-        <v>6938009</v>
+        <v>6937949</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16087,10 +16077,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121226794</v>
+        <v>121222671</v>
       </c>
       <c r="B152" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16099,41 +16089,41 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526478</v>
+        <v>526275</v>
       </c>
       <c r="R152" t="n">
-        <v>6938348</v>
+        <v>6938199</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16163,6 +16153,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16189,10 +16184,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121226818</v>
+        <v>121212785</v>
       </c>
       <c r="B153" t="n">
-        <v>98105</v>
+        <v>78254</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16201,25 +16196,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16229,10 +16224,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526525</v>
+        <v>526753</v>
       </c>
       <c r="R153" t="n">
-        <v>6938312</v>
+        <v>6938395</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16259,12 +16254,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16291,10 +16286,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226817</v>
+        <v>121226793</v>
       </c>
       <c r="B154" t="n">
-        <v>98105</v>
+        <v>90740</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16303,25 +16298,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16331,10 +16326,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526581</v>
+        <v>526519</v>
       </c>
       <c r="R154" t="n">
-        <v>6938053</v>
+        <v>6938315</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16393,10 +16388,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121223305</v>
+        <v>121226805</v>
       </c>
       <c r="B155" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16405,41 +16400,41 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>526584</v>
+        <v>526203</v>
       </c>
       <c r="R155" t="n">
-        <v>6938052</v>
+        <v>6938195</v>
       </c>
       <c r="S155" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16495,10 +16490,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121212789</v>
+        <v>121226791</v>
       </c>
       <c r="B156" t="n">
-        <v>91996</v>
+        <v>89769</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16507,25 +16502,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16535,10 +16530,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526823</v>
+        <v>526205</v>
       </c>
       <c r="R156" t="n">
-        <v>6938405</v>
+        <v>6938282</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16565,12 +16560,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16597,10 +16592,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121226802</v>
+        <v>121223305</v>
       </c>
       <c r="B157" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16609,41 +16604,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526716</v>
+        <v>526584</v>
       </c>
       <c r="R157" t="n">
-        <v>6937997</v>
+        <v>6938052</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16699,7 +16694,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226801</v>
+        <v>121226809</v>
       </c>
       <c r="B158" t="n">
         <v>79690</v>
@@ -16739,10 +16734,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526714</v>
+        <v>526518</v>
       </c>
       <c r="R158" t="n">
-        <v>6938008</v>
+        <v>6938295</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16801,10 +16796,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121212791</v>
+        <v>121226811</v>
       </c>
       <c r="B159" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16813,25 +16808,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16841,10 +16836,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>527094</v>
+        <v>526545</v>
       </c>
       <c r="R159" t="n">
-        <v>6938358</v>
+        <v>6938319</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16871,12 +16866,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16903,10 +16898,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226815</v>
+        <v>121226796</v>
       </c>
       <c r="B160" t="n">
-        <v>78345</v>
+        <v>91006</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16919,21 +16914,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16943,10 +16938,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526527</v>
+        <v>526796</v>
       </c>
       <c r="R160" t="n">
-        <v>6938317</v>
+        <v>6937966</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17005,10 +17000,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226792</v>
+        <v>121226810</v>
       </c>
       <c r="B161" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17021,21 +17016,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17045,10 +17040,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526796</v>
+        <v>526533</v>
       </c>
       <c r="R161" t="n">
-        <v>6937966</v>
+        <v>6938315</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17107,7 +17102,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>121226816</v>
+        <v>121220916</v>
       </c>
       <c r="B162" t="n">
         <v>98105</v>
@@ -17143,17 +17138,17 @@
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>526789</v>
+        <v>526647</v>
       </c>
       <c r="R162" t="n">
-        <v>6937993</v>
+        <v>6938174</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -17209,10 +17204,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226805</v>
+        <v>121226815</v>
       </c>
       <c r="B163" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17225,21 +17220,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526203</v>
+        <v>526527</v>
       </c>
       <c r="R163" t="n">
-        <v>6938195</v>
+        <v>6938317</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17311,10 +17306,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226808</v>
+        <v>121226813</v>
       </c>
       <c r="B164" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17327,21 +17322,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17351,10 +17346,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526482</v>
+        <v>526365</v>
       </c>
       <c r="R164" t="n">
-        <v>6938338</v>
+        <v>6938404</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17413,10 +17408,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226819</v>
+        <v>121226806</v>
       </c>
       <c r="B165" t="n">
-        <v>98105</v>
+        <v>79690</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17425,25 +17420,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17453,10 +17448,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526646</v>
+        <v>526182</v>
       </c>
       <c r="R165" t="n">
-        <v>6938173</v>
+        <v>6938206</v>
       </c>
       <c r="S165" t="n">
         <v>25</v>
@@ -17515,10 +17510,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226791</v>
+        <v>121226816</v>
       </c>
       <c r="B166" t="n">
-        <v>89769</v>
+        <v>98105</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17527,25 +17522,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17555,10 +17550,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526205</v>
+        <v>526789</v>
       </c>
       <c r="R166" t="n">
-        <v>6938282</v>
+        <v>6937993</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17617,7 +17612,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121212778</v>
+        <v>121226821</v>
       </c>
       <c r="B167" t="n">
         <v>78609</v>
@@ -17657,10 +17652,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>527288</v>
+        <v>526199</v>
       </c>
       <c r="R167" t="n">
-        <v>6938221</v>
+        <v>6938254</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17687,12 +17682,17 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121212785</v>
+        <v>121226824</v>
       </c>
       <c r="B168" t="n">
-        <v>78254</v>
+        <v>91282</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,25 +17731,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>353</v>
+        <v>760</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526753</v>
+        <v>526747</v>
       </c>
       <c r="R168" t="n">
-        <v>6938395</v>
+        <v>6937983</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17789,12 +17789,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD168" t="b">

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -12910,10 +12910,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121212776</v>
+        <v>121226794</v>
       </c>
       <c r="B121" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12922,25 +12922,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12950,10 +12950,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>527090</v>
+        <v>526478</v>
       </c>
       <c r="R121" t="n">
-        <v>6938365</v>
+        <v>6938348</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -12980,12 +12980,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13012,10 +13012,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121226799</v>
+        <v>121226814</v>
       </c>
       <c r="B122" t="n">
-        <v>79690</v>
+        <v>78345</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13028,21 +13028,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13052,10 +13052,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>526747</v>
+        <v>526515</v>
       </c>
       <c r="R122" t="n">
-        <v>6937983</v>
+        <v>6938303</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13114,10 +13114,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121212791</v>
+        <v>121212779</v>
       </c>
       <c r="B123" t="n">
-        <v>79725</v>
+        <v>78609</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13126,20 +13126,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>527094</v>
+        <v>527495</v>
       </c>
       <c r="R123" t="n">
-        <v>6938358</v>
+        <v>6938009</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -13216,10 +13216,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121226817</v>
+        <v>121226821</v>
       </c>
       <c r="B124" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13228,25 +13228,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>526581</v>
+        <v>526199</v>
       </c>
       <c r="R124" t="n">
-        <v>6938053</v>
+        <v>6938254</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -13292,6 +13292,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13318,10 +13323,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121226820</v>
+        <v>121219658</v>
       </c>
       <c r="B125" t="n">
-        <v>90734</v>
+        <v>90685</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13330,41 +13335,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>526660</v>
+        <v>526953</v>
       </c>
       <c r="R125" t="n">
-        <v>6938167</v>
+        <v>6937958</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13420,7 +13425,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121226803</v>
+        <v>121226809</v>
       </c>
       <c r="B126" t="n">
         <v>79690</v>
@@ -13460,10 +13465,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>526335</v>
+        <v>526518</v>
       </c>
       <c r="R126" t="n">
-        <v>6938150</v>
+        <v>6938295</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -13522,10 +13527,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121226822</v>
+        <v>121226808</v>
       </c>
       <c r="B127" t="n">
-        <v>91996</v>
+        <v>79690</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13534,25 +13539,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13562,10 +13567,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>526182</v>
+        <v>526482</v>
       </c>
       <c r="R127" t="n">
-        <v>6938234</v>
+        <v>6938338</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -13624,10 +13629,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121221199</v>
+        <v>121226801</v>
       </c>
       <c r="B128" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13640,37 +13645,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>526592</v>
+        <v>526714</v>
       </c>
       <c r="R128" t="n">
-        <v>6938232</v>
+        <v>6938008</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13726,10 +13731,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121226792</v>
+        <v>121221199</v>
       </c>
       <c r="B129" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13742,37 +13747,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>526796</v>
+        <v>526592</v>
       </c>
       <c r="R129" t="n">
-        <v>6937966</v>
+        <v>6938232</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13828,10 +13833,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121226819</v>
+        <v>121226824</v>
       </c>
       <c r="B130" t="n">
-        <v>98105</v>
+        <v>91282</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13844,21 +13849,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13868,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>526646</v>
+        <v>526747</v>
       </c>
       <c r="R130" t="n">
-        <v>6938173</v>
+        <v>6937983</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -13930,10 +13935,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121212778</v>
+        <v>121226818</v>
       </c>
       <c r="B131" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13942,25 +13947,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13970,10 +13975,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>527288</v>
+        <v>526525</v>
       </c>
       <c r="R131" t="n">
-        <v>6938221</v>
+        <v>6938312</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14000,12 +14005,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14032,10 +14037,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121212788</v>
+        <v>121221064</v>
       </c>
       <c r="B132" t="n">
-        <v>91996</v>
+        <v>90734</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14044,41 +14049,41 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>526776</v>
+        <v>526664</v>
       </c>
       <c r="R132" t="n">
-        <v>6938419</v>
+        <v>6938176</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14102,12 +14107,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14134,10 +14139,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121226808</v>
+        <v>121212778</v>
       </c>
       <c r="B133" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14150,21 +14155,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14174,10 +14179,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>526482</v>
+        <v>527288</v>
       </c>
       <c r="R133" t="n">
-        <v>6938338</v>
+        <v>6938221</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -14204,12 +14209,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14236,10 +14241,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121226802</v>
+        <v>121226792</v>
       </c>
       <c r="B134" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14252,21 +14257,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14276,10 +14281,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>526716</v>
+        <v>526796</v>
       </c>
       <c r="R134" t="n">
-        <v>6937997</v>
+        <v>6937966</v>
       </c>
       <c r="S134" t="n">
         <v>25</v>
@@ -14338,10 +14343,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121212783</v>
+        <v>121226803</v>
       </c>
       <c r="B135" t="n">
-        <v>78254</v>
+        <v>79690</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14354,21 +14359,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14378,10 +14383,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>526761</v>
+        <v>526335</v>
       </c>
       <c r="R135" t="n">
-        <v>6938348</v>
+        <v>6938150</v>
       </c>
       <c r="S135" t="n">
         <v>25</v>
@@ -14408,12 +14413,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14440,10 +14445,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121212779</v>
+        <v>121220094</v>
       </c>
       <c r="B136" t="n">
-        <v>78609</v>
+        <v>78345</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14456,37 +14461,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>527495</v>
+        <v>526766</v>
       </c>
       <c r="R136" t="n">
-        <v>6938009</v>
+        <v>6938100</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14510,12 +14515,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14542,7 +14547,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121226814</v>
+        <v>121226813</v>
       </c>
       <c r="B137" t="n">
         <v>78345</v>
@@ -14582,10 +14587,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>526515</v>
+        <v>526365</v>
       </c>
       <c r="R137" t="n">
-        <v>6938303</v>
+        <v>6938404</v>
       </c>
       <c r="S137" t="n">
         <v>25</v>
@@ -14644,10 +14649,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121226812</v>
+        <v>121222671</v>
       </c>
       <c r="B138" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14660,37 +14665,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>526551</v>
+        <v>526275</v>
       </c>
       <c r="R138" t="n">
-        <v>6938312</v>
+        <v>6938199</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14720,6 +14725,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14746,10 +14756,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121226804</v>
+        <v>121212776</v>
       </c>
       <c r="B139" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14762,21 +14772,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14786,10 +14796,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>526224</v>
+        <v>527090</v>
       </c>
       <c r="R139" t="n">
-        <v>6938191</v>
+        <v>6938365</v>
       </c>
       <c r="S139" t="n">
         <v>25</v>
@@ -14816,12 +14826,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14848,10 +14858,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121226794</v>
+        <v>121226812</v>
       </c>
       <c r="B140" t="n">
-        <v>79719</v>
+        <v>79690</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14860,25 +14870,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14888,10 +14898,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>526478</v>
+        <v>526551</v>
       </c>
       <c r="R140" t="n">
-        <v>6938348</v>
+        <v>6938312</v>
       </c>
       <c r="S140" t="n">
         <v>25</v>
@@ -14950,10 +14960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121219596</v>
+        <v>121226797</v>
       </c>
       <c r="B141" t="n">
-        <v>78345</v>
+        <v>79690</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14966,37 +14976,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>526982</v>
+        <v>526496</v>
       </c>
       <c r="R141" t="n">
-        <v>6937928</v>
+        <v>6938343</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15026,6 +15036,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15052,10 +15067,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121219658</v>
+        <v>121212780</v>
       </c>
       <c r="B142" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15064,41 +15079,41 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>526953</v>
+        <v>527567</v>
       </c>
       <c r="R142" t="n">
-        <v>6937958</v>
+        <v>6937949</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15122,12 +15137,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15154,10 +15169,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121226807</v>
+        <v>121226819</v>
       </c>
       <c r="B143" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15166,25 +15181,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15194,10 +15209,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>526201</v>
+        <v>526646</v>
       </c>
       <c r="R143" t="n">
-        <v>6938252</v>
+        <v>6938173</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15256,10 +15271,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121226797</v>
+        <v>121226820</v>
       </c>
       <c r="B144" t="n">
-        <v>79690</v>
+        <v>90734</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15272,21 +15287,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15296,10 +15311,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>526496</v>
+        <v>526660</v>
       </c>
       <c r="R144" t="n">
-        <v>6938343</v>
+        <v>6938167</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15332,11 +15347,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15363,10 +15373,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121226818</v>
+        <v>121212783</v>
       </c>
       <c r="B145" t="n">
-        <v>98105</v>
+        <v>78254</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15375,25 +15385,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15403,10 +15413,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>526525</v>
+        <v>526761</v>
       </c>
       <c r="R145" t="n">
-        <v>6938312</v>
+        <v>6938348</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -15433,12 +15443,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15465,10 +15475,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121212789</v>
+        <v>121212791</v>
       </c>
       <c r="B146" t="n">
-        <v>91996</v>
+        <v>79725</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15481,21 +15491,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15505,10 +15515,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>526823</v>
+        <v>527094</v>
       </c>
       <c r="R146" t="n">
-        <v>6938405</v>
+        <v>6938358</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -15567,10 +15577,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121220094</v>
+        <v>121226791</v>
       </c>
       <c r="B147" t="n">
-        <v>78345</v>
+        <v>89769</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15583,37 +15593,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>526766</v>
+        <v>526205</v>
       </c>
       <c r="R147" t="n">
-        <v>6938100</v>
+        <v>6938282</v>
       </c>
       <c r="S147" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15669,10 +15679,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121226795</v>
+        <v>121219596</v>
       </c>
       <c r="B148" t="n">
-        <v>79691</v>
+        <v>78345</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15685,37 +15695,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>526554</v>
+        <v>526982</v>
       </c>
       <c r="R148" t="n">
-        <v>6938311</v>
+        <v>6937928</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15771,10 +15781,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121226801</v>
+        <v>121226796</v>
       </c>
       <c r="B149" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15787,21 +15797,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15811,10 +15821,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>526714</v>
+        <v>526796</v>
       </c>
       <c r="R149" t="n">
-        <v>6938008</v>
+        <v>6937966</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -15873,10 +15883,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121221064</v>
+        <v>121226807</v>
       </c>
       <c r="B150" t="n">
-        <v>90734</v>
+        <v>79690</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15889,37 +15899,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>526664</v>
+        <v>526201</v>
       </c>
       <c r="R150" t="n">
-        <v>6938176</v>
+        <v>6938252</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15975,10 +15985,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121212780</v>
+        <v>121226804</v>
       </c>
       <c r="B151" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15991,21 +16001,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16015,10 +16025,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>527567</v>
+        <v>526224</v>
       </c>
       <c r="R151" t="n">
-        <v>6937949</v>
+        <v>6938191</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16045,12 +16055,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16077,10 +16087,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121222671</v>
+        <v>121226802</v>
       </c>
       <c r="B152" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16093,37 +16103,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>526275</v>
+        <v>526716</v>
       </c>
       <c r="R152" t="n">
-        <v>6938199</v>
+        <v>6937997</v>
       </c>
       <c r="S152" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16153,11 +16163,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16184,10 +16189,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121212785</v>
+        <v>121212788</v>
       </c>
       <c r="B153" t="n">
-        <v>78254</v>
+        <v>91996</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16196,25 +16201,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16224,10 +16229,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>526753</v>
+        <v>526776</v>
       </c>
       <c r="R153" t="n">
-        <v>6938395</v>
+        <v>6938419</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16286,10 +16291,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121226793</v>
+        <v>121226811</v>
       </c>
       <c r="B154" t="n">
-        <v>90740</v>
+        <v>79690</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16302,21 +16307,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16326,10 +16331,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>526519</v>
+        <v>526545</v>
       </c>
       <c r="R154" t="n">
-        <v>6938315</v>
+        <v>6938319</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16490,10 +16495,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121226791</v>
+        <v>121226798</v>
       </c>
       <c r="B156" t="n">
-        <v>89769</v>
+        <v>79690</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16506,21 +16511,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16530,10 +16535,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>526205</v>
+        <v>526747</v>
       </c>
       <c r="R156" t="n">
-        <v>6938282</v>
+        <v>6937983</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -16592,10 +16597,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121223305</v>
+        <v>121212789</v>
       </c>
       <c r="B157" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16604,41 +16609,41 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Getryggen, Getryggen, Mpd</t>
+          <t>Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>526584</v>
+        <v>526823</v>
       </c>
       <c r="R157" t="n">
-        <v>6938052</v>
+        <v>6938405</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16662,12 +16667,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16694,10 +16699,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121226809</v>
+        <v>121226795</v>
       </c>
       <c r="B158" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16710,21 +16715,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16734,10 +16739,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>526518</v>
+        <v>526554</v>
       </c>
       <c r="R158" t="n">
-        <v>6938295</v>
+        <v>6938311</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -16796,7 +16801,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121226811</v>
+        <v>121226810</v>
       </c>
       <c r="B159" t="n">
         <v>79690</v>
@@ -16836,10 +16841,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>526545</v>
+        <v>526533</v>
       </c>
       <c r="R159" t="n">
-        <v>6938319</v>
+        <v>6938315</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -16898,10 +16903,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121226796</v>
+        <v>121212785</v>
       </c>
       <c r="B160" t="n">
-        <v>91006</v>
+        <v>78254</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16914,21 +16919,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>658</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16938,10 +16943,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>526796</v>
+        <v>526753</v>
       </c>
       <c r="R160" t="n">
-        <v>6937966</v>
+        <v>6938395</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -16968,12 +16973,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17000,7 +17005,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121226810</v>
+        <v>121226806</v>
       </c>
       <c r="B161" t="n">
         <v>79690</v>
@@ -17040,10 +17045,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>526533</v>
+        <v>526182</v>
       </c>
       <c r="R161" t="n">
-        <v>6938315</v>
+        <v>6938206</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17204,10 +17209,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>121226815</v>
+        <v>121226816</v>
       </c>
       <c r="B163" t="n">
-        <v>78345</v>
+        <v>98105</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17216,25 +17221,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17244,10 +17249,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>526527</v>
+        <v>526789</v>
       </c>
       <c r="R163" t="n">
-        <v>6938317</v>
+        <v>6937993</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -17306,10 +17311,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>121226813</v>
+        <v>121226822</v>
       </c>
       <c r="B164" t="n">
-        <v>78345</v>
+        <v>91996</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17318,25 +17323,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17346,10 +17351,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>526365</v>
+        <v>526182</v>
       </c>
       <c r="R164" t="n">
-        <v>6938404</v>
+        <v>6938234</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -17408,10 +17413,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121226806</v>
+        <v>121223305</v>
       </c>
       <c r="B165" t="n">
-        <v>79690</v>
+        <v>98105</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17420,41 +17425,41 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Getryggen, Mpd</t>
+          <t>Getryggen, Getryggen, Mpd</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>526182</v>
+        <v>526584</v>
       </c>
       <c r="R165" t="n">
-        <v>6938206</v>
+        <v>6938052</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17510,7 +17515,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121226816</v>
+        <v>121226817</v>
       </c>
       <c r="B166" t="n">
         <v>98105</v>
@@ -17550,10 +17555,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>526789</v>
+        <v>526581</v>
       </c>
       <c r="R166" t="n">
-        <v>6937993</v>
+        <v>6938053</v>
       </c>
       <c r="S166" t="n">
         <v>25</v>
@@ -17612,10 +17617,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121226821</v>
+        <v>121226793</v>
       </c>
       <c r="B167" t="n">
-        <v>78609</v>
+        <v>90740</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17628,21 +17633,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17652,10 +17657,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>526199</v>
+        <v>526519</v>
       </c>
       <c r="R167" t="n">
-        <v>6938254</v>
+        <v>6938315</v>
       </c>
       <c r="S167" t="n">
         <v>25</v>
@@ -17688,11 +17693,6 @@
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -17719,10 +17719,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121226824</v>
+        <v>121226815</v>
       </c>
       <c r="B168" t="n">
-        <v>91282</v>
+        <v>78345</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17731,25 +17731,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17759,10 +17759,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>526747</v>
+        <v>526527</v>
       </c>
       <c r="R168" t="n">
-        <v>6937983</v>
+        <v>6938317</v>
       </c>
       <c r="S168" t="n">
         <v>25</v>
@@ -17821,10 +17821,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121246286</v>
+        <v>121212693</v>
       </c>
       <c r="B169" t="n">
-        <v>92025</v>
+        <v>92000</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17837,24 +17837,27 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>232140</v>
+        <v>4365</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -17901,7 +17904,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Även smalfotad taggsvamp under samma låga</t>
+          <t>Tajgataggsvamp under samma tallåga</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17910,6 +17913,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17928,10 +17932,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121212693</v>
+        <v>121246286</v>
       </c>
       <c r="B170" t="n">
-        <v>92000</v>
+        <v>92025</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17944,27 +17948,24 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4365</v>
+        <v>232140</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Getryggen, Mpd</t>
@@ -18011,7 +18012,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp under samma tallåga</t>
+          <t>Även smalfotad taggsvamp under samma låga</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18020,7 +18021,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -18042,11 +18042,11 @@
         <v>121179849</v>
       </c>
       <c r="B171" t="n">
-        <v>91159</v>
+        <v>91168</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">

--- a/artfynd/A 64514-2023 artfynd.xlsx
+++ b/artfynd/A 64514-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY190"/>
+  <dimension ref="A1:AZ190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185395</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105265</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212783</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212785</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121179876</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185406</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,6 +1826,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185407</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1868,6 +1928,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212701</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1965,6 +2030,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212702</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2062,6 +2132,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212703</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2159,6 +2234,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212704</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2256,6 +2336,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212705</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,6 +2438,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212706</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2450,6 +2540,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226796</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2547,6 +2642,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226824</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2644,6 +2744,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185435</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2741,6 +2846,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212687</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2838,6 +2948,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212750</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2935,6 +3050,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185398</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3032,6 +3152,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185399</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3129,6 +3254,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185400</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3226,6 +3356,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185401</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3323,6 +3458,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212690</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3420,6 +3560,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226792</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3517,6 +3662,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121221064</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3614,6 +3764,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226820</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3711,6 +3866,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212700</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3808,6 +3968,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226791</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3905,6 +4070,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212697</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4002,6 +4172,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212698</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4099,6 +4274,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121226795</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4210,6 +4390,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441472</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4307,6 +4492,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102466367</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4404,6 +4594,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185429</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4501,6 +4696,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185430</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4598,6 +4798,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185431</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4695,6 +4900,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185432</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4792,6 +5002,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121185433</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4889,6 +5104,11 @@
         </is>
       </c>
       <c r="AY44" t